--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EC1EA8-2C6E-4EC3-94A5-E0208F982DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7F49A6-7881-4CCD-BC27-6A3F8FECECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -3116,12 +3116,49 @@
 4.Click Login,click,,"//button[@type='submit']"
 5.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
 6.Load User App,switch_to,user,
-7.wait,5000,,
-8.Click English  Icon,tap,,"//android.widget.Button[@content-desc="English"]"
-9.Click Next,tap,,"//android.widget.Button[@content-desc="Next"]"
-9.wait,3000,,
-10.Load Driver App,switch_to,driver,
-11.wait,5000,,
+7.Click English  Icon,tap,,"//android.widget.Button[@content-desc="English"]"
+8.Click Next,tap,,"//android.widget.Button[@content-desc="Next"]"
+9.Click Mobile Number,tap,,"//android.widget.Button[@content-desc="Mobile Number"]"
+10.Click Close,tap,,"//android.widget.ImageView[@content-desc="Cancel"]"
+11.wait,1000,,
+12.Load Driver App,switch_to,driver,
+13.Click English  Icon,tap,,"//android.widget.Button[@content-desc="English"]"
+14.Click Next,tap,,"//android.widget.Button[@content-desc="Next"]"
+15.Click Mobile Number,tap,,"//android.widget.Button[@content-desc="Mobile Number"]"
+16.Click Close,tap,,"//android.widget.ImageView[@content-desc="Cancel"]"
+17.wait,1000,,
+18.Load  Super Admn,switch_to,web,
+19.wait,1000,,
+20. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
+21.Click City area menu,click,,"//span[normalize-space()='City Area']"
+22.Verify City Area List,verify,,"//div[contains(text(),'City Area List')]"
+23.Click Add City Area button , click ,, "//button[contains(@class, 'buttonWidget') and contains(text(), 'Add City Area')]"
+24.Verify City Area heading,verify,,"//div[contains(text(), 'City Area') and contains(@style, 'font-weight: 700')]"
+25.Enter Area Name, type, triplicane_{timestamp} &gt;&gt; areaName, "//input[@placeholder='Area Name']"
+26.Open Status Dropdown,click,,"//span[@aria-label='select status']"
+27.Select Active,click,,"//li[@role='option'][contains(.,'Active')]"
+28.Enter City Area, type, triplicane, "//input[@placeholder='Search location']"
+29.wait,1000,,
+30.Select First Option,arrow_down,,"//input[@placeholder='Search location']"
+31.Confirm Option,press_enter,,"//input[@placeholder='Search location']"
+32.wait,1000,,
+33. draw polygon, "-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120", //div[@class='ol-layer']//canvas
+34. Click Submit,click,,"//button[normalize-space()='Submit']"
+35. Verify Success Message,verify,,"//div[@aria-label='Added Successfully']"
+36. Click Transport Services,click,,"//div[.//h2[normalize-space()='Transport Services']]"
+37. Verify Transport Page,verify,,"//div[contains(text(),'TRANSPORT SERVICES')]"
+38. Click Add Category,click,,"//button[normalize-space()='Add Category']"
+39. Open Select City Dropdown,click,,"//div[@class='p-element p-multiselect-label-container']"
+40. Search City Area,type,{areaName},"//input[contains(@class,'p-multiselect-filter')]"
+41. Verify Area in Dropdown,verify,,"//li[@role='option'][contains(.,'{areaName}')]"
+42. Click close,click,,"//button[normalize-space()='Close']"
+43. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
+44. Click City admin menu,click,,"//span[normalize-space()='City Admin']"
+45. Verify City Admin List,verify,,"//div[contains(text(),'City Admin List')]"
+46.Click Add City Admin button , click ,, "//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
+47. Open Select City Dropdown,click,,"//select[@id='cityId']"
+48. Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
+49. Verify Selection,verify,,"//select[@id='cityId'][contains(.,'{areaName}')]"
 </t>
   </si>
 </sst>
@@ -4253,7 +4290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>108</v>
       </c>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,29 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7F49A6-7881-4CCD-BC27-6A3F8FECECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04DED92-5AA5-4ED7-8740-52D855B120B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
-    <sheet name="UniversalFlow" sheetId="31" r:id="rId2"/>
-    <sheet name="AddCustomer" sheetId="13" r:id="rId3"/>
-    <sheet name="AddCityArea" sheetId="1" r:id="rId4"/>
-    <sheet name="AddCityAdmin" sheetId="2" r:id="rId5"/>
-    <sheet name="AddAutoDriver" sheetId="3" r:id="rId6"/>
-    <sheet name="AddBikeDriver" sheetId="4" r:id="rId7"/>
-    <sheet name="AddTaxiDriver" sheetId="5" r:id="rId8"/>
-    <sheet name="TransportServiceCompleteTest" sheetId="15" r:id="rId9"/>
-    <sheet name="AddStore" sheetId="7" r:id="rId10"/>
-    <sheet name="StoreOperations" sheetId="8" r:id="rId11"/>
-    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId12"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId13"/>
-    <sheet name="AddProvider" sheetId="11" r:id="rId14"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId15"/>
-    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId16"/>
-    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId17"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId18"/>
+    <sheet name="AddCustomer" sheetId="13" r:id="rId2"/>
+    <sheet name="AddCityArea" sheetId="1" r:id="rId3"/>
+    <sheet name="AddCityAdmin" sheetId="2" r:id="rId4"/>
+    <sheet name="AddAutoDriver" sheetId="3" r:id="rId5"/>
+    <sheet name="AddBikeDriver" sheetId="4" r:id="rId6"/>
+    <sheet name="AddTaxiDriver" sheetId="5" r:id="rId7"/>
+    <sheet name="TransportServiceCompleteTest" sheetId="15" r:id="rId8"/>
+    <sheet name="AddStore" sheetId="7" r:id="rId9"/>
+    <sheet name="StoreOperations" sheetId="8" r:id="rId10"/>
+    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId11"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId12"/>
+    <sheet name="AddProvider" sheetId="11" r:id="rId13"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId14"/>
+    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId15"/>
+    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId16"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="108">
   <si>
     <t>City Area</t>
   </si>
@@ -3096,70 +3095,6 @@
 176.Click  Submit,click,,"//button[normalize-space()='Submit']"
 177.Verify Sucess, verify, , "//div[@aria-label='Info']"
 178.wait,2000,,</t>
-  </si>
-  <si>
-    <t>SA_TS_33</t>
-  </si>
-  <si>
-    <t>UniversalFlow</t>
-  </si>
-  <si>
-    <t>TC_CA_00_Universal_Flow</t>
-  </si>
-  <si>
-    <t>UniversalFlow is verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Load Site,navigate,https://dev.we1.co/#/login,
-2.Enter  Email , type , super_admin@gmail.com, "//input[@placeholder='Enter your email']"
-3.Enter Password,type,R1mep@321, "//input[@placeholder='Enter your password']"
-4.Click Login,click,,"//button[@type='submit']"
-5.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
-6.Load User App,switch_to,user,
-7.Click English  Icon,tap,,"//android.widget.Button[@content-desc="English"]"
-8.Click Next,tap,,"//android.widget.Button[@content-desc="Next"]"
-9.Click Mobile Number,tap,,"//android.widget.Button[@content-desc="Mobile Number"]"
-10.Click Close,tap,,"//android.widget.ImageView[@content-desc="Cancel"]"
-11.wait,1000,,
-12.Load Driver App,switch_to,driver,
-13.Click English  Icon,tap,,"//android.widget.Button[@content-desc="English"]"
-14.Click Next,tap,,"//android.widget.Button[@content-desc="Next"]"
-15.Click Mobile Number,tap,,"//android.widget.Button[@content-desc="Mobile Number"]"
-16.Click Close,tap,,"//android.widget.ImageView[@content-desc="Cancel"]"
-17.wait,1000,,
-18.Load  Super Admn,switch_to,web,
-19.wait,1000,,
-20. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-21.Click City area menu,click,,"//span[normalize-space()='City Area']"
-22.Verify City Area List,verify,,"//div[contains(text(),'City Area List')]"
-23.Click Add City Area button , click ,, "//button[contains(@class, 'buttonWidget') and contains(text(), 'Add City Area')]"
-24.Verify City Area heading,verify,,"//div[contains(text(), 'City Area') and contains(@style, 'font-weight: 700')]"
-25.Enter Area Name, type, triplicane_{timestamp} &gt;&gt; areaName, "//input[@placeholder='Area Name']"
-26.Open Status Dropdown,click,,"//span[@aria-label='select status']"
-27.Select Active,click,,"//li[@role='option'][contains(.,'Active')]"
-28.Enter City Area, type, triplicane, "//input[@placeholder='Search location']"
-29.wait,1000,,
-30.Select First Option,arrow_down,,"//input[@placeholder='Search location']"
-31.Confirm Option,press_enter,,"//input[@placeholder='Search location']"
-32.wait,1000,,
-33. draw polygon, "-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120", //div[@class='ol-layer']//canvas
-34. Click Submit,click,,"//button[normalize-space()='Submit']"
-35. Verify Success Message,verify,,"//div[@aria-label='Added Successfully']"
-36. Click Transport Services,click,,"//div[.//h2[normalize-space()='Transport Services']]"
-37. Verify Transport Page,verify,,"//div[contains(text(),'TRANSPORT SERVICES')]"
-38. Click Add Category,click,,"//button[normalize-space()='Add Category']"
-39. Open Select City Dropdown,click,,"//div[@class='p-element p-multiselect-label-container']"
-40. Search City Area,type,{areaName},"//input[contains(@class,'p-multiselect-filter')]"
-41. Verify Area in Dropdown,verify,,"//li[@role='option'][contains(.,'{areaName}')]"
-42. Click close,click,,"//button[normalize-space()='Close']"
-43. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-44. Click City admin menu,click,,"//span[normalize-space()='City Admin']"
-45. Verify City Admin List,verify,,"//div[contains(text(),'City Admin List')]"
-46.Click Add City Admin button , click ,, "//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
-47. Open Select City Dropdown,click,,"//select[@id='cityId']"
-48. Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
-49. Verify Selection,verify,,"//select[@id='cityId'][contains(.,'{areaName}')]"
-</t>
   </si>
 </sst>
 </file>
@@ -3607,78 +3542,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A4538F-421E-4B0B-A965-0382A5BEF523}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3750,7 +3613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57207608-1AD9-408F-B018-55A141C9A651}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3822,7 +3685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73960651-1493-478A-BEDA-A31CF297E315}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3894,7 +3757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F63FB6C5-854C-4D7D-9CEB-846B4D7D2F52}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3966,7 +3829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319ADEF0-2336-4246-BBC3-461C4994D500}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4038,7 +3901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F6277B-DBCF-4BFF-819C-1E90748D3258}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4110,7 +3973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B7FC7-76CD-491F-AC51-1837B3B068AC}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4175,7 +4038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4250,82 +4113,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1717BC20-9348-4B52-9588-34F52BC8B75D}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="36.88671875" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46ECEE02-404F-4AF1-8311-95653C3B218B}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4401,7 +4188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4477,7 +4264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9466ABF-463D-46B5-A321-4AC4765F1CE7}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4542,7 +4329,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A75689-8D07-4A99-AA90-48806EECB90F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4614,7 +4401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4197A722-266E-4219-9B46-8F4D56D7D7A1}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4686,7 +4473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790BFFF3-3BE5-4068-A6FF-6214BEDD72BA}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4758,7 +4545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DB4E5D-EBF5-4B6A-BF83-7934D70C5535}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4829,4 +4616,76 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04DED92-5AA5-4ED7-8740-52D855B120B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F870781B-A199-4D5B-A1F8-5168EBE3C61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ACB132-3CED-47AB-9032-CAFCB3B4D90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF66921-EDF0-49EC-BE24-DF4079088636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -3027,7 +3027,7 @@
 10.Upload Profile Image, uploadfile, "src/main/resources/test-data/customer.jpg", "admin.customer.upload_profile_img"
 11.Click Submit, click, , "admin.customer.submit_btn"
 12.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-13. Click Customer Icon,click,,"admin.menu.customer_icon"
+13. Click Dashboard,click,,"admin.menu.dashboard"
 14. Click Customer Icon,click,,"admin.menu.customer_icon"
 15.Click Verified Customers,click,,"admin.menu.verified_customers"
 16. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
@@ -3048,7 +3048,7 @@
 31.Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
 32.Click Submit, click, , "admin.customer.submit_btn"
 33.Verify Saved Succesfully, verify, , "admin.customer.toast_added_success"
-34. Click Customer Icon,click,,"admin.menu.customer_icon"
+34. Click dashbaord Icon,click,,"admin.menu.dashboard"
 35. Click Customer Icon,click,,"admin.menu.customer_icon"
 36.Click Verified Customers,click,,"admin.menu.verified_customers"
 37. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
@@ -3071,7 +3071,7 @@
 54.Enter Points, type, 10, "admin.customer.loyalty.input_points"
 55.Click Submit, click, , "admin.customer.submit_btn"
 56.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-57. Click Customer Icon,click,,"admin.menu.customer_icon"
+57. Click Dashboard Icon,click,,"admin.menu.dashboard"
 58. Click Customer Icon,click,,"admin.menu.customer_icon"
 59.Click Verified Customers,click,,"admin.menu.verified_customers"
 60. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
@@ -3082,14 +3082,14 @@
 65.Disable Reason,type,Client Complaints,"admin.customer.dialog.textarea_reason"
 66.Click Reject Yes,click,,"admin.customer.dialog.btn_confirm_yes"
 67.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-68. Click Customer Icon,click,,"admin.menu.customer_icon"
+68. Click Dashboard Icon,click,,"admin.menu.dashboard"
 69. Click Customer Icon,click,,"admin.menu.customer_icon"
 70.Click Blocked Customers,click,,"admin.menu.blocked_customers"
 71.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
 72.Scroll Grid, tab, 10, "admin.customer.filter_name"
 73.Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
 74.Click Enable Yes,click,,"admin.customer.dialog.btn_confirm_yes"
-75. Click Customer Icon,click,,"admin.menu.customer_icon"
+75. Click Dashboard Icon,click,,"admin.menu.dashboard"
 76. Click Customer Icon,click,,"admin.menu.customer_icon"
 77.Click Verified Customers,click,,"admin.menu.verified_customers"
 78. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF66921-EDF0-49EC-BE24-DF4079088636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B0356B-E3FD-4B43-95F8-B87BD805C748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -1740,39 +1740,6 @@
   </si>
   <si>
     <t>This test case validates the end-to-end management of subscription plan architectures across four distinct user entities: Store, Driver, Provider, and Customer. The workflow systematically executes the creation of localized "Premium" plans for various service categories—such as Food Delivery and Pest Control—featuring integrated multi-language support in Arabic, Tamil, and Hindi. The validation cycle spans from defining plan durations, pricing, and free-ride quotas to conducting administrative audits including localized description verification, active/inactive state toggling, and data filtering. The process concludes by confirming the operational lifecycle through record modification and final deletion, ensuring the functional stability and localized integrity of the platform’s commercial monetization modules.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-2. Click City area menu,click,,"//span[normalize-space()='City Area']"
-3. Verify City Area List,verify,,"//div[contains(text(),'City Area List')]"
-4. Click Add City Area button , click ,, "//button[contains(@class, 'buttonWidget') and contains(text(), 'Add City Area')]"
-5. Verify City Area heading,verify,,"//div[contains(text(), 'City Area') and contains(@style, 'font-weight: 700')]"
-6. Enter Area Name, type, triplicane_{timestamp} &gt;&gt; areaName, "//input[@placeholder='Area Name']"
-7. Open Status Dropdown,click,,"//span[@aria-label='select status']"
-8. Select Active,click,,"//li[@role='option'][contains(.,'Active')]"
-9.Enter City Area, type, triplicane, "//input[@placeholder='Search location']"
-10.wait,1000,,
-11.Select First Option,arrow_down,,"//input[@placeholder='Search location']"
-12.Confirm Option,press_enter,,"//input[@placeholder='Search location']"
-13.wait,1000,,
-14. draw polygon, "-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120", //div[@class='ol-layer']//canvas
-15. Click Submit,click,,"//button[normalize-space()='Submit']"
-16. Verify Success Message,verify,,"//div[@aria-label='Added Successfully']"
-17. Click Transport Services,click,,"//div[.//h2[normalize-space()='Transport Services']]"
-18. Verify Transport Page,verify,,"//div[contains(text(),'TRANSPORT SERVICES')]"
-19. Click Add Category,click,,"//button[normalize-space()='Add Category']"
-20. Open Select City Dropdown,click,,"//div[@class='p-element p-multiselect-label-container']"
-21. Search City Area,type,{areaName},"//input[contains(@class,'p-multiselect-filter')]"
-22. Verify Area in Dropdown,verify,,"//li[@role='option'][contains(.,'{areaName}')]"
-23. Click close,click,,"//button[normalize-space()='Close']"
-19. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-24. Click City admin menu,click,,"//span[normalize-space()='City Admin']"
-25. Verify City Admin List,verify,,"//div[contains(text(),'City Admin List')]"
-26. Click Add City Admin button , click ,, "//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
-27. Open Select City Dropdown,click,,"//select[@id='cityId']"
-28. Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
-29. Verify Selection,verify,,"//select[@id='cityId'][contains(.,'{areaName}')]"
-</t>
   </si>
   <si>
     <t>1. Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
@@ -3009,91 +2976,124 @@
 </t>
   </si>
   <si>
-    <t>1. Enter  Email , type , super_admin@gmail.com, "admin.login.email"
-2. Enter Password,type,R1mep@321, "admin.login.password"
-3. Click Login,click,,"admin.login.submit_btn"
-4. Verify Dashboard,verify,,"admin.dashboard.statistics_header"</t>
+    <t>1. Enter  Email , type , super_admin@gmail.com, "web.global.login.email"
+2. Enter Password,type,R1mep@321, "web.global.login.password"
+3. Click Login,click,,"web.global.login.submit_btn"
+4. Verify Dashboard,verify,,"web.global.dashboard.statistics_header"</t>
   </si>
   <si>
     <t>1. Click Customer Icon,click,,"admin.menu.customer_icon"
-2.Click Add Customers,click,,"admin.menu.add_customers"
+2. Click Add Customers,click,,"admin.menu.add_customers"
 3. Verify Add Customer Heading,verify,,"admin.customer.add_heading"
-4.Enter Customer Name, type, customer{randomAlpha} &gt;&gt; customerName, "admin.customer.input_name"
-5.Enter Email, type, customer_{timestamp}@gmail.com&gt;&gt;customerEmail, "admin.customer.input_email"
-6.Enter Contact Number, type, {randomPhone}, "admin.customer.input_phone"
-7.Enter Video Call Limit, type, 60, "admin.customer.input_video_limit"
-8.Open Gender,click,,"admin.customer.dropdown_gender"
-9.Select Male,click,,"admin.customer.select_gender_male"
-10.Upload Profile Image, uploadfile, "src/main/resources/test-data/customer.jpg", "admin.customer.upload_profile_img"
-11.Click Submit, click, , "admin.customer.submit_btn"
-12.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-13. Click Dashboard,click,,"admin.menu.dashboard"
+4. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+5. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+6. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
+7. Enter Video Call Limit,type,60,"admin.customer.input_video_limit"
+8. Open Gender,click,,"admin.customer.dropdown_gender"
+9. Select Male,click,,"admin.customer.select_gender_male"
+10. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+11. Click Submit,click,,"web.global.action.submit"
+12. Verify Added Successfully,verify,,"web.global.toast.info"
+13. Click Dashboard,click,,"web.global.menu.dashboard"
 14. Click Customer Icon,click,,"admin.menu.customer_icon"
-15.Click Verified Customers,click,,"admin.menu.verified_customers"
+15. Click Verified Customers,click,,"admin.menu.verified_customers"
 16. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-17.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-18.Scroll Grid, tab, 7, "admin.customer.filter_name"
-19.Click Edit Icon ,click,,"admin.customer.grid.btn_edit"
-20.Click Close, click, , "admin.customer.grid.btn_close"
-21.Click Wallet Icon ,click,,"admin.customer.grid.btn_wallet"
-22.Click Add Money ,click,,"admin.customer.wallet.btn_add_money"
-23.Enter Wallet Amount, type, 1000, "admin.customer.wallet.input_amount"
-24.Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-25.Select Add Money,click,,"admin.customer.wallet.select_add_money"
-26.Click Submit, click, , "admin.customer.submit_btn"
-27.Verify Saved Succesfully, verify, , "admin.customer.toast_added_success"
-28.Click Add Money ,click,,"admin.customer.wallet.btn_add_money"
-29.Enter Wallet Amount, type, 200, "admin.customer.wallet.input_amount"
-30.Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-31.Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
-32.Click Submit, click, , "admin.customer.submit_btn"
-33.Verify Saved Succesfully, verify, , "admin.customer.toast_added_success"
-34. Click dashbaord Icon,click,,"admin.menu.dashboard"
+17. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+18. Scroll Grid,tab,7,"admin.customer.filter_name"
+19. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
+20. Click Close,click,,"web.global.action.close"
+21. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
+22. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+23. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
+24. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+25. Select Add Money,click,,"admin.customer.wallet.select_add_money"
+26. Click Submit,click,,"web.global.action.submit"
+27. Verify Saved Successfully,verify,,"web.global.toast.success"
+28. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+29. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
+30. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+31. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+32. Click Submit,click,,"web.global.action.submit"
+33. Verify Saved Successfully,verify,,"web.global.toast.success"
+34. Click dashboard Icon,click,,"web.global.menu.dashboard"
 35. Click Customer Icon,click,,"admin.menu.customer_icon"
-36.Click Verified Customers,click,,"admin.menu.verified_customers"
+36. Click Verified Customers,click,,"admin.menu.verified_customers"
 37. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-38.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-39.Scroll Grid, tab, 7, "admin.customer.filter_name"
-40.Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
-41.Click Manage Loyality Points, click, , "admin.customer.loyalty.btn_manage"
-42.Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-43.Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-44.Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-45.Select Add Points,click,,"admin.customer.loyalty.select_add_points"
-46.Enter Points, type, 30, "admin.customer.loyalty.input_points"
-47.Click Submit, click, , "admin.customer.submit_btn"
-48.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-49.Click Manage Loyality Points, click, , "admin.customer.loyalty.btn_manage"
-50.Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-51.Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-52.Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-53.Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
-54.Enter Points, type, 10, "admin.customer.loyalty.input_points"
-55.Click Submit, click, , "admin.customer.submit_btn"
-56.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-57. Click Dashboard Icon,click,,"admin.menu.dashboard"
+38. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+39. Scroll Grid,tab,7,"admin.customer.filter_name"
+40. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+41. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+42. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+43. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+44. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+45. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+46. Enter Points,type,30,"admin.customer.loyalty.input_points"
+47. Click Submit,click,,"web.global.action.submit"
+48. Verify Added Successfully,verify,,"web.global.toast.info"
+49. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+50. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+51. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+52. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+53. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+54. Enter Points,type,10,"admin.customer.loyalty.input_points"
+55. Click Submit,click,,"web.global.action.submit"
+56. Verify Added Successfully,verify,,"web.global.toast.info"
+57. Click Dashboard Icon,click,,"web.global.menu.dashboard"
 58. Click Customer Icon,click,,"admin.menu.customer_icon"
-59.Click Verified Customers,click,,"admin.menu.verified_customers"
+59. Click Verified Customers,click,,"admin.menu.verified_customers"
 60. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-61.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-62.Scroll Grid, tab, 7, "admin.customer.filter_name"
-63.Click Disable Icon,click,,"admin.customer.grid.btn_block"
-64.Click Disable User Yes,click,,"admin.customer.dialog.btn_confirm_yes"
-65.Disable Reason,type,Client Complaints,"admin.customer.dialog.textarea_reason"
-66.Click Reject Yes,click,,"admin.customer.dialog.btn_confirm_yes"
-67.Verify Added Succesfully, verify, , "admin.customer.toast_info"
-68. Click Dashboard Icon,click,,"admin.menu.dashboard"
+61. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+62. Scroll Grid,tab,7,"admin.customer.filter_name"
+63. Click Disable Icon,click,,"admin.customer.grid.btn_block"
+64. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
+65. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
+66. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+67. Verify Added Successfully,verify,,"web.global.toast.info"
+68. Click Dashboard Icon,click,,"web.global.menu.dashboard"
 69. Click Customer Icon,click,,"admin.menu.customer_icon"
-70.Click Blocked Customers,click,,"admin.menu.blocked_customers"
-71.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-72.Scroll Grid, tab, 10, "admin.customer.filter_name"
-73.Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
-74.Click Enable Yes,click,,"admin.customer.dialog.btn_confirm_yes"
-75. Click Dashboard Icon,click,,"admin.menu.dashboard"
+70. Click Blocked Customers,click,,"admin.menu.blocked_customers"
+71. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+72. Scroll Grid,tab,10,"admin.customer.filter_name"
+73. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+74. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
+75. Click Dashboard Icon,click,,"web.global.menu.dashboard"
 76. Click Customer Icon,click,,"admin.menu.customer_icon"
-77.Click Verified Customers,click,,"admin.menu.verified_customers"
+77. Click Verified Customers,click,,"admin.menu.verified_customers"
 78. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-79.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+79. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Setting menu,click,,"web.global.menu.settings"
+2. Click City area menu,click,,"admin.menu.city_area"
+3. Verify City Area List,verify,,"admin.city_area.list_heading"
+4. Click Add City Area button,click,,"admin.city_area.btn_add"
+5. Verify City Area heading,verify,,"admin.city_area.add_heading"
+6. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
+7. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
+8. Select Active,click,,"admin.city_area.select_status_active"
+9. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
+10. wait,1000,,
+11. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+12. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+13. wait,1000,,
+14. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+15. Click Submit,click,,"web.global.action.submit"
+16. Verify Success Message,verify,,"web.global.toast.success"
+17. Click Transport Services,click,,"admin.transport.card_link"
+18. Verify Transport Page,verify,,"admin.transport.page_heading"
+19. Click Add Category,click,,"admin.transport.btn_add_category"
+20. Open Select City Dropdown,click,,"admin.transport.dropdown_city_multiselect"
+21. Search City Area,type,{areaName},"admin.transport.input_filter_city"
+22. Verify Area in Dropdown,verify,,"admin.transport.select_filtered_option"
+23. Click close,click,,"web.global.action.close"
+24. Click Setting menu,click,,"web.global.menu.settings"
+25. Click City admin menu,click,,"admin.menu.city_admin"
+26. Verify City Admin List,verify,,"admin.city_admin.list_heading"
+27. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+28. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+29. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+30. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
+</t>
   </si>
 </sst>
 </file>
@@ -3510,7 +3510,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -3519,7 +3519,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
@@ -3588,7 +3588,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
@@ -3660,13 +3660,13 @@
         <v>33</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>47</v>
@@ -3732,13 +3732,13 @@
         <v>56</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -3804,7 +3804,7 @@
         <v>36</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>37</v>
@@ -3876,7 +3876,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>58</v>
@@ -3948,13 +3948,13 @@
         <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>74</v>
@@ -4017,19 +4017,19 @@
         <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4079,19 +4079,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4166,7 +4166,7 @@
         <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
@@ -4317,7 +4317,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>39</v>
@@ -4376,13 +4376,13 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>44</v>
@@ -4448,13 +4448,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -4520,13 +4520,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -4592,13 +4592,13 @@
         <v>62</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>64</v>
@@ -4665,13 +4665,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>47</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B60783-E1EF-4901-A479-BBF4161F3A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5DFE3E-5BF2-403F-A2BB-AD8A965689B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
     <sheet name="AddCustomer" sheetId="31" r:id="rId2"/>
     <sheet name="AddCityArea" sheetId="1" r:id="rId3"/>
-    <sheet name="AddCityAdmin" sheetId="2" r:id="rId4"/>
+    <sheet name="AddCityAdmin" sheetId="32" r:id="rId4"/>
     <sheet name="AddAutoDriver" sheetId="3" r:id="rId5"/>
     <sheet name="AddBikeDriver" sheetId="4" r:id="rId6"/>
     <sheet name="AddTaxiDriver" sheetId="5" r:id="rId7"/>
@@ -2930,145 +2930,18 @@
 178.wait,2000,,</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-2. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-3. Click City admin menu,click,,"//span[normalize-space()='City Admin']"
-4. Verify City Admin List,verify,,"//div[normalize-space()='City Admin List']"
-5. Click Add City Admin button,click,,"//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
-6. Verify City Admin heading,verify,,"//h2[@class='text-base font-semibold text-gray-800']"
-7.Select Name field,click ,, "//input[@id='name']"
-8. Enter Admin Name, type, faizal{randomAlpha} &gt;&gt; adminName, "//input[@id='name']"
-9.Select Email field,click,, "//input[@id='email']"
-10. Enter Email, type, faizal_{timestamp}@gmail.com, "//input[@id='email']"
-11.select the password field,click,, "//input[@id='password']"
-12.Enter the Password as "faizal@123". "//input[@id='password']"
-13.Open Select City Dropdown,click,,"//select[@id='cityId']"
-14.Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
-15. Click on the "Transport Service" → "Auto Ride" checkbox. "//label[normalize-space()='Auto Ride']"
-16.Click on the "Customers" → "Add Customers" checkbox. "//label[normalize-space()='Add Customers']"
-17.Click on the "Customers" → "Verified Customers"checkbox. "//label[normalize-space()='Verified Customers']"
-18.Click on the "Customers" → "Non Verified Customers" checkbox. "//label[normalize-space()='Non Verified Customers']"
-19.Click on the "Customers" → "Blocked Customers" checkbox. "//label[normalize-space()='Blocked Customers']"
-20.Click on the "Customers" → "Deleted Customers" checkbox. "//label[normalize-space()='Deleted Customers']"
-21.Click on the "Customers" → "Pending Customers" checkbox. "//label[normalize-space()='Pending Customers']"
-22.Click on the "Providers" → "Transport Providers List" checkbox. "//label[normalize-space()='Transport Providers List']"
-23.Click on the "Drivers" → "Add Driver" checkbox."//label[normalize-space()='Add Driver']"
-24.Click on the "Drivers" → "Approved Drivers" checkbox. "//label[normalize-space()='Approved Drivers']"
-25.Click on the "Drivers" → "Un-Approved Drivers" checkbox. "//label[normalize-space()='Un-Approved Drivers']"
-26.Click on the "Drivers" → "Blocked Drivers" checkbox. "//label[normalize-space()='Blocked Drivers']"
-27.Click on the "Drivers" → "Reject Drivers" checkbox. "//label[normalize-space()='Reject Drivers']"
-28.Click on the "Drivers" → "Deleted Drivers" checkbox. "//label[normalize-space()='Deleted Drivers']"
-29.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox. "//label[normalize-space()='Driver Subscription Plan']"
-30.Click on the "Cash Out" → "Driver Cash Out" checkbox. "//label[normalize-space()='Driver Cash Out']"
-31.Click on the "Report Issue" → "Customer Report Issues" checkbox. "//label[normalize-space()='Customer Report Issues']"
-32.Click on the "Report Issue" → "Driver Report Issues" checkbox. "//label[normalize-space()='Driver Report Issues']"
-33.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,"//label[normalize-space()='Provider Report Issues']"
-34.Click on the "Report Issue" → "Report issue settings" checkbox. "//label[normalize-space()='Report issue settings']"
-35.Click on the "Report Issue" → "FAQs" checkbox. "(//h3[contains(.,'Report Issue')]/following-sibling::div//label[contains(.,'FAQs')])[1]"
-36.Click on the "Website Settings" → "Header &amp; Footer Settings" checkbox. "//label[normalize-space()='Header &amp; Footer']"
-37.Click on the "Website Settings" → "Home Page Settings" checkbox. "//label[normalize-space()='Home Page']"
-38.Click on the "Website Settings" → "Delivery Settings" checkbox. "//div[h3[contains(.,'Website Settings')]]//label[contains(.,'Delivery')]"
-39.Click on the "Website Settings" → "Transport Settings" checkbox. "//div[.//h3[contains(text(),'Website Settings')]]//label[contains(.,'Transport')]"
-40.Click on the "Website Settings" → "FAQs" checkbox. "(//h3[contains(.,'Website Settings')]/following-sibling::div//label[contains(.,'FAQs')])[1]"
-41.Click Submit,click,,"//button[@type='submit']"
-42. Verify Success Message,verify,,"//div[@aria-label='Info']"
-43.Filter admin name,type,{adminName},"//input[@aria-label='Name Filter Input']"
-</t>
-  </si>
-  <si>
     <t>1. Enter  Email , type , super_admin@gmail.com, "web.global.login.email"
 2. Enter Password,type,R1mep@321, "web.global.login.password"
 3. Click Login,click,,"web.global.login.submit_btn"
-4. Verify Dashboard,verify,,"web.global.dashboard.statistics_header"</t>
-  </si>
-  <si>
-    <t>1. Click Customer Icon,click,,"admin.menu.customer_icon"
-2. Click Add Customers,click,,"admin.menu.add_customers"
-3. Verify Add Customer Heading,verify,,"admin.customer.add_heading"
-4. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
-5. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
-6. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
-7. Enter Video Call Limit,type,60,"admin.customer.input_video_limit"
-8. Open Gender,click,,"admin.customer.dropdown_gender"
-9. Select Male,click,,"admin.customer.select_gender_male"
-10. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
-11. Click Submit,click,,"web.global.action.submit"
-12. Verify Added Successfully,verify,,"web.global.toast.info"
-13. Click Dashboard,click,,"web.global.menu.dashboard"
-14. Click Customer Icon,click,,"admin.menu.customer_icon"
-15. Click Verified Customers,click,,"admin.menu.verified_customers"
-16. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-17. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-18. Scroll Grid,tab,7,"admin.customer.filter_name"
-19. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
-20. Click Close,click,,"web.global.action.close"
-21. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
-22. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-23. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
-24. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-25. Select Add Money,click,,"admin.customer.wallet.select_add_money"
-26. Click Submit,click,,"web.global.action.submit"
-27. Verify Saved Successfully,verify,,"web.global.toast.success"
-28. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-29. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
-30. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-31. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
-32. Click Submit,click,,"web.global.action.submit"
-33. Verify Saved Successfully,verify,,"web.global.toast.success"
-34. Click dashboard Icon,click,,"web.global.menu.dashboard"
-35. Click Customer Icon,click,,"admin.menu.customer_icon"
-36. Click Verified Customers,click,,"admin.menu.verified_customers"
-37. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-38. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-39. Scroll Grid,tab,7,"admin.customer.filter_name"
-40. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
-41. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-42. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-43. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-44. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-45. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
-46. Enter Points,type,30,"admin.customer.loyalty.input_points"
-47. Click Submit,click,,"web.global.action.submit"
-48. Verify Added Successfully,verify,,"web.global.toast.info"
-49. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-50. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-51. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-52. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-53. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
-54. Enter Points,type,10,"admin.customer.loyalty.input_points"
-55. Click Submit,click,,"web.global.action.submit"
-56. Verify Added Successfully,verify,,"web.global.toast.info"
-57. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-58. Click Customer Icon,click,,"admin.menu.customer_icon"
-59. Click Verified Customers,click,,"admin.menu.verified_customers"
-60. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-61. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-62. Scroll Grid,tab,7,"admin.customer.filter_name"
-63. Click Disable Icon,click,,"admin.customer.grid.btn_block"
-64. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
-65. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
-66. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-67. Verify Added Successfully,verify,,"web.global.toast.info"
-68. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-69. Click Customer Icon,click,,"admin.menu.customer_icon"
-70. Click Blocked Customers,click,,"admin.menu.blocked_customers"
-71. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-72. Scroll Grid,tab,10,"admin.customer.filter_name"
-73. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
-74. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
-75. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-76. Click Customer Icon,click,,"admin.menu.customer_icon"
-77. Click Verified Customers,click,,"admin.menu.verified_customers"
-78. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
-79. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+4.Load Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
 2. Click Setting menu,click,,"web.global.menu.settings"
 3. Click City area menu,click,,"admin.menu.city_area"
-4. Verify City Area List,verify,,"admin.city_area.list_heading"
+4. Wait For Area List,wait_until_visible,,"admin.city_area.list_heading"
 5. Click Add City Area button,click,,"admin.city_area.btn_add"
-6. Verify City Area heading,verify,,"admin.city_area.add_heading"
+6. Wait For City Area heading,wait_until_visible,,"admin.city_area.add_heading"
 7. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
 8. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
 9. Select Active,click,,"admin.city_area.select_status_active"
@@ -3079,22 +2952,151 @@
 14. wait,1000,,
 15. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
 16. Click Submit,click,,"web.global.action.submit"
-17. Verify Success Message,verify,,"web.global.toast.success"
+17. Wait For Success Message,wait_until_visible,,"web.global.toast.success"
 18. Click Transport Services,click,,"admin.transport.card_link"
-19. Verify Transport Page,verify,,"admin.transport.page_heading"
+19. Wait For Transport Page,wait_until_visible,,"admin.transport.page_heading"
 20. Click Add Category,click,,"admin.transport.btn_add_category"
 21. Open Select City Dropdown,click,,"admin.transport.dropdown_city_multiselect"
 22. Search City Area,type,{areaName},"admin.transport.input_filter_city"
 23. Verify Area in Dropdown,verify,,"admin.transport.select_filtered_option"
 24. Click close,click,,"web.global.action.close"
-25. Click Setting menu,click,,"web.global.menu.settings"
-26. Click City admin menu,click,,"admin.menu.city_admin"
-27. Verify City Admin List,verify,,"admin.city_admin.list_heading"
-28. Click Add City Admin button,click,,"admin.city_admin.btn_add"
-29. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
-30. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
-31. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
+25.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+26. Click Setting menu,click,,"web.global.menu.settings"
+27. Click City admin menu,click,,"admin.menu.city_admin"
+28. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
+29. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+30. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+31. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+32. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
 </t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Setting menu,click,,web.global.menu.settings
+3. Click City admin menu,click,,admin.menu.city_admin
+4. Wait For City Admin List,wait_until_visible,,admin.city_admin.list_heading
+5. Click Add City Admin button,click,,admin.city_admin.btn_add
+6. Wait For Admin heading,wait_until_visible,,admin.city_admin.add_heading
+7.Select Name field,click,,admin.city_admin.input_name
+8. Enter Admin Name,type,faizal{randomAlpha} &gt;&gt; adminName,admin.city_admin.input_name
+9.Select Email field,click,,admin.city_admin.input_email
+10. Enter Email,type,faizal_{timestamp}@gmail.com,admin.city_admin.input_email
+11.select the password field,click,,admin.city_admin.input_password
+12.Enter the Password as "faizal@123",type,faizal@123,admin.city_admin.input_password
+13.Open Select City Dropdown,click,,admin.city_admin.select_city_dropdown
+14.Select {areaName},click,,admin.city_admin.select_dynamic_option
+15. Click on the "Transport Service" → "Auto Ride" checkbox,click,,admin.city_admin.chk_transport_autoride
+16.Click on the "Customers" → "Add Customers" checkbox,click,,admin.city_admin.chk_customer_add
+17.Click on the "Customers" → "Verified Customers"checkbox,click,,admin.city_admin.chk_customer_verified
+18.Click on the "Customers" → "Non Verified Customers" checkbox,click,,admin.city_admin.chk_customer_unverified
+19.Click on the "Customers" → "Blocked Customers" checkbox,click,,admin.city_admin.chk_customer_blocked
+20.Click on the "Customers" → "Deleted Customers" checkbox,click,,admin.city_admin.chk_customer_deleted
+21.Click on the "Customers" → "Pending Customers" checkbox,click,,admin.city_admin.chk_customer_pending
+22.Click on the "Providers" → "Transport Providers List" checkbox,click,,admin.city_admin.chk_provider_list
+23.Click on the "Drivers" → "Add Driver" checkbox,click,,admin.city_admin.chk_driver_add
+24.Click on the "Drivers" → "Approved Drivers" checkbox,click,,admin.city_admin.chk_driver_approved
+25.Click on the "Drivers" → "Un-Approved Drivers" checkbox,click,,admin.city_admin.chk_driver_unapproved
+26.Click on the "Drivers" → "Blocked Drivers" checkbox,click,,admin.city_admin.chk_driver_blocked
+27.Click on the "Drivers" → "Reject Drivers" checkbox,click,,admin.city_admin.chk_driver_rejected
+28.Click on the "Drivers" → "Deleted Drivers" checkbox,click,,admin.city_admin.chk_driver_deleted
+29.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox,click,,admin.city_admin.chk_subscription_plan
+30.Click on the "Cash Out" → "Driver Cash Out" checkbox,click,,admin.city_admin.chk_cashout
+31.Click on the "Report Issue" → "Customer Report Issues" checkbox,click,,admin.city_admin.chk_report_customer
+32.Click on the "Report Issue" → "Driver Report Issues" checkbox,click,,admin.city_admin.chk_report_driver
+33.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,admin.city_admin.chk_report_provider
+34.Click on the "Report Issue" → "Report issue settings" checkbox,click,,admin.city_admin.chk_report_settings
+35.Click on the "Report Issue" → "FAQs" checkbox,click,,admin.city_admin.chk_report_faqs
+36.Click on the "Website Settings" → "Header &amp; Footer Settings" checkbox,click,,admin.city_admin.chk_web_header_footer
+37.Click on the "Website Settings" → "Home Page Settings" checkbox,click,,admin.city_admin.chk_web_homepage
+38.Click on the "Website Settings" → "Delivery Settings" checkbox,click,,admin.city_admin.chk_web_delivery
+39.Click on the "Website Settings" → "Transport Settings" checkbox,click,,admin.city_admin.chk_web_transport
+40.Click on the "Website Settings" → "FAQs" checkbox,click,,admin.city_admin.chk_web_faqs
+41.Click Submit,click,,web.global.login.submit_btn
+42. Wait For Success Message,wait_until_visible,,web.global.toast.info
+43.Filter admin name,type,{adminName},admin.city_admin.input_name_filter</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Customer Icon,click,,"admin.menu.customer_icon"
+3. Click Add Customers,click,,"admin.menu.add_customers"
+4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
+8. Enter Video Call Limit,type,60,"admin.customer.input_video_limit"
+9. Open Gender,click,,"admin.customer.dropdown_gender"
+10. Select Male,click,,"admin.customer.select_gender_male"
+11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+12. Click Submit,click,,"web.global.action.submit"
+13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+14. Click Dashboard,click,,"web.global.menu.dashboard"
+15. Click Customer Icon,click,,"admin.menu.customer_icon"
+16. Click Verified Customers,click,,"admin.menu.verified_customers"
+17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+19. Scroll Grid,tab,7,"admin.customer.filter_name"
+20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
+21. Click Close,click,,"web.global.action.close"
+22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
+23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
+25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
+27. Click Submit,click,,"web.global.action.submit"
+28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
+31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+33. Click Submit,click,,"web.global.action.submit"
+34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+35. Click dashboard Icon,click,,"web.global.menu.dashboard"
+36. Click Customer Icon,click,,"admin.menu.customer_icon"
+37. Click Verified Customers,click,,"admin.menu.verified_customers"
+38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+40. Scroll Grid,tab,7,"admin.customer.filter_name"
+41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+44. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+47. Enter Points,type,30,"admin.customer.loyalty.input_points"
+48. Click Submit,click,,"web.global.action.submit"
+49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+52. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+55. Enter Points,type,10,"admin.customer.loyalty.input_points"
+56. Click Submit,click,,"web.global.action.submit"
+57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+59. Click Customer Icon,click,,"admin.menu.customer_icon"
+60. Click Verified Customers,click,,"admin.menu.verified_customers"
+61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+63. Scroll Grid,tab,7,"admin.customer.filter_name"
+64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
+65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
+66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
+67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+68. Verify Added Successfully,verify,,"web.global.toast.info"
+69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+70. Click Customer Icon,click,,"admin.menu.customer_icon"
+71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
+72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+73. Scroll Grid,tab,10,"admin.customer.filter_name"
+74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
+75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+78. Click Customer Icon,click,,"admin.menu.customer_icon"
+79. Click Verified Customers,click,,"admin.menu.verified_customers"
+80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
   </si>
 </sst>
 </file>
@@ -3520,7 +3522,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
@@ -4167,7 +4169,7 @@
         <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
@@ -4243,7 +4245,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
@@ -4265,7 +4267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9466ABF-463D-46B5-A321-4AC4765F1CE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB63C6AC-3593-403C-90C0-44D30EC92C43}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4318,7 +4320,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>39</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,27 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5DFE3E-5BF2-403F-A2BB-AD8A965689B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34816D78-B912-4358-B4A5-4C37AB9A8B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
     <sheet name="AddCustomer" sheetId="31" r:id="rId2"/>
     <sheet name="AddCityArea" sheetId="1" r:id="rId3"/>
     <sheet name="AddCityAdmin" sheetId="32" r:id="rId4"/>
-    <sheet name="AddAutoDriver" sheetId="3" r:id="rId5"/>
-    <sheet name="AddBikeDriver" sheetId="4" r:id="rId6"/>
-    <sheet name="AddTaxiDriver" sheetId="5" r:id="rId7"/>
+    <sheet name="AddAutoDriver" sheetId="33" r:id="rId5"/>
+    <sheet name="AddBikeDriver" sheetId="34" r:id="rId6"/>
+    <sheet name="AddTaxiDriver" sheetId="35" r:id="rId7"/>
     <sheet name="TransportServiceCompleteTest" sheetId="15" r:id="rId8"/>
-    <sheet name="AddStore" sheetId="7" r:id="rId9"/>
-    <sheet name="StoreOperations" sheetId="8" r:id="rId10"/>
-    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId11"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId12"/>
-    <sheet name="AddProvider" sheetId="11" r:id="rId13"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId14"/>
-    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId15"/>
-    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId16"/>
+    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId9"/>
+    <sheet name="AddStore" sheetId="7" r:id="rId10"/>
+    <sheet name="StoreOperations" sheetId="8" r:id="rId11"/>
+    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId12"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId13"/>
+    <sheet name="AddProvider" sheetId="11" r:id="rId14"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId15"/>
+    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId16"/>
     <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="110">
   <si>
     <t>City Area</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>This test validates the end-to-end lifecycle of a delivery store's operational setup, focusing on catalog management, financial provisioning, and logistics readiness. The workflow begins by navigating through the delivery services hierarchy to locate a specific store, where it performs a menu expansion by adding new products with precise attributes including pricing, imagery, and discount logic. Following inventory setup, the script executes a comprehensive financial audit by performing both credit and debit transactions within the store’s wallet to ensure backend accounting synchronization. Finally, the test secures the store's fulfillment capabilities by registering a new private driver, capturing personal and vehicle details alongside document uploads, thereby ensuring the merchant is fully prepared to manage products, finances, and last-mile delivery.</t>
-  </si>
-  <si>
-    <t>SA_TS_8</t>
   </si>
   <si>
     <t>Store Status Mangement</t>
@@ -1740,116 +1737,6 @@
   </si>
   <si>
     <t>This test case validates the end-to-end management of subscription plan architectures across four distinct user entities: Store, Driver, Provider, and Customer. The workflow systematically executes the creation of localized "Premium" plans for various service categories—such as Food Delivery and Pest Control—featuring integrated multi-language support in Arabic, Tamil, and Hindi. The validation cycle spans from defining plan durations, pricing, and free-ride quotas to conducting administrative audits including localized description verification, active/inactive state toggling, and data filtering. The process concludes by confirming the operational lifecycle through record modification and final deletion, ensuring the functional stability and localized integrity of the platform’s commercial monetization modules.</t>
-  </si>
-  <si>
-    <t>1. Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-2. Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-3. Click Add Driver menu,click,,"//span[normalize-space()='Add Driver']"
-4. Verify Add Driver,verify,,"//div[contains(text(),'Add Driver')]"
-5.Click Service Category Dropdown,click,,"//span[@aria-label='Select Service category']"
-6.Select Bike Ride Option,click,,"//span[normalize-space()='Bike Ride']"
-7. Click Checkbox, click, , "//div[contains(@class, 'mdc-checkbox')][1]"
-8. Enter Driver Name, type, bikedriver{randomAlpha}&gt;&gt; bikeName, "//label[contains(.,'Full Name')]/following::input[1]"
-9. Enter Email, type, bikedriver_{timestamp}@gmail.com&gt;&gt;bikeEmail, "//label[contains(.,'Email')]/following::input[1]"
-10. Enter Contact Number, type, {randomPhone}, "//input[@type='tel']"
-11. Upload Profile Image, uploadfile, "src/main/resources/test-data/bikedriver.jpg", "//input[@type='file']"
-12. Select Male Gender, click, , "//div[contains(@class, 'genlabel') and text()='Male']"
-13.Click Vehicle Type Dropdown,click,,"//span[contains(@aria-label,'vehicle type')]"
-14.Select  Scooter Option,click,,"//li[@role='option']//span[text()='Scooter']"
-15. Enter Model Year, type, 2013, "//label[contains(.,'Model Year')]/following::input[1]"
-16.Enter Vehicle Company, type, bikeCompany{randomAlpha}&gt;&gt; bikeCompanyName, "//label[contains(.,'Vehicle Company')]/following::input[1]"
-17. Enter Plate No, type, KL-01-AB-1634, "//label[contains(.,'Plate No')]/following::input[1]"
-18. Enter Model Name, type, activa, "//label[contains(.,'Model Name')]/following::input[1]"
-19. Upload Vehicle Image, uploadfile, "src/main/resources/test-data/bike.jpg", "(//input[@type='file'])[2]"
-20. Enter Vehicle Color, type, white, "//label[contains(.,'Vehicle Color')]/following::input[1]"
-21. Enter Bank Name, type, HDFC Bank, "//label[contains(.,'Bank Name')]/following::input[1]"
-22. Enter Bank Location, type, Chennai, "//label[contains(.,'Bank Location')]/following::input[1]"
-23. Enter Account Number, type, 50100123456789, "//label[contains(.,'Account Number')]/following::input[1]"
-24. Enter Account Holder Name, type, {bikeName}, "//label[contains(.,'Account Holder Name')]/following::input[1]"
-25. Enter Payment Email Address, type, {bikeEmail}, "//label[contains(.,'Payment Email Address')]/following::input[1]"
-26. Enter IFSC Code, type, HDFC0001234, "//label[contains(.,'IFSC Code')]/following::input[1]"
-27. Click Submit, click, , "//button[contains(.,'Submit')]"
-28. Verify Driver Added, verify, , "//div[@aria-label='Added Successfully']"
-29. Wait for Toast to hide, wait, 1000,
-30.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-31.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-32.Click Pending Documents,click,,"//span[normalize-space()='Pending Documents']"
-33.Filter by Name,type,{bikeName},"//input[@aria-label='Driver Name Filter Input']"
-34.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-35.Click Doc Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-36.Driver Required Documents,verify,,"//div[contains(text(),'Driver Required Documents')]"
-37.FilterDocumet List,type,Vehicle Permit Copy,"//input[@aria-label='Document Name Filter Input']"
-38.Add Vehicle Permit Copy,click,,"//i[@title='Edit']"
-39.Upload Vehicle Permit Copy, uploadfile, "src/main/resources/test-data/license.jpg", "//input[@type='file']"
-40.Enter Expiry Date,type,12-12-2026,"//input[@placeholder='DD/MM/YYYY']"
-41.Click Submit, click, , "//button[normalize-space()='Submit']"
-42.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-43.Click Approve Driver,click,,"//i[@title='Approve']"
-44.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-45.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-46.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-47.Click Approved Drivers,click,,"//span[normalize-space()='Approved Drivers']"
-48.Approved Drivers List,verify,,"//div[contains(text(),' Approved Drivers List')]"
-49.Filter Approved Driver,type,{bikeName},"//input[@aria-label='Driver Name Filter Input']"
-50.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-51.Click Doc Icon,click,,"//i[@title='Document']"
-52.Click Eye Icon,click,,"//i[@title='View']"
-53.wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-2. Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-3. Click Add Driver menu,click,,"//span[normalize-space()='Add Driver']"
-4. Verify Add Driver,verify,,"//div[contains(text(),'Add Driver')]"
-5.Click Service Category Dropdown,click,,"//span[@aria-label='Select Service category']"
-6.Select Taxi Ride Option,click,,"//span[normalize-space()='Taxi Ride']"
-7. Click Checkbox, click, , "//div[contains(@class, 'mdc-checkbox')][1]"
-8. Enter Driver Name, type, taxidriver{randomAlpha} &gt;&gt; taxiName, "//label[contains(.,'Full Name')]/following::input[1]"
-9. Enter Email, type, taxidriver_{timestamp}@gmail.com&gt;&gt;taxiEmail, "//label[contains(.,'Email')]/following::input[1]"
-10. Enter Contact Number, type, {randomPhone}, "//input[@type='tel']"
-11. Upload Profile Image, uploadfile, "src/main/resources/test-data/taxidriver.jpg", "//input[@type='file']"
-12. Select Male Gender, click, , "//div[contains(@class, 'genlabel') and text()='Male']"
-13.Click Vehicle Type Dropdown,click,,"//span[contains(@aria-label,'vehicle type')]"
-14.Select  Suv Option,click,,"//li[@role='option']//span[text()='SUV']"
-15. Enter Model Year, type, 2013, "//label[contains(.,'Model Year')]/following::input[1]"
-16.Enter Vehicle Company, type, taxiCompany{randomAlpha}&gt;&gt; taxiCompanyName, "//label[contains(.,'Vehicle Company')]/following::input[1]"
-17. Enter Plate No, type, KL-01-AB-1634, "//label[contains(.,'Plate No')]/following::input[1]"
-18. Enter Model Name, type, etios, "//label[contains(.,'Model Name')]/following::input[1]"
-19.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/taxi.jpg", "(//input[@type='file'])[2]"
-20. Enter Vehicle Color, type, white, "//label[contains(.,'Vehicle Color')]/following::input[1]"
-21. Enter Bank Name, type, HDFC Bank, "//label[contains(.,'Bank Name')]/following::input[1]"
-22. Enter Bank Location, type, Chennai, "//label[contains(.,'Bank Location')]/following::input[1]"
-23. Enter Account Number, type, 50100123456789, "//label[contains(.,'Account Number')]/following::input[1]"
-24. Enter Account Holder Name, type, {taxiName}, "//label[contains(.,'Account Holder Name')]/following::input[1]"
-25. Enter Payment Email Address, type, {taxiEmail}, "//label[contains(.,'Payment Email Address')]/following::input[1]"
-26. Enter IFSC Code, type, HDFC0001234, "//label[contains(.,'IFSC Code')]/following::input[1]"
-27. Click Submit, click, , "//button[contains(.,'Submit')]"
-28. Verify Driver Added, verify, , "//div[@aria-label='Added Successfully']"
-29. Wait for Toast to hide, wait, 1000,
-30.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-31.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-32.Click Pending Documents,click,,"//span[normalize-space()='Pending Documents']"
-33.Filter by Name,type,{taxiName},"//input[@aria-label='Driver Name Filter Input']"
-34.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-35.Click Doc Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-36. Driver Required Documents,verify,,"//div[contains(text(),'Driver Required Documents')]"
-37.FilterDocumet List,type,Driving Licence,"//input[@aria-label='Document Name Filter Input']"
-38.Add Driving License,click,,"//i[@title='Edit']"
-39.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "//input[@type='file']"
-40.Enter Expiry Date,type,12-12-2026,"//input[@placeholder='DD/MM/YYYY']"
-41.Click Submit, click, , "//button[normalize-space()='Submit']"
-42.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-43.Click Approve Driver,click,,"//i[@title='Approve']"
-44.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-45.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-46.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-47.Click Approved Drivers,click,,"//span[normalize-space()='Approved Drivers']"
-48.Approved Drivers List,verify,,"//div[contains(text(),'Approved Drivers List')]"
-49.Filter Approved Driver,type,{taxiName},"//input[@aria-label='Driver Name Filter Input']"
-50.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-51.Click Doc Icon,click,,"//i[@title='Document']"
-52.Click Eye Icon,click,,"//i[@title='View']"
-53.wait,1000,,</t>
   </si>
   <si>
     <t>Super Admin Login</t>
@@ -2526,30 +2413,6 @@
     <t>TC_CA_07_transport_service_complete_test</t>
   </si>
   <si>
-    <t>TC_CA_08_add_store</t>
-  </si>
-  <si>
-    <t>TC_CA_9_store_oprerations</t>
-  </si>
-  <si>
-    <t>TC_CA_10_store_status_management</t>
-  </si>
-  <si>
-    <t>TC_CA_11_delivery_service_complete_test</t>
-  </si>
-  <si>
-    <t>TC_CA_12_add_provider</t>
-  </si>
-  <si>
-    <t>TC_CA_13_provider_service_full_lifecycle_test</t>
-  </si>
-  <si>
-    <t>TC_CA_14_subscription_plan_test</t>
-  </si>
-  <si>
-    <t>TC_CA_15_add_transport_city_admin</t>
-  </si>
-  <si>
     <t>This test case validates the end-to-end lifecycle of an tranport city admin. The workflow initiates with the configuration of a new City Admin profile—integrating dynamic data generation for credentials and city mapping—while assigning permissions across specific transport services (Bike, Taxi, Auto) and driver management modules.The process systematically transitions from the super-admin creation phase to a live login validation, where the new admin’s restricted environment is audited to ensure the presence of authorized transport menus and the successful exclusion of unauthorized delivery and provider service modules. The validation cycle culminates in the execution of complex driver onboarding within the newly created admin account—spanning personal, vehicle, and banking data integration—thereby confirming the platform’s security architecture, hierarchical permission integrity, and the operational stability of city-specific administrative workflows.</t>
   </si>
   <si>
@@ -2694,60 +2557,6 @@
 49.Remove  Transport Ride,sql delete,,"DELETE FROM we1.service_category WHERE name = '{lorryTransportName}';"
 50.Remove Transport City Admin,sql delete,,"DELETE FROM we1.super_admin WHERE name = '{transAdminName}';"
 51.wait,2000,,</t>
-  </si>
-  <si>
-    <t>1. Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-2. Click Add Driver menu,click,,"//span[normalize-space()='Add Driver']"
-3. Verify Add Driver,verify,,"//div[contains(text(),'Add Driver')]"
-4.Click Service Category Dropdown,click,,"//span[@aria-label='Select Service category']"
-5.Select Auto Ride Option,click,,"//span[normalize-space()='Auto Ride']"
-6. Click Checkbox, click, , "//div[contains(@class, 'mdc-checkbox')][1]"
-7. Enter Driver Name, type, autodriver{randomAlpha} &gt;&gt; autoName, "//label[contains(.,'Full Name')]/following::input[1]"
-8. Enter Email, type, autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail, "//label[contains(.,'Email')]/following::input[1]"
-9. Enter Contact Number, type, {randomPhone}, "//input[@type='tel']"
-10. Upload Profile Image, uploadfile, "src/main/resources/test-data/autodriver.jpg", "//input[@type='file']"
-11. Select Male Gender, click, , "//div[contains(@class, 'genlabel') and text()='Male']"
-12.Click Vehicle Type Dropdown,click,,"//span[contains(@aria-label,'vehicle type')]"
-13.Select  Auto Option,click,,"//span[normalize-space()='Auto']"
-14. Enter Model Year, type, 2013, "//label[contains(.,'Model Year')]/following::input[1]"
-15.Enter Vehicle Company, type, autoCompany{randomAlpha}&gt;&gt; autoCompanyName, "//label[contains(.,'Vehicle Company')]/following::input[1]"
-16. Enter Plate No, type, KL-01-AB-1234, "//label[contains(.,'Plate No')]/following::input[1]"
-17. Enter Model Name, type, petrol, "//label[contains(.,'Model Name')]/following::input[1]"
-18. Upload Vehicle Image, uploadfile, "src/main/resources/test-data/vehicle.jpg", "(//input[@type='file'])[2]"
-19. Enter Vehicle Color, type, Red, "//label[contains(.,'Vehicle Color')]/following::input[1]"
-20. Enter Bank Name, type, HDFC Bank, "//label[contains(.,'Bank Name')]/following::input[1]"
-21. Enter Bank Location, type, Chennai, "//label[contains(.,'Bank Location')]/following::input[1]"
-22. Enter Account Number, type, 50100123456789, "//label[contains(.,'Account Number')]/following::input[1]"
-23. Enter Account Holder Name, type,{autoName}, "//label[contains(.,'Account Holder Name')]/following::input[1]"
-24. Enter Payment Email Address, type, {autoEmail}, "//label[contains(.,'Payment Email Address')]/following::input[1]"
-25. Enter IFSC Code, type, HDFC0001234, "//label[contains(.,'IFSC Code')]/following::input[1]"
-26. Click Submit, click, , "//button[contains(.,'Submit')]"
-27. Verify Driver Added, verify, , "//div[@aria-label='Added Successfully']"
-28. Wait for Toast to hide, wait, 1000,
-29.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-30.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-31.Click Pending Documents,click,,"//span[normalize-space()='Pending Documents']"
-32.Filter by Name,type,{autoName},"//input[@aria-label='Driver Name Filter Input']"
-33.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-34.Click Doc Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-35. Driver Required Documents,verify,,"//div[contains(text(),'Driver Required Documents')]"
-36.FilterDocumet List,type,Driving Licence,"//input[@aria-label='Document Name Filter Input']"
-37.Add Driving License,click,,"//i[@title='Edit']"
-38.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "//input[@type='file']"
-39.Enter Expiry Date,type,12-12-2026,"//input[@placeholder='DD/MM/YYYY']"
-40.Click Submit, click, , "//button[normalize-space()='Submit']"
-41.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-42.Click Approve Driver,click,,"//i[@title='Approve']"
-43.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-43.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-45.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-46.Click Approved Drivers,click,,"//span[normalize-space()='Approved Drivers']"
-47.Approved Drivers List,verify,,"//div[contains(text(),'Approved Drivers List')]"
-48.Filter Approved Driver,type,{autoName},"//input[@aria-label='Driver Name Filter Input']"
-49.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-50.Click Doc Icon,click,,"//i[@title='Document']"
-51.Click Eye Icon,click,,"//i[@title='View']"
-52.wait,1000,,</t>
   </si>
   <si>
     <t>1.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
@@ -3097,6 +2906,209 @@
 79. Click Verified Customers,click,,"admin.menu.verified_customers"
 80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
 81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+  </si>
+  <si>
+    <t>SA_TS_08</t>
+  </si>
+  <si>
+    <t>TC_CA_08_add_transport_city_admin</t>
+  </si>
+  <si>
+    <t>TC_CA_09_add_store</t>
+  </si>
+  <si>
+    <t>TC_CA_10_store_oprerations</t>
+  </si>
+  <si>
+    <t>TC_CA_11_store_status_management</t>
+  </si>
+  <si>
+    <t>TC_CA_12_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_CA_13_add_provider</t>
+  </si>
+  <si>
+    <t>TC_CA_14_provider_service_full_lifecycle_test</t>
+  </si>
+  <si>
+    <t>TC_CA_15_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click drivers menu,click,,"admin.drivers.menu.icon"
+3. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+6.Select Auto Ride Option,click,,"admin.drivers.service_option.autoride"
+7. Enter Driver Name,type,autodriver{randomAlpha} &gt;&gt; autoName,"admin.drivers.fullname.input"
+8. Enter Email,type,autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail,"admin.drivers.email.input"
+9.Enter Contact Number,type,{randomPhone}&gt;&gt;autoPhone,"admin.drivers.phone.input"
+10.Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
+11.Enter Whatspp Number,type,{autoPhone},"admin.drivers.whatsapp_phone.input"
+12.Upload Profile Image,uploadfile,"src/main/resources/test-data/autodriver.jpg","admin.drivers.profile_image.file"
+13.Select Source,click,,"admin.drivers.source_dropdown.select"
+14.Select Instagram,click,,"admin.drivers.instagram_option.span"
+15.Select Male Gender,click,,"admin.drivers.male_gender.div"
+16.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+17.Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
+18. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+19.Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
+20.Enter Model Name,type,petrol,"admin.drivers.modelname.input"
+21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/vehicle.jpg","admin.drivers.vehicle_image.file"
+22. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
+23. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
+24.Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
+25.Enter Account Holder Name,type,{autoName},"admin.drivers.accountholder.input"
+26. Enter Payment Email Address,type,{autoEmail},"admin.drivers.paymentemail.input"
+27. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
+28. Click Submit,click,,"web.global.action.submit"
+29. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+30. Wait for Toast to hide,wait,1000,
+31.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+32.Click drivers menu,click,,"admin.drivers.menu.icon"
+33.Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+34.Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
+35.Scroll Grid,tab,7,"admin.drivers.name_filter.input"
+36.Click Doc Icon,click,,"admin.drivers.docs.icon"
+37. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
+38.FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+39.Add Driving License,click,,"admin.drivers.docs.edit_icon"
+40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg","admin.drivers.profile_image.file"
+41.Enter Expiry Date,type,12-12-2026,"admin.drivers.doc_expiry.input"
+42.Click Submit,click,,"web.global.action.submit"
+43.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+44.Click Approve Driver,click,,"admin.drivers.docs.approval"
+45.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+46.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+47.Click drivers menu,click,,"admin.drivers.menu.icon"
+48.Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+49.Wait For Drivers List,wait_until_visible,,"admin.drivers.approved_page.header"
+50.Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
+51.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+52.Click Doc Icon,click,,"admin.drivers.approved_docs.grid_icon"
+53.Click Eye Icon,click,,"admin.drivers.approved_docs.eye_icon"
+54.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click drivers menu,click,, "admin.drivers.menu.icon"
+3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+6.Select Bike Ride Option,click,, "admin.drivers.service_option.bikeride"
+7. Enter Driver Name,type,bikedriver{randomAlpha} &gt;&gt; bikeName, "admin.drivers.fullname.input"
+8. Enter Email,type,bikedriver_{timestamp}@gmail.com&gt;&gt;bikeEmail, "admin.drivers.email.input"
+9.Enter Contact Number,type,{randomPhone}&gt;&gt;bikePhone, "admin.drivers.phone.input"
+10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+11.Enter Whatspp Number,type,{bikePhone}, "admin.drivers.whatsapp_phone.input"
+12.Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg", "admin.drivers.profile_image.file"
+13.Select Source,click,, "admin.drivers.source_dropdown.select"
+14.Select Instagram,click,, "admin.drivers.instagram_option.span"
+15.Select Male Gender,click,, "admin.drivers.male_gender.div"
+16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+17.Select  Bike Option,click,, "admin.drivers.vehicle_option.scooter"
+18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
+19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
+20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
+21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg", "admin.drivers.vehicle_image.file"
+22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
+23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
+24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
+25.Enter Account Holder Name,type,{bikeName}, "admin.drivers.accountholder.input"
+26. Enter Payment Email Address,type,{bikeEmail}, "admin.drivers.paymentemail.input"
+27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
+28. Click Submit,click,, "web.global.action.submit"
+29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
+30. Wait for Toast to hide,wait,1000,
+31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+32.Click drivers menu,click,, "admin.drivers.menu.icon"
+33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+34.Filter by Name,type,{bikeName}, "admin.drivers.name_filter.input"
+35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
+36.Click Doc Icon,click,, "admin.drivers.docs.icon"
+37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
+39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
+42.Click Submit,click,, "web.global.action.submit"
+43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+44.Click Approve Driver,click,, "admin.drivers.docs.approval"
+45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+47.Click drivers menu,click,, "admin.drivers.menu.icon"
+48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
+50.Filter Approved Driver,type,{bikeName}, "admin.drivers.name_filter.input"
+51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
+52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
+53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
+54.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click drivers menu,click,, "admin.drivers.menu.icon"
+3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+6.Select Taxi Ride Option,click,, "admin.drivers.service_option.taxiride"
+7. Enter Driver Name,type,taxidriver{randomAlpha} &gt;&gt; taxiName, "admin.drivers.fullname.input"
+8. Enter Email,type,taxidriver_{timestamp}@gmail.com&gt;&gt;taxiEmail, "admin.drivers.email.input"
+9.Enter Contact Number,type,{randomPhone}&gt;&gt;taxiPhone, "admin.drivers.phone.input"
+10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+11.Enter Whatspp Number,type,{taxiPhone}, "admin.drivers.whatsapp_phone.input"
+12.Upload Profile Image,uploadfile,"src/main/resources/test-data/taxidriver.jpg", "admin.drivers.profile_image.file"
+13.Select Source,click,, "admin.drivers.source_dropdown.select"
+14.Select Instagram,click,, "admin.drivers.instagram_option.span"
+15.Select Male Gender,click,, "admin.drivers.male_gender.div"
+16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+17.Select  Suv Option,click,, "admin.drivers.vehicle_option.suv"
+18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
+19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
+20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
+21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/taxi.jpg", "admin.drivers.vehicle_image.file"
+22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
+23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
+24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
+25.Enter Account Holder Name,type,{taxiName}, "admin.drivers.accountholder.input"
+26. Enter Payment Email Address,type,{taxiEmail}, "admin.drivers.paymentemail.input"
+27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
+28. Click Submit,click,, "web.global.action.submit"
+29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
+30. Wait for Toast to hide,wait,1000,
+31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+32.Click drivers menu,click,, "admin.drivers.menu.icon"
+33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+34.Filter by Name,type,{taxiName}, "admin.drivers.name_filter.input"
+35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
+36.Click Doc Icon,click,, "admin.drivers.docs.icon"
+37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
+39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
+42.Click Submit,click,, "web.global.action.submit"
+43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+44.Click Approve Driver,click,, "admin.drivers.docs.approval"
+45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+47.Click drivers menu,click,, "admin.drivers.menu.icon"
+48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
+50.Filter Approved Driver,type,{taxiName}, "admin.drivers.name_filter.input"
+51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
+52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
+53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
+54.wait,1000,</t>
+  </si>
+  <si>
+    <t>Removed Steps</t>
+  </si>
+  <si>
+    <t>7.Select Auto Ride Option,click,,"//span[normalize-space()='Auto Ride']"
+8.Wait for Auto Ride,wait_until_visible,,"//label[contains(.,'Driver Services')]/following-sibling::mat-checkbox"
+9.Click Auto Ride, click, , "//label[contains(.,'Driver Services')]/following-sibling::mat-checkbox"</t>
   </si>
 </sst>
 </file>
@@ -3513,7 +3525,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -3522,10 +3534,10 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3544,6 +3556,78 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A4538F-421E-4B0B-A965-0382A5BEF523}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3585,22 +3669,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3615,7 +3699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57207608-1AD9-408F-B018-55A141C9A651}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3657,22 +3741,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3687,7 +3771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73960651-1493-478A-BEDA-A31CF297E315}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3729,22 +3813,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3759,7 +3843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F63FB6C5-854C-4D7D-9CEB-846B4D7D2F52}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3801,22 +3885,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3831,7 +3915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319ADEF0-2336-4246-BBC3-461C4994D500}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3873,22 +3957,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3903,7 +3987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F6277B-DBCF-4BFF-819C-1E90748D3258}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3945,22 +4029,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3969,71 +4053,6 @@
       <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B7FC7-76CD-491F-AC51-1837B3B068AC}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
-    <col min="4" max="4" width="34.77734375" customWidth="1"/>
-    <col min="5" max="5" width="64" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4082,22 +4101,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4160,19 +4179,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4239,16 +4258,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4314,16 +4333,16 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4332,7 +4351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A75689-8D07-4A99-AA90-48806EECB90F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603F1167-C5E0-4A83-A433-4756502E0A3E}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4342,7 +4361,7 @@
     <col min="4" max="4" width="35.5546875" customWidth="1"/>
     <col min="5" max="5" width="71.44140625" customWidth="1"/>
     <col min="6" max="6" width="29.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="59.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4365,7 +4384,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4379,16 +4398,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4404,7 +4426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4197A722-266E-4219-9B46-8F4D56D7D7A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E919CD9C-25F0-4379-9D1E-02428B737EB3}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4414,7 +4436,7 @@
     <col min="4" max="4" width="35.5546875" customWidth="1"/>
     <col min="5" max="5" width="71.44140625" customWidth="1"/>
     <col min="6" max="6" width="29.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4437,7 +4459,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4451,16 +4473,19 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4476,7 +4501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790BFFF3-3BE5-4068-A6FF-6214BEDD72BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF62477-5019-4694-8947-A26FED9A3AD4}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4486,7 +4511,7 @@
     <col min="4" max="4" width="35.5546875" customWidth="1"/>
     <col min="5" max="5" width="71.44140625" customWidth="1"/>
     <col min="6" max="6" width="29.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4509,7 +4534,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4523,16 +4548,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4592,19 +4620,19 @@
         <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4621,30 +4649,30 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
-  <dimension ref="A1:H3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B7FC7-76CD-491F-AC51-1837B3B068AC}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="34.77734375" customWidth="1"/>
+    <col min="5" max="5" width="64" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -4662,30 +4690,23 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106C96A7-C8B0-4924-B6A1-AEF71A3DCFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1430B7B-3368-4E28-944A-634D6BB3EFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="AddBikeDriver" sheetId="34" r:id="rId6"/>
     <sheet name="AddTaxiDriver" sheetId="35" r:id="rId7"/>
     <sheet name="TransportServiceCompleteTest" sheetId="37" r:id="rId8"/>
-    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId9"/>
+    <sheet name="AddTransportCityAdmin" sheetId="39" r:id="rId9"/>
     <sheet name="AddStore" sheetId="7" r:id="rId10"/>
     <sheet name="StoreOperations" sheetId="8" r:id="rId11"/>
     <sheet name="StoreStatusManagement" sheetId="10" r:id="rId12"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="116">
   <si>
     <t>City Area</t>
   </si>
@@ -2379,275 +2379,12 @@
 51.wait,2000,,</t>
   </si>
   <si>
-    <t>1.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
-2.Click Transports Services Menu,click,,"//h2[normalize-space()='Transport Services']"
-3.Verify Transport Services,verify,,"//div[normalize-space()='TRANSPORT SERVICES']"
-4.Click  Add Category,click,,"//button[normalize-space()='Add Category']"
-5.Enter Service Name, type, lorryRide{randomAlpha}&gt;&gt;lorryTransportName, "//input[@placeholder='Service Name']"
-6.Enter Service Name Arabic, type, رحلة بالحافلة, "//input[@placeholder='Service Name (in Arabic)']"
-7.Enter Slug, type,{lorryTransportName}, "//input[@placeholder='Slug']"
-8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/lorry.png", "//input[@type='file' and @accept='image/*']"
-9.wait,2000,,
-10.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-11.Select Activate,click,,"//li[@aria-label='Activate']"
-12.Open Select City Dropdown,click,,"//span[text()='Select City']/ancestor::app-drop-down//div[contains(@class, 'p-multiselect-label-container')]"
-13.Select {areaName},click,,"//li[@aria-label='{areaName}']"
-14.Click  Submit,click,,"//button[normalize-space()='Submit']"
-15.Verify Sucess, verify, , "//div[@aria-label='Info']"
-16.wait,2000,,
-17.Click Dashboard Home Icon,click,,"//i[@class='fa-house-chimney fa-solid iconstyle']"
-18.Click Dashboard menu,click,,"//h2[normalize-space()='Dashboard']"
-19.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
-20.Click Transports Services Menu,click,,"//h2[normalize-space()='Transport Services']"
-21.Filter Services List,type,{lorryTransportName},"//input[@aria-label='Services Filter Input']"
-22.Click Home Icon ,click,,"//i[@title='Home']"
-23.Click Settings ,click,,"//button[contains(., 'Settings')]"
-24.Click Vehicle Type,click,,"//div[normalize-space()='Vehicle Type']"
-25.Click Add Vehicle Type,click,,"//button[normalize-space()='Add Vehicle Type']"
-26.Enter Vehicle Type Name, type, tempo{randomAlpha}&gt;&gt;lorryTypeName, "//input[@placeholder='Enter Vehicle Type']"
-27.Enter Base Fare, type, 150, "//input[@placeholder='Enter base fare']"
-28.Enter Base Fare Max Kilometer, type, 10, "//input[@placeholder='Enter Base Fare KM Limit']"
-29.Open Extra Distance Fare Dropdown,click,"//label[contains(., 'Extra Distance Fare Type')]/following-sibling::p-dropdown"
-30.Select Amount,click,,"//li[@aria-label='Amount']"
-31.Enter Extra Distance Fare , type, 10, "//input[@placeholder='Extra Distance Fare (Per Km)']"
-32.Enter Free Waiting Time , type, 10, "//label[contains(., 'Free Waiting Time')]/following::input[1]"
-33.Open Waiting Charge Dropdown,click,"((//label[contains(., 'Waiting Charge Type')]/following::p-dropdown)[1])"
-34.Select Amount,click,,"//li[@aria-label='Amount']"
-35.Enter Waiting Rate , type, 10, "//input[@placeholder='Waiting Rate (per min)']"
-36.Enter Included Trip Waiting , type, 10, "//input[@placeholder='Included Trip Waiting']"
-37.Open Trip Waiting Charge Dropdown,click,"((//label[contains(., 'Waiting Charge Type')]/following::p-dropdown)[2])"
-38.Select Amount,click,,"//li[@aria-label='Amount']"
-39.Enter Trip Waiting Rate , type,50, "//input[@placeholder='Trip Waiting Rate (per min)']"
-40.Enter Free Pickup Distance , type,5, "//input[@placeholder='Free Pickup Distance (In kms)']"
-41.Open Pickup Charge Dropdown,click,"//label[contains(., 'Pickup Charge Type')]/following-sibling::p-dropdown"
-42.Select Amount,click,,"//li[@aria-label='Amount']"
-43.Enter Pickup Fee, type,50, "//input[@placeholder='Pickup Fee (Per Km)']"
-44.Open Customer Fee  Dropdown,click,"//span[@aria-label='Customer Fee Type']"
-45.Select Amount,click,,"//li[@aria-label='Amount']"
-46.Enter Customer Fee, type,50, "//input[@placeholder='Customer Fee']"
-47.Open Customer GST  Dropdown,click,"//label[contains(., 'Customer GST type')]/following-sibling::p-dropdown"
-48.Select Amount,click,,"//li[@aria-label='Amount']"
-49.Enter  GST amount, type,50, "//input[contains(@placeholder,'Enter GST amount or percentage')]"
-50.Open Driver Fee  Dropdown,click,"//span[@aria-label='Driver Fee Type']"
-51.Select Amount,click,,"//li[@aria-label='Amount']"
-52.Enter  Driver Fee, type,50, "//input[@placeholder='Driver Fee']"
-53.Open Driver GST  Dropdown,click,"//label[contains(., 'Driver GST type')]/following-sibling::p-dropdown"
-54.Select Amount,click,,"//li[@aria-label='Amount']"
-55.Enter Driver Gst,type,50," //input[@placeholder='Driver GST in amount or percentage']"
-56.Open Status Dropdown,click,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-57.Select Active,click,,"//li[@aria-label='Active']"
-58.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/tempo.jpg", "//app-image-upload//input[@type='file' and @accept='image/*']"
-59.Enter Notifiacation,type,50,"//input[@placeholder='User will be notified when pickup km exceeds this']"
-60.Enter Driver Request ETA,type,50,"//input[@placeholder='Enter Driver ETA Limit']"
-61.Enter Driver Request KM,type,50,"//input[@placeholder='Driver Request KM Limit']"
-62.Click Surcharge Time Checkbox, click, , "//div[text()='EveryDay']/preceding-sibling::mat-checkbox"
-63.Enter From Time, type, 100000AM, "((//input[@placeholder='--:--:-- --'])[1])"
-64.Enter To Time, type, 220000PM, "((//input[@placeholder='--:--:-- --'])[2])"
-65.Open  Dropdown,click,"((//span[@aria-label='select type'])[1])"
-66.Select Amount,click,,"//li[@aria-label='Amount']"
-67.Enter  Price, type,50, "//input[@placeholder='Enter Price']"
-68.Click  Submit,click,,"//button[normalize-space()='Submit']"
-69.Verify Sucess, verify, , "//div[@aria-label='Info']"
-70.wait,3000,,
-71.Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-72.Click City admin menu,click,,"//span[normalize-space()='City Admin']"
-73. Verify City Admin List,verify,,"//div[normalize-space()='City Admin List']"
-74.Click Add City Admin button,click,,"//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
-75.Verify City Admin heading,verify,,"//h2[@class='text-base font-semibold text-gray-800']"
-76.Select Name field,click ,, "//input[@id='name']"
-77. Enter Admin Name, type, newAdmin{randomAlpha} &gt;&gt; transAdminName, "//input[@id='name']"
-78.Select Email field,click,, "//input[@id='email']"
-79. Enter Email, type, transAdmin_{timestamp}@gmail.com &gt;&gt; transAdminEmail, "//input[@id='email']"
-80.select the password field,click,, "//input[@id='password']"
-81.Enter the Password ,type,password{timestamp}&gt;&gt; transAdminPassword, "//input[@id='password']"
-82.Open Select City Dropdown,click,,"//select[@id='cityId']"
-83.Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
-84. Click on the "Transport Service" → "Bike Ride" checkbox. "//label[normalize-space()='Bike Ride']"
-85.Click on the "Transport Service" → "Taxi Ride" checkbox. "//label[normalize-space()='Taxi Ride']"
-86.Click on the "Transport Service" → "Auto Ride" checkbox. "//label[normalize-space()='Auto Ride']"
-87.Click on the "Transport Service" → "{lorryTransportName}" checkbox. "//label[normalize-space()='{lorryTransportName}']"
-88.Click on the "Drivers" → "Add Driver" checkbox."//label[normalize-space()='Add Driver']"
-89.Click on the "Drivers" → "Approved Drivers" checkbox. "//label[normalize-space()='Approved Drivers']"
-90.Click on the "Drivers" → "Un-Approved Drivers" checkbox. "//label[normalize-space()='Un-Approved Drivers']"
-91.Click on the "Drivers" → "Blocked Drivers" checkbox. "//label[normalize-space()='Blocked Drivers']"
-92.Click on the "Drivers" → "Reject Drivers" checkbox. "//label[normalize-space()='Reject Drivers']"
-93.Click on the "Drivers" → "Deleted Drivers" checkbox. "//label[normalize-space()='Deleted Drivers']"
-94.Click on the "Drivers" → "Driver Peding Documents" checkbox. "//label[normalize-space()='Driver Peding Documents']"
-95.Click on the "Drivers" → "Driver Expired Documents" checkbox. "//label[normalize-space()='Driver Expired Documents']"
-96.Click on the "Add City Admin" button. "//button[@type='submit']"
-97. Verify Success Message,verify,,"//div[@aria-label='Info']"
-98.Filter admin name,type,{transAdminName},"//input[@aria-label='Name Filter Input']"
-99.wait,1000,,
-100.Click Logout Icon,click,,"//i[@class='fa-right-from-bracket fa-solid iconstyle']"
-101.Click Confirm Logout,click,,"//button[normalize-space()='Logout']"
-102.wait,1000,,
-103.Enter  Email , type , {transAdminEmail}, "//input[@placeholder='Enter your email']"
-104.Enter Password,type,{transAdminPassword}, "//input[@placeholder='Enter your password']"
-105.Click Login,click,,"//button[@type='submit']"
-106.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
-107.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-108.Click Add Driver menu,click,,"//span[normalize-space()='Add Driver']"
-109.Verify Add Driver,verify,,"//div[contains(text(),'Add Driver')]"
-110.Click Service Category Dropdown,click,,"//span[@aria-label='Select Service category']"
-111.Select Lorry Ride Option,click,,"//span[normalize-space()='{lorryTransportName}']"
-112.Click Checkbox, click, , "//div[contains(@class, 'mdc-checkbox')][1]"
-113.Enter Driver Name, type, lorrydriver{randomAlpha} &gt;&gt; lorrydriverName, "//label[contains(.,'Full Name')]/following::input[1]"
-114.Enter Email, type, lorrydriver_{timestamp}@gmail.com&gt;&gt;lorrydriverEmail, "//label[contains(.,'Email')]/following::input[1]"
-115.Enter Contact Number, type, {randomPhone}, "//input[@type='tel']"
-116.Upload Profile Image, uploadfile, "src/main/resources/test-data/lorrydriver.jpg", "//input[@type='file']"
-117.Select Male Gender, click, , "//div[contains(@class, 'genlabel') and text()='Male']"
-118.Click Vehicle Type Dropdown,click,,"//span[contains(@aria-label,'vehicle type')]"
-119.Select  Lorry Option,click,,"//span[normalize-space()='{lorryTypeName}']"
-120. Enter Model Year, type, 2013, "//label[contains(.,'Model Year')]/following::input[1]"
-121.Enter Vehicle Company, type, lorryCompany{randomAlpha}&gt;&gt; lorrycompanyName, "//label[contains(.,'Vehicle Company')]/following::input[1]"
-122. Enter Plate No, type, KL-01-AB-1234, "//label[contains(.,'Plate No')]/following::input[1]"
-123.Enter Model Name, type, petrol, "//label[contains(.,'Model Name')]/following::input[1]"
-124.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/lorry.png", "(//input[@type='file'])[2]"
-125.Enter Vehicle Color, type, Red, "//label[contains(.,'Vehicle Color')]/following::input[1]"
-126.Enter Bank Name, type, HDFC Bank, "//label[contains(.,'Bank Name')]/following::input[1]"
-127.Enter Bank Location, type, Chennai, "//label[contains(.,'Bank Location')]/following::input[1]"
-128.Enter Account Number, type, 50100123456789, "//label[contains(.,'Account Number')]/following::input[1]"
-129.Enter Account Holder Name, type,{lorrydriverName}, "//label[contains(.,'Account Holder Name')]/following::input[1]"
-130.Enter Payment Email Address, type, {driverEmail}, "//label[contains(.,'Payment Email Address')]/following::input[1]"
-131.Enter IFSC Code, type, HDFC0001234, "//label[contains(.,'IFSC Code')]/following::input[1]"
-132.Click Submit, click, , "//button[contains(.,'Submit')]"
-133.Verify Driver Added, verify, , "//div[@aria-label='Added Successfully']"
-134.wait,5000,,
-135.Click sidebar,click,,"//*[local-name()='svg' and @id='Layer_1']"
-136.wait,2000,,
-137.Check Transport Menu exists,element_present , , "//h2[normalize-space()='Transport Services']"
-138.wait,2000,,
-139.Check Deleivery Service exists, element_absent, , "//h2[normalize-space()='Delivery Services']"
-140.wait,2000,,
-141.Check Provider Service exists, element_absent, , "//h2[normalize-space()='Provider Services']"
-142.wait,2000,,
-143.Check Add Driver exists, element_present, , " //span[normalize-space()='Add Driver']"
-144.wait,2000,,
-145.Check Approved Driver exists, element_present, , " //span[normalize-space()='Approved Drivers']"
-146.wait,2000,,
-147. Check Un-Approved Drivers exists, element_present, , " //span[normalize-space()='Un-Approved Drivers']"
-148.wait,2000,,
-149.Check  Blocked Driver exists, element_present, , "//span[normalize-space()='Blocked Drivers']"
-150.wait,2000,,
-151.Check  Reject Driver exists, element_present, , "//span[normalize-space()='Reject Drivers']"
-152.wait,2000,,
-153.Check  Deleted Driver exists, element_present, , "//span[normalize-space()='Deleted Drivers']"
-154.wait,2000,,
-155.Check  Driver Documents exists, element_present, , "//span[normalize-space()='Driver Peding Documents']"
-156.wait,2000,,
-157.Check  Driver Expired Documents exists, element_present, , "//span[normalize-space()='Driver Expired Documents']"
-158.wait,2000,,
-159.Click Logout Icon,click,,"//h2[normalize-space()='Logout']"
-160.Click Confirm Logout,click,,"//button[normalize-space()='Logout']"
-161.wait,2000,,
-162.Enter  Email , type , super_admin@gmail.com, "//input[@placeholder='Enter your email']"
-163.Enter Password,type,R1mep@321, "//input[@placeholder='Enter your password']"
-164.Click Login,click,,"//button[@type='submit']"
-165.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
-166.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
-167.Click Transports Services Menu,click,,"//h2[normalize-space()='Transport Services']"
-168.Verify Transport Services,verify,,"//div[normalize-space()='TRANSPORT SERVICES']"
-169.Filter Services List,type,{lorryTransportName},"//input[@aria-label='Services Filter Input']"
-170.Click Edit Icon ,click,,"//i[@title='Edit']"
-171.wait,2000,,
-172.Scroll Grid, tab, 5, "//input[@placeholder='Service Name']"
-173.wait,2000,,
-174.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-175.Select Deactivate,click,,"//li[@aria-label='Deactivate']"
-176.Click  Submit,click,,"//button[normalize-space()='Submit']"
-177.Verify Sucess, verify, , "//div[@aria-label='Info']"
-178.wait,2000,,</t>
-  </si>
-  <si>
     <t>1. Enter  Email , type , super_admin@gmail.com, "web.global.login.email"
 2. Enter Password,type,R1mep@321, "web.global.login.password"
 3. Click Login,click,,"web.global.login.submit_btn"
 4.Load Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"</t>
   </si>
   <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Customer Icon,click,,"admin.menu.customer_icon"
-3. Click Add Customers,click,,"admin.menu.add_customers"
-4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
-5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
-6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
-7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
-8. Enter Video Call Limit,type,60,"admin.customer.input_video_limit"
-9. Open Gender,click,,"admin.customer.dropdown_gender"
-10. Select Male,click,,"admin.customer.select_gender_male"
-11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
-12. Click Submit,click,,"web.global.action.submit"
-13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-14. Click Dashboard,click,,"web.global.menu.dashboard"
-15. Click Customer Icon,click,,"admin.menu.customer_icon"
-16. Click Verified Customers,click,,"admin.menu.verified_customers"
-17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-19. Scroll Grid,tab,7,"admin.customer.filter_name"
-20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
-21. Click Close,click,,"web.global.action.close"
-22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
-23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
-25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
-27. Click Submit,click,,"web.global.action.submit"
-28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
-31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
-33. Click Submit,click,,"web.global.action.submit"
-34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-35. Click dashboard Icon,click,,"web.global.menu.dashboard"
-36. Click Customer Icon,click,,"admin.menu.customer_icon"
-37. Click Verified Customers,click,,"admin.menu.verified_customers"
-38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-40. Scroll Grid,tab,7,"admin.customer.filter_name"
-41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
-42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-44. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
-47. Enter Points,type,30,"admin.customer.loyalty.input_points"
-48. Click Submit,click,,"web.global.action.submit"
-49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-52. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
-55. Enter Points,type,10,"admin.customer.loyalty.input_points"
-56. Click Submit,click,,"web.global.action.submit"
-57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-59. Click Customer Icon,click,,"admin.menu.customer_icon"
-60. Click Verified Customers,click,,"admin.menu.verified_customers"
-61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-63. Scroll Grid,tab,7,"admin.customer.filter_name"
-64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
-65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
-66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
-67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-68. Verify Added Successfully,verify,,"web.global.toast.info"
-69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-70. Click Customer Icon,click,,"admin.menu.customer_icon"
-71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
-72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-73. Scroll Grid,tab,10,"admin.customer.filter_name"
-74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
-75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
-76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
-77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-78. Click Customer Icon,click,,"admin.menu.customer_icon"
-79. Click Verified Customers,click,,"admin.menu.verified_customers"
-80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
-  </si>
-  <si>
     <t>SA_TS_08</t>
   </si>
   <si>
@@ -2673,174 +2410,6 @@
   </si>
   <si>
     <t>TC_CA_15_subscription_plan_test</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click drivers menu,click,,"admin.drivers.menu.icon"
-3. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
-4. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
-5.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
-6.Select Auto Ride Option,click,,"admin.drivers.service_option.autoride"
-7. Enter Driver Name,type,autodriver{randomAlpha} &gt;&gt; autoName,"admin.drivers.fullname.input"
-8. Enter Email,type,autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail,"admin.drivers.email.input"
-9.Enter Contact Number,type,{randomPhone}&gt;&gt;autoPhone,"admin.drivers.phone.input"
-10.Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
-11.Enter Whatspp Number,type,{autoPhone},"admin.drivers.whatsapp_phone.input"
-12.Upload Profile Image,uploadfile,"src/main/resources/test-data/autodriver.jpg","admin.drivers.profile_image.file"
-13.Select Source,click,,"admin.drivers.source_dropdown.select"
-14.Select Instagram,click,,"admin.drivers.instagram_option.span"
-15.Select Male Gender,click,,"admin.drivers.male_gender.div"
-16.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
-17.Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
-18. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
-19.Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
-20.Enter Model Name,type,petrol,"admin.drivers.modelname.input"
-21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/vehicle.jpg","admin.drivers.vehicle_image.file"
-22. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
-23. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
-24.Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
-25.Enter Account Holder Name,type,{autoName},"admin.drivers.accountholder.input"
-26. Enter Payment Email Address,type,{autoEmail},"admin.drivers.paymentemail.input"
-27. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
-28. Click Submit,click,,"web.global.action.submit"
-29. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
-30. Wait for Toast to hide,wait,1000,
-31.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-32.Click drivers menu,click,,"admin.drivers.menu.icon"
-33.Click Pending Documents,click,,"admin.drivers.pending_docs.link"
-34.Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
-35.Scroll Grid,tab,7,"admin.drivers.name_filter.input"
-36.Click Doc Icon,click,,"admin.drivers.docs.icon"
-37. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
-38.FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
-39.Add Driving License,click,,"admin.drivers.docs.edit_icon"
-40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg","admin.drivers.profile_image.file"
-41.Enter Expiry Date,type,12-12-2026,"admin.drivers.doc_expiry.input"
-42.Click Submit,click,,"web.global.action.submit"
-43.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-44.Click Approve Driver,click,,"admin.drivers.docs.approval"
-45.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-46.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-47.Click drivers menu,click,,"admin.drivers.menu.icon"
-48.Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
-49.Wait For Drivers List,wait_until_visible,,"admin.drivers.approved_page.header"
-50.Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
-51.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
-52.Click Doc Icon,click,,"admin.drivers.approved_docs.grid_icon"
-53.Click Eye Icon,click,,"admin.drivers.approved_docs.eye_icon"
-54.wait,1000,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click drivers menu,click,, "admin.drivers.menu.icon"
-3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
-4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
-5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
-6.Select Bike Ride Option,click,, "admin.drivers.service_option.bikeride"
-7. Enter Driver Name,type,bikedriver{randomAlpha} &gt;&gt; bikeName, "admin.drivers.fullname.input"
-8. Enter Email,type,bikedriver_{timestamp}@gmail.com&gt;&gt;bikeEmail, "admin.drivers.email.input"
-9.Enter Contact Number,type,{randomPhone}&gt;&gt;bikePhone, "admin.drivers.phone.input"
-10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
-11.Enter Whatspp Number,type,{bikePhone}, "admin.drivers.whatsapp_phone.input"
-12.Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg", "admin.drivers.profile_image.file"
-13.Select Source,click,, "admin.drivers.source_dropdown.select"
-14.Select Instagram,click,, "admin.drivers.instagram_option.span"
-15.Select Male Gender,click,, "admin.drivers.male_gender.div"
-16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
-17.Select  Bike Option,click,, "admin.drivers.vehicle_option.scooter"
-18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
-19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
-20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
-21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg", "admin.drivers.vehicle_image.file"
-22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
-23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
-24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
-25.Enter Account Holder Name,type,{bikeName}, "admin.drivers.accountholder.input"
-26. Enter Payment Email Address,type,{bikeEmail}, "admin.drivers.paymentemail.input"
-27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
-28. Click Submit,click,, "web.global.action.submit"
-29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
-30. Wait for Toast to hide,wait,1000,
-31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-32.Click drivers menu,click,, "admin.drivers.menu.icon"
-33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
-34.Filter by Name,type,{bikeName}, "admin.drivers.name_filter.input"
-35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
-36.Click Doc Icon,click,, "admin.drivers.docs.icon"
-37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
-38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
-39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
-40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
-41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
-42.Click Submit,click,, "web.global.action.submit"
-43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-44.Click Approve Driver,click,, "admin.drivers.docs.approval"
-45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-47.Click drivers menu,click,, "admin.drivers.menu.icon"
-48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
-49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
-50.Filter Approved Driver,type,{bikeName}, "admin.drivers.name_filter.input"
-51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
-52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
-53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
-54.wait,1000,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click drivers menu,click,, "admin.drivers.menu.icon"
-3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
-4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
-5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
-6.Select Taxi Ride Option,click,, "admin.drivers.service_option.taxiride"
-7. Enter Driver Name,type,taxidriver{randomAlpha} &gt;&gt; taxiName, "admin.drivers.fullname.input"
-8. Enter Email,type,taxidriver_{timestamp}@gmail.com&gt;&gt;taxiEmail, "admin.drivers.email.input"
-9.Enter Contact Number,type,{randomPhone}&gt;&gt;taxiPhone, "admin.drivers.phone.input"
-10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
-11.Enter Whatspp Number,type,{taxiPhone}, "admin.drivers.whatsapp_phone.input"
-12.Upload Profile Image,uploadfile,"src/main/resources/test-data/taxidriver.jpg", "admin.drivers.profile_image.file"
-13.Select Source,click,, "admin.drivers.source_dropdown.select"
-14.Select Instagram,click,, "admin.drivers.instagram_option.span"
-15.Select Male Gender,click,, "admin.drivers.male_gender.div"
-16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
-17.Select  Suv Option,click,, "admin.drivers.vehicle_option.suv"
-18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
-19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
-20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
-21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/taxi.jpg", "admin.drivers.vehicle_image.file"
-22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
-23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
-24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
-25.Enter Account Holder Name,type,{taxiName}, "admin.drivers.accountholder.input"
-26. Enter Payment Email Address,type,{taxiEmail}, "admin.drivers.paymentemail.input"
-27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
-28. Click Submit,click,, "web.global.action.submit"
-29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
-30. Wait for Toast to hide,wait,1000,
-31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-32.Click drivers menu,click,, "admin.drivers.menu.icon"
-33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
-34.Filter by Name,type,{taxiName}, "admin.drivers.name_filter.input"
-35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
-36.Click Doc Icon,click,, "admin.drivers.docs.icon"
-37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
-38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
-39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
-40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
-41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
-42.Click Submit,click,, "web.global.action.submit"
-43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-44.Click Approve Driver,click,, "admin.drivers.docs.approval"
-45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-47.Click drivers menu,click,, "admin.drivers.menu.icon"
-48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
-49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
-50.Filter Approved Driver,type,{taxiName}, "admin.drivers.name_filter.input"
-51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
-52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
-53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
-54.wait,1000,</t>
   </si>
   <si>
     <t>Removed Steps</t>
@@ -2896,45 +2465,6 @@
 37.Click on the "Website Settings" → "Delivery Settings" checkbox,click,,admin.city_admin.chk_web_delivery
 38.Click on the "Website Settings" → "Transport Settings" checkbox,click,,admin.city_admin.chk_web_transport
 39.Click on the "Website Settings" → "FAQs" checkbox,click,,admin.city_admin.chk_web_faqs</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Setting menu,click,,"web.global.menu.settings"
-3. Click City admin menu,click,,"admin.menu.city_admin"
-4. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
-5. Click Add City Admin button,click,,"admin.city_admin.btn_add"
-6. Wait For Admin heading,wait_until_visible,,"admin.city_admin.add_heading"
-7.Select Name field,click,,"admin.city_admin.input_name"
-8. Enter Admin Name,type,faizal{randomAlpha} &gt;&gt; adminName,"admin.city_admin.input_name"
-9.Select Email field,click,,"admin.city_admin.input_email"
-10. Enter Email,type,faizal_{timestamp}@gmail.com,"admin.city_admin.input_email"
-11.select the password field,click,,"admin.city_admin.input_password"
-12.Enter the Password as "faizal@123",type,faizal@123,"admin.city_admin.input_password"
-13.Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
-14.Select {areaName},click,,"admin.city_admin.select_dynamic_option"
-15. Click on the "Transport Service" → "Auto Ride" checkbox,click,,"admin.city_admin.chk_transport_autoride"
-16.Click on the "Customers" → "Add Customers" checkbox,click,,"admin.city_admin.chk_customer_add"
-17.Click on the "Customers" → "Verified Customers"checkbox,click,,"admin.city_admin.chk_customer_verified"
-18.Click on the "Customers" → "Non Verified Customers" checkbox,click,,"admin.city_admin.chk_customer_unverified"
-19.Click on the "Customers" → "Blocked Customers" checkbox,click,,"admin.city_admin.chk_customer_blocked"
-20.Click on the "Customers" → "Deleted Customers" checkbox,click,,"admin.city_admin.chk_customer_deleted"
-21.Click on the "Providers" → "Transport Providers List" checkbox,click,,"admin.city_admin.chk_provider_list"
-22.Click on the "Drivers" → "Add Driver" checkbox,click,,"admin.city_admin.chk_driver_add"
-23.Click on the "Drivers" → "Approved Drivers" checkbox,click,,"admin.city_admin.chk_driver_approved"
-24.Click on the "Drivers" → "Un-Approved Drivers" checkbox,click,,"admin.city_admin.chk_driver_unapproved"
-25.Click on the "Drivers" → "Blocked Drivers" checkbox,click,,"admin.city_admin.chk_driver_blocked"
-26.Click on the "Drivers" → "Reject Drivers" checkbox,click,,"admin.city_admin.chk_driver_rejected"
-27.Click on the "Drivers" → "Deleted Drivers" checkbox,click,,"admin.city_admin.chk_driver_deleted"
-28.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox,click,,"admin.city_admin.chk_subscription_plan"
-29.Click on the "Cash Out" → "Driver Cash Out" checkbox,click,,"admin.city_admin.chk_cashout"
-30.Click on the "Report Issue" → "Customer Report Issues" checkbox,click,,"admin.city_admin.chk_report_customer"
-31.Click on the "Report Issue" → "Driver Report Issues" checkbox,click,,"admin.city_admin.chk_report_driver"
-32.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,"admin.city_admin.chk_report_provider"
-33.Click on the "Report Issue" → "Report issue settings" checkbox,click,,"admin.city_admin.chk_report_settings"
-34.Click on the "Report Issue" → "FAQs" checkbox,click,,"admin.city_admin.chk_report_faqs"
-35.Click Submit,click,,"web.global.login.submit_btn"
-36. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-37.Filter admin name,type,{adminName},"admin.city_admin.input_name_filter"</t>
   </si>
   <si>
     <t>Test Steps Deleted</t>
@@ -3125,6 +2655,481 @@
 171.Click  Submit,click,, "web.global.action.submit"
 172.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
 173.wait,2000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click drivers menu,click,,"admin.drivers.menu.icon"
+3. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+6.Select Auto Ride Option,click,,"admin.drivers.service_dropdown.auto_ride"
+7. Enter Driver Name,type,autodriver{randomAlpha} &gt;&gt; autoName,"admin.drivers.fullname.input"
+8. Enter Email,type,autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail,"admin.drivers.email.input"
+9.Enter Contact Number,type,{randomPhone}&gt;&gt;autoPhone,"admin.drivers.phone.input"
+10.Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
+11.Enter Whatspp Number,type,{autoPhone},"admin.drivers.whatsapp_phone.input"
+12.Upload Profile Image,uploadfile,"src/main/resources/test-data/autodriver.jpg","admin.drivers.profile_image.file"
+13.Select Source,click,,"admin.drivers.source_dropdown.select"
+14.Select Instagram,click,,"admin.drivers.instagram_option.span"
+15.Select Male Gender,click,,"admin.drivers.male_gender.div"
+16.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+17.Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
+18. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+19.Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
+20.Enter Model Name,type,petrol,"admin.drivers.modelname.input"
+21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/vehicle.jpg","admin.drivers.vehicle_image.file"
+22. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
+23. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
+24.Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
+25.Enter Account Holder Name,type,{autoName},"admin.drivers.accountholder.input"
+26. Enter Payment Email Address,type,{autoEmail},"admin.drivers.paymentemail.input"
+27. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
+28. Click Submit,click,,"web.global.action.submit"
+29. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+30. Wait for Toast to hide,wait,1000,
+31.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+32.Click drivers menu,click,,"admin.drivers.menu.icon"
+33.Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+34.Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
+35.Scroll Grid,tab,7,"admin.drivers.name_filter.input"
+36.Click Doc Icon,click,,"admin.drivers.docs.icon"
+37. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
+38.FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+39.Add Driving License,click,,"admin.drivers.docs.edit_icon"
+40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg","admin.drivers.profile_image.file"
+41.Enter Expiry Date,type,12-12-2026,"admin.drivers.doc_expiry.input"
+42.Click Submit,click,,"web.global.action.submit"
+43.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+44.Click Approve Driver,click,,"admin.drivers.docs.approval"
+45.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+46.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+47.Click drivers menu,click,,"admin.drivers.menu.icon"
+48.Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+49.Wait For Drivers List,wait_until_visible,,"admin.drivers.approved_page.header"
+50.Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
+51.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+52.Click Doc Icon,click,,"admin.drivers.approved_docs.grid_icon"
+53.Click Eye Icon,click,,"admin.drivers.approved_docs.eye_icon"
+54.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click drivers menu,click,, "admin.drivers.menu.icon"
+3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+6.Select Bike Ride Option,click,, "admin.drivers.service_dropdown.bike_ride"
+7. Enter Driver Name,type,bikedriver{randomAlpha} &gt;&gt; bikeName, "admin.drivers.fullname.input"
+8. Enter Email,type,bikedriver_{timestamp}@gmail.com&gt;&gt;bikeEmail, "admin.drivers.email.input"
+9.Enter Contact Number,type,{randomPhone}&gt;&gt;bikePhone, "admin.drivers.phone.input"
+10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+11.Enter Whatspp Number,type,{bikePhone}, "admin.drivers.whatsapp_phone.input"
+12.Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg", "admin.drivers.profile_image.file"
+13.Select Source,click,, "admin.drivers.source_dropdown.select"
+14.Select Instagram,click,, "admin.drivers.instagram_option.span"
+15.Select Male Gender,click,, "admin.drivers.male_gender.div"
+16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+17.Select  Bike Option,click,, "admin.drivers.vehicle_option.scooter"
+18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
+19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
+20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
+21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg", "admin.drivers.vehicle_image.file"
+22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
+23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
+24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
+25.Enter Account Holder Name,type,{bikeName}, "admin.drivers.accountholder.input"
+26. Enter Payment Email Address,type,{bikeEmail}, "admin.drivers.paymentemail.input"
+27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
+28. Click Submit,click,, "web.global.action.submit"
+29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
+30. Wait for Toast to hide,wait,1000,
+31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+32.Click drivers menu,click,, "admin.drivers.menu.icon"
+33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+34.Filter by Name,type,{bikeName}, "admin.drivers.name_filter.input"
+35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
+36.Click Doc Icon,click,, "admin.drivers.docs.icon"
+37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
+39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
+42.Click Submit,click,, "web.global.action.submit"
+43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+44.Click Approve Driver,click,, "admin.drivers.docs.approval"
+45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+47.Click drivers menu,click,, "admin.drivers.menu.icon"
+48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
+50.Filter Approved Driver,type,{bikeName}, "admin.drivers.name_filter.input"
+51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
+52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
+53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
+54.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click drivers menu,click,, "admin.drivers.menu.icon"
+3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+6.Select Taxi Ride Option,click,, "admin.drivers.service_dropdown.taxi_ride"
+7. Enter Driver Name,type,taxidriver{randomAlpha} &gt;&gt; taxiName, "admin.drivers.fullname.input"
+8. Enter Email,type,taxidriver_{timestamp}@gmail.com&gt;&gt;taxiEmail, "admin.drivers.email.input"
+9.Enter Contact Number,type,{randomPhone}&gt;&gt;taxiPhone, "admin.drivers.phone.input"
+10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+11.Enter Whatspp Number,type,{taxiPhone}, "admin.drivers.whatsapp_phone.input"
+12.Upload Profile Image,uploadfile,"src/main/resources/test-data/taxidriver.jpg", "admin.drivers.profile_image.file"
+13.Select Source,click,, "admin.drivers.source_dropdown.select"
+14.Select Instagram,click,, "admin.drivers.instagram_option.span"
+15.Select Male Gender,click,, "admin.drivers.male_gender.div"
+16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+17.Select  Suv Option,click,, "admin.drivers.vehicle_option.suv"
+18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
+19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
+20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
+21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/taxi.jpg", "admin.drivers.vehicle_image.file"
+22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
+23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
+24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
+25.Enter Account Holder Name,type,{taxiName}, "admin.drivers.accountholder.input"
+26. Enter Payment Email Address,type,{taxiEmail}, "admin.drivers.paymentemail.input"
+27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
+28. Click Submit,click,, "web.global.action.submit"
+29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
+30. Wait for Toast to hide,wait,1000,
+31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+32.Click drivers menu,click,, "admin.drivers.menu.icon"
+33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+34.Filter by Name,type,{taxiName}, "admin.drivers.name_filter.input"
+35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
+36.Click Doc Icon,click,, "admin.drivers.docs.icon"
+37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
+39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
+42.Click Submit,click,, "web.global.action.submit"
+43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+44.Click Approve Driver,click,, "admin.drivers.docs.approval"
+45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+47.Click drivers menu,click,, "admin.drivers.menu.icon"
+48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
+50.Filter Approved Driver,type,{taxiName}, "admin.drivers.name_filter.input"
+51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
+52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
+53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
+54.wait,1000,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Transports Services Menu,click,,"admin.transport.menu.card"
+3. Wait For Transport Services,wait_until_visible,,"admin.transport.page.header"
+4. Click Add Category,click,,"admin.transport.add_category.btn"
+5. Enter Service Name,type,lorryRide{randomAlpha}&gt;&gt;lorryTransportName,"admin.transport.name.input"
+6. Enter Service Name Arabic,type,رحلة بالحافلة,"admin.transport.name_ar.input"
+7. Enter Slug,type,{lorryTransportName},"admin.transport.slug.input"
+8. Upload Transport Service Image,uploadfile,"src/main/resources/test-data/lorry.png","admin.transport.image.file"
+9. wait,2000,,
+10. Open status Dropdown,click,,"admin.transport.status.dropdown"
+11. Select Activate,click,,"admin.transport.status.activate_option"
+12. Open Select City Dropdown,click,,"admin.transport.city.dropdown"
+13. Select {areaName},click,,"admin.transport.city.dynamic_option"
+14. Click Submit,click,,"web.global.action.submit"
+15. Sucess,wait_until_visible,,"web.global.toast.info"
+16. wait,2000,,
+17. Click Dashboard Home Icon,click,,"web.global.menu.dashboard"
+18. Click Transports Services Menu,click,,"admin.transport.menu.card"
+19. Filter Services List,type,{lorryTransportName},"admin.transport.grid.name_filter"
+20. Click Home Icon,click,,"admin.transport.home.icon"
+21. Click Settings,click,,"admin.transport.menu.settings"
+22. Click Vehicle Type,click,,"admin.transport.settings.vehicle_type"
+23. Click Add Vehicle Type,click,,"admin.transport.vehicle.add_type.btn"
+24. Enter Vehicle Type Name,type,tempo{randomAlpha}&gt;&gt;lorryTypeName,"admin.transport.vehicle.name.input"
+25. Enter Base Fare,type,150,"admin.transport.vehicle.base_fare.input"
+26. Enter Base Fare Max Kilometer,type,10,"admin.transport.vehicle.base_km.input"
+27. Open Extra Distance Fare Dropdown,click,,"admin.transport.vehicle.extra_fare_type.dropdown"
+28. Select Amount,click,,"admin.transport.status.amount_option"
+29. Enter Extra Distance Fare,type,10,"admin.transport.vehicle.extra_fare.input"
+30. Enter Free Waiting Time,type,10,"admin.transport.vehicle.waiting_free.input"
+31. Open Waiting Charge Dropdown,click,,"admin.transport.vehicle.waiting_type.dropdown"
+32. Select Amount,click,,"admin.transport.status.amount_option"
+33. Enter Waiting Rate,type,10,"admin.transport.vehicle.waiting_rate.input"
+34. Enter Included Trip Waiting,type,10,"admin.transport.vehicle.trip_waiting_free.input"
+35. Open Trip Waiting Charge Dropdown,click,,"admin.transport.vehicle.trip_waiting_type.dropdown"
+36. Select Amount,click,,"admin.transport.status.amount_option"
+37. Enter Trip Waiting Rate,type,50,"admin.transport.vehicle.trip_waiting_rate.input"
+38. Enter Free Pickup Distance,type,5,"admin.transport.vehicle.pickup_free.input"
+39. Open Pickup Charge Dropdown,click,,"admin.transport.vehicle.pickup_type.dropdown"
+40. Select Amount,click,,"admin.transport.status.amount_option"
+41. Enter Pickup Fee,type,50,"admin.transport.vehicle.pickup_fee.input"
+42. Open Customer Fee Dropdown,click,,"admin.transport.vehicle.customer_type.dropdown"
+43. Select Amount,click,,"admin.transport.status.amount_option"
+44. Enter Customer Fee,type,50,"admin.transport.vehicle.customer_fee.input"
+45. Open Customer GST Dropdown,click,,"admin.transport.vehicle.customer_gst_type.dropdown"
+46. Select Amount,click,,"admin.transport.status.amount_option"
+47. Enter GST amount,type,50,"admin.transport.vehicle.customer_gst.input"
+48. Open Driver Fee Dropdown,click,,"admin.transport.vehicle.driver_type.dropdown"
+49. Select Amount,click,,"admin.transport.status.amount_option"
+50. Enter Driver Fee,type,50,"admin.transport.vehicle.driver_fee.input"
+51. Open Driver GST Dropdown,click,,"admin.transport.vehicle.driver_gst_type.dropdown"
+52. Select Amount,click,,"admin.transport.status.amount_option"
+53. Enter Driver Gst,type,50,"admin.transport.vehicle.driver_gst.input"
+54. Open Status Dropdown,click,,"admin.transport.vehicle.status.dropdown"
+55. Select Active,click,,"admin.transport.status.active_option"
+56. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/tempo.jpg","admin.transport.vehicle.image.file"
+57. Enter Notifiacation,type,50,"admin.transport.vehicle.notify_km.input"
+58. Enter Driver Request ETA,type,50,"admin.transport.vehicle.eta_limit.input"
+59. Enter Driver Request KM,type,50,"admin.transport.vehicle.km_limit.input"
+60. Open Night Charge Timing Status Dropdown,click,,"admin.transport.night.status.dropdown"
+61. Select Active,click,,"admin.transport.status.active_option"
+62. Click Surcharge Time Checkbox,click,,"admin.transport.night.everyday.checkbox"
+63. Enter From Time,type,100000AM,"admin.transport.night.from_time.input"
+64. Enter To Time,type,220000PM,"admin.transport.night.to_time.input"
+65. Open Dropdown,click,,"admin.transport.night.type.dropdown"
+66. Select Amount,click,,"admin.transport.status.amount_option"
+67. Enter Price,type,50,"admin.transport.night.price.input"
+68. Click Submit,click,,"web.global.action.submit"
+69. Wait Until Sucess,wait_until_visible,,"web.global.toast.info"
+70. Click Setting menu,click,,"web.global.menu.settings"
+71. Click City admin menu,click,,"admin.menu.city_admin"
+72. Verify City Admin List,verify,,"admin.city_admin.list_heading"
+73. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+74. Verify City Admin heading,verify,,"admin.city_admin.add_heading"
+75. Select Name field,click,,"admin.city_admin.input_name"
+76. Enter Admin Name,type,newAdmin{randomAlpha} &gt;&gt; transAdminName,"admin.city_admin.input_name"
+77. Select Email field,click,,"admin.city_admin.input_email"
+78. Enter Email,type,transAdmin_{timestamp}@gmail.com &gt;&gt; transAdminEmail,"admin.city_admin.input_email"
+79. select the password field,click,,"admin.city_admin.input_password"
+80. Enter the Password,type,password{timestamp}&gt;&gt; transAdminPassword,"admin.city_admin.input_password"
+81. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+82. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+83. Click on the Bike Ride checkbox,click,,"admin.city_admin.chk_transport_bike_ride"
+84. Click on the Taxi Ride checkbox,click,,"admin.city_admin.chk_transport_taxi_ride"
+85. Click on the Auto Ride checkbox,click,,"admin.city_admin.chk_transport_auto_ride"
+86. Click on the dynamic service checkbox,click,,"admin.transport.dropdown.dynamic_lorry_service"
+87. Click on the Add Driver checkbox,click,,"admin.city_admin.chk_driver_add"
+88. Click on the Approved Drivers checkbox,click,,"admin.city_admin.chk_driver_approved"
+89. Click on the Un-Approved Drivers checkbox,click,,"admin.city_admin.chk_driver_unapproved"
+90. Click on the Blocked Drivers checkbox,click,,"admin.city_admin.chk_driver_blocked"
+91. Click on the Reject Drivers checkbox,click,,"admin.city_admin.chk_driver_rejected"
+92. Click on the Deleted Drivers checkbox,click,,"admin.city_admin.chk_driver_deleted"
+93. Click on the Driver Pending Documents checkbox,click,,"admin.city_admin.chk_driver_pending_docs"
+94. Click on the Driver Expired Documents checkbox,click,,"admin.city_admin.chk_driver_expired_docs"
+95. Click Submit,click,,"web.global.login.submit_btn"
+96. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+97. Filter admin name,type,{transAdminName},"admin.city_admin.input_name_filter"
+98. Click Logout Icon,click,,"web.global.action.logout_link"
+99. Click Confirm Logout,click,,"web.global.action.logout_confirm"
+100. Wait For Login Page,wait_until_visible,,"web.global.login.email"
+101. Enter Email,type,{transAdminEmail},"web.global.login.email"
+102. Enter Password,type,{transAdminPassword},"web.global.login.password"
+103. Click Login,click,,"web.global.login.submit_btn"
+104. Wait For Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"
+105. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+106. Click drivers menu,click,,"admin.drivers.menu.icon"
+107. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+108. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
+109. Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+110. Select Lorry Ride Option,click,,"admin.transport.dropdown.dynamic_lorry_transport_service"
+111. Enter Driver Name,type,lorrydriver{randomAlpha} &gt;&gt; lorrydriverName,"admin.drivers.fullname.input"
+112. Enter Email,type,lorrydriver_{timestamp}@gmail.com&gt;&gt;lorrydriverEmail,"admin.drivers.email.input"
+113. Enter Contact Number,type,{randomPhone}&gt;&gt;lorryPhone,"admin.drivers.phone.input"
+114. Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
+115. Enter Whatspp Number,type,{lorryPhone},"admin.drivers.whatsapp_phone.input"
+116. Upload Profile Image,uploadfile,"src/main/resources/test-data/lorrydriver.jpg","admin.drivers.profile_image.file"
+117. Select Source,click,,"admin.drivers.source_dropdown.select"
+118. Select Instagram,click,,"admin.drivers.instagram_option.span"
+119. Select Male Gender,click,,"admin.drivers.male_gender.div"
+120. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+121. Select Lorry Option,click,,"admin.transport.dropdown.dynamic_vehicle_lorry_type"
+122. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+123. Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
+124. Enter Model Name,type,petrol,"admin.drivers.modelname.input"
+125. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/lorry.png","admin.drivers.vehicle_image.file"
+126. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
+127. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
+128. Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
+129. Enter Account Holder Name,type,{lorrydriverName},"admin.drivers.accountholder.input"
+130. Enter Payment Email Address,type,{lorrydriverEmail},"admin.drivers.paymentemail.input"
+131. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
+132. Click Submit,click,,"web.global.action.submit"
+133. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+134. wait,5000,,
+135. Click sidebar,click,,"web.global.action.sidebar_toggle"
+136. wait,2000,,
+137. Check Transport Menu exists,element_present,,"admin.transport.menu.card"
+138. wait,2000,,
+139. Check Deleivery Service exists,element_absent,,"admin.city_admin.chk_web_delivery"
+140. wait,2000,,
+141. Check Provider Service exists,element_absent,,"admin.city_admin.chk_provider_list"
+142. wait,2000,,
+143. Check Add Driver exists,element_present,,"admin.drivers.add_menu.link"
+144. wait,2000,,
+145. Check Approved Driver exists,element_present,,"admin.drivers.approved_docs.link"
+146. wait,2000,,
+147. Check Un-Approved Drivers exists,element_present,,"admin.drivers.unapproved_docs.link"
+148. wait,2000,,
+149. Check Blocked Driver exists,element_present,,"admin.drivers.blocked_docs.link"
+150. wait,2000,,
+151. Check Reject Driver exists,element_present,,"admin.drivers.reject_docs.link"
+152. wait,2000,,
+153. Check Deleted Driver exists,element_present,,"admin.drivers.deleted_docs.link"
+154. wait,2000,,
+155. Check pending Documents exists,element_present,,"admin.drivers.driver_pending_docs.link"
+156. wait,2000,,
+157. Check Driver Expired Documents exists,element_present,,"admin.drivers.driver_expired_docs.link"
+158. wait,2000,,
+159. Click Logout Icon,click,,"web.global.action.sidebar_logout_btn"
+160. Click Confirm Logout,click,,"web.global.action.logout_confirm"
+161. Wait For Login Page,wait_until_visible,,"web.global.login.email"
+162. Enter Email,type,super_admin@gmail.com,"web.global.login.email"
+163. Enter Password,type,R1mep@321,"web.global.login.password"
+164. Click Login,click,,"web.global.login.submit_btn"
+165. Wait For Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"
+166. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+167. Click Transports Services Menu,click,,"admin.transport.menu.card"
+168. Wait For Transport Services,wait_until_visible,,"admin.transport.page.header"
+169. Filter Services List,type,{lorryTransportName},"admin.transport.grid.name_filter"
+170. Click Edit Icon,click,,"admin.transport.docs.edit_icon"
+171. wait,2000,,
+172. Scroll Grid,tab,5,"admin.transport.name.input"
+173. wait,2000,,
+174. Open status Dropdown,click,,"admin.transport.status.dropdown"
+175. Select Deactivate,click,,"admin.transport.status.deactivate_option"
+176. Click Submit,click,,"web.global.action.submit"
+177. Wait For Sucess,wait_until_visible,,"web.global.toast.info"
+178. wait,2000,,</t>
+  </si>
+  <si>
+    <t>Deleted Test Steps</t>
+  </si>
+  <si>
+    <t>8. Enter Video Call Limit,type,60,"admin.customer.input_video_limit"</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Customer Icon,click,,"admin.menu.customer_icon"
+3. Click Add Customers,click,,"admin.menu.add_customers"
+4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
+8. Open Gender,click,,"admin.customer.dropdown_gender"
+9. Select Male,click,,"admin.customer.select_gender_male"
+10. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+11. Click Submit,click,,"web.global.action.submit"
+12. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+13. Click Dashboard,click,,"web.global.menu.dashboard"
+14. Click Customer Icon,click,,"admin.menu.customer_icon"
+15. Click Verified Customers,click,,"admin.menu.verified_customers"
+16. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+17. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+18. Scroll Grid,tab,7,"admin.customer.filter_name"
+19. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
+20. Click Close,click,,"web.global.action.close"
+21. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
+22. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+23. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
+24. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+25. Select Add Money,click,,"admin.customer.wallet.select_add_money"
+26. Click Submit,click,,"web.global.action.submit"
+27. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+28. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+29. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
+30. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+31. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+32. Click Submit,click,,"web.global.action.submit"
+33. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+34. Click dashboard Icon,click,,"web.global.menu.dashboard"
+35. Click Customer Icon,click,,"admin.menu.customer_icon"
+36. Click Verified Customers,click,,"admin.menu.verified_customers"
+37. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+38. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+39. Scroll Grid,tab,7,"admin.customer.filter_name"
+40. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+41. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+42. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+43. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+44. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+45. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+46. Enter Points,type,30,"admin.customer.loyalty.input_points"
+47. Click Submit,click,,"web.global.action.submit"
+48. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+49. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+50. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+51. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+52. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+53. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+54. Enter Points,type,10,"admin.customer.loyalty.input_points"
+55. Click Submit,click,,"web.global.action.submit"
+56. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+57. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+58. Click Customer Icon,click,,"admin.menu.customer_icon"
+59. Click Verified Customers,click,,"admin.menu.verified_customers"
+60. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+61. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+62. Scroll Grid,tab,7,"admin.customer.filter_name"
+63. Click Disable Icon,click,,"admin.customer.grid.btn_block"
+64. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
+65. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
+66. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+67. Verify Added Successfully,verify,,"web.global.toast.info"
+68. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+69. Click Customer Icon,click,,"admin.menu.customer_icon"
+70. Click Blocked Customers,click,,"admin.menu.blocked_customers"
+71. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+72. Scroll Grid,tab,10,"admin.customer.filter_name"
+73.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
+74. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+75. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
+76. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+77. Click Customer Icon,click,,"admin.menu.customer_icon"
+78. Click Verified Customers,click,,"admin.menu.verified_customers"
+79. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+80. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Setting menu,click,,"web.global.menu.settings"
+3. Click City admin menu,click,,"admin.menu.city_admin"
+4. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
+5. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+6. Wait For Admin heading,wait_until_visible,,"admin.city_admin.add_heading"
+7.Select Name field,click,,"admin.city_admin.input_name"
+8. Enter Admin Name,type,faizal{randomAlpha} &gt;&gt; adminName,"admin.city_admin.input_name"
+9.Select Email field,click,,"admin.city_admin.input_email"
+10. Enter Email,type,faizal_{timestamp}@gmail.com,"admin.city_admin.input_email"
+11.select the password field,click,,"admin.city_admin.input_password"
+12.Enter the Password as "faizal@123",type,faizal@123,"admin.city_admin.input_password"
+13.Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+14.Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+15. Click on the "Transport Service" → "Auto Ride" checkbox,click,,"admin.city_admin.chk_transport_auto_ride"
+16.Click on the "Customers" → "Add Customers" checkbox,click,,"admin.city_admin.chk_customer_add"
+17.Click on the "Customers" → "Verified Customers"checkbox,click,,"admin.city_admin.chk_customer_verified"
+18.Click on the "Customers" → "Non Verified Customers" checkbox,click,,"admin.city_admin.chk_customer_unverified"
+19.Click on the "Customers" → "Blocked Customers" checkbox,click,,"admin.city_admin.chk_customer_blocked"
+20.Click on the "Customers" → "Deleted Customers" checkbox,click,,"admin.city_admin.chk_customer_deleted"
+21.Click on the "Providers" → "Transport Providers List" checkbox,click,,"admin.city_admin.chk_provider_list"
+22.Click on the "Drivers" → "Add Driver" checkbox,click,,"admin.city_admin.chk_driver_add"
+23.Click on the "Drivers" → "Approved Drivers" checkbox,click,,"admin.city_admin.chk_driver_approved"
+24.Click on the "Drivers" → "Un-Approved Drivers" checkbox,click,,"admin.city_admin.chk_driver_unapproved"
+25.Click on the "Drivers" → "Blocked Drivers" checkbox,click,,"admin.city_admin.chk_driver_blocked"
+26.Click on the "Drivers" → "Reject Drivers" checkbox,click,,"admin.city_admin.chk_driver_rejected"
+27.Click on the "Drivers" → "Deleted Drivers" checkbox,click,,"admin.city_admin.chk_driver_deleted"
+28.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox,click,,"admin.city_admin.chk_subscription_plan"
+29.Click on the "Cash Out" → "Driver Cash Out" checkbox,click,,"admin.city_admin.chk_cashout"
+30.Click on the "Report Issue" → "Customer Report Issues" checkbox,click,,"admin.city_admin.chk_report_customer"
+31.Click on the "Report Issue" → "Driver Report Issues" checkbox,click,,"admin.city_admin.chk_report_driver"
+32.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,"admin.city_admin.chk_report_provider"
+33.Click on the "Report Issue" → "Report issue settings" checkbox,click,,"admin.city_admin.chk_report_settings"
+34.Click on the "Report Issue" → "FAQs" checkbox,click,,"admin.city_admin.chk_report_faqs"
+35.Click Submit,click,,"web.global.login.submit_btn"
+36. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+37.Filter admin name,type,{adminName},"admin.city_admin.input_name_filter"</t>
   </si>
 </sst>
 </file>
@@ -3550,7 +3555,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -3619,7 +3624,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
@@ -3691,7 +3696,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
@@ -3763,7 +3768,7 @@
         <v>32</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
@@ -3835,7 +3840,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>58</v>
@@ -3907,7 +3912,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
@@ -3979,7 +3984,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>57</v>
@@ -4051,7 +4056,7 @@
         <v>71</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>74</v>
@@ -4160,7 +4165,7 @@
     <col min="4" max="4" width="31.6640625" customWidth="1"/>
     <col min="5" max="5" width="53.21875" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="38.6640625" customWidth="1"/>
     <col min="8" max="8" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4184,7 +4189,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4204,10 +4209,13 @@
         <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4280,7 +4288,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
@@ -4335,7 +4343,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4355,13 +4363,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +4411,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4423,13 +4431,13 @@
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4478,7 +4486,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4498,13 +4506,13 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4553,7 +4561,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4573,13 +4581,13 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4628,7 +4636,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4648,13 +4656,13 @@
         <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4671,7 +4679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B7FC7-76CD-491F-AC51-1837B3B068AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17220503-D468-40D2-B5A5-294329C90611}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4712,19 +4720,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>88</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1430B7B-3368-4E28-944A-634D6BB3EFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD14C14E-4EE3-469A-A511-DAF31C968419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -22,9 +22,9 @@
     <sheet name="AddTaxiDriver" sheetId="35" r:id="rId7"/>
     <sheet name="TransportServiceCompleteTest" sheetId="37" r:id="rId8"/>
     <sheet name="AddTransportCityAdmin" sheetId="39" r:id="rId9"/>
-    <sheet name="AddStore" sheetId="7" r:id="rId10"/>
-    <sheet name="StoreOperations" sheetId="8" r:id="rId11"/>
-    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId12"/>
+    <sheet name="AddStore" sheetId="40" r:id="rId10"/>
+    <sheet name="StoreOperations" sheetId="42" r:id="rId11"/>
+    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId12"/>
     <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId13"/>
     <sheet name="AddProvider" sheetId="11" r:id="rId14"/>
     <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId15"/>
@@ -331,76 +331,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The City Area created in the previous AddCityArea must be in an "Active" status to be visible in the cityId dropdown selection.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Data Dependency: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The AddStore test suite must be always executed before this test. This is critical because the StoreOperations process utilizes the dynamic {storeName} variable generated and stored during the AddStore creation phase.
-RunSheet: AddStore
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Authentication State: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The user is already authenticated as a Super Admin and the session is active.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Navigation State:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The browser is currently on the Dashboard page. Ensure the dashboard.url is configured as https://dev.we1.co/#/page-module/dashboard_dynamic in the config.properties file.
-</t>
     </r>
   </si>
   <si>
@@ -1449,73 +1379,6 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>1.Click badge,click,,"//i[contains(@class, 'fa-user-shield')]"
-2.Click Delivery Services,click,,"//h2[contains(text(), 'Delivery Services')]"
-3.Verify Delivery Services,verify,,"//div[contains(text(),'DELIVERY SERVICES')]"
-4.Click Home Icon Food Delivery,click,,"//div[@role='row'][.//span[text()='Food Delivery']]//i[@title='Home']"
-5.Verify Food Delivery Summary,verify,,"//div[normalize-space()='Food Delivery Summary']"
-6.Click  Stores,click,,"//button[contains(., 'Stores')]"
-7.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-8.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-9.Filter Store List,type,{storeName},"//input[@aria-label='Store Name Filter Input']"
-10.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-11.Click Product Icon,click,,"//i[@title='Product View']"
-12.Click  Add  Products,click,,"//button[normalize-space()='Add Products']"
-13.Open Product Category Dropdown,click,,"(//label[contains(text(),'Product Category')]/following-sibling::p-dropdown/div)[1]"
-14.Select Grill Chicken,click,,"//li[@role='option'][contains(.,'Grill Chicken')]"
-15.Enter Product Name, type, kfcProduct{randomAlpha}&gt;&gt; kfcProductName, "//label[contains(.,'Product Name')]/following-sibling::input"
-16.Enter Product Amount, type, 500, "//label[contains(.,'Product Amount')]/following-sibling::input"
-17.Enter Product Description, type, KFC special grill chicken, "//label[contains(text(),'Product Description')]/following-sibling::textarea"
-18.Upload Product Image, uploadfile, "src/main/resources/test-data/grillchicken.jpg", "//input[@type='file' and @accept='image/*']"
-19.Open Product Category Dropdown,click,,"(//label[contains(text(),'Product Category')]/following-sibling::p-dropdown/div)[2]"
-20.Select Activate,click,,"//li[@role='option'][contains(.,'Activate')]"
-21.Open Discount Type Dropdown,click,,"//label[contains(.,'Discount Type')]/following-sibling::select/option[text()='Discount in Amount']"
-22.Enter Discount Amount, type, 50, "//label[contains(.,'Discount Amount')]/following-sibling::input"
-23.Click Save, click, , "//button[normalize-space()='Save']"
-24.Verify Saved Succesfully, verify, , "//div[@aria-label='Product added successfully']"
-25.Verify Store Products,verify,,"//div[normalize-space()='Store Products']"
-26.Filter Product List,type,{kfcProductName},"//input[@aria-label='Product Name Filter Input']"
-27.Click Back, click, , "//button[normalize-space()='Back']"
-28.Filter Store List,type,{storeName},"//input[@aria-label='Store Name Filter Input']"
-29.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-30.Click Wallet Icon,click,,"//i[@title='Wallet']"
-31.Click Manage Transaction, click, , "//button[normalize-space()='Manage Transaction']"
-32.Enter Wallet Amount, type, 1000, "//input[@placeholder='Enter Wallet Amount']"
-33.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-34.Select Add Money,click,,"//li[@role='option' and @aria-label='Add Money']"
-35.Click Submit, click, , "//button[normalize-space()='Submit']"
-36.Verify Saved Succesfully, verify, , "//div[@aria-label='Added Successfully']"
-37.Click Manage Transaction, click, , "//button[normalize-space()='Manage Transaction']"
-38.Enter Wallet Amount, type, 200, "//input[@placeholder='Enter Wallet Amount']"
-39.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-40.Select Deduct Money,click,,"//li[@role='option'][contains(.,'Deduct Money')]"
-41.Click Submit, click, , "//button[normalize-space()='Submit']"
-42.Verify Saved Succesfully, verify, , "//div[@aria-label='Added Successfully']"
-43.Click Back, click, , "//button[normalize-space()='Back']"
-44.Filter Store List,type,{storeName},"//input[@aria-label='Store Name Filter Input']"
-45.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-46.Click Drivers Icon,click,,"//i[@title='Drivers']"
-47.Click Add Private Driver, click, , "//button[normalize-space()='Add Private Driver']"
-48.Enter Driver Name, type, kfcdriver_{timestamp} &gt;&gt; kfcdriverName, "//label[contains(., 'Driver Full Name')]/following-sibling::div//input"
-49.Enter Email, type, kfcdriver_{timestamp}@gmail.com, "//label[contains(., 'Email')]/following-sibling::div//input"
-50.Enter Contact Number, type, {randomPhone}, "//label[contains(., 'Contact No')]/following-sibling::div//input"
-51.Upload Profile Image, uploadfile, "src/main/resources/test-data/bikedriver.jpg", "//input[@type='file' and @accept='image/*']"
-52. Select Male Gender, click, , "//div[contains(text(), 'Male')]/preceding-sibling::mat-radio-button"
-53.Click Vehicle Type Dropdown,click,,"//label[contains(., 'Vehicle Type')]/following-sibling::p-dropdown"
-54.Select  Scooter Option,click,,"//li[@role='option'][contains(.,'Scooter')]"
-55. Enter Model Year, type, 2013, "//label[span[text()='Model Year']]/following::input[1]"
-56.Enter Vehicle Company, type, kfcBikeCompany{randomAlpha}&gt;&gt; kfcBikeCompanyName, "//label[contains(., 'Vehicle Company')]/following-sibling::div//input"
-57. Enter Plate No, type, KL-01-AB-1634, "//label[contains(., 'Plate No')]/following-sibling::div//input"
-58. Enter Model Name, type, activa, "//label[contains(., 'Model Name')]/following-sibling::div//input"
-59. Upload Vehicle Image, uploadfile, "src/main/resources/test-data/bike.jpg", "(//app-image-upload//input[@type='file'])[2]"
-60. Enter Vehicle Color, type, white, "//label[contains(., 'Vehicle Color')]/following::input[1]"
-61. Click Submit, click, , "//button[contains(.,'Submit')]"
-62. Verify Driver Added, verify, , "//div[@aria-label='Added Successfully']"
-63.Filter Driver List,type,{kfcdriverName},"//input[@aria-label='Driver Name Filter Input']"
-64.Click Eye Icon,click,,"//i[@class='bi bi-eye cursor-pointer gridIcon View']"
-65.wait,1000,,</t>
   </si>
   <si>
     <t>1.Click badge,click,,"//i[contains(@class, 'fa-user-secret')]"
@@ -1740,180 +1603,6 @@
   </si>
   <si>
     <t>Super Admin Login</t>
-  </si>
-  <si>
-    <t>1.Click badge,click,,"//i[contains(@class, 'fa-user-shield')]"
-2.Click Delivery Services,click,,"//h2[contains(text(), 'Delivery Services')]"
-3.Verify Delivery Services,verify,,"//div[contains(text(),'DELIVERY SERVICES')]"
-4.Click Home Icon Food Delivery,click,,"//div[@role='row'][.//span[text()='Food Delivery']]//i[@title='Home']"
-5.Verify Food Delivery Summary,verify,,"//div[normalize-space()='Food Delivery Summary']"
-6.Click  Stores,click,,"//button[contains(., 'Stores')]"
-7.Select Add Store,click,,"//div[contains(text(), 'Add Store')]"
-8.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Add Store')]"
-9.Enter Store Name, type, KFC_{timestamp} &gt;&gt; storeName, "//input[@placeholder='Store Name']"
-10.Open Delivery Radius Dropdown,click,,"//span[@aria-label='select radius']"
-11.Select Twenty Five Kilometer,click,,"//li[@role='option'][contains(.,'25 KM')]"
-12.Open Estimated Delivery Time,click,,"//span[@aria-label='Estimated Delivery Time']"
-13. Select Thirty Minute,click,,"//li[@role='option'][contains(.,'30 MIN')]"
-14.Enter Order Minimum Amount, type, 300, "//input[@placeholder='Order Min Amount']"
-15.Enter Packaging Charges, type, 50, "//input[@placeholder='Packaging Charges']"
-16.Enter Short Description, type, KFC is a global fast-food giant famous for its Original Recipe fried chicken, "//input[@placeholder="Type here"]"
-17.Upload Banner Image, uploadfile, "src/main/resources/test-data/kfcbanner.jpg", "//input[@type='file']"
-18.Open Driver Notification,click,,"//span[@aria-label='select driver type']"
-19.Select Both Driver,click,,"//li[@role='option'][contains(.,'Both Driver')]"
-20.Click Checkbox Allow For Pickup , click, , "//label[contains(., "Do You Want ?")]/following-sibling::div//mat-checkbox"
-21.Open Current Status Dropdown,click,,"//span[@aria-label='Active']"
-22.Select Active,click,,"//li[@role='option'][contains(.,'Active')]"
-23..Enter Store Address, type, KFC chennai, "//input[@placeholder='Search location']"
-24.wait,1000,,
-25.Select First Option,arrow_down,,"//input[@placeholder='Search location']"
-26.Confirm Option,press_enter,,"//input[@placeholder='Search location']"
-27.wait,1000,,
-28.Click Storewise Comission Checkbox, click, , "//div[contains(text(),'Store Wise Commission')]/preceding-sibling::mat-checkbox"
-29.Enter Store Commision, type, 25, "//label[contains(.,'Commission (in %)')]/following-sibling::div//input"
-30.Open Driver Notification,click,,"//span[@aria-label='select offer type']"
-31.Select Amount,click,,"//li[@role='option'][contains(.,'Amount')]"
-32.Enter Offer Amount, type, 50, "//label[contains(.,'Offer Amount')]/following-sibling::div//input"
-33.Enter Offer Min Amount, type, 500, "//label[contains(.,'Offer Min Amount')]/following-sibling::div//input"
-34.Enter Contact Person Full Name, type, storeowner_{timestamp} &gt;&gt; storeOwner, "//label[contains(.,'Contact Person Full Name')]/following-sibling::div//input"
-35.Enter Email, type, kfc_{timestamp}@gmail.com&gt;&gt;storeEmail, "//label[contains(.,'Email Address')]/following-sibling::div//input"
-36.Enter Contact Number, type, {randomPhone}, "//label[contains(.,'Contact Number')]/following-sibling::div//input"
-37.Upload Store Image, uploadfile, "src/main/resources/test-data/kfcstore.jpg", "(//input[@type='file'])[2]"
-38.Enter Bank Name, type, federal, "//label[contains(.,'Bank Name')]/following-sibling::div//input"
-39.Enter Bank Location,type, chennai, "//label[contains(.,'Bank Location(City Name)')]/following-sibling::div//input"
-40.Enter Account Number, type, 123456789012, "//label[contains(.,'Account Number')]/following-sibling::div//input"
-41.Enter Accont Holder Name, type, {storeOwner}, "//label[contains(.,'Account Holder Name')]/following-sibling::div//input"
-42.Enter Payment Email Address, type, {storeEmail}, "//label[contains(.,'Payment Email Address')]/following-sibling::div//input"
-43.Enter BIC Code, type, 1234, "//label[contains(.,'BIC Code')]/following-sibling::div//input"
-44.Click Store Timing Checkbox, click, , "//div[contains(text(),'Every Day')]/preceding-sibling::mat-checkbox"
-45.Enter From Time, type, 100000AM, "((//input[@placeholder='--:--:-- --'])[1])"
-46.Enter To Time, type, 100000PM, "((//input[@placeholder='--:--:-- --'])[2])"
-47.Submit Add Store,click,,"//button[normalize-space()='Submit']"
-48. Verify Success Message,verify,,"//div[@aria-label='Info']"
-49.Click  Stores,click,,"//button[contains(., 'Stores')]"
-50.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-51.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-52.Filter Store List,type,{storeName},"//input[@aria-label='Store Name Filter Input']"
-53.Click  Stores,click,,"//button[contains(., 'Stores')]"
-54.Select Pending Documents Stores List,click,,"//div[contains(text(), 'Pending Documents Stores')]"
-55.Verify Add Store,verify,,"//div[normalize-space()='Pending Documents Store']"
-56.Filter Pending Document Store List,type,{storeName},"//input[@aria-label='Store Name Filter Input']"
-57.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-58.Click Doc Icon,click,,"//i[contains(@class, 'bi-file-earmark-medical-fill') and contains(@class, 'Navigate')]"
-59. Store Required Documents,verify,,"//div[contains(text(),'Documents')]"
-60.Add Address Proof,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-61.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "//input[@type='file']"
-62.Enter Expiry Date,type,2026-12-12,"//input[@placeholder='YYYY/MM/DD']"
-63.Click Submit, click, , "//button[normalize-space()='Submit']"
-64.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-65.Click Approve Store,click,,"//i[@class='bi bi-hand-thumbs-up-fill cursor-pointer gridIcon Modify']"
-66.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-67.Click Back, click, , "//button[@class='buttonWidget']"
-68.Click  Stores,click,,"//button[contains(., 'Stores')]"
-69.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-70.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-71.Filter Store List,type,{storeName},"//input[@aria-label='Store Name Filter Input']"
-72.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-73.Click Doc Icon,click,,"//i[contains(@class, 'bi-file-earmark-medical-fill') and contains(@class, 'Navigate')]"
-74.Click Eye Icon,click,,"//i[@class='bi bi-eye cursor-pointer gridIcon View']"
-75.wait,1000,,</t>
-  </si>
-  <si>
-    <t>1.Click badge,click,,"//i[contains(@class, 'fa-user-shield')]"
-2.Click Delivery Services,click,,"//h2[contains(text(), 'Delivery Services')]"
-3.Verify Delivery Services,verify,,"//div[contains(text(),' DELIVERY SERVICES')]"
-4.Click Home Icon Food Delivery,click,,"//div[@role='row'][.//span[text()='Food Delivery']]//i[@title='Home']"
-5.Verify Food Delivery Summary,verify,,"//div[normalize-space()='Food Delivery Summary']"
-6.Click  Stores,click,,"//button[contains(., 'Stores')]"
-7.Select Add Store,click,,"//div[contains(text(), 'Add Store')]"
-8.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Add Store')]"
-9.Enter Store Name, type, bilal_{timestamp} &gt;&gt; hotelName, "//input[@placeholder='Store Name']"
-10.Open Delivery Radius Dropdown,click,,"//span[@aria-label='select radius']"
-11.Select Twenty Five Kilometer,click,,"//li[@role='option'][contains(.,'25 KM')]"
-12.Open Estimated Delivery Time,click,,"//span[@aria-label='Estimated Delivery Time']"
-13. Select Thirty Minute,click,,"//li[@role='option'][contains(.,'30 MIN')]"
-14.Enter Order Minimum Amount, type, 300, "//input[@placeholder='Order Min Amount']"
-15.Enter Packaging Charges, type, 50, "//input[@placeholder='Packaging Charges']"
-16.Enter Short Description, type, KFC is a global fast-food giant famous for its Original Recipe fried chicken, "//input[@placeholder="Type here"]"
-17.Upload Banner Image, uploadfile, "src/main/resources/test-data/kfcbanner.jpg", "//input[@type='file']"
-18.Open Driver Notification,click,,"//span[@aria-label='select driver type']"
-19.Select Both Driver,click,,"//li[@role='option'][contains(.,'Both Driver')]"
-20.Click Checkbox Allow For Pickup , click, , "//label[contains(., "Do You Want ?")]/following-sibling::div//mat-checkbox"
-21.Open Current Status Dropdown,click,,"//span[@aria-label='Active']"
-22.Select Active,click,,"//li[@role='option'][contains(.,'Active')]"
-23..Enter Store Address, type, KFC chennai, "//input[@placeholder='Search location']"
-24.wait,1000,,
-25.Select First Option,arrow_down,,"//input[@placeholder='Search location']"
-26.Confirm Option,press_enter,,"//input[@placeholder='Search location']"
-27.wait,1000,,
-28.Click Storewise Comission Checkbox, click, , "//div[contains(text(),'Store Wise Commission')]/preceding-sibling::mat-checkbox"
-29.Enter Store Commision, type, 25, "//label[contains(.,'Commission (in %)')]/following-sibling::div//input"
-30.Open Driver Notification,click,,"//span[@aria-label='select offer type']"
-31.Select Amount,click,,"//li[@role='option'][contains(.,'Amount')]"
-32.Enter Offer Amount, type, 50, "//label[contains(.,'Offer Amount')]/following-sibling::div//input"
-33.Enter Offer Min Amount, type, 500, "//label[contains(.,'Offer Min Amount')]/following-sibling::div//input"
-34.Enter Contact Person Full Name, type, bilalowner_{timestamp} &gt;&gt; hotelOwner, "//label[contains(.,'Contact Person Full Name')]/following-sibling::div//input"
-35.Enter Email, type, bilal_{timestamp}@gmail.com&gt;&gt;storeEmail, "//label[contains(.,'Email Address')]/following-sibling::div//input"
-36.Enter Contact Number, type, {randomPhone}, "//label[contains(.,'Contact Number')]/following-sibling::div//input"
-37.Upload Store Image, uploadfile, "src/main/resources/test-data/kfcstore.jpg", "(//input[@type='file'])[2]"
-38.Enter Bank Name, type, federal, "//label[contains(.,'Bank Name')]/following-sibling::div//input"
-39.Enter Bank Location,type, chennai, "//label[contains(.,'Bank Location(City Name)')]/following-sibling::div//input"
-40.Enter Account Number, type, 123456789012, "//label[contains(.,'Account Number')]/following-sibling::div//input"
-41.Enter Accont Holder Name, type, {hotelOwner}, "//label[contains(.,'Account Holder Name')]/following-sibling::div//input"
-42.Enter Payment Email Address, type, {storeEmail}, "//label[contains(.,'Payment Email Address')]/following-sibling::div//input"
-43.Enter BIC Code, type, 1234, "//label[contains(.,'BIC Code')]/following-sibling::div//input"
-44.Click Store Timing Checkbox, click, , "//div[contains(text(),'Every Day')]/preceding-sibling::mat-checkbox"
-45.Enter From Time, type, 100000AM, "((//input[@placeholder='--:--:-- --'])[1])"
-46.Enter To Time, type, 100000PM, "((//input[@placeholder='--:--:-- --'])[2])"
-47.Submit Add Store,click,,"//button[normalize-space()='Submit']"
-48. Verify Success Message,verify,,"//div[@aria-label='Info']"
-49.Click  Stores,click,,"//button[contains(., 'Stores')]"
-50.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-51.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-52.Filter Store List,type,{hotelName},"//input[@aria-label='Store Name Filter Input']"
-53.Click  Stores,click,,"//button[contains(., 'Stores')]"
-54.Select Pending Documents Stores List,click,,"//div[contains(text(), 'Pending Documents Stores')]"
-55.Verify Add Store,verify,,"//div[normalize-space()='Pending Documents Store']"
-56.Filter Pending Document Store List,type,{hotelName},"//input[@aria-label='Store Name Filter Input']"
-57.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-58.Click Doc Icon,click,,"//i[contains(@class, 'bi-file-earmark-medical-fill') and contains(@class, 'Navigate')]"
-59. Store Required Documents,verify,,"//div[contains(text(),'Documents')]"
-60.Add Address Proof,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-61.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "//input[@type='file']"
-62.Enter Expiry Date,type,2026-12-12,"//input[@placeholder='YYYY/MM/DD']"
-63.Click Submit, click, , "//button[normalize-space()='Submit']"
-64.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-65.Click Approve Store,click,,"//i[@class='bi bi-hand-thumbs-up-fill cursor-pointer gridIcon Modify']"
-66.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-67.Click Back, click, , "//button[@class='buttonWidget']"
-68.Click  Stores,click,,"//button[contains(., 'Stores')]"
-69.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-70.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-71.Filter Store List,type,{hotelName},"//input[@aria-label='Store Name Filter Input']"
-72.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-73.Click Block Icon,click,,"//i[@title='Blocked']"
-74.Click Block  Yes,click,,"//button[normalize-space()='Yes']"
-75.Click  Stores,click,,"//button[contains(., 'Stores')]"
-76.Select Blocked Store,click,,"//div[normalize-space()='Blocked Stores']"
-77.Filter Store List,type,{hotelName},"//input[@aria-label='Store Name Filter Input']"
-78.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-79.Click unBlock Icon,click,,"//i[@class='bi bi-hand-thumbs-down-fill cursor-pointer gridIcon Modify']"
-80.Click  Stores,click,,"//button[contains(., 'Stores')]"
-81.Select Rejected Store,click,,"//div[normalize-space()='Rejected Stores']"
-82.Filter Store List,type,{hotelName},"//input[@aria-label='Store Name Filter Input']"
-83.Scroll Grid, tab, 7, "//input[@aria-label='Store Name Filter Input']"
-84.Click Approve Icon,click,,"//i[@title='Approve']"
-85.Click  Stores,click,,"//button[contains(., 'Stores')]"
-86.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-87.Filter Store List,type,{hotelName},"//input[@aria-label='Store Name Filter Input']"
-88.wait,3000,,
-89.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-90.Click Doc Icon,click,,"//i[@title='Document']"
-91.Click UnApprove Icon,click,,"//i[@class='bi bi-hand-thumbs-down-fill cursor-pointer gridIcon Modify']"
-92.Click Reject  Yes,click,,"//button[normalize-space()='Yes']"
-93.Rejection Reason,type,document insufficent,"//textarea[@id='swal2-textarea']"
-94.Click Reject  Yes,click,,"//button[normalize-space()='Yes']"
-95.wait,1000,,</t>
   </si>
   <si>
     <t>1.Click badge,click,,"//i[@class='fa-solid fa-user-shield iconstyle']"
@@ -3130,6 +2819,321 @@
 35.Click Submit,click,,"web.global.login.submit_btn"
 36. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
 37.Filter admin name,type,{adminName},"admin.city_admin.input_name_filter"</t>
+  </si>
+  <si>
+    <t>1. Click badge,click,,"admin.store.badge.shield"
+2. Click Delivery Services,click,,"admin.store.delivery_services.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.store.delivery_services.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
+37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Store Required Documents,verify,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Verify Add Store,verify,,"admin.store.list_page.header"
+73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+77. wait,1000,,</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Dependency: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The AddStore test suite must be always executed before this test. This is critical because the StoreOperations process utilizes the dynamic {storeName} variable generated and stored during the AddStore creation phase.
+RunSheet: AddStore2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Authentication State: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The user is already authenticated as a Super Admin and the session is active.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Navigation State:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The browser is currently on the Dashboard page. Ensure the dashboard.url is configured as https://dev.we1.co/#/page-module/dashboard_dynamic in the config.properties file.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Click badge,click,,"admin.store.badge.shield"
+2. Click Delivery Services,click,,"admin.store.delivery_services.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.store.delivery_services.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Store List,click,,"admin.store.submenu.store_list"
+8. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+9. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+10. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+11. Click Product Icon,click,,"admin.store.products.grid_icon"
+12. Click Add Products,click,,"admin.store.products.add_btn"
+13. Open Product Category Dropdown,click,,"admin.store.products.category_dropdown"
+14. Select Grill Chicken,click,,"admin.store.products.category_option_grill"
+15. Enter Product Name,type,kfcProduct{randomAlpha}&gt;&gt; kfcProductName,"admin.store.products.name_input"
+16. Enter Product Amount,type,500,"admin.store.products.amount_input"
+17. Enter Product Description,type,KFC special grill chicken,"admin.store.products.description_textarea"
+18. Upload Product Image,uploadfile,"src/main/resources/test-data/grillchicken.jpg","admin.store.products.image.file"
+19. Open Product Category Dropdown,click,,"admin.store.products.status_dropdown"
+20. Select Activate,click,,"admin.store.products.status_option_active"
+21. Open Discount Type Dropdown,click,,"admin.store.products.discount_dropdown"
+22. Enter Discount Amount,type,50,"admin.store.products.discount_input"
+23. Click Save,click,,"admin.store.products.save_btn"
+24. Wait For Saved Succesfully,wait_until_visible,,"admin.store.products.toast_success"
+25. Wait For Store Products,wait_until_visible,,"admin.store.products.header"
+26. Filter Product List,type,{kfcProductName},"admin.store.products.name_filter"
+27. Click Back,click,,"admin.store.products.back_btn"
+28. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+29. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+30. Click Wallet Icon,click,,"admin.store.wallet.grid_icon"
+31. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
+32. Enter Wallet Amount,type,1000,"admin.store.wallet.amount_input"
+33. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
+34. Select Add Money,click,,"admin.store.wallet.option_add"
+35. Click Submit,click,,"web.global.action.submit"
+36. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
+37. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
+38. Enter Wallet Amount,type,200,"admin.store.wallet.amount_input"
+39. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
+40. Select Deduct Money,click,,"admin.store.wallet.option_deduct"
+41. Click Submit,click,,"web.global.action.submit"
+42. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
+43. Click Back,click,,"admin.store.products.back_btn"
+44. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+45. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+46. Click Drivers Icon,click,,"admin.store.drivers.grid_icon"
+47. Click Add Private Driver,click,,"admin.store.drivers.add_private_btn"
+48. Enter Driver Name,type,kfcdriver_{timestamp} &gt;&gt; kfcdriverName,"admin.drivers.fullname.input"
+49. Enter Email,type,kfcdriver_{timestamp}@gmail.com,"admin.drivers.email.input"
+50. Enter Contact Number,type,{randomPhone},"admin.drivers.phone.input"
+51. Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg","admin.drivers.profile_image.file"
+52. Select Male Gender,click,,"admin.drivers.male_gender.div"
+53. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+54. Select Scooter Option,click,,"admin.drivers.vehicle_option.scooter"
+55. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+56. Enter Vehicle Company,type,kfcBikeCompany{randomAlpha}&gt;&gt; kfcBikeCompanyName,"admin.drivers.companyname.input"
+57. Enter Plate No,type,KL-01-AB-1634,"admin.drivers.plateno.input"
+58. Enter Model Name,type,activa,"admin.drivers.modelname.input"
+59. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg","admin.drivers.vehicle_image.file"
+60. Enter Vehicle Color,type,white,"admin.drivers.vehicle_color.input"
+61. Click Submit,click,,"web.global.action.submit"
+62. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+63. Filter Driver List,type,{kfcdriverName},"admin.drivers.name_filter.input"
+64. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+65. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click badge,click,,"admin.store.badge.shield"
+2. Click Delivery Services,click,,"admin.store.delivery_services.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.store.delivery_services.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
+37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Block Icon,click,,"admin.store.grid.block_icon"
+76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Stores,click,,"admin.store.menu.toggle_btn"
+78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
+79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
+82. Click Stores,click,,"admin.store.menu.toggle_btn"
+83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
+84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
+86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
+87. Click Stores,click,,"admin.store.menu.toggle_btn"
+88. Select Store List,click,,"admin.store.submenu.store_list"
+89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+90. wait,3000,,
+91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+92. Click Doc Icon,click,,"admin.store.grid.document_icon"
+93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
+94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+97. wait,1000,,</t>
   </si>
 </sst>
 </file>
@@ -3546,7 +3550,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -3555,7 +3559,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -3577,7 +3581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3624,16 +3628,16 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3649,7 +3653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A4538F-421E-4B0B-A965-0382A5BEF523}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3690,22 +3694,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3721,7 +3725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57207608-1AD9-408F-B018-55A141C9A651}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3762,22 +3766,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3834,22 +3838,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3906,22 +3910,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3978,22 +3982,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4050,22 +4054,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4122,22 +4126,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4189,7 +4193,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4200,22 +4204,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4282,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4343,7 +4347,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4357,19 +4361,19 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4411,7 +4415,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4425,19 +4429,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4486,7 +4490,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4500,19 +4504,19 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4561,7 +4565,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4575,19 +4579,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4636,7 +4640,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4647,22 +4651,22 @@
         <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4720,22 +4724,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD14C14E-4EE3-469A-A511-DAF31C968419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BF513C-6185-45BE-8062-0F8880287EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="AddStore" sheetId="40" r:id="rId10"/>
     <sheet name="StoreOperations" sheetId="42" r:id="rId11"/>
     <sheet name="StoreStatusManagement" sheetId="43" r:id="rId12"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId13"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId13"/>
     <sheet name="AddProvider" sheetId="11" r:id="rId14"/>
     <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId15"/>
     <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId16"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="120">
   <si>
     <t>City Area</t>
   </si>
@@ -1603,177 +1603,6 @@
   </si>
   <si>
     <t>Super Admin Login</t>
-  </si>
-  <si>
-    <t>1.Click badge,click,,"//i[@class='fa-solid fa-user-shield iconstyle']"
-2.Click Delivery Services,click,,"//h2[normalize-space()='Delivery Services']"
-3.Verify Delivery Services,verify,,"//div[normalize-space()='DELIVERY SERVICES']"
-4.Click  Add Service Category,click,,"//button[normalize-space()='Add Service Category']"
-5.Enter Category Name, type, milk Delivery{randomAlpha}&gt;&gt; deliveryName, "//input[@placeholder='Category Name']"
-6.Enter Slug, type, Milk Delivery, "//input[@placeholder='Slug']"
-7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "//input[@type='file' and @accept='image/*']"
-8.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-9.Select Activate,click,,"//li[@aria-label='Activate']"
-10.Open Category Flow Dropdown,click,,"//label[contains(., 'Category Flow')]/following-sibling::p-dropdown"
-11.Select default flow(food-delivery),click,,"//li[@aria-label='default flow(food-delivery)']"
-12.Enter Delivery Name Tamil, type,பால்காரர், "//input[@placeholder='Enter in Tamil']"
-13.Enter Delivery Name Arabic, type, لبّان, "//input[@placeholder='Enter in Arabic']"
-14.Enter Delivery Name Hindi, type, दूधवाला, "//input[@placeholder='Enter in Hindi']"
-15.Click  Submit,click,,"//button[normalize-space()='Submit']"
-16.Verify Sucess, verify, , "//div[@aria-label='Info']"
-17.Filter Services List,type,{deliveryName},"//input[@aria-label='Services Filter Input']"
-18.Click Home Icon ,click,,"//i[@title='Home']"
-19.Click Settings ,click,,"//button[contains(., 'Settings')]"
-20.Click Requirment Document ,click,,"//div[contains(text(), 'Required Documents')]"
-21.Click Add Document ,click,,"//button[normalize-space()='Add Document']"
-22.Enter Name, type, documet{randomAlpha}&gt;&gt; deliveryDocumentName, "//input[@placeholder='Type here']"
-23.Open status Dropdown,click,,"//span[@aria-label='select status']"
-24.Select Active,click,,"//li[@aria-label='Active']"
-25.Click Document Expiry ,click,,"//div[./div[contains(text(), 'Document Expiry')]]//input"
-26.Click Document Expiry ,click,,"//div[./div[contains(text(), 'Document Expiry')]]//input"
-27.Click Mandatory Document ,click,,"//div[./div[contains(text(), 'Mandatory Document')]]//input"
-28.Click  Require Proof Number,click,,"//div[./div[contains(text(), 'Require Proof Number')]]//input"
-29.Enter Display Order, type, 10,"//input[@placeholder='Display Order']"
-30.Click Submit ,click,,"//button[normalize-space()='Submit']"
-31.Verify Sucess, verify, , "//div[@aria-label='Info']"
-32.Filter Document List,type,{deliveryDocumentName},"//input[@aria-label='Name Filter Input']"
-33.wait,2000,,
-33.Click Settings ,click,,"//button[contains(., 'Settings')]"
-34.Click Promocode ,click,,"//div[normalize-space()='Promocode']"
-35.Click Add Promo Code ,click,,"//button[normalize-space()='Add Promo Code']"
-36.Open User List Dropdown,click,,"//label[contains(., 'User List')]/following-sibling::p-multiselect//div[contains(@class, 'p-multiselect-label-container')]"
-37.Select User,click,,"//li[@aria-label='{customerName}']"
-38.Click Code Name Box,click,,"//input[@placeholder='Code Name']"
-39.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; deliveryPromoCodeName, "//input[@placeholder='Code Name']"
-40.Open Discout Type Dropdown,click,,"//span[@aria-label='Select Discount Type']"
-41.Select Discout Type,click,,"//li[@aria-label='Discount in Amount ']"
-42.Enter Expiry Date,type,12122026,"//div[label[contains(., 'Expiry Date')]]//input"
-43.Enter Discount Amount, type, 100, "//input[@placeholder='Discount Amount']"
-44.Enter Minimum Order Amount, type, 1000, "//input[@placeholder='Min Order Amount']"
-45.Enter Maximum Discount Amount, type, 100, "//input[@placeholder='Max DiscountAmount']"
-46.Enter Coupon Limit, type, 5,"//div[label[contains(., 'Coupon Limit')]]//input"
-47.Enter Usage Limit for One User, type, 2,"//div[label[contains(., 'Usage Limit For One User')]]//input"
-48.Enter Promo Code Description, type, Promo Dode For Gold Member,"//textarea[@placeholder='PromoCode Description']"
-49.Click Submit ,click,,"//button[normalize-space()='Submit']"
-50.Verify Sucess, verify, , "//div[@aria-label='Info']"
-51.Filter PromoCode List,type,{deliveryPromoCodeName},"//input[@aria-label='promocode Filter Input']"
-52.wait,2000,,
-53.Click Settings ,click,,"//button[contains(., 'Settings')]"
-54.Click Service Settings ,click,,"//div[normalize-space()='Service Settings']"
-55.Enter Driver Serach Radius, type, 50, "//span[contains(text(), 'Driver search Radius')]/ancestor::app-input//input"
-56.Open Tax Type Dropdown,click,,"//span[@aria-label='Select Tax Type']"
-57.Select Amount,click,,"//li[@aria-label='Amount']"
-58.Enter Tax, type, 20, "//span[contains(text(), 'Tax')]/ancestor::app-input//input"
-59.Open Platform Fee Type Dropdown,click,,"//span[@aria-label='Seelct Type']"
-60.Select Amount,click,,"//li[@aria-label='Amount']"
-61.Enter Platform Fee, type, 20, "//span[contains(text(), 'Platform Fee')]/ancestor::app-input//input"
-62.Enter Cancel Charge (in %):, type, 20, "//span[contains(text(), 'Cancel Charge (in %):')]/ancestor::app-input//input"
-63.Enter Driver Accept Timeout (in Second):, type, 20, "//span[contains(text(), 'Driver Accept Timeout (in Second):')]/ancestor::app-input//input"
-64.Click Submit ,click,,"//button[normalize-space()='Submit']"
-65.Verify Sucess, verify, , "//div[@aria-label='Info']"
-66.Click  Stores,click,,"//button[contains(., 'Stores')]"
-67.Select Add Store,click,,"//div[contains(text(), 'Add Store')]"
-68.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Add Store')]"
-69.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "//input[@placeholder='Store Name']"
-70.Open Delivery Radius Dropdown,click,,"//span[@aria-label='select radius']"
-71.Select Twenty Five Kilometer,click,,"//li[@role='option'][contains(.,'25 KM')]"
-72.Open Estimated Delivery Time,click,,"//span[@aria-label='Estimated Delivery Time']"
-73. Select Thirty Minute,click,,"//li[@role='option'][contains(.,'30 MIN')]"
-74.Enter Order Minimum Amount, type, 300, "//input[@placeholder='Order Min Amount']"
-75.Enter Packaging Charges, type, 50, "//input[@placeholder='Packaging Charges']"
-76.Enter Short Description, type, amul taste of india, "//input[@placeholder="Type here"]"
-77.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "//input[@type='file']"
-78.Open Driver Notification,click,,"//span[@aria-label='select driver type']"
-79.Select Both Driver,click,,"//li[@role='option'][contains(.,'Both Driver')]"
-80.Click Checkbox Allow For Pickup , click, , "//label[contains(., "Do You Want ?")]/following-sibling::div//mat-checkbox"
-81.Open Current Status Dropdown,click,,"//span[@aria-label='Active']"
-82.Select Active,click,,"//li[@role='option'][contains(.,'Active')]"
-83..Enter Store Address, type, Amul chennai, "//input[@placeholder='Search location']"
-84.wait,1000,,
-85.Select First Option,arrow_down,,"//input[@placeholder='Search location']"
-86.Confirm Option,press_enter,,"//input[@placeholder='Search location']"
-87.wait,1000,,
-88.Click Storewise Comission Checkbox, click, , "//div[contains(text(),'Store Wise Commission')]/preceding-sibling::mat-checkbox"
-89.Enter Store Commision, type, 25, "//label[contains(.,'Commission (in %)')]/following-sibling::div//input"
-90.Open Driver Notification,click,,"//span[@aria-label='select offer type']"
-91.Select Amount,click,,"//li[@role='option'][contains(.,'Amount')]"
-92.Enter Offer Amount, type, 50, "//label[contains(.,'Offer Amount')]/following-sibling::div//input"
-93.Enter Offer Min Amount, type, 500, "//label[contains(.,'Offer Min Amount')]/following-sibling::div//input"
-94.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "//label[contains(.,'Contact Person Full Name')]/following-sibling::div//input"
-95.Enter Email, type, amul_{timestamp}@gmail.com&gt;&gt;storeEmail, "//label[contains(.,'Email Address')]/following-sibling::div//input"
-96.Enter Contact Number, type, {randomPhone}, "//label[contains(.,'Contact Number')]/following-sibling::div//input"
-97.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "(//input[@type='file'])[2]"
-98.Enter Bank Name, type, federal, "//label[contains(.,'Bank Name')]/following-sibling::div//input"
-99.Enter Bank Location,type, chennai, "//label[contains(.,'Bank Location(City Name)')]/following-sibling::div//input"
-100.Enter Account Number, type, 123456789012, "//label[contains(.,'Account Number')]/following-sibling::div//input"
-101.Enter Accont Holder Name, type, {milkStoreOwner}, "//label[contains(.,'Account Holder Name')]/following-sibling::div//input"
-102.Enter Payment Email Address, type, {storeEmail}, "//label[contains(.,'Payment Email Address')]/following-sibling::div//input"
-103.Enter BIC Code, type, 1234, "//label[contains(.,'BIC Code')]/following-sibling::div//input"
-104.Click Store Timing Checkbox, click, , "//div[contains(text(),'Every Day')]/preceding-sibling::mat-checkbox"
-105.Enter From Time, type, 100000AM, "((//input[@placeholder='--:--:-- --'])[1])"
-106.Enter To Time, type, 100000PM, "((//input[@placeholder='--:--:-- --'])[2])"
-107.Submit Add Store,click,,"//button[normalize-space()='Submit']"
-108. Verify Success Message,verify,,"//div[@aria-label='Info']"
-109.Click  Stores,click,,"//button[contains(., 'Stores')]"
-110.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-111.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-112.Filter Store List,type,{milkStore},"//input[@aria-label='Store Name Filter Input']"
-113.Click  Stores,click,,"//button[contains(., 'Stores')]"
-114.Select Pending Documents Stores List,click,,"//div[contains(text(), 'Pending Documents Stores')]"
-115.Verify Add Store,verify,,"//div[normalize-space()='Pending Documents Store']"
-116.Filter Pending Document Store List,type,{milkStore},"//input[@aria-label='Store Name Filter Input']"
-117.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-118.Click Doc Icon,click,,"//i[contains(@class, 'bi-file-earmark-medical-fill') and contains(@class, 'Navigate')]"
-119. Store Required Documents,verify,,"//div[contains(text(),'Documents')]"
-120.Add Address Proof,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-121.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "//input[@type='file']"
-122.Enter Expiry Date,type,2026-12-12,"//input[@placeholder='YYYY/MM/DD']"
-123.Click Submit, click, , "//button[normalize-space()='Submit']"
-124.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-125.Click Approve Store,click,,"//i[@class='bi bi-hand-thumbs-up-fill cursor-pointer gridIcon Modify']"
-126.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-127.Click Back, click, , "//button[@class='buttonWidget']"
-128.Click  Stores,click,,"//button[contains(., 'Stores')]"
-129.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-130.Verify Add Store,verify,,"//app-text[@class='ng-star-inserted']//div[contains(text(),'Store List')]"
-131.Filter Store List,type,{milkStore},"//input[@aria-label='Store Name Filter Input']"
-132.Scroll Grid, tab, 8, "//input[@aria-label='Store Name Filter Input']"
-133.Click Doc Icon,click,,"//i[contains(@class, 'bi-file-earmark-medical-fill') and contains(@class, 'Navigate')]"
-134.Click Back, click, , "//button[@class='buttonWidget']"
-135.Click Category, click, , "//button[normalize-space()='Category']"
-136.Click  Add New Category,click,,"//button[normalize-space()='Add Category']"
-137.Enter Category Name, type,curd{randomAlpha}&gt;&gt; MilkCategoryName, "//span[contains(text(), 'Category Name')]/ancestor::app-input//input"
-138.Enter Category Name Arabic, type, رائب, "//span[contains(text(), 'Language Value (in Arabic)')]/ancestor::app-input//input"
-139.Enter Category Name Tamil, type, தயிர், "//span[contains(text(), 'Language Value (in Tamil)')]/ancestor::app-input//input"
-140.Enter Category Name Hindi, type, दही, "//span[contains(text(), 'Language Value (in Hindi)')]/ancestor::app-input//input"
-141.Open Category status Dropdown,click,,"//span[@aria-label='status']"
-142.Select Active,click,,"//li[@aria-label='active']"
-143.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "//input[@type='file' and @accept='image/*']"
-144.wait,2000,,
-145.Enter Slug Name, type, curd, "//span[text()='Slug']/ancestor::app-input//input"
-146.Click  Submit,click,,"//button[normalize-space()='Submit']"
-147.Verify Success Message,verify,,"//div[@aria-label='Info']"
-148.Filter Category Name,type,{MilkCategoryName},"//input[@aria-label='Category Name Filter Input']"
-149.Click  Stores,click,,"//button[contains(., 'Stores')]"
-150.Select Store List,click,,"//div[contains(text(), 'Store List')]"
-151.Filter Store List,type,{milkStore},"//input[@aria-label='Store Name Filter Input']"
-152.Scroll Grid, tab, 9, "//input[@aria-label='Store Name Filter Input']"
-153.Click Product Icon,click,,"//i[@title='Product View']"
-154.Click  Add  Products,click,,"//button[normalize-space()='Add Products']"
-155.Open Product Category Dropdown,click,,"(//label[contains(text(),'Product Category')]/following-sibling::p-dropdown/div)[1]"
-156.Select curd,click,,"//li[@role='option'][contains(.,'{MilkCategoryName}')]"
-157.wait,1000,,
-158.Click badge,click,,"//i[@class='fa-solid fa-user-shield iconstyle']"
-159.Click Delivery Services,click,,"//h2[normalize-space()='Delivery Services']"
-160.Verify Delivery Services,verify,,"//div[normalize-space()='DELIVERY SERVICES']"
-161.Filter Services List,type,{deliveryName},"//input[@aria-label='Services Filter Input']"
-162.Click Edit Icon ,click,,"//i[@title='Edit']"
-163.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-164.wait,1000,,
-164.Select Dectivate,click,,"//li[@aria-label='Deactivate']"
-165.Click Submit ,click,,"//button[normalize-space()='Submit']"
-166.Filter Services List,type,{deliveryName},"//input[@aria-label='Services Filter Input']"
-167.wait,1000,,</t>
   </si>
   <si>
     <t xml:space="preserve">1.Click badge,click,,"//i[contains(@class, 'fa-hand-holding-usd fa-solid iconstyle')]"
@@ -2821,9 +2650,433 @@
 37.Filter admin name,type,{adminName},"admin.city_admin.input_name_filter"</t>
   </si>
   <si>
-    <t>1. Click badge,click,,"admin.store.badge.shield"
-2. Click Delivery Services,click,,"admin.store.delivery_services.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.store.delivery_services.header"
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Dependency: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The AddStore test suite must be always executed before this test. This is critical because the StoreOperations process utilizes the dynamic {storeName} variable generated and stored during the AddStore creation phase.
+RunSheet: AddStore2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Authentication State: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The user is already authenticated as a Super Admin and the session is active.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Navigation State:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The browser is currently on the Dashboard page. Ensure the dashboard.url is configured as https://dev.we1.co/#/page-module/dashboard_dynamic in the config.properties file.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Actual Test Steps</t>
+  </si>
+  <si>
+    <t>1.Click badge, click, , "admin.store.badge.shield"
+2.Click Delivery Services, click, , "admin.store.delivery_services.menu"
+3.Verify Delivery Services, verify, , "admin.store.delivery_services.header"
+4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
+5.Enter Category Name, type, milk Delivery{randomAlpha} &gt;&gt; deliveryName, "admin.deliveryservice.category_name.input"
+6.Enter Slug, type, Milk Delivery, "admin.deliveryservice.slug.input"
+7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "admin.deliveryservice.image.file"
+8.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+9.Select Activate, click, , "admin.deliveryservice.status.option_activate"
+10.Open Category Flow Dropdown, click, , "admin.deliveryservice.flow.dropdown"
+11.Select default flow(food-delivery), click, , "admin.deliveryservice.flow.option_food_delivery"
+12.Enter Delivery Name Tamil, type, பால்காரர், "admin.deliveryservice.lang_tamil.input"
+13.Enter Delivery Name Arabic, type, لبّان, "admin.deliveryservice.lang_arabic.input"
+14.Enter Delivery Name Hindi, type, दूधवाला, "admin.deliveryservice.lang_hindi.input"
+15.Click Submit, click, , "web.global.action.submit"
+16.Verify Success, verify, , "web.global.toast.info"
+17.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+18.Click Home Icon, click, , "admin.store.food_delivery.home_icon"
+19.Click Settings, click, , "admin.deliveryservice.menu.toggle_btn"
+20.Click Requirement Document, click, , "admin.deliveryservice.submenu.required_docs"
+21.Click Add Document, click, , "admin.deliveryservice.docs.add_btn"
+22.Enter Name, type, document{randomAlpha} &gt;&gt; deliveryDocumentName, "admin.deliveryservice.docs.name_input"
+23.Open status Dropdown, click, , "admin.deliveryservice.docs.status_dropdown"
+24.Select Active, click, , "admin.deliveryservice.docs.status_option_active"
+25.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+26.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+27.Click Mandatory Document, click, , "admin.deliveryservice.docs.mandatory_checkbox"
+28.Click Require Proof Number, click, , "admin.deliveryservice.docs.proof_number_checkbox"
+29.Enter Display Order, type, 10, "admin.deliveryservice.docs.display_order_input"
+30.Click Submit, click, , "web.global.action.submit"
+31.Verify Success, verify, , "web.global.toast.info"
+32.Filter Document List, type, {deliveryDocumentName}, "admin.deliveryservice.docs.grid.filter_input"
+33.wait, 2000, , ""
+34.Click Settings, click, , "admin.deliveryservice.menu.toggle_btn"
+35.Click Promocode, click, , "admin.deliveryservice.submenu.promocode"
+36.Click Add Promo Code, click, , "admin.deliveryservice.promo.add_btn"
+37.Open User List Dropdown, click, , "admin.deliveryservice.promo.user_list_dropdown"
+38.Select User, click, , "admin.deliveryservice.promo.user_option_dynamic"
+39.Click Code Name Box, click, , "admin.deliveryservice.promo.code_name_box"
+40.Enter Code Name, type, promoCode{randomAlpha} &gt;&gt; deliveryPromoCodeName, "admin.deliveryservice.promo.code_name_box"
+41.Open Discount Type Dropdown, click, , "admin.deliveryservice.promo.discount_type_dropdown"
+42.Select Discount Type, click, , "admin.deliveryservice.promo.discount_type_option_amount"
+43.Enter Expiry Date, type, 12122026, "admin.deliveryservice.promo.expiry_date_input"
+44.Enter Discount Amount, type, 100, "admin.deliveryservice.promo.discount_amount_input"
+45.Enter Minimum Order Amount, type, 1000, "admin.deliveryservice.promo.min_order_input"
+46.Enter Maximum Discount Amount, type, 100, "admin.deliveryservice.promo.max_discount_input"
+47.Enter Coupon Limit, type, 5, "admin.deliveryservice.promo.coupon_limit_input"
+48.Enter Usage Limit for One User, type, 2, "admin.deliveryservice.promo.user_usage_limit_input"
+49.Enter Promo Code Description, type, Promo Code For Gold Member, "admin.deliveryservice.promo.description_textarea"
+50.Click Submit, click, , "web.global.action.submit"
+51.Verify Success, verify, , "web.global.toast.info"
+52.Filter PromoCode List, type, {deliveryPromoCodeName}, "admin.deliveryservice.promo.grid.filter_input"
+53.wait, 2000, , ""
+54.Click Settings, click, , "admin.deliveryservice.menu.toggle_btn"
+55.Click Service Settings, click, , "admin.deliveryservice.submenu.service_settings"
+56.Enter Driver Search Radius, type, 50, "admin.deliveryservice.config.search_radius_input"
+57.Open Tax Type Dropdown, click, , "admin.deliveryservice.config.tax_type_dropdown"
+58.Select Amount, click, , "admin.deliveryservice.config.tax_type_option_amount"
+59.Enter Tax, type, 20, "admin.deliveryservice.config.tax_input"
+60.Open Platform Fee Type Dropdown, click, , "admin.deliveryservice.config.fee_type_dropdown"
+61.Select Amount, click, , "admin.deliveryservice.config.fee_type_option_amount"
+62.Enter Platform Fee, type, 20, "admin.deliveryservice.config.platform_fee_input"
+63.Enter Cancel Charge (in %):, type, 20, "admin.deliveryservice.config.cancel_charge_input"
+64.Enter Driver Accept Timeout (in Second):, type, 20, "admin.deliveryservice.config.driver_timeout_input"
+65.Click Submit, click, , "web.global.action.submit"
+66.Verify Success, verify, , "web.global.toast.info"
+67.Click Stores, click, , "admin.store.menu.toggle_btn"
+68.Select Add Store, click, , "admin.store.submenu.add_store"
+69.Verify Add Store, verify, , "admin.store.add_page.header"
+70.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "admin.store.name.input"
+71.Open Delivery Radius Dropdown, click, , "admin.store.radius.dropdown"
+72.Select Twenty Five Kilometer, click, , "admin.store.radius.option_25km"
+73.Open Estimated Delivery Time, click, , "admin.store.eta.dropdown"
+74.Select Thirty Minute, click, , "admin.store.eta.option_30min"
+75.Enter Order Minimum Amount, type, 300, "admin.store.min_amount.input"
+76.Enter Packaging Charges, type, 50, "admin.store.packaging_charge.input"
+77.Enter Short Description, type, amul taste of india, "admin.store.description.input"
+78.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "admin.store.banner.file"
+79.Open Driver Notification, click, , "admin.store.driver_notification.dropdown"
+80.Select Both Driver, click, , "admin.store.driver_notification.option_both"
+81.Click Checkbox Allow For Pickup, click, , "admin.store.allow_pickup.checkbox"
+82.Open Current Status Dropdown, click, , "admin.store.current_status.dropdown"
+83.Select Active, click, , "admin.store.current_status.option_active"
+84.Enter Store Address, type, Amul chennai, "admin.store.location.input"
+85.wait, 3000, , ""
+86.Confirm Store Address, press_enter, , "admin.store.location.input"
+87.wait, 3000, , ""
+88.Select First Option, arrow_down, , "admin.store.location.input"
+89.Confirm Option, press_enter, , "admin.store.location.input"
+90.wait, 2000, , ""
+91.Click Storewise Commission Checkbox, click, , "admin.store.commission.checkbox"
+92.Enter Store Commission, type, 25, "admin.store.commission_rate.input"
+93.Open Driver Notification, click, , "admin.store.offer_type.dropdown"
+94.Select Amount, click, , "admin.store.offer_type.option_amount"
+95.Enter Offer Amount, type, 50, "admin.store.offer_amount.input"
+96.Enter Offer Min Amount, type, 500, "admin.store.offer_min_amount.input"
+97.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "admin.store.contact_name.input"
+98.Enter Email, type, amul_{timestamp}@gmail.com &gt;&gt; storeEmail, "admin.store.email.input"
+99.Enter Contact Number, type, {randomPhone}, "admin.store.phone.input"
+100.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "admin.store.profile.file"
+101.Enter Bank Name, type, federal, "admin.store.bank.name_input"
+102.Enter Bank Location, type, chennai, "admin.store.bank.location_input"
+103.Enter Account Number, type, 123456789012, "admin.store.bank.account_input"
+104.Enter Account Holder Name, type, {milkStoreOwner}, "admin.store.bank.holder_input"
+105.Enter Payment Email Address, type, {storeEmail}, "admin.store.bank.payment_email"
+106.Enter BIC Code, type, 1234, "admin.store.bank.bic_input"
+107.Click Store Timing Checkbox, click, , "admin.store.timing.everyday_checkbox"
+108.Enter From Time, type, 100000AM, "admin.store.timing.from_input"
+109.Enter To Time, type, 100000PM, "admin.store.timing.to_input"
+110.Submit Add Store, click, , "web.global.action.submit"
+111.Verify Success Message, verify, , "web.global.toast.info"
+112.Click Stores, click, , "admin.store.menu.toggle_btn"
+113.Select Store List, click, , "admin.store.submenu.store_list"
+114.Verify Add Store, verify, , "admin.store.list_page.header"
+115.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+116.Click Stores, click, , "admin.store.menu.toggle_btn"
+117.Select Pending Documents Stores List, click, , "admin.store.submenu.pending_docs"
+118.Verify Add Store, verify, , "admin.store.pending_page.header"
+119.Filter Pending Document Store List, type, {milkStore}, "admin.store.grid.name_filter"
+120.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+121.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+122.Store Required Documents, verify, , "admin.store.documents_page.header"
+123.Add Address Proof, click, , "admin.store.grid.edit_doc_icon"
+124.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.store.doc.file_input"
+125.Enter Expiry Date, type, 2026-12-12, "admin.store.doc.expiry_input"
+126.Click Submit, click, , "web.global.action.submit"
+127.Verify Updated Successfully, verify, , "web.global.toast.updated"
+128.Click Approve Store, click, , "admin.store.grid.approve_doc_icon"
+129.Verify Updated Successfully, verify, , "web.global.toast.updated"
+130.Click Back, click, , "admin.store.grid.back_btn"
+131.Click Stores, click, , "admin.store.menu.toggle_btn"
+132.Select Store List, click, , "admin.store.submenu.store_list"
+133.Verify Add Store, verify, , "admin.store.list_page.header"
+134.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+135.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+136.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+137.Click Back, click, , "admin.store.grid.back_btn"
+138.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
+139.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
+140.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
+141.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
+142.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
+143.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
+144.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
+145.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
+146.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
+147.wait, 2000, , ""
+148.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
+149.Click Submit, click, , "web.global.action.submit"
+150.Verify Success Message, verify, , "web.global.toast.info"
+151.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
+152.Click Stores, click, , "admin.store.menu.toggle_btn"
+153.Select Store List, click, , "admin.store.submenu.store_list"
+154.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+155.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
+156.Click Product Icon, click, , "admin.store.products.grid_icon"
+157.Click Add Products, click, , "admin.store.products.add_btn"
+158.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
+159.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
+160.wait, 1000, , ""
+161.Click badge, click, , "admin.store.badge.shield"
+162.Click Delivery Services, click, , "admin.store.delivery_services.menu"
+163.Verify Delivery Services, verify, , "admin.store.delivery_services.header"
+164.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+165.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
+166.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+167.wait, 1000, , ""
+168.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
+169.Click Submit, click, , "web.global.action.submit"
+170.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+171.wait, 1000, , ""</t>
+  </si>
+  <si>
+    <t>Deleted Steps</t>
+  </si>
+  <si>
+    <t>34.Click Settings, click, , "admin.deliveryservice.menu.toggle_btn"
+35.Click Promocode, click, , "admin.deliveryservice.submenu.promocode"
+36.Click Add Promo Code, click, , "admin.deliveryservice.promo.add_btn"
+37.Open User List Dropdown, click, , "admin.deliveryservice.promo.user_list_dropdown"
+38.Select User, click, , "admin.deliveryservice.promo.user_option_dynamic"
+39.Click Code Name Box, click, , "admin.deliveryservice.promo.code_name_box"
+40.Enter Code Name, type, promoCode{randomAlpha} &gt;&gt; deliveryPromoCodeName, "admin.deliveryservice.promo.code_name_box"
+41.Open Discount Type Dropdown, click, , "admin.deliveryservice.promo.discount_type_dropdown"
+42.Select Discount Type, click, , "admin.deliveryservice.promo.discount_type_option_amount"
+43.Enter Expiry Date, type, 12122026, "admin.deliveryservice.promo.expiry_date_input"
+44.Enter Discount Amount, type, 100, "admin.deliveryservice.promo.discount_amount_input"
+45.Enter Minimum Order Amount, type, 1000, "admin.deliveryservice.promo.min_order_input"
+46.Enter Maximum Discount Amount, type, 100, "admin.deliveryservice.promo.max_discount_input"
+47.Enter Coupon Limit, type, 5, "admin.deliveryservice.promo.coupon_limit_input"
+48.Enter Usage Limit for One User, type, 2, "admin.deliveryservice.promo.user_usage_limit_input"
+49.Enter Promo Code Description, type, Promo Code For Gold Member, "admin.deliveryservice.promo.description_textarea"
+50.Click Submit, click, , "web.global.action.submit"
+51.Verify Success, verify, , "web.global.toast.info"
+52.Filter PromoCode List, type, {deliveryPromoCodeName}, "admin.deliveryservice.promo.grid.filter_input"
+53.wait, 2000, , ""</t>
+  </si>
+  <si>
+    <t>1.Click badge, click, , "admin.deliveryservice.badge.shield"
+2.Click Delivery Services, click, , "admin.deliveryservice.menu"
+3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
+5.Enter Category Name, type, milk Delivery{randomAlpha} &gt;&gt; deliveryName, "admin.deliveryservice.category_name.input"
+6.Enter Slug, type, Milk Delivery, "admin.deliveryservice.slug.input"
+7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "admin.deliveryservice.image.file"
+8.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+9.Select Activate, click, , "admin.deliveryservice.status.option_activate"
+10.Open Category Flow Dropdown, click, , "admin.deliveryservice.flow.dropdown"
+11.Select default flow(food-delivery), click, , "admin.deliveryservice.flow.option_food_delivery"
+12.Enter Delivery Name Tamil, type, பால்காரர், "admin.deliveryservice.lang_tamil.input"
+13.Enter Delivery Name Arabic, type, لبّان, "admin.deliveryservice.lang_arabic.input"
+14.Enter Delivery Name Hindi, type, दूधवाला, "admin.deliveryservice.lang_hindi.input"
+15.Click Submit, click, , "web.global.action.submit"
+16.Verify Success, verify, , "web.global.toast.info"
+17.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+18.Click Home Icon, click, , "admin.deliveryservice.home.icon"
+19.Click Settings, click, , "admin.deliveryservice.settings.menu"
+20.Click Requirement Document, click, , "admin.deliveryservice.required_docs"
+21.Click Add Document, click, , "admin.deliveryservice.docs.add_btn"
+22.Enter Name, type, document{randomAlpha} &gt;&gt; deliveryDocumentName, "admin.deliveryservice.docs.name_input"
+23.Open status Dropdown, click, , "admin.deliveryservice.docs.status_dropdown"
+24.Select Active, click, , "admin.deliveryservice.docs.status_option_active"
+25.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+26.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+27.Click Mandatory Document, click, , "admin.deliveryservice.docs.mandatory_checkbox"
+28.Click Require Proof Number, click, , "admin.deliveryservice.docs.proof_number_checkbox"
+29.Enter Display Order, type, 10, "admin.deliveryservice.docs.display_order_input"
+30.Click Submit, click, , "web.global.action.submit"
+31.Verify Success, verify, , "web.global.toast.info"
+32.Filter Document List, type, {deliveryDocumentName}, "admin.deliveryservice.docs.grid.filter_input"
+33.wait, 2000, , ""
+34.Click Settings, click, , "admin.deliveryservice.settings.menu"
+35.Click Service Settings, click, , "admin.deliveryservice.submenu.service_settings"
+36.Enter Driver Search Radius, type, 50, "admin.deliveryservice.config.search_radius_input"
+37.Open Tax Type Dropdown, click, , "admin.deliveryservice.config.tax_type_dropdown"
+38.Select Amount, click, , "admin.deliveryservice.config.tax_type_option_amount"
+39.Enter Tax, type, 20, "admin.deliveryservice.config.tax_input"
+40.Open Platform Fee Type Dropdown, click, , "admin.deliveryservice.config.fee_type_dropdown"
+41.Select Amount, click, , "admin.deliveryservice.config.fee_type_option_amount"
+42.Enter Platform Fee, type, 20, "admin.deliveryservice.config.platform_fee_input"
+43.Enter Cancel Charge (in %):, type, 20, "admin.deliveryservice.config.cancel_charge_input"
+44.Enter Driver Accept Timeout (in Second):, type, 20, "admin.deliveryservice.config.driver_timeout_input"
+45.Click Submit, click, , "web.global.action.submit"
+46.Verify Success, verify, , "web.global.toast.info"
+47.Click Stores, click, , "admin.store.menu.toggle_btn"
+48.Select Add Store, click, , "admin.store.submenu.add_store"
+49.Verify Add Store, verify, , "admin.store.add_page.header"
+50.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "admin.store.name.input"
+51.Open Delivery Radius Dropdown, click, , "admin.store.radius.dropdown"
+52.Select Twenty Five Kilometer, click, , "admin.store.radius.option_25km"
+53.Open Estimated Delivery Time, click, , "admin.store.eta.dropdown"
+54.Select Thirty Minute, click, , "admin.store.eta.option_30min"
+55.Enter Order Minimum Amount, type, 300, "admin.store.min_amount.input"
+56.Enter Packaging Charges, type, 50, "admin.store.packaging_charge.input"
+57.Enter Short Description, type, amul taste of india, "admin.store.description.input"
+58.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "admin.store.banner.file"
+59.Open Driver Notification, click, , "admin.store.driver_notification.dropdown"
+60.Select Both Driver, click, , "admin.store.driver_notification.option_both"
+61.Click Checkbox Allow For Pickup, click, , "admin.store.allow_pickup.checkbox"
+62.Open Current Status Dropdown, click, , "admin.store.current_status.dropdown"
+63.Select Active, click, , "admin.store.current_status.option_active"
+64.Enter Store Address, type, Amul chennai, "admin.store.location.input"
+65.wait, 3000, , ""
+66.Confirm Store Address, press_enter, , "admin.store.location.input"
+67.wait, 3000, , ""
+68.Select First Option, arrow_down, , "admin.store.location.input"
+69.Confirm Option, press_enter, , "admin.store.location.input"
+70.wait, 2000, , ""
+71.Click Storewise Commission Checkbox, click, , "admin.store.commission.checkbox"
+72.Enter Store Commission, type, 25, "admin.store.commission_rate.input"
+73.Open Driver Notification, click, , "admin.store.offer_type.dropdown"
+74.Select Amount, click, , "admin.store.offer_type.option_amount"
+75.Enter Offer Amount, type, 50, "admin.store.offer_amount.input"
+76.Enter Offer Min Amount, type, 500, "admin.store.offer_min_amount.input"
+77.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "admin.store.contact_name.input"
+78.Enter Email, type, amul_{timestamp}@gmail.com &gt;&gt; storeEmail, "admin.store.email.input"
+79.Enter Contact Number, type, {randomPhone}, "admin.store.phone.input"
+80.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "admin.store.profile.file"
+81.Enter Bank Name, type, federal, "admin.store.bank.name_input"
+82.Enter Bank Location, type, chennai, "admin.store.bank.location_input"
+83.Enter Account Number, type, 123456789012, "admin.store.bank.account_input"
+84.Enter Account Holder Name, type, {milkStoreOwner}, "admin.store.bank.holder_input"
+85.Enter Payment Email Address, type, {storeEmail}, "admin.store.bank.payment_email"
+86.Enter BIC Code, type, 1234, "admin.store.bank.bic_input"
+87.Click Store Timing Checkbox, click, , "admin.store.timing.everyday_checkbox"
+88.Enter From Time, type, 100000AM, "admin.store.timing.from_input"
+89.Enter To Time, type, 100000PM, "admin.store.timing.to_input"
+90.Submit Add Store, click, , "web.global.action.submit"
+91.Verify Success Message, verify, , "web.global.toast.info"
+92.Click Stores, click, , "admin.store.menu.toggle_btn"
+93.Select Store List, click, , "admin.store.submenu.store_list"
+94.Verify Add Store, verify, , "admin.store.list_page.header"
+95.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+96.Click Stores, click, , "admin.store.menu.toggle_btn"
+97.Select Pending Documents Stores List, click, , "admin.store.submenu.pending_docs"
+98.Verify Add Store, verify, , "admin.store.pending_page.header"
+99.Filter Pending Document Store List, type, {milkStore}, "admin.store.grid.name_filter"
+100.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+101.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+102.Store Required Documents, verify, , "admin.store.documents_page.header"
+103.Add Address Proof, click, , "admin.store.grid.edit_doc_icon"
+104.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.store.doc.file_input"
+105.Enter Expiry Date, type, 2026-12-12, "admin.store.doc.expiry_input"
+106.Click Submit, click, , "web.global.action.submit"
+107.Verify Updated Successfully, verify, , "web.global.toast.updated"
+108.Click Approve Store, click, , "admin.store.grid.approve_doc_icon"
+109.Verify Updated Successfully, verify, , "web.global.toast.updated"
+110.Click Back, click, , "admin.store.grid.back_btn"
+111.Click Stores, click, , "admin.store.menu.toggle_btn"
+112.Select Store List, click, , "admin.store.submenu.store_list"
+113.Verify Add Store, verify, , "admin.store.list_page.header"
+114.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+115.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+116.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+117.Click Back, click, , "admin.store.grid.back_btn"
+118.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
+119.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
+120.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
+121.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
+122.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
+123.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
+124.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
+125.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
+126.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
+127.wait, 2000, , ""
+128.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
+129.Click Submit, click, , "web.global.action.submit"
+130.Verify Success Message, verify, , "web.global.toast.info"
+131.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
+132.Click Stores, click, , "admin.store.menu.toggle_btn"
+133.Select Store List, click, , "admin.store.submenu.store_list"
+134.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+135.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
+136.Click Product Icon, click, , "admin.store.products.grid_icon"
+137.Click Add Products, click, , "admin.store.products.add_btn"
+138.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
+139.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
+140.wait, 1000, ,""
+141.Click badge, click, , "admin.deliveryservice.badge.shield"
+142.Click Delivery Services, click, , "admin.deliveryservice.menu"
+143.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+144.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+145.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
+146.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+147.wait, 1000, , ""
+148.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
+149.Click Submit, click, , "web.global.action.submit"
+150.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+151.wait, 1000, ,</t>
+  </si>
+  <si>
+    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
 5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
 6. Click Stores,click,,"admin.store.menu.toggle_btn"
@@ -2900,79 +3153,9 @@
 77. wait,1000,,</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Data Dependency: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The AddStore test suite must be always executed before this test. This is critical because the StoreOperations process utilizes the dynamic {storeName} variable generated and stored during the AddStore creation phase.
-RunSheet: AddStore2
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Authentication State: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The user is already authenticated as a Super Admin and the session is active.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Navigation State:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The browser is currently on the Dashboard page. Ensure the dashboard.url is configured as https://dev.we1.co/#/page-module/dashboard_dynamic in the config.properties file.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>1. Click badge,click,,"admin.store.badge.shield"
-2. Click Delivery Services,click,,"admin.store.delivery_services.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.store.delivery_services.header"
+    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
 5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
 6. Click Stores,click,,"admin.store.menu.toggle_btn"
@@ -3037,9 +3220,9 @@
 65. wait,1000,,</t>
   </si>
   <si>
-    <t>1. Click badge,click,,"admin.store.badge.shield"
-2. Click Delivery Services,click,,"admin.store.delivery_services.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.store.delivery_services.header"
+    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
 5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
 6. Click Stores,click,,"admin.store.menu.toggle_btn"
@@ -3559,7 +3742,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -3628,13 +3811,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -3700,16 +3883,16 @@
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3772,13 +3955,13 @@
         <v>32</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -3797,7 +3980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73960651-1493-478A-BEDA-A31CF297E315}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3807,7 +3990,8 @@
     <col min="4" max="4" width="34.109375" customWidth="1"/>
     <col min="5" max="5" width="69.33203125" customWidth="1"/>
     <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="44.33203125" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -3830,10 +4014,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
@@ -3844,16 +4028,22 @@
         <v>54</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3916,7 +4106,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
@@ -3988,7 +4178,7 @@
         <v>40</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>56</v>
@@ -4060,13 +4250,13 @@
         <v>69</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
@@ -4126,19 +4316,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>67</v>
@@ -4193,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4213,13 +4403,13 @@
         <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4292,7 +4482,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
@@ -4347,7 +4537,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4367,13 +4557,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4415,7 +4605,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4429,19 +4619,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4490,7 +4680,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4504,19 +4694,19 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4565,7 +4755,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4579,19 +4769,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4640,7 +4830,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4654,19 +4844,19 @@
         <v>60</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4724,22 +4914,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BF513C-6185-45BE-8062-0F8880287EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC13A97E-358D-43E7-AB26-196297D4DAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2921,6 +2921,251 @@
 53.wait, 2000, , ""</t>
   </si>
   <si>
+    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
+37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Store Required Documents,verify,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Verify Add Store,verify,,"admin.store.list_page.header"
+73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+77. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Store List,click,,"admin.store.submenu.store_list"
+8. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+9. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+10. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+11. Click Product Icon,click,,"admin.store.products.grid_icon"
+12. Click Add Products,click,,"admin.store.products.add_btn"
+13. Open Product Category Dropdown,click,,"admin.store.products.category_dropdown"
+14. Select Grill Chicken,click,,"admin.store.products.category_option_grill"
+15. Enter Product Name,type,kfcProduct{randomAlpha}&gt;&gt; kfcProductName,"admin.store.products.name_input"
+16. Enter Product Amount,type,500,"admin.store.products.amount_input"
+17. Enter Product Description,type,KFC special grill chicken,"admin.store.products.description_textarea"
+18. Upload Product Image,uploadfile,"src/main/resources/test-data/grillchicken.jpg","admin.store.products.image.file"
+19. Open Product Category Dropdown,click,,"admin.store.products.status_dropdown"
+20. Select Activate,click,,"admin.store.products.status_option_active"
+21. Open Discount Type Dropdown,click,,"admin.store.products.discount_dropdown"
+22. Enter Discount Amount,type,50,"admin.store.products.discount_input"
+23. Click Save,click,,"admin.store.products.save_btn"
+24. Wait For Saved Succesfully,wait_until_visible,,"admin.store.products.toast_success"
+25. Wait For Store Products,wait_until_visible,,"admin.store.products.header"
+26. Filter Product List,type,{kfcProductName},"admin.store.products.name_filter"
+27. Click Back,click,,"admin.store.products.back_btn"
+28. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+29. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+30. Click Wallet Icon,click,,"admin.store.wallet.grid_icon"
+31. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
+32. Enter Wallet Amount,type,1000,"admin.store.wallet.amount_input"
+33. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
+34. Select Add Money,click,,"admin.store.wallet.option_add"
+35. Click Submit,click,,"web.global.action.submit"
+36. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
+37. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
+38. Enter Wallet Amount,type,200,"admin.store.wallet.amount_input"
+39. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
+40. Select Deduct Money,click,,"admin.store.wallet.option_deduct"
+41. Click Submit,click,,"web.global.action.submit"
+42. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
+43. Click Back,click,,"admin.store.products.back_btn"
+44. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+45. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+46. Click Drivers Icon,click,,"admin.store.drivers.grid_icon"
+47. Click Add Private Driver,click,,"admin.store.drivers.add_private_btn"
+48. Enter Driver Name,type,kfcdriver_{timestamp} &gt;&gt; kfcdriverName,"admin.drivers.fullname.input"
+49. Enter Email,type,kfcdriver_{timestamp}@gmail.com,"admin.drivers.email.input"
+50. Enter Contact Number,type,{randomPhone},"admin.drivers.phone.input"
+51. Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg","admin.drivers.profile_image.file"
+52. Select Male Gender,click,,"admin.drivers.male_gender.div"
+53. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+54. Select Scooter Option,click,,"admin.drivers.vehicle_option.scooter"
+55. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+56. Enter Vehicle Company,type,kfcBikeCompany{randomAlpha}&gt;&gt; kfcBikeCompanyName,"admin.drivers.companyname.input"
+57. Enter Plate No,type,KL-01-AB-1634,"admin.drivers.plateno.input"
+58. Enter Model Name,type,activa,"admin.drivers.modelname.input"
+59. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg","admin.drivers.vehicle_image.file"
+60. Enter Vehicle Color,type,white,"admin.drivers.vehicle_color.input"
+61. Click Submit,click,,"web.global.action.submit"
+62. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+63. Filter Driver List,type,{kfcdriverName},"admin.drivers.name_filter.input"
+64. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+65. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
+37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Block Icon,click,,"admin.store.grid.block_icon"
+76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Stores,click,,"admin.store.menu.toggle_btn"
+78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
+79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
+82. Click Stores,click,,"admin.store.menu.toggle_btn"
+83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
+84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
+86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
+87. Click Stores,click,,"admin.store.menu.toggle_btn"
+88. Select Store List,click,,"admin.store.submenu.store_list"
+89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+90. wait,3000,,
+91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+92. Click Doc Icon,click,,"admin.store.grid.document_icon"
+93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
+94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+97. wait,1000,,</t>
+  </si>
+  <si>
     <t>1.Click badge, click, , "admin.deliveryservice.badge.shield"
 2.Click Delivery Services, click, , "admin.deliveryservice.menu"
 3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
@@ -3037,286 +3282,42 @@
 114.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
 115.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
 116.Click Doc Icon, click, , "admin.store.grid.doc_icon"
-117.Click Back, click, , "admin.store.grid.back_btn"
-118.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
-119.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
-120.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
-121.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
-122.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
-123.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
-124.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
-125.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
-126.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
-127.wait, 2000, , ""
-128.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
-129.Click Submit, click, , "web.global.action.submit"
-130.Verify Success Message, verify, , "web.global.toast.info"
-131.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
-132.Click Stores, click, , "admin.store.menu.toggle_btn"
-133.Select Store List, click, , "admin.store.submenu.store_list"
-134.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-135.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
-136.Click Product Icon, click, , "admin.store.products.grid_icon"
-137.Click Add Products, click, , "admin.store.products.add_btn"
-138.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
-139.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
-140.wait, 1000, ,""
-141.Click badge, click, , "admin.deliveryservice.badge.shield"
-142.Click Delivery Services, click, , "admin.deliveryservice.menu"
-143.Verify Delivery Services, verify, , "admin.deliveryservice.header"
-144.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-145.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
-146.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
-147.wait, 1000, , ""
-148.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
-149.Click Submit, click, , "web.global.action.submit"
-150.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-151.wait, 1000, ,</t>
-  </si>
-  <si>
-    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Add Store,click,,"admin.store.submenu.add_store"
-8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
-9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
-10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
-11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
-12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
-13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
-14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
-15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
-16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
-17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
-18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
-19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
-20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
-21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
-22. Select Active,click,,"admin.store.current_status.option_active"
-23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
-24. wait,3000,,
-25. Confirm Store Address,press_enter,,"admin.store.location.input"
-26. wait,3000,,
-27. Select First Option,arrow_down,,"admin.store.location.input"
-28. Confirm Option,press_enter,,"admin.store.location.input"
-29. wait,2000,,
-30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
-31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
-32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
-33. Select Amount,click,,"admin.store.offer_type.option_amount"
-34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
-35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
-36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
-37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
-38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
-39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
-40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
-41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
-42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
-43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
-44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
-45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
-46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
-47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
-48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
-49. Submit Add Store,click,,"web.global.action.submit"
-50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-51. Click Stores,click,,"admin.store.menu.toggle_btn"
-52. Select Store List,click,,"admin.store.submenu.store_list"
-53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-55. Click Stores,click,,"admin.store.menu.toggle_btn"
-56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
-57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
-58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
-59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-61. Store Required Documents,verify,,"admin.store.documents_page.header"
-62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
-63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
-64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
-65. Click Submit,click,,"web.global.action.submit"
-66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
-68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-69. Click Back,click,,"admin.store.grid.back_btn"
-70. Click Stores,click,,"admin.store.menu.toggle_btn"
-71. Select Store List,click,,"admin.store.submenu.store_list"
-72. Verify Add Store,verify,,"admin.store.list_page.header"
-73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
-77. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Store List,click,,"admin.store.submenu.store_list"
-8. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-9. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-10. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-11. Click Product Icon,click,,"admin.store.products.grid_icon"
-12. Click Add Products,click,,"admin.store.products.add_btn"
-13. Open Product Category Dropdown,click,,"admin.store.products.category_dropdown"
-14. Select Grill Chicken,click,,"admin.store.products.category_option_grill"
-15. Enter Product Name,type,kfcProduct{randomAlpha}&gt;&gt; kfcProductName,"admin.store.products.name_input"
-16. Enter Product Amount,type,500,"admin.store.products.amount_input"
-17. Enter Product Description,type,KFC special grill chicken,"admin.store.products.description_textarea"
-18. Upload Product Image,uploadfile,"src/main/resources/test-data/grillchicken.jpg","admin.store.products.image.file"
-19. Open Product Category Dropdown,click,,"admin.store.products.status_dropdown"
-20. Select Activate,click,,"admin.store.products.status_option_active"
-21. Open Discount Type Dropdown,click,,"admin.store.products.discount_dropdown"
-22. Enter Discount Amount,type,50,"admin.store.products.discount_input"
-23. Click Save,click,,"admin.store.products.save_btn"
-24. Wait For Saved Succesfully,wait_until_visible,,"admin.store.products.toast_success"
-25. Wait For Store Products,wait_until_visible,,"admin.store.products.header"
-26. Filter Product List,type,{kfcProductName},"admin.store.products.name_filter"
-27. Click Back,click,,"admin.store.products.back_btn"
-28. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-29. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-30. Click Wallet Icon,click,,"admin.store.wallet.grid_icon"
-31. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
-32. Enter Wallet Amount,type,1000,"admin.store.wallet.amount_input"
-33. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
-34. Select Add Money,click,,"admin.store.wallet.option_add"
-35. Click Submit,click,,"web.global.action.submit"
-36. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
-37. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
-38. Enter Wallet Amount,type,200,"admin.store.wallet.amount_input"
-39. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
-40. Select Deduct Money,click,,"admin.store.wallet.option_deduct"
-41. Click Submit,click,,"web.global.action.submit"
-42. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
-43. Click Back,click,,"admin.store.products.back_btn"
-44. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-45. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-46. Click Drivers Icon,click,,"admin.store.drivers.grid_icon"
-47. Click Add Private Driver,click,,"admin.store.drivers.add_private_btn"
-48. Enter Driver Name,type,kfcdriver_{timestamp} &gt;&gt; kfcdriverName,"admin.drivers.fullname.input"
-49. Enter Email,type,kfcdriver_{timestamp}@gmail.com,"admin.drivers.email.input"
-50. Enter Contact Number,type,{randomPhone},"admin.drivers.phone.input"
-51. Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg","admin.drivers.profile_image.file"
-52. Select Male Gender,click,,"admin.drivers.male_gender.div"
-53. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
-54. Select Scooter Option,click,,"admin.drivers.vehicle_option.scooter"
-55. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
-56. Enter Vehicle Company,type,kfcBikeCompany{randomAlpha}&gt;&gt; kfcBikeCompanyName,"admin.drivers.companyname.input"
-57. Enter Plate No,type,KL-01-AB-1634,"admin.drivers.plateno.input"
-58. Enter Model Name,type,activa,"admin.drivers.modelname.input"
-59. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg","admin.drivers.vehicle_image.file"
-60. Enter Vehicle Color,type,white,"admin.drivers.vehicle_color.input"
-61. Click Submit,click,,"web.global.action.submit"
-62. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
-63. Filter Driver List,type,{kfcdriverName},"admin.drivers.name_filter.input"
-64. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
-65. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Add Store,click,,"admin.store.submenu.add_store"
-8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
-9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
-10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
-11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
-12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
-13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
-14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
-15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
-16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
-17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
-18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
-19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
-20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
-21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
-22. Select Active,click,,"admin.store.current_status.option_active"
-23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
-24. wait,3000,,
-25. Confirm Store Address,press_enter,,"admin.store.location.input"
-26. wait,3000,,
-27. Select First Option,arrow_down,,"admin.store.location.input"
-28. Confirm Option,press_enter,,"admin.store.location.input"
-29. wait,2000,,
-30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
-31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
-32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
-33. Select Amount,click,,"admin.store.offer_type.option_amount"
-34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
-35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
-36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
-37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
-38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
-39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
-40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
-41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
-42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
-43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
-44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
-45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
-46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
-47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
-48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
-49. Submit Add Store,click,,"web.global.action.submit"
-50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-51. Click Stores,click,,"admin.store.menu.toggle_btn"
-52. Select Store List,click,,"admin.store.submenu.store_list"
-53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-55. Click Stores,click,,"admin.store.menu.toggle_btn"
-56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
-57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
-58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
-59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
-62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
-63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
-64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
-65. Click Submit,click,,"web.global.action.submit"
-66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
-68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-69. Click Back,click,,"admin.store.grid.back_btn"
-70. Click Stores,click,,"admin.store.menu.toggle_btn"
-71. Select Store List,click,,"admin.store.submenu.store_list"
-72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-75. Click Block Icon,click,,"admin.store.grid.block_icon"
-76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
-77. Click Stores,click,,"admin.store.menu.toggle_btn"
-78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
-79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
-82. Click Stores,click,,"admin.store.menu.toggle_btn"
-83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
-84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
-86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
-87. Click Stores,click,,"admin.store.menu.toggle_btn"
-88. Select Store List,click,,"admin.store.submenu.store_list"
-89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-90. wait,3000,,
-91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-92. Click Doc Icon,click,,"admin.store.grid.document_icon"
-93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
-94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
-96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-97. wait,1000,,</t>
+117.wait for back button,wait,3000,
+118.Click Back, click, , "admin.store.grid.back_btn"
+119.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
+120.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
+121.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
+122.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
+123.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
+124.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
+125.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
+126.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
+127.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
+128.wait, 2000, , ""
+129.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
+130.Click Submit, click, , "web.global.action.submit"
+131.Verify Success Message, verify, , "web.global.toast.info"
+132.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
+133.Click Stores, click, , "admin.store.menu.toggle_btn"
+134.Select Store List, click, , "admin.store.submenu.store_list"
+135.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+136.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
+137.Click Product Icon, click, , "admin.store.products.grid_icon"
+138.Click Add Products, click, , "admin.store.products.add_btn"
+139.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
+140.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
+141.wait, 1000, ,""
+142.Click badge, click, , "admin.deliveryservice.badge.shield"
+143.Click Delivery Services, click, , "admin.deliveryservice.menu"
+144.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+145.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+146.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
+147.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+148.wait, 1000, , ""
+149.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
+150.Click Submit, click, , "web.global.action.submit"
+151.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+152.wait, 1000, ,</t>
   </si>
 </sst>
 </file>
@@ -3817,7 +3818,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -3889,7 +3890,7 @@
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>111</v>
@@ -3961,7 +3962,7 @@
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -4034,7 +4035,7 @@
         <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2782A3-6539-4CC8-BB61-AFA4B194CB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932F4E60-82DC-4110-89C7-7715EDEB7920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -29,7 +29,8 @@
     <sheet name="AddProvider" sheetId="45" r:id="rId14"/>
     <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId15"/>
     <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId16"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId17"/>
+    <sheet name="PanicCallTest" sheetId="49" r:id="rId17"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="125">
   <si>
     <t>City Area</t>
   </si>
@@ -3317,6 +3318,38 @@
 141.Click provider Services,click,,"admin.provider_service.menu_link"
 142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
 143.wait,1000,,</t>
+  </si>
+  <si>
+    <t>TC_CA_16_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>Verify the complete lifecycle of a panic call configuration—including creation with multilingual names (English, Tamil, Hindi), searching, updating its status to inactive, and successful deletion.</t>
+  </si>
+  <si>
+    <t>Panic Call Test</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
+2.Click Setting,click,,"admin.setting.sidebar.menu"
+3.Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
+4.Click Add panic call button,click,,"admin.setting.panic_call.add_btn"
+5.Enter name,type,police_{randomAlpha}&gt;&gt;policeName,"admin.setting.panic_call.name_input"
+6.Enter name in tamil,type,காவல்துறை,"admin.setting.panic_call.tamil_name_input"
+7.Enter name in hindi,type,पुलिस,"admin.setting.panic_call.hindi_name_input"
+8.Contact number,type,{randomPhone},"admin.setting.panic_call.contact_number"
+9.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
+10.Select Active status,click,,"admin.setting.panic_call.activate_status_dropdown"
+11.Submit button,click,,"web.global.action.submit"
+12.Search name,type,{policeName},"admin.setting.panic_call.search_name"
+13.Click Edit Button,click,,"admin.setting.panic_call.edit_btn"
+14.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
+15.Select Deactive status button,click,,"admin.setting.panic_call.deactivate_status_dropdown"
+16.Click Submit button,click,,"web.global.action.submit"
+17.Click Delete button,click,,"admin.setting.panic_call.delete_btn"
+18.Click Yes delete it button,click,,"admin.setting.panic_call.confirm_delete_btn"</t>
+  </si>
+  <si>
+    <t>SA_TS_17</t>
   </si>
 </sst>
 </file>
@@ -4275,6 +4308,78 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4316,7 +4421,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>64</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9C63FF-BF89-4D41-8468-98271F6D31C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CD8D22-D938-471C-9746-0A3DAF50DB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -22,18 +22,18 @@
     <sheet name="AddTaxiDriver" sheetId="35" r:id="rId7"/>
     <sheet name="TransportServiceCompleteTest" sheetId="37" r:id="rId8"/>
     <sheet name="AddTransportCityAdmin" sheetId="39" r:id="rId9"/>
-    <sheet name="AddStore" sheetId="40" r:id="rId10"/>
-    <sheet name="StoreOperations" sheetId="42" r:id="rId11"/>
-    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId12"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId13"/>
-    <sheet name="AddProvider" sheetId="45" r:id="rId14"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId15"/>
-    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId16"/>
-    <sheet name="PanicCallTest" sheetId="49" r:id="rId17"/>
-    <sheet name="DashboardTest" sheetId="50" r:id="rId18"/>
-    <sheet name="TransportServiceStatisticsTest" sheetId="51" r:id="rId19"/>
-    <sheet name="TransportDriverStatisticsTest" sheetId="52" r:id="rId20"/>
-    <sheet name="TransportServiceRidesTest" sheetId="53" r:id="rId21"/>
+    <sheet name="TransportServiceStatisticsTest" sheetId="51" r:id="rId10"/>
+    <sheet name="TransportDriverStatisticsTest" sheetId="52" r:id="rId11"/>
+    <sheet name="TransportServiceRidesTest" sheetId="53" r:id="rId12"/>
+    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId13"/>
+    <sheet name="PanicCallTest" sheetId="49" r:id="rId14"/>
+    <sheet name="DashboardTest" sheetId="50" r:id="rId15"/>
+    <sheet name="AddStore" sheetId="40" r:id="rId16"/>
+    <sheet name="StoreOperations" sheetId="42" r:id="rId17"/>
+    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId18"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId19"/>
+    <sheet name="AddProvider" sheetId="45" r:id="rId20"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId21"/>
     <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId22"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="142">
   <si>
     <t>City Area</t>
   </si>
@@ -75,30 +75,15 @@
     <t>Requirement ID</t>
   </si>
   <si>
-    <t>SA_TS_2</t>
-  </si>
-  <si>
-    <t>SA_TS_1</t>
-  </si>
-  <si>
     <t>CityAdmin</t>
   </si>
   <si>
-    <t>SA_TS_3</t>
-  </si>
-  <si>
-    <t>SA_TS_4</t>
-  </si>
-  <si>
     <t>Auto Driver Registration</t>
   </si>
   <si>
     <t>Bike Driver Registration</t>
   </si>
   <si>
-    <t>SA_TS_5</t>
-  </si>
-  <si>
     <t>Taxi Driver Registration</t>
   </si>
   <si>
@@ -111,9 +96,6 @@
     <t>Validate that the admin can successfully add a new Auto driver by entering valid driver details and vehicle details and approve him from pendind documents by adding documents and verify he is coming in on approved drivers list .</t>
   </si>
   <si>
-    <t>SA_TS_0</t>
-  </si>
-  <si>
     <t>TC_CA_00_super_admin_login</t>
   </si>
   <si>
@@ -126,18 +108,12 @@
     <t>To verify that the Super Admin can successfully create a new City Admin account by providing valid personal details, associating them with a specific city, and granting multiple service and module-level permissions.</t>
   </si>
   <si>
-    <t>SA_TS_6</t>
-  </si>
-  <si>
     <t>Add New Store &amp; Approve</t>
   </si>
   <si>
     <t>This test validates the complete administrative workflow for registering and authorizing a new merchant within the food delivery system. The automation navigates to the Add Store module to dynamically create a unique store profile, populating operational data including delivery radius, commission structures, and banking details. Following creation, the script transitions to the Compliance phase, where it filters for the new store in the "Pending Documents" list, automates the upload of regulatory files, and sets document expiry dates. The workflow concludes by triggering the Final Approval and verifying the store’s successful migration to the active Store List, ensuring end-to-end data consistency and functional status transitions.</t>
   </si>
   <si>
-    <t>SA_TS_7</t>
-  </si>
-  <si>
     <t>Store Operations</t>
   </si>
   <si>
@@ -148,9 +124,6 @@
   </si>
   <si>
     <t>This test validates the complete lifecycle of a store within a delivery services platform, beginning with the creation of a new store (using dynamic timestamps for uniqueness) and the configuration of its operational settings, bank details, and timing. It then navigates through various administrative states, including uploading and verifying compliance documents, moving the store from a pending status to approved, and then testing the blocking/unblocking functionality. Finally, the script validates the rejection workflow by moving a store to the rejected list with a specific reason, ensuring that status transitions and data filtering across the "Store List," "Pending," and "Blocked" modules are functioning as expected.</t>
-  </si>
-  <si>
-    <t>SA_TS_9</t>
   </si>
   <si>
     <t>Add New Provider &amp; Approve</t>
@@ -1470,59 +1443,6 @@
       </rPr>
       <t xml:space="preserve"> The City Area created in the previous AddCityArea must be in an "Active" status to be visible in the cityId dropdown selection.</t>
     </r>
-  </si>
-  <si>
-    <t>1.Remove Test Area,sql delete,,"DELETE FROM we1.admin_area_list WHERE name = '{areaName}';"
-2.Remove Customer,sql delete,,"DELETE FROM we1.users WHERE first_name = '{customerName}';"
-3.Remove City Admin,sql delete,,"DELETE FROM we1.super_admin WHERE name = '{adminName}';"
-4.Remove Auto Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{autoName}';"
-5.Remove Auto Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{autoName}';"
-6.Remove Auto Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{autoCompanyName}';"
-7.Remove Bike Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{bikeName}';"
-8.Remove Bike Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{bikeName}';"
-9.Remove Bike Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{bikeCompanyName}';"
-10.Remove Taxi Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{taxiName}';"
-11.Remove Taxi Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{taxiName}';"
-12.Remove Taxi Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{taxiCompanyName}';"
-13.Remove Bus Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{busDriverName}';"
-14.Remove Bus Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{busDriverName}';"
-15.Remove Bus Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{busCompanyName}';"
-16.Remove Bus Driver Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{documentName}';"
-17.Remove Transport Service PromoCode,sql delete,,"DELETE FROM we1.promocode_details WHERE promo_code = '{promoCodeName}';"
-18.Remove Bus Vehicle Variation Volvo,sql delete,,"DELETE FROM we1.transport_vehicle_type WHERE name = '{busTypeName}';"
-19.Remove  Transport Ride,sql delete,,"DELETE FROM we1.service_category WHERE name = '{transportName}';"
-20.Remove Kfc Private Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{kfcdriverName}';"
-21.Remove Kfc Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{kfcBikeCompanyName}';"
-22.Remove Kfc Product Details,sql delete,,"DELETE FROM we1.store_product_details WHERE name = '{kfcProductName}';"
-23.Remove Kfc Owner Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{storeOwner}';"
-24.Remove Kfc Owner From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{storeOwner}';"
-25.Remove Kfc Store Details,sql delete,,"DELETE FROM we1.store_details WHERE name = '{storeName}';"
-26.Remove Bilal Owner Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{hotelOwner}';"
-27.Remove Bilal Owner From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{hotelOwner}';"
-28.Remove Bilal Store Details,sql delete,,"DELETE FROM we1.store_details WHERE name = '{hotelName}';"
-29.Remove Amul Owner Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{milkStoreOwner}';"
-30.Remove Amul Owner From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{milkStoreOwner}';"
-31.Remove Amul Store Details,sql delete,,"DELETE FROM we1.store_details WHERE name = '{milkStore}';"
-32.Remove Curd Product Category,sql delete,,"DELETE FROM we1.store_product_category WHERE name = '{MilkCategoryName}';"
-33.Remove Delievery Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{deliveryDocumentName}';"
-34.Remove Delievery Service PromoCode,sql delete,,"DELETE FROM we1.promocode_details WHERE promo_code = '{deliveryPromoCodeName}';"
-35.Remove  Deleivrey Service,sql delete,,"DELETE FROM we1.service_category WHERE name = '{deliveryName}';"
-36.Remove Plumber Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{plumberName}';"
-37.Remove Plumber Provider Details,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{plumberName}';"
-38.Remove Painter Package,sql delete,,"DELETE FROM we1.other_service_provider_packages WHERE name = '{packageName}';"
-39.Remove Painter Sub Category,sql delete,,"DELETE FROM we1.other_service_sub_category WHERE name = '{painterCategoryName}';"
-40.Remove Provider Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{providerDocumentName}';"
-41.Remove Provider Service PromoCode,sql delete,,"DELETE FROM we1.promocode_details WHERE promo_code = '{providerPromoCodeName}';"
-42.Remove Painter Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{painterName}';"
-43.Remove Painter From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{painterName}';"
-44.Remove Provider Service,sql delete,,"DELETE FROM we1.service_category WHERE name = '{serviceName}';"
-45.Remove Lorry Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{lorrydriverName}';"
-46.Remove Bus Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{lorrydriverName}';"
-47.Remove Lorry Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{lorrycompanyName}';"
-48.Remove Lorry Vehicle Variation tempo,sql delete,,"DELETE FROM we1.transport_vehicle_type WHERE name = '{lorryTypeName}';"
-49.Remove  Transport Ride,sql delete,,"DELETE FROM we1.service_category WHERE name = '{lorryTransportName}';"
-50.Remove Transport City Admin,sql delete,,"DELETE FROM we1.super_admin WHERE name = '{transAdminName}';"
-51.wait,2000,,</t>
   </si>
   <si>
     <t>1. Enter  Email , type , super_admin@gmail.com, "web.global.login.email"
@@ -1535,27 +1455,6 @@
   </si>
   <si>
     <t>TC_CA_08_add_transport_city_admin</t>
-  </si>
-  <si>
-    <t>TC_CA_09_add_store</t>
-  </si>
-  <si>
-    <t>TC_CA_10_store_oprerations</t>
-  </si>
-  <si>
-    <t>TC_CA_11_store_status_management</t>
-  </si>
-  <si>
-    <t>TC_CA_12_delivery_service_complete_test</t>
-  </si>
-  <si>
-    <t>TC_CA_13_add_provider</t>
-  </si>
-  <si>
-    <t>TC_CA_14_provider_service_full_lifecycle_test</t>
-  </si>
-  <si>
-    <t>TC_CA_15_subscription_plan_test</t>
   </si>
   <si>
     <t>Removed Steps</t>
@@ -2292,6 +2191,984 @@
 53.wait, 2000, , ""</t>
   </si>
   <si>
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
+37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Store Required Documents,verify,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Verify Add Store,verify,,"admin.store.list_page.header"
+73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+77. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Store List,click,,"admin.store.submenu.store_list"
+8. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+9. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+10. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+11. Click Product Icon,click,,"admin.store.products.grid_icon"
+12. Click Add Products,click,,"admin.store.products.add_btn"
+13. Open Product Category Dropdown,click,,"admin.store.products.category_dropdown"
+14. Select Grill Chicken,click,,"admin.store.products.category_option_grill"
+15. Enter Product Name,type,kfcProduct{randomAlpha}&gt;&gt; kfcProductName,"admin.store.products.name_input"
+16. Enter Product Amount,type,500,"admin.store.products.amount_input"
+17. Enter Product Description,type,KFC special grill chicken,"admin.store.products.description_textarea"
+18. Upload Product Image,uploadfile,"src/main/resources/test-data/grillchicken.jpg","admin.store.products.image.file"
+19. Open Product Category Dropdown,click,,"admin.store.products.status_dropdown"
+20. Select Activate,click,,"admin.store.products.status_option_active"
+21. Open Discount Type Dropdown,click,,"admin.store.products.discount_dropdown"
+22. Enter Discount Amount,type,50,"admin.store.products.discount_input"
+23. Click Save,click,,"admin.store.products.save_btn"
+24. Wait For Saved Succesfully,wait_until_visible,,"admin.store.products.toast_success"
+25. Wait For Store Products,wait_until_visible,,"admin.store.products.header"
+26. Filter Product List,type,{kfcProductName},"admin.store.products.name_filter"
+27. Click Back,click,,"admin.store.products.back_btn"
+28. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+29. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+30. Click Wallet Icon,click,,"admin.store.wallet.grid_icon"
+31. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
+32. Enter Wallet Amount,type,1000,"admin.store.wallet.amount_input"
+33. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
+34. Select Add Money,click,,"admin.store.wallet.option_add"
+35. Click Submit,click,,"web.global.action.submit"
+36. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
+37. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
+38. Enter Wallet Amount,type,200,"admin.store.wallet.amount_input"
+39. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
+40. Select Deduct Money,click,,"admin.store.wallet.option_deduct"
+41. Click Submit,click,,"web.global.action.submit"
+42. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
+43. Click Back,click,,"admin.store.products.back_btn"
+44. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+45. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+46. Click Drivers Icon,click,,"admin.store.drivers.grid_icon"
+47. Click Add Private Driver,click,,"admin.store.drivers.add_private_btn"
+48. Enter Driver Name,type,kfcdriver_{timestamp} &gt;&gt; kfcdriverName,"admin.drivers.fullname.input"
+49. Enter Email,type,kfcdriver_{timestamp}@gmail.com,"admin.drivers.email.input"
+50. Enter Contact Number,type,{randomPhone},"admin.drivers.phone.input"
+51. Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg","admin.drivers.profile_image.file"
+52. Select Male Gender,click,,"admin.drivers.male_gender.div"
+53. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+54. Select Scooter Option,click,,"admin.drivers.vehicle_option.scooter"
+55. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+56. Enter Vehicle Company,type,kfcBikeCompany{randomAlpha}&gt;&gt; kfcBikeCompanyName,"admin.drivers.companyname.input"
+57. Enter Plate No,type,KL-01-AB-1634,"admin.drivers.plateno.input"
+58. Enter Model Name,type,activa,"admin.drivers.modelname.input"
+59. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg","admin.drivers.vehicle_image.file"
+60. Enter Vehicle Color,type,white,"admin.drivers.vehicle_color.input"
+61. Click Submit,click,,"web.global.action.submit"
+62. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+63. Filter Driver List,type,{kfcdriverName},"admin.drivers.name_filter.input"
+64. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+65. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
+37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Block Icon,click,,"admin.store.grid.block_icon"
+76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Stores,click,,"admin.store.menu.toggle_btn"
+78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
+79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
+82. Click Stores,click,,"admin.store.menu.toggle_btn"
+83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
+84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
+86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
+87. Click Stores,click,,"admin.store.menu.toggle_btn"
+88. Select Store List,click,,"admin.store.submenu.store_list"
+89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+90. wait,3000,,
+91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+92. Click Doc Icon,click,,"admin.store.grid.document_icon"
+93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
+94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+97. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Delivery Services, click, , "admin.deliveryservice.menu"
+3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
+5.Enter Category Name, type, milk Delivery{randomAlpha} &gt;&gt; deliveryName, "admin.deliveryservice.category_name.input"
+6.Enter Slug, type, Milk Delivery, "admin.deliveryservice.slug.input"
+7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "admin.deliveryservice.image.file"
+8.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+9.Select Activate, click, , "admin.deliveryservice.status.option_activate"
+10.Open Category Flow Dropdown, click, , "admin.deliveryservice.flow.dropdown"
+11.Select default flow(food-delivery), click, , "admin.deliveryservice.flow.option_food_delivery"
+12.Enter Delivery Name Tamil, type, பால்காரர், "admin.deliveryservice.lang_tamil.input"
+13.Enter Delivery Name Arabic, type, لبّان, "admin.deliveryservice.lang_arabic.input"
+14.Enter Delivery Name Hindi, type, दूधवाला, "admin.deliveryservice.lang_hindi.input"
+15.Click Submit, click, , "web.global.action.submit"
+16.Verify Success, verify, , "web.global.toast.info"
+17.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+18.Click Home Icon, click, , "admin.deliveryservice.home.icon"
+19.Click Settings, click, , "admin.deliveryservice.settings.menu"
+20.Click Requirement Document, click, , "admin.deliveryservice.required_docs"
+21.Click Add Document, click, , "admin.deliveryservice.docs.add_btn"
+22.Enter Name, type, document{randomAlpha} &gt;&gt; deliveryDocumentName, "admin.deliveryservice.docs.name_input"
+23.Open status Dropdown, click, , "admin.deliveryservice.docs.status_dropdown"
+24.Select Active, click, , "admin.deliveryservice.docs.status_option_active"
+25.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+26.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+27.Click Mandatory Document, click, , "admin.deliveryservice.docs.mandatory_checkbox"
+28.Click Require Proof Number, click, , "admin.deliveryservice.docs.proof_number_checkbox"
+29.Enter Display Order, type, 10, "admin.deliveryservice.docs.display_order_input"
+30.Click Submit, click, , "web.global.action.submit"
+31.Verify Success, verify, , "web.global.toast.info"
+32.Filter Document List, type, {deliveryDocumentName}, "admin.deliveryservice.docs.grid.filter_input"
+33.wait, 2000, , ""
+34.Click Settings, click, , "admin.deliveryservice.settings.menu"
+35.Click Service Settings, click, , "admin.deliveryservice.submenu.service_settings"
+36.Enter Driver Search Radius, type, 50, "admin.deliveryservice.config.search_radius_input"
+37.Open Tax Type Dropdown, click, , "admin.deliveryservice.config.tax_type_dropdown"
+38.Select Amount, click, , "admin.deliveryservice.config.tax_type_option_amount"
+39.Enter Tax, type, 20, "admin.deliveryservice.config.tax_input"
+40.Open Platform Fee Type Dropdown, click, , "admin.deliveryservice.config.fee_type_dropdown"
+41.Select Amount, click, , "admin.deliveryservice.config.fee_type_option_amount"
+42.Enter Platform Fee, type, 20, "admin.deliveryservice.config.platform_fee_input"
+43.Enter Cancel Charge (in %):, type, 20, "admin.deliveryservice.config.cancel_charge_input"
+44.Enter Driver Accept Timeout (in Second):, type, 20, "admin.deliveryservice.config.driver_timeout_input"
+45.Click Submit, click, , "web.global.action.submit"
+46.Verify Success, verify, , "web.global.toast.info"
+47.Click Stores, click, , "admin.store.menu.toggle_btn"
+48.Select Add Store, click, , "admin.store.submenu.add_store"
+49.Verify Add Store, verify, , "admin.store.add_page.header"
+50.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "admin.store.name.input"
+51.Open Delivery Radius Dropdown, click, , "admin.store.radius.dropdown"
+52.Select Twenty Five Kilometer, click, , "admin.store.radius.option_25km"
+53.Open Estimated Delivery Time, click, , "admin.store.eta.dropdown"
+54.Select Thirty Minute, click, , "admin.store.eta.option_30min"
+55.Enter Order Minimum Amount, type, 300, "admin.store.min_amount.input"
+56.Enter Packaging Charges, type, 50, "admin.store.packaging_charge.input"
+57.Enter Short Description, type, amul taste of india, "admin.store.description.input"
+58.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "admin.store.banner.file"
+59.Open Driver Notification, click, , "admin.store.driver_notification.dropdown"
+60.Select Both Driver, click, , "admin.store.driver_notification.option_both"
+61.Click Checkbox Allow For Pickup, click, , "admin.store.allow_pickup.checkbox"
+62.Open Current Status Dropdown, click, , "admin.store.current_status.dropdown"
+63.Select Active, click, , "admin.store.current_status.option_active"
+64.Enter Store Address, type, Amul chennai, "admin.store.location.input"
+65.wait, 3000, , ""
+66.Confirm Store Address, press_enter, , "admin.store.location.input"
+67.wait, 3000, , ""
+68.Select First Option, arrow_down, , "admin.store.location.input"
+69.Confirm Option, press_enter, , "admin.store.location.input"
+70.wait, 2000, , ""
+71.Click Storewise Commission Checkbox, click, , "admin.store.commission.checkbox"
+72.Enter Store Commission, type, 25, "admin.store.commission_rate.input"
+73.Open Driver Notification, click, , "admin.store.offer_type.dropdown"
+74.Select Amount, click, , "admin.store.offer_type.option_amount"
+75.Enter Offer Amount, type, 50, "admin.store.offer_amount.input"
+76.Enter Offer Min Amount, type, 500, "admin.store.offer_min_amount.input"
+77.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "admin.store.contact_name.input"
+78.Enter Email, type, amul_{timestamp}@gmail.com &gt;&gt; storeEmail, "admin.store.email.input"
+79.Enter Contact Number, type, {randomPhone}, "admin.store.phone.input"
+80.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "admin.store.profile.file"
+81.Enter Bank Name, type, federal, "admin.store.bank.name_input"
+82.Enter Bank Location, type, chennai, "admin.store.bank.location_input"
+83.Enter Account Number, type, 123456789012, "admin.store.bank.account_input"
+84.Enter Account Holder Name, type, {milkStoreOwner}, "admin.store.bank.holder_input"
+85.Enter Payment Email Address, type, {storeEmail}, "admin.store.bank.payment_email"
+86.Enter BIC Code, type, 1234, "admin.store.bank.bic_input"
+87.Click Store Timing Checkbox, click, , "admin.store.timing.everyday_checkbox"
+88.Enter From Time, type, 100000AM, "admin.store.timing.from_input"
+89.Enter To Time, type, 100000PM, "admin.store.timing.to_input"
+90.Submit Add Store, click, , "web.global.action.submit"
+91.Verify Success Message, verify, , "web.global.toast.info"
+92.Click Stores, click, , "admin.store.menu.toggle_btn"
+93.Select Store List, click, , "admin.store.submenu.store_list"
+94.Verify Add Store, verify, , "admin.store.list_page.header"
+95.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+96.Click Stores, click, , "admin.store.menu.toggle_btn"
+97.Select Pending Documents Stores List, click, , "admin.store.submenu.pending_docs"
+98.Verify Add Store, verify, , "admin.store.pending_page.header"
+99.Filter Pending Document Store List, type, {milkStore}, "admin.store.grid.name_filter"
+100.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+101.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+102.Store Required Documents, verify, , "admin.store.documents_page.header"
+103.Add Address Proof, click, , "admin.store.grid.edit_doc_icon"
+104.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.store.doc.file_input"
+105.Enter Expiry Date, type, 2026-12-12, "admin.store.doc.expiry_input"
+106.Click Submit, click, , "web.global.action.submit"
+107.Verify Updated Successfully, verify, , "web.global.toast.updated"
+108.Click Approve Store, click, , "admin.store.grid.approve_doc_icon"
+109.Verify Updated Successfully, verify, , "web.global.toast.updated"
+110.Click Back, click, , "admin.store.grid.back_btn"
+111.Click Stores, click, , "admin.store.menu.toggle_btn"
+112.Select Store List, click, , "admin.store.submenu.store_list"
+113.Verify Add Store, verify, , "admin.store.list_page.header"
+114.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+115.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+116.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+117.wait for back button,wait,3000,
+118.Click Back, click, , "admin.store.grid.back_btn"
+119.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
+120.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
+121.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
+122.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
+123.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
+124.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
+125.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
+126.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
+127.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
+128.wait, 2000, , ""
+129.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
+130.Click Submit, click, , "web.global.action.submit"
+131.Verify Success Message, verify, , "web.global.toast.info"
+132.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
+133.Click Stores, click, , "admin.store.menu.toggle_btn"
+134.Select Store List, click, , "admin.store.submenu.store_list"
+135.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+136.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
+137.Click Product Icon, click, , "admin.store.products.grid_icon"
+138.Click Add Products, click, , "admin.store.products.add_btn"
+139.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
+140.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
+141.wait, 1000, ,""
+142.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+143.Click Delivery Services, click, , "admin.deliveryservice.menu"
+144.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+145.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+146.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
+147.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+148.wait, 1000, , ""
+149.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
+150.Click Submit, click, , "web.global.action.submit"
+151.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+152.wait, 1000, ,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Delivery Services,click,,"admin.provider_service.menu_link"
+3.Verify Delivery Services,verify,,"admin.provider_service.on_demand_header"
+4.Filter service List,type,Plumbers,"admin.provider_service.services.filter.input"
+5.Click Home Icon Plumbers,click,,"admin.provider_service.services.home.icon_by_row_plumbers"
+6.Verify Plumbers Summary,verify,,"admin.provider_service.services.plumbers_summary.header"
+7.Click Providers,click,,"admin.provider_service.providers.root.button"
+8.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
+9.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
+10.Enter Provider Full Name, type, Plumber{randomAlpha}&gt;&gt; plumberName, "admin.provider_service.provider_form.fullname.input"
+11.Upload Plumber Image, uploadfile, "src/main/resources/test-data/plumber.jpg", "admin.provider_service.provider_form.avatar.file"
+12.Enter Email, type, Plumber_{timestamp}@gmail.com&gt;&gt;plumberEmail, "admin.provider_service.provider_form.email.input"
+13.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
+14.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
+15.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
+16.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
+17.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
+18.Enter Provider Address, type, plumber chennai, "admin.provider_service.provider_form.address.input"
+19.wait,1000,,
+20.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
+21.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
+22.wait,1000,,
+23.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
+24.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
+25.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
+26.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
+27.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
+28.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
+29.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
+30.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
+31.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
+32.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
+33.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
+34.Enter Account Holder Name, type, {plumberName}, "admin.provider_service.provider_form.account_holder.input"
+35.Enter Payment Email Address, type, {plumberEmail}, "admin.provider_service.provider_form.payment_email.input"
+36.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
+37.Click Save, click, , "web.global.login.submit_btn"
+38.Verify Sucess, verify, , "web.global.toast.info"
+39.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+40.Click Providers,click,,"admin.provider_service.providers.root.button"
+41.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
+42.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+43.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
+44.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
+45.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+46.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
+47.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
+48.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
+49.Click Submit, click, , "web.global.action.submit"
+50.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+51.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+52.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
+53.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+54.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+55.Click Providers,click,,"admin.provider_service.providers.root.button"
+56.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
+57.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
+58.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+59.Click Doc Icon,click,,"admin.provider_service.providers.grid.document.icon"
+60.Click Eye Icon,click,,"admin.provider_service.providers.grid.view_eye.icon"
+61.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+62.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
+63.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+64.Scroll Grid, tab, 11, "admin.provider_service.providers.grid.name_filter"
+65.Click Wallet Icon,click,,"admin.provider_service.providers.grid.wallet.icon"
+66.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
+67.Enter Wallet Amount, type, 1000, "admin.provider_service.wallet.amount.input"
+68.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
+69.Select Add Money,click, , "admin.provider_service.wallet.options.add_money"
+70.Click Submit, click, , "web.global.action.submit"
+71.Verify Saved Succesfully, verify, , "web.global.toast.success"
+72.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
+73.Enter Wallet Amount, type, 200, "admin.provider_service.wallet.amount.input"
+74.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
+75.Select Deduct Money,click, , "admin.provider_service.wallet.options.deduct_money"
+76.Click Submit, click, , "web.global.action.submit"
+77.Verify Saved Succesfully, verify, , "web.global.toast.success"
+78.Click Back, click, , "admin.provider_service.global.action.back_normal_btn"
+79.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+80.Click Doc Icon,click, , "admin.provider_service.providers.grid.document.icon"
+81.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+82.Click Reject Document,click, , "admin.provider_service.provider_docs.reject.icon"
+83.Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
+84.Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+85..Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
+86.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+87.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+88.Scroll Grid, tab, 13, "admin.provider_service.providers.grid.name_filter"
+89.Click Block Provider,click, , "admin.provider_service.providers.grid.block.icon"
+90.Click Block Yes,click, , "web.global.dialog.btn_confirm_yes"
+91.Blocking Reason,type,customer complaints,"web.global.dialog.textarea_reason"
+92.Click block Yes,click, , "web.global.dialog.btn_confirm_yes"
+93.Click Providers,click, , "admin.provider_service.providers.root.button"
+94.Select Blocked Providers,click, , "admin.provider_service.providers.blocked_list.menu"
+95.Verify Blocked Provider,verify, , "admin.provider_service.providers.grid.blocked_plumbers.header"
+96.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+97.Scroll Grid, tab, 12, "admin.provider_service.providers.grid.name_filter"
+98.Click Unblock Provider,click, , "admin.provider_service.providers.grid.unblock.icon"
+99.Click Providers,click, , "admin.provider_service.providers.root.button"
+100.Select Provider List,click, , "admin.provider_service.providers.provider_list.menu"
+101.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+102.wait,1000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Provider Services,click,,"admin.provider_service.menu_link"
+3.Verify Provider Services,verify,,"admin.provider_service.on_demand_header"
+4.Click Add New Services,click,,"admin.provider_service.services.add_new.btn"
+5.Enter Service Name, type, Painter{randomAlpha}&gt;&gt; serviceName, "admin.provider_service.services.name.input"
+6.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
+7.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
+8.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
+9.Enter Slug, type, painter, "admin.provider_service.services.slug.input"
+10.Upload Service Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.services.image.file"
+11.wait,2000,,
+12.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
+13.Select Activate,click,,"admin.provider_service.services.status.option_activate"
+14.Open Select City Dropdown,click,,"admin.provider_service.services.city.dropdown"
+15.Select {areaName},click,,"admin.provider_service.services.city.option_dynamic"
+16.Click Submit,click,,"web.global.action.submit"
+17.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+18.Click Home Icon ,click,,"admin.provider_service.services.home.icon"
+19.Click Settings ,click,,"admin.provider_service.settings.menu.button"
+20.Click Requirment Document ,click,,"admin.provider_service.settings.req_document.tab"
+21.Click Add Document ,click,,"admin.provider_service.req_docs.add.btn"
+22.Enter Name, type, documet{randomAlpha}&gt;&gt; providerDocumentName, "admin.provider_service.req_docs.name.input"
+23.Open status Dropdown,click,,"admin.provider_service.req_docs.status.dropdown"
+24.Select Active,click,,"admin.provider_service.req_docs.status.option_active"
+25.Click Document Expiry ,click,,"admin.provider_service.req_docs.expiry_toggle"
+26.Click Mandatory Document ,click,,"admin.provider_service.req_docs.mandatory_toggle"
+27.Click Submit ,click,,"web.global.action.submit"
+28.Verify Sucess, verify, , "web.global.toast.info"
+29.Filter Document List,type,{providerDocumentName},"admin.provider_service.req_docs.filter.input"
+30.Click Settings ,click,,"admin.provider_service.settings.menu.button"
+31.Click Promocode ,click,,"admin.provider_service.settings.promocode.tab"
+32.Click Add Promo Code ,click,,"admin.provider_service.promocode.add.btn"
+33.Open User List Dropdown,click,,"admin.provider_service.promocode.user_list.dropdown"
+34.Select User,click,,"admin.provider_service.promocode.user_list.option_dynamic"
+35.Click Code Name Box,click,,"admin.provider_service.promocode.code_name.box"
+36.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; providerPromoCodeName, "admin.provider_service.promocode.code_name.box"
+37.Open Discout Type Dropdown,click,,"admin.provider_service.promocode.discount_type.dropdown"
+38.Select Discout Type,click,,"admin.provider_service.promocode.discount_type.option_amount"
+39.Enter Expiry Date,type,12122026,"admin.provider_service.promocode.expiry_date.input"
+40.Enter Discount Amount, type, 100, "admin.provider_service.promocode.discount_amount.input"
+41.Enter Minimum Order Amount, type, 1000, "admin.provider_service.promocode.min_order_amount.input"
+42.Enter Maximum Discount Amount, type, 100, "admin.provider_service.promocode.max_discount.input"
+43.Enter Coupon Limit, type, 5,"admin.provider_service.promocode.coupon_limit.input"
+44.Enter Usage Limit for One User, type, 2,"admin.provider_service.promocode.usage_limit_per_user.input"
+45.Enter Promo Code Description, type, Promo Dode For Gold Member,"admin.provider_service.promocode.description.textarea"
+46.Click Submit ,click,,"web.global.action.submit"
+47.Verify Sucess, verify, , "web.global.toast.info"
+48.Filter PromoCode List,type,{providerPromoCodeName},"admin.provider_service.promocode.filter.input"
+49.Click Providers,click,,"admin.provider_service.providers.root.button"
+50.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
+51.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
+52.Enter Provider Full Name, type, Painter{randomAlpha}&gt;&gt; painterName, "admin.provider_service.provider_form.fullname.input"
+53.Upload Painter Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.provider_form.avatar.file"
+54.Enter Email, type, Painter_{timestamp}@gmail.com&gt;&gt;painterEmail, "admin.provider_service.provider_form.email.input"
+55.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
+56.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
+57.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
+58.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
+59.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
+60.Enter Provider Address, type, painter chennai, "admin.provider_service.provider_form.address.input"
+61.wait,1000,,
+62.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
+63.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
+64.wait,1000,,
+65.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
+66.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
+67.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
+68.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
+69.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
+70.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
+71.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
+72.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
+73.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
+74.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
+75.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
+76.Enter Accont Holder Name, type, {painterName}, "admin.provider_service.provider_form.account_holder.input"
+77.Enter Payment Email Address, type, {painterEmail}, "admin.provider_service.provider_form.payment_email.input"
+78.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
+79.Click Save, click, , "web.global.login.submit_btn"
+80.Verify Sucess, verify, , "web.global.toast.info"
+81.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+82.Click Providers,click,,"admin.provider_service.providers.root.button"
+83.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
+84.Filter Plumber List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+85.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
+86.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
+87.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
+88.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
+89.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
+90.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
+91.Click Submit, click, , "web.global.action.submit"
+92.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+93.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
+94.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
+95.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+96.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+97.Click Providers,click,,"admin.provider_service.products.menu_category_btn"
+98.Click Add New Category,click,,"admin.provider_service.category.add_new.btn"
+99.Enter Category Name, type,residentialPainter{randomAlpha}&gt;&gt; painterCategoryName, "admin.provider_service.category.name.input"
+100.Enter Category Name Tamil, type, குடியிருப்பு பெயிண்டர், "admin.provider_service.category.name_tamil.input"
+101.Enter Category Name Arabic, type, دهان سكني, "admin.provider_service.category.name_arabic.input"
+102.Enter Category Name Hindi, type, आवासीय पेंटर, "admin.provider_service.category.name_hindi.input"
+103.Open Category status Dropdown,click,,"admin.provider_service.category.status.dropdown"
+104.Select Activate,click,,"admin.provider_service.category.status.option_active"
+105.Upload Category Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.category.image.file"
+106.wait,2000,,
+107.Click Submit,click,,"web.global.action.submit"
+108.Filter Category Name,type,{painterCategoryName},"admin.provider_service.category.filter.input"
+109.Click Providers,click,,"admin.provider_service.providers.root.button"
+110.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
+111.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+112.Scroll Grid, tab, 7, "admin.provider_service.providers.grid.name_filter"
+113.Click Package Icon,click,,"admin.provider_service.packages.icon"
+114.Click Add Package,click,,"admin.provider_service.packages.add_new.btn"
+115.Open Category Dropdown,click,,"admin.provider_service.packages.category.dropdown"
+116.Select Activate,click,,"admin.provider_service.packages.category.option_dynamic"
+117.Enter Package Name, type, package{randomAlpha}&gt;&gt; packageName, "admin.provider_service.packages.name.input"
+118.Enter Amount, type, 1000, "admin.provider_service.packages.amount.input"
+119.Open Max Book Quantity Dropdown,click,,"admin.provider_service.packages.max_book_qty.dropdown"
+120.Select 4,click,,"admin.provider_service.packages.max_book_qty.option_4"
+121.Open Status Dropdown,click,,"admin.provider_service.packages.status.dropdown"
+122.Select Activate,click,,"admin.provider_service.packages.status.option_activate"
+123.Enter Description, type, Premium residential painting package, "admin.provider_service.packages.description.textarea"
+124.Click Submit,click,,"web.global.action.submit"
+125.wait,1000,,
+126.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
+127.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+128.Click Delivery Services,click,,"admin.provider_service.menu_link"
+129.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+130.Click Edit Icon ,click,,"admin.provider_service.services.edit.icon"
+131.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
+132.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
+133.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
+134.Scroll Grid, tab, 4, "admin.provider_service.services.name_hindi.input"
+135.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
+136.Select Deactivate,click,,"admin.provider_service.services.status.option_deactivate"
+137.Click Submit,click,,"web.global.action.submit"
+138.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
+139. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+140.Click badge,click,,"admin.provider_service.badge.icon"
+141.Click provider Services,click,,"admin.provider_service.menu_link"
+142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+143.wait,1000,,</t>
+  </si>
+  <si>
+    <t>Verify the complete lifecycle of a panic call configuration—including creation with multilingual names (English, Tamil, Hindi), searching, updating its status to inactive, and successful deletion.</t>
+  </si>
+  <si>
+    <t>Panic Call Test</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
+2.Click Setting,click,,"admin.setting.sidebar.menu"
+3.Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
+4.Click Add panic call button,click,,"admin.setting.panic_call.add_btn"
+5.Enter name,type,police_{randomAlpha}&gt;&gt;policeName,"admin.setting.panic_call.name_input"
+6.Enter name in tamil,type,காவல்துறை,"admin.setting.panic_call.tamil_name_input"
+7.Enter name in hindi,type,पुलिस,"admin.setting.panic_call.hindi_name_input"
+8.Contact number,type,{randomPhone},"admin.setting.panic_call.contact_number"
+9.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
+10.Select Active status,click,,"admin.setting.panic_call.activate_status_dropdown"
+11.Submit button,click,,"web.global.action.submit"
+12.Search name,type,{policeName},"admin.setting.panic_call.search_name"
+13.Click Edit Button,click,,"admin.setting.panic_call.edit_btn"
+14.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
+15.Select Deactive status button,click,,"admin.setting.panic_call.deactivate_status_dropdown"
+16.Click Submit button,click,,"web.global.action.submit"
+17.Click Delete button,click,,"admin.setting.panic_call.delete_btn"
+18.Click Yes delete it button,click,,"admin.setting.panic_call.confirm_delete_btn"</t>
+  </si>
+  <si>
+    <t>SA_TS_17</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Customer Icon,click,,"admin.menu.customer_icon"
+3. Click Add Customers,click,,"admin.menu.add_customers"
+4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
+8.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
+9. Open Gender,click,,"admin.customer.dropdown_gender"
+10. Select Male,click,,"admin.customer.select_gender_male"
+11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+12. Click Submit,click,,"web.global.action.submit"
+13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+14. Click Dashboard,click,,"web.global.menu.dashboard"
+15. Click Customer Icon,click,,"admin.menu.customer_icon"
+16. Click Verified Customers,click,,"admin.menu.verified_customers"
+17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+19. Scroll Grid,tab,7,"admin.customer.filter_name"
+20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
+21. Click Close,click,,"web.global.action.close"
+22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
+23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
+25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
+27. Click Submit,click,,"web.global.action.submit"
+28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
+31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+33. Click Submit,click,,"web.global.action.submit"
+34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+35. Click dashboard Icon,click,,"web.global.menu.dashboard"
+36. Click Customer Icon,click,,"admin.menu.customer_icon"
+37. Click Verified Customers,click,,"admin.menu.verified_customers"
+38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+40. Scroll Grid,tab,7,"admin.customer.filter_name"
+41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+44. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+47. Enter Points,type,30,"admin.customer.loyalty.input_points"
+48. Click Submit,click,,"web.global.action.submit"
+49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+52. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+55. Enter Points,type,10,"admin.customer.loyalty.input_points"
+56. Click Submit,click,,"web.global.action.submit"
+57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+59. Click Customer Icon,click,,"admin.menu.customer_icon"
+60. Click Verified Customers,click,,"admin.menu.verified_customers"
+61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+63. Scroll Grid,tab,7,"admin.customer.filter_name"
+64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
+65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
+66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
+67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+68. Verify Added Successfully,verify,,"web.global.toast.info"
+69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+70. Click Customer Icon,click,,"admin.menu.customer_icon"
+71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
+72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+73. Scroll Grid,tab,10,"admin.customer.filter_name"
+74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
+75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+78. Click Customer Icon,click,,"admin.menu.customer_icon"
+79. Click Verified Customers,click,,"admin.menu.verified_customers"
+80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+  </si>
+  <si>
+    <t>Dashboard Test</t>
+  </si>
+  <si>
+    <t>1.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+2.Click Search Button,Click,,"web.global.dashboard.search_btn"
+3.Wait For Today Statistics,wait,2000,
+4.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+5.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+6.Click Search Button,Click,,"web.global.dashboard.search_btn"
+7.Wait For Yesterday Statistics,wait,2000,
+8.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+9.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+10.Click Search Button,Click,,"web.global.dashboard.search_btn"
+11.Wait For This Week Statistics,wait,2000,
+12.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+13.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+14.Click Search Button,Click,,"web.global.dashboard.search_btn"
+15.Wait For This Month Statistics,wait,2000,
+16.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"web.global.dashboard.search_btn"
+19.Wait For Last Month Statistics,wait,2000,
+20.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+21.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+22.Click Search Button,Click,,"web.global.dashboard.search_btn"
+23.Wait For This Year Statistics,wait,2000,
+24.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+25.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+26.Click Search Button,Click,,"web.global.dashboard.search_btn"
+27.Wait For Last Year Statistics,wait,2000,
+28.Click Clear Button,click,,"web.global.dashboard.clear_btn"</t>
+  </si>
+  <si>
+    <t>This test suite validates the dynamic filtering and search functionality of the global dashboard dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
+  </si>
+  <si>
+    <t>SA_TS_18</t>
+  </si>
+  <si>
+    <t>Tranport Service Statistic Test</t>
+  </si>
+  <si>
+    <t>This test suite validates the dynamic filtering and search functionality of the transport Serivice dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Home Icon ,click,, "admin.transport.home.icon"
+5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+6.Click Search Button,Click,,"web.global.dashboard.search_btn"
+7.wait For Today Statistics,wait,2000,
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,Click,,"web.global.dashboard.search_btn"
+10.wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Click Search Button,Click,,"web.global.dashboard.search_btn"
+13.wait For This Week Statistics,wait,2000,
+14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+15.Click Search Button,Click,,"web.global.dashboard.search_btn"
+16.wait For This Month Statistics,wait,2000,
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"web.global.dashboard.search_btn"
+19.wait For Last Month Statistics,wait,2000,
+20.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+21.Click Search Button,Click,,"web.global.dashboard.search_btn"
+22.wait For This Year Statistics,wait,2000,
+23.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+24.Click Search Button,Click,,"web.global.dashboard.search_btn"
+25.wait For Last Year Statistics,wait,2000,</t>
+  </si>
+  <si>
+    <t>SA_TS_19</t>
+  </si>
+  <si>
+    <t>This test suite validates the dynamic filtering and search functionality of the transport Serivice driver dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
+  </si>
+  <si>
+    <t>Tranport Driver Statistic Test</t>
+  </si>
+  <si>
+    <t>SA_TS_20</t>
+  </si>
+  <si>
+    <t>Transport Service Ride Tests</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Drivers Icon,Click,,"admin.transport.driver.icon"
+5.Wait For Load,wait,2000,
+6.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+7.Click Search Button,Click,,"web.global.dashboard.search_btn"
+8.wait For Today Statistics,wait,2000,
+9.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+10.Click Search Button,Click,,"web.global.dashboard.search_btn"
+11.wait For Yesterday Statistics,wait,2000,
+12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+13.Click Search Button,Click,,"web.global.dashboard.search_btn"
+14.wait For This Week Statistics,wait,2000,
+15.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+16.Click Search Button,Click,,"web.global.dashboard.search_btn"
+17.wait For This Month Statistics,wait,2000,
+18.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+19.Click Search Button,Click,,"web.global.dashboard.search_btn"
+20.wait For Last Month Statistics,wait,2000,
+21.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+22.Click Search Button,Click,,"web.global.dashboard.search_btn"
+23.wait For Last Year Statistics,wait,2000,
+24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+25.Click Search Button,Click,,"web.global.dashboard.search_btn"
+26.wait For This Year Statistics,wait,2000,
+27.Click Select Driver Dropdown,Click,,"admin.drivers.approved_driver.driver_dropdown"
+28.Enter Name In Drop Down,type,regression.approved_driver.name,"admin.drivers.approved_driver.driver_dropdown_searchbox"
+29.Click Driver Name,Click,,"admin.drivers.approved_driver.driver_dropdown_first"
+30.Click Vehicle Type Dropdown,Click,,"admin.drivers.approved_driver.vehicle_dropdown"
+31.Enter Vehicle Name,type,pink Auto,"admin.drivers.approved_driver.driver_dropdown_searchbox"
+32.Click Vehicle Name,click,,"admin.drivers.approved_driver.vehicle_dropdown_first"
+33.Click Service Dropdown,click,,"admin.drivers.approved_driver.service_dropdown"
+34.Select Service,type,Auto Ride,"admin.drivers.approved_driver.driver_dropdown_searchbox"
+35.Click Service Option,click,,"admin.drivers.approved_driver.service_dropdown_first"
+36.Click Search Button,Click,,"web.global.dashboard.search_btn"
+37.wait for Approved Driver Filtering,wait,3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Ride Button,click,,"admin.transport.rides.icon"
+5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+6.Click Search Button,Click,,"admin.transport.search_btn"
+7.wait For Today Statistics,wait,2000,
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,Click,,"admin.transport.search_btn"
+10.wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Click Search Button,Click,,"admin.transport.search_btn"
+13.wait For This Week Statistics,wait,2000,
+14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+15.Click Search Button,Click,,"admin.transport.search_btn"
+16.wait For This Month Statistics,wait,2000,
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"admin.transport.search_btn"
+19.wait For Last Month Statistics,wait,2000,
+20.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+21.Click Search Button,Click,,"admin.transport.search_btn"
+22.wait For Last Year Statistics,wait,2000,
+23.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+24.Click Search Button,Click,,"admin.transport.search_btn"
+25.wait For This Year Statistics,wait,2000,
+26.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
+27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+28.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
+29.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
+30.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+31.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
+32.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
+33.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
+34.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
+35.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+36.Enter Status Type In Drop Down,type,Completed Rides,"admin.transport.status_type_dropdown_searchbox"
+37.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+38.Click Search Button,click,,"admin.transport.search_btn"
+39.Click Status Filter Input,click,,"admin.transport.status_filter_input"
+40.Enter Status,type,complete,"admin.transport.status_filter_input"
+41.Click Chat Box,click,,"admin.transport.chat_box.icon"
+42.Wait For Chat,wait,2000,
+43.Close Chat,click,,"admin.transport.rides.messages_close.btn"
+44.Click Ride Detail Button,click,,"admin.transport.ride_details.icon" 
+45.Wait For Ride Detail,wait,2000
+46.Show Ride Details,click,,"admin.transport.ride_details.arrival_time_box"
+47.Wait For Ride Detail,wait,2000
+48.Click Back Button,click,,"admin.transport.ride_details.back_btn"
+49.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
+50.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+51.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
+52.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
+53.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+54.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
+55.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
+56.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
+57.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
+58.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+59.Enter Status Type In Drop Down,type,Incomplete Rides,"admin.transport.status_type_dropdown_searchbox"
+60.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+61.Click Search Button,click,,"admin.transport.search_btn"
+62.Wait For Incomplete Rides,wait,2000,
+63.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+64.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+65.Enter Status Type In Drop Down,type,Cancelled Rides,"admin.transport.status_type_dropdown_searchbox"
+66.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+67.Click Search Button,click,,"admin.transport.search_btn"
+68.Wait For Cancelled Rides,wait,2000,
+69.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+70.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+71.Enter Status Type In Drop Down,type,Scheduled Rides,"admin.transport.status_type_dropdown_searchbox"
+72.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+73.Click Search Button,click,,"admin.transport.search_btn"
+74.Wait For Scheduled Rides,wait,2000,
+75.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+76.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+77.Enter Status Type In Drop Down,type,Pre-Acceptance Cancel Rides,"admin.transport.status_type_dropdown_searchbox"
+78.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+79.Click Search Button,click,,"admin.transport.search_btn"
+80.Wait For Pre-Acceptance Cancel Rides,wait,2000,
+</t>
+  </si>
+  <si>
+    <t>SA_TS_21</t>
+  </si>
+  <si>
+    <t>TC_CA_21_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>This end-to-end regression test suite thoroughly validates the data filtering, search capabilities, and transaction monitoring matrices within the Transport Services administration panel. The test starts by targeting a specific vehicle class ("Auto Ride") and systematically loops through chronological milestone filters—ranging from Today to Last Year—to verify date-partitioned metrics rendering. It then transitions to a complex granular query verification phase by isolating discrete parameters across multiple dependent dropdown elements, including specific customer names, registered driver profiles, vehicle types ("Pink Auto"), and ride lifecycles (Completed, Incomplete, Cancelled, Scheduled, and Pre-Acceptance Cancel Rides). Additionally, the script tests contextual UI elements by verifying the operational initialization of intra-ride chat boxes and auditing specialized tracking panels, such as arrival time breakdowns and deep-dive ride detail metrics grids, ensuring robust data reporting with zero caching conflicts across state changes.</t>
+  </si>
+  <si>
     <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
 2.Click Subscription Plan,click,,"admin.subscription.menu_link"
 3.Click Store subscription plan,click,,"admin.subscription.store.tab"
@@ -2359,7 +3236,7 @@
 65.Verify Provider Subscription Plan Lists ,verify,,"admin.subscription.provider.header"
 66.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_widget"
 67.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
-68.Select Pest Control,click,,"admin.subscription.common.category.option_pest"
+68.Select Pest Control,click,,"admin.subscription.common.category.option_plumbers"
 69.Enter Provider Plan Name, type, ProviderPlan{randomAlpha}&gt;&gt; providerSubscriptionName, "admin.subscription.common.name.input"
 70.Enter Provider Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.alt_input"
 71.Enter Provider Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.alt_input"
@@ -2389,7 +3266,7 @@
 95.Verify Customer Subscription Plan Lists ,verify,,"admin.subscription.customer.header"
 96.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_widget"
 97.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
-98.Select Pest Control,click,,"admin.subscription.common.category.option_pest"
+98.Select Pest Control,click,,"admin.subscription.common.category.option_plumbers"
 99.Enter Customer Plan Name, type,CustomerPlan{randomAlpha}&gt;&gt; custometSubscriptionName, "admin.subscription.common.name.input"
 100.Enter Driver Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.input"
 101.Enter Driver Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.alt_input"
@@ -2581,1007 +3458,127 @@
 163.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
 164.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
 165.Click Edit Icon ,click,, "admin.drivers.docs.edit_icon"
-166.wait,2000,,
-167.Scroll Grid, tab, 5, "admin.transport.name.input"
-168.wait,2000,,
-169.Open status Dropdown,click,, "admin.transport.status.dropdown"
-170.Select Deactivate,click,, "admin.transport.status.deactivate_option"
-171.Click  Submit,click,, "web.global.action.submit"
-172.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-173.wait,2000,,</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Add Store,click,,"admin.store.submenu.add_store"
-8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
-9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
-10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
-11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
-12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
-13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
-14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
-15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
-16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
-17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
-18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
-19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
-20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
-21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
-22. Select Active,click,,"admin.store.current_status.option_active"
-23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
-24. wait,3000,,
-25. Confirm Store Address,press_enter,,"admin.store.location.input"
-26. wait,3000,,
-27. Select First Option,arrow_down,,"admin.store.location.input"
-28. Confirm Option,press_enter,,"admin.store.location.input"
-29. wait,2000,,
-30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
-31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
-32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
-33. Select Amount,click,,"admin.store.offer_type.option_amount"
-34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
-35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
-36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
-37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
-38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
-39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
-40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
-41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
-42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
-43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
-44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
-45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
-46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
-47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
-48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
-49. Submit Add Store,click,,"web.global.action.submit"
-50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-51. Click Stores,click,,"admin.store.menu.toggle_btn"
-52. Select Store List,click,,"admin.store.submenu.store_list"
-53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-55. Click Stores,click,,"admin.store.menu.toggle_btn"
-56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
-57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
-58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
-59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-61. Store Required Documents,verify,,"admin.store.documents_page.header"
-62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
-63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
-64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
-65. Click Submit,click,,"web.global.action.submit"
-66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
-68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-69. Click Back,click,,"admin.store.grid.back_btn"
-70. Click Stores,click,,"admin.store.menu.toggle_btn"
-71. Select Store List,click,,"admin.store.submenu.store_list"
-72. Verify Add Store,verify,,"admin.store.list_page.header"
-73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
-77. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Store List,click,,"admin.store.submenu.store_list"
-8. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-9. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-10. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-11. Click Product Icon,click,,"admin.store.products.grid_icon"
-12. Click Add Products,click,,"admin.store.products.add_btn"
-13. Open Product Category Dropdown,click,,"admin.store.products.category_dropdown"
-14. Select Grill Chicken,click,,"admin.store.products.category_option_grill"
-15. Enter Product Name,type,kfcProduct{randomAlpha}&gt;&gt; kfcProductName,"admin.store.products.name_input"
-16. Enter Product Amount,type,500,"admin.store.products.amount_input"
-17. Enter Product Description,type,KFC special grill chicken,"admin.store.products.description_textarea"
-18. Upload Product Image,uploadfile,"src/main/resources/test-data/grillchicken.jpg","admin.store.products.image.file"
-19. Open Product Category Dropdown,click,,"admin.store.products.status_dropdown"
-20. Select Activate,click,,"admin.store.products.status_option_active"
-21. Open Discount Type Dropdown,click,,"admin.store.products.discount_dropdown"
-22. Enter Discount Amount,type,50,"admin.store.products.discount_input"
-23. Click Save,click,,"admin.store.products.save_btn"
-24. Wait For Saved Succesfully,wait_until_visible,,"admin.store.products.toast_success"
-25. Wait For Store Products,wait_until_visible,,"admin.store.products.header"
-26. Filter Product List,type,{kfcProductName},"admin.store.products.name_filter"
-27. Click Back,click,,"admin.store.products.back_btn"
-28. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-29. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-30. Click Wallet Icon,click,,"admin.store.wallet.grid_icon"
-31. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
-32. Enter Wallet Amount,type,1000,"admin.store.wallet.amount_input"
-33. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
-34. Select Add Money,click,,"admin.store.wallet.option_add"
-35. Click Submit,click,,"web.global.action.submit"
-36. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
-37. Click Manage Transaction,click,,"admin.store.wallet.manage_transaction_btn"
-38. Enter Wallet Amount,type,200,"admin.store.wallet.amount_input"
-39. Open Choose Option Dropdown,click,,"admin.store.wallet.option_dropdown"
-40. Select Deduct Money,click,,"admin.store.wallet.option_deduct"
-41. Click Submit,click,,"web.global.action.submit"
-42. Wait For Saved Succesfully,wait_until_visible,,"web.global.toast.success"
-43. Click Back,click,,"admin.store.products.back_btn"
-44. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-45. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-46. Click Drivers Icon,click,,"admin.store.drivers.grid_icon"
-47. Click Add Private Driver,click,,"admin.store.drivers.add_private_btn"
-48. Enter Driver Name,type,kfcdriver_{timestamp} &gt;&gt; kfcdriverName,"admin.drivers.fullname.input"
-49. Enter Email,type,kfcdriver_{timestamp}@gmail.com,"admin.drivers.email.input"
-50. Enter Contact Number,type,{randomPhone},"admin.drivers.phone.input"
-51. Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg","admin.drivers.profile_image.file"
-52. Select Male Gender,click,,"admin.drivers.male_gender.div"
-53. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
-54. Select Scooter Option,click,,"admin.drivers.vehicle_option.scooter"
-55. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
-56. Enter Vehicle Company,type,kfcBikeCompany{randomAlpha}&gt;&gt; kfcBikeCompanyName,"admin.drivers.companyname.input"
-57. Enter Plate No,type,KL-01-AB-1634,"admin.drivers.plateno.input"
-58. Enter Model Name,type,activa,"admin.drivers.modelname.input"
-59. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg","admin.drivers.vehicle_image.file"
-60. Enter Vehicle Color,type,white,"admin.drivers.vehicle_color.input"
-61. Click Submit,click,,"web.global.action.submit"
-62. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
-63. Filter Driver List,type,{kfcdriverName},"admin.drivers.name_filter.input"
-64. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
-65. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Add Store,click,,"admin.store.submenu.add_store"
-8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
-9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
-10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
-11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
-12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
-13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
-14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
-15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
-16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
-17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
-18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
-19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
-20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
-21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
-22. Select Active,click,,"admin.store.current_status.option_active"
-23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
-24. wait,3000,,
-25. Confirm Store Address,press_enter,,"admin.store.location.input"
-26. wait,3000,,
-27. Select First Option,arrow_down,,"admin.store.location.input"
-28. Confirm Option,press_enter,,"admin.store.location.input"
-29. wait,2000,,
-30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
-31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
-32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
-33. Select Amount,click,,"admin.store.offer_type.option_amount"
-34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
-35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
-36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
-37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
-38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
-39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
-40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
-41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
-42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
-43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
-44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
-45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
-46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
-47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
-48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
-49. Submit Add Store,click,,"web.global.action.submit"
-50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-51. Click Stores,click,,"admin.store.menu.toggle_btn"
-52. Select Store List,click,,"admin.store.submenu.store_list"
-53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-55. Click Stores,click,,"admin.store.menu.toggle_btn"
-56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
-57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
-58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
-59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
-62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
-63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
-64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
-65. Click Submit,click,,"web.global.action.submit"
-66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
-68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-69. Click Back,click,,"admin.store.grid.back_btn"
-70. Click Stores,click,,"admin.store.menu.toggle_btn"
-71. Select Store List,click,,"admin.store.submenu.store_list"
-72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-75. Click Block Icon,click,,"admin.store.grid.block_icon"
-76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
-77. Click Stores,click,,"admin.store.menu.toggle_btn"
-78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
-79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
-82. Click Stores,click,,"admin.store.menu.toggle_btn"
-83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
-84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
-86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
-87. Click Stores,click,,"admin.store.menu.toggle_btn"
-88. Select Store List,click,,"admin.store.submenu.store_list"
-89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-90. wait,3000,,
-91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-92. Click Doc Icon,click,,"admin.store.grid.document_icon"
-93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
-94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
-96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-97. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Delivery Services, click, , "admin.deliveryservice.menu"
-3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
-4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
-5.Enter Category Name, type, milk Delivery{randomAlpha} &gt;&gt; deliveryName, "admin.deliveryservice.category_name.input"
-6.Enter Slug, type, Milk Delivery, "admin.deliveryservice.slug.input"
-7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "admin.deliveryservice.image.file"
-8.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
-9.Select Activate, click, , "admin.deliveryservice.status.option_activate"
-10.Open Category Flow Dropdown, click, , "admin.deliveryservice.flow.dropdown"
-11.Select default flow(food-delivery), click, , "admin.deliveryservice.flow.option_food_delivery"
-12.Enter Delivery Name Tamil, type, பால்காரர், "admin.deliveryservice.lang_tamil.input"
-13.Enter Delivery Name Arabic, type, لبّان, "admin.deliveryservice.lang_arabic.input"
-14.Enter Delivery Name Hindi, type, दूधवाला, "admin.deliveryservice.lang_hindi.input"
-15.Click Submit, click, , "web.global.action.submit"
-16.Verify Success, verify, , "web.global.toast.info"
-17.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-18.Click Home Icon, click, , "admin.deliveryservice.home.icon"
-19.Click Settings, click, , "admin.deliveryservice.settings.menu"
-20.Click Requirement Document, click, , "admin.deliveryservice.required_docs"
-21.Click Add Document, click, , "admin.deliveryservice.docs.add_btn"
-22.Enter Name, type, document{randomAlpha} &gt;&gt; deliveryDocumentName, "admin.deliveryservice.docs.name_input"
-23.Open status Dropdown, click, , "admin.deliveryservice.docs.status_dropdown"
-24.Select Active, click, , "admin.deliveryservice.docs.status_option_active"
-25.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
-26.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
-27.Click Mandatory Document, click, , "admin.deliveryservice.docs.mandatory_checkbox"
-28.Click Require Proof Number, click, , "admin.deliveryservice.docs.proof_number_checkbox"
-29.Enter Display Order, type, 10, "admin.deliveryservice.docs.display_order_input"
-30.Click Submit, click, , "web.global.action.submit"
-31.Verify Success, verify, , "web.global.toast.info"
-32.Filter Document List, type, {deliveryDocumentName}, "admin.deliveryservice.docs.grid.filter_input"
-33.wait, 2000, , ""
-34.Click Settings, click, , "admin.deliveryservice.settings.menu"
-35.Click Service Settings, click, , "admin.deliveryservice.submenu.service_settings"
-36.Enter Driver Search Radius, type, 50, "admin.deliveryservice.config.search_radius_input"
-37.Open Tax Type Dropdown, click, , "admin.deliveryservice.config.tax_type_dropdown"
-38.Select Amount, click, , "admin.deliveryservice.config.tax_type_option_amount"
-39.Enter Tax, type, 20, "admin.deliveryservice.config.tax_input"
-40.Open Platform Fee Type Dropdown, click, , "admin.deliveryservice.config.fee_type_dropdown"
-41.Select Amount, click, , "admin.deliveryservice.config.fee_type_option_amount"
-42.Enter Platform Fee, type, 20, "admin.deliveryservice.config.platform_fee_input"
-43.Enter Cancel Charge (in %):, type, 20, "admin.deliveryservice.config.cancel_charge_input"
-44.Enter Driver Accept Timeout (in Second):, type, 20, "admin.deliveryservice.config.driver_timeout_input"
-45.Click Submit, click, , "web.global.action.submit"
-46.Verify Success, verify, , "web.global.toast.info"
-47.Click Stores, click, , "admin.store.menu.toggle_btn"
-48.Select Add Store, click, , "admin.store.submenu.add_store"
-49.Verify Add Store, verify, , "admin.store.add_page.header"
-50.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "admin.store.name.input"
-51.Open Delivery Radius Dropdown, click, , "admin.store.radius.dropdown"
-52.Select Twenty Five Kilometer, click, , "admin.store.radius.option_25km"
-53.Open Estimated Delivery Time, click, , "admin.store.eta.dropdown"
-54.Select Thirty Minute, click, , "admin.store.eta.option_30min"
-55.Enter Order Minimum Amount, type, 300, "admin.store.min_amount.input"
-56.Enter Packaging Charges, type, 50, "admin.store.packaging_charge.input"
-57.Enter Short Description, type, amul taste of india, "admin.store.description.input"
-58.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "admin.store.banner.file"
-59.Open Driver Notification, click, , "admin.store.driver_notification.dropdown"
-60.Select Both Driver, click, , "admin.store.driver_notification.option_both"
-61.Click Checkbox Allow For Pickup, click, , "admin.store.allow_pickup.checkbox"
-62.Open Current Status Dropdown, click, , "admin.store.current_status.dropdown"
-63.Select Active, click, , "admin.store.current_status.option_active"
-64.Enter Store Address, type, Amul chennai, "admin.store.location.input"
-65.wait, 3000, , ""
-66.Confirm Store Address, press_enter, , "admin.store.location.input"
-67.wait, 3000, , ""
-68.Select First Option, arrow_down, , "admin.store.location.input"
-69.Confirm Option, press_enter, , "admin.store.location.input"
-70.wait, 2000, , ""
-71.Click Storewise Commission Checkbox, click, , "admin.store.commission.checkbox"
-72.Enter Store Commission, type, 25, "admin.store.commission_rate.input"
-73.Open Driver Notification, click, , "admin.store.offer_type.dropdown"
-74.Select Amount, click, , "admin.store.offer_type.option_amount"
-75.Enter Offer Amount, type, 50, "admin.store.offer_amount.input"
-76.Enter Offer Min Amount, type, 500, "admin.store.offer_min_amount.input"
-77.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "admin.store.contact_name.input"
-78.Enter Email, type, amul_{timestamp}@gmail.com &gt;&gt; storeEmail, "admin.store.email.input"
-79.Enter Contact Number, type, {randomPhone}, "admin.store.phone.input"
-80.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "admin.store.profile.file"
-81.Enter Bank Name, type, federal, "admin.store.bank.name_input"
-82.Enter Bank Location, type, chennai, "admin.store.bank.location_input"
-83.Enter Account Number, type, 123456789012, "admin.store.bank.account_input"
-84.Enter Account Holder Name, type, {milkStoreOwner}, "admin.store.bank.holder_input"
-85.Enter Payment Email Address, type, {storeEmail}, "admin.store.bank.payment_email"
-86.Enter BIC Code, type, 1234, "admin.store.bank.bic_input"
-87.Click Store Timing Checkbox, click, , "admin.store.timing.everyday_checkbox"
-88.Enter From Time, type, 100000AM, "admin.store.timing.from_input"
-89.Enter To Time, type, 100000PM, "admin.store.timing.to_input"
-90.Submit Add Store, click, , "web.global.action.submit"
-91.Verify Success Message, verify, , "web.global.toast.info"
-92.Click Stores, click, , "admin.store.menu.toggle_btn"
-93.Select Store List, click, , "admin.store.submenu.store_list"
-94.Verify Add Store, verify, , "admin.store.list_page.header"
-95.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-96.Click Stores, click, , "admin.store.menu.toggle_btn"
-97.Select Pending Documents Stores List, click, , "admin.store.submenu.pending_docs"
-98.Verify Add Store, verify, , "admin.store.pending_page.header"
-99.Filter Pending Document Store List, type, {milkStore}, "admin.store.grid.name_filter"
-100.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
-101.Click Doc Icon, click, , "admin.store.grid.doc_icon"
-102.Store Required Documents, verify, , "admin.store.documents_page.header"
-103.Add Address Proof, click, , "admin.store.grid.edit_doc_icon"
-104.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.store.doc.file_input"
-105.Enter Expiry Date, type, 2026-12-12, "admin.store.doc.expiry_input"
-106.Click Submit, click, , "web.global.action.submit"
-107.Verify Updated Successfully, verify, , "web.global.toast.updated"
-108.Click Approve Store, click, , "admin.store.grid.approve_doc_icon"
-109.Verify Updated Successfully, verify, , "web.global.toast.updated"
-110.Click Back, click, , "admin.store.grid.back_btn"
-111.Click Stores, click, , "admin.store.menu.toggle_btn"
-112.Select Store List, click, , "admin.store.submenu.store_list"
-113.Verify Add Store, verify, , "admin.store.list_page.header"
-114.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-115.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
-116.Click Doc Icon, click, , "admin.store.grid.doc_icon"
-117.wait for back button,wait,3000,
-118.Click Back, click, , "admin.store.grid.back_btn"
-119.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
-120.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
-121.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
-122.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
-123.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
-124.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
-125.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
-126.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
-127.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
-128.wait, 2000, , ""
-129.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
-130.Click Submit, click, , "web.global.action.submit"
-131.Verify Success Message, verify, , "web.global.toast.info"
-132.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
-133.Click Stores, click, , "admin.store.menu.toggle_btn"
-134.Select Store List, click, , "admin.store.submenu.store_list"
-135.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-136.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
-137.Click Product Icon, click, , "admin.store.products.grid_icon"
-138.Click Add Products, click, , "admin.store.products.add_btn"
-139.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
-140.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
-141.wait, 1000, ,""
-142.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-143.Click Delivery Services, click, , "admin.deliveryservice.menu"
-144.Verify Delivery Services, verify, , "admin.deliveryservice.header"
-145.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-146.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
-147.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
-148.wait, 1000, , ""
-149.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
-150.Click Submit, click, , "web.global.action.submit"
-151.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-152.wait, 1000, ,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Delivery Services,click,,"admin.provider_service.menu_link"
-3.Verify Delivery Services,verify,,"admin.provider_service.on_demand_header"
-4.Filter service List,type,Plumbers,"admin.provider_service.services.filter.input"
-5.Click Home Icon Plumbers,click,,"admin.provider_service.services.home.icon_by_row_plumbers"
-6.Verify Plumbers Summary,verify,,"admin.provider_service.services.plumbers_summary.header"
-7.Click Providers,click,,"admin.provider_service.providers.root.button"
-8.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
-9.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
-10.Enter Provider Full Name, type, Plumber{randomAlpha}&gt;&gt; plumberName, "admin.provider_service.provider_form.fullname.input"
-11.Upload Plumber Image, uploadfile, "src/main/resources/test-data/plumber.jpg", "admin.provider_service.provider_form.avatar.file"
-12.Enter Email, type, Plumber_{timestamp}@gmail.com&gt;&gt;plumberEmail, "admin.provider_service.provider_form.email.input"
-13.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
-14.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
-15.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
-16.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
-17.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
-18.Enter Provider Address, type, plumber chennai, "admin.provider_service.provider_form.address.input"
-19.wait,1000,,
-20.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
-21.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
-22.wait,1000,,
-23.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
-24.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
-25.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
-26.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
-27.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
-28.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
-29.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
-30.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
-31.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
-32.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
-33.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
-34.Enter Account Holder Name, type, {plumberName}, "admin.provider_service.provider_form.account_holder.input"
-35.Enter Payment Email Address, type, {plumberEmail}, "admin.provider_service.provider_form.payment_email.input"
-36.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
-37.Click Save, click, , "web.global.login.submit_btn"
-38.Verify Sucess, verify, , "web.global.toast.info"
-39.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-40.Click Providers,click,,"admin.provider_service.providers.root.button"
-41.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
-42.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-43.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
-44.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
-45.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
-46.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
-47.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
-48.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
-49.Click Submit, click, , "web.global.action.submit"
-50.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-51.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
-52.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
-53.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-54.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-55.Click Providers,click,,"admin.provider_service.providers.root.button"
-56.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
-57.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
-58.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-59.Click Doc Icon,click,,"admin.provider_service.providers.grid.document.icon"
-60.Click Eye Icon,click,,"admin.provider_service.providers.grid.view_eye.icon"
-61.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-62.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
-63.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-64.Scroll Grid, tab, 11, "admin.provider_service.providers.grid.name_filter"
-65.Click Wallet Icon,click,,"admin.provider_service.providers.grid.wallet.icon"
-66.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
-67.Enter Wallet Amount, type, 1000, "admin.provider_service.wallet.amount.input"
-68.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
-69.Select Add Money,click, , "admin.provider_service.wallet.options.add_money"
-70.Click Submit, click, , "web.global.action.submit"
-71.Verify Saved Succesfully, verify, , "web.global.toast.success"
-72.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
-73.Enter Wallet Amount, type, 200, "admin.provider_service.wallet.amount.input"
-74.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
-75.Select Deduct Money,click, , "admin.provider_service.wallet.options.deduct_money"
-76.Click Submit, click, , "web.global.action.submit"
-77.Verify Saved Succesfully, verify, , "web.global.toast.success"
-78.Click Back, click, , "admin.provider_service.global.action.back_normal_btn"
-79.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-80.Click Doc Icon,click, , "admin.provider_service.providers.grid.document.icon"
-81.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
-82.Click Reject Document,click, , "admin.provider_service.provider_docs.reject.icon"
-83.Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
-84.Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
-85..Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
-86.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-87.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-88.Scroll Grid, tab, 13, "admin.provider_service.providers.grid.name_filter"
-89.Click Block Provider,click, , "admin.provider_service.providers.grid.block.icon"
-90.Click Block Yes,click, , "web.global.dialog.btn_confirm_yes"
-91.Blocking Reason,type,customer complaints,"web.global.dialog.textarea_reason"
-92.Click block Yes,click, , "web.global.dialog.btn_confirm_yes"
-93.Click Providers,click, , "admin.provider_service.providers.root.button"
-94.Select Blocked Providers,click, , "admin.provider_service.providers.blocked_list.menu"
-95.Verify Blocked Provider,verify, , "admin.provider_service.providers.grid.blocked_plumbers.header"
-96.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-97.Scroll Grid, tab, 12, "admin.provider_service.providers.grid.name_filter"
-98.Click Unblock Provider,click, , "admin.provider_service.providers.grid.unblock.icon"
-99.Click Providers,click, , "admin.provider_service.providers.root.button"
-100.Select Provider List,click, , "admin.provider_service.providers.provider_list.menu"
-101.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-102.wait,1000,,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Provider Services,click,,"admin.provider_service.menu_link"
-3.Verify Provider Services,verify,,"admin.provider_service.on_demand_header"
-4.Click Add New Services,click,,"admin.provider_service.services.add_new.btn"
-5.Enter Service Name, type, Painter{randomAlpha}&gt;&gt; serviceName, "admin.provider_service.services.name.input"
-6.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
-7.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
-8.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
-9.Enter Slug, type, painter, "admin.provider_service.services.slug.input"
-10.Upload Service Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.services.image.file"
-11.wait,2000,,
-12.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
-13.Select Activate,click,,"admin.provider_service.services.status.option_activate"
-14.Open Select City Dropdown,click,,"admin.provider_service.services.city.dropdown"
-15.Select {areaName},click,,"admin.provider_service.services.city.option_dynamic"
-16.Click Submit,click,,"web.global.action.submit"
-17.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
-18.Click Home Icon ,click,,"admin.provider_service.services.home.icon"
-19.Click Settings ,click,,"admin.provider_service.settings.menu.button"
-20.Click Requirment Document ,click,,"admin.provider_service.settings.req_document.tab"
-21.Click Add Document ,click,,"admin.provider_service.req_docs.add.btn"
-22.Enter Name, type, documet{randomAlpha}&gt;&gt; providerDocumentName, "admin.provider_service.req_docs.name.input"
-23.Open status Dropdown,click,,"admin.provider_service.req_docs.status.dropdown"
-24.Select Active,click,,"admin.provider_service.req_docs.status.option_active"
-25.Click Document Expiry ,click,,"admin.provider_service.req_docs.expiry_toggle"
-26.Click Mandatory Document ,click,,"admin.provider_service.req_docs.mandatory_toggle"
-27.Click Submit ,click,,"web.global.action.submit"
-28.Verify Sucess, verify, , "web.global.toast.info"
-29.Filter Document List,type,{providerDocumentName},"admin.provider_service.req_docs.filter.input"
-30.Click Settings ,click,,"admin.provider_service.settings.menu.button"
-31.Click Promocode ,click,,"admin.provider_service.settings.promocode.tab"
-32.Click Add Promo Code ,click,,"admin.provider_service.promocode.add.btn"
-33.Open User List Dropdown,click,,"admin.provider_service.promocode.user_list.dropdown"
-34.Select User,click,,"admin.provider_service.promocode.user_list.option_dynamic"
-35.Click Code Name Box,click,,"admin.provider_service.promocode.code_name.box"
-36.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; providerPromoCodeName, "admin.provider_service.promocode.code_name.box"
-37.Open Discout Type Dropdown,click,,"admin.provider_service.promocode.discount_type.dropdown"
-38.Select Discout Type,click,,"admin.provider_service.promocode.discount_type.option_amount"
-39.Enter Expiry Date,type,12122026,"admin.provider_service.promocode.expiry_date.input"
-40.Enter Discount Amount, type, 100, "admin.provider_service.promocode.discount_amount.input"
-41.Enter Minimum Order Amount, type, 1000, "admin.provider_service.promocode.min_order_amount.input"
-42.Enter Maximum Discount Amount, type, 100, "admin.provider_service.promocode.max_discount.input"
-43.Enter Coupon Limit, type, 5,"admin.provider_service.promocode.coupon_limit.input"
-44.Enter Usage Limit for One User, type, 2,"admin.provider_service.promocode.usage_limit_per_user.input"
-45.Enter Promo Code Description, type, Promo Dode For Gold Member,"admin.provider_service.promocode.description.textarea"
-46.Click Submit ,click,,"web.global.action.submit"
-47.Verify Sucess, verify, , "web.global.toast.info"
-48.Filter PromoCode List,type,{providerPromoCodeName},"admin.provider_service.promocode.filter.input"
-49.Click Providers,click,,"admin.provider_service.providers.root.button"
-50.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
-51.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
-52.Enter Provider Full Name, type, Painter{randomAlpha}&gt;&gt; painterName, "admin.provider_service.provider_form.fullname.input"
-53.Upload Painter Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.provider_form.avatar.file"
-54.Enter Email, type, Painter_{timestamp}@gmail.com&gt;&gt;painterEmail, "admin.provider_service.provider_form.email.input"
-55.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
-56.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
-57.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
-58.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
-59.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
-60.Enter Provider Address, type, painter chennai, "admin.provider_service.provider_form.address.input"
-61.wait,1000,,
-62.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
-63.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
-64.wait,1000,,
-65.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
-66.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
-67.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
-68.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
-69.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
-70.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
-71.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
-72.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
-73.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
-74.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
-75.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
-76.Enter Accont Holder Name, type, {painterName}, "admin.provider_service.provider_form.account_holder.input"
-77.Enter Payment Email Address, type, {painterEmail}, "admin.provider_service.provider_form.payment_email.input"
-78.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
-79.Click Save, click, , "web.global.login.submit_btn"
-80.Verify Sucess, verify, , "web.global.toast.info"
-81.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
-82.Click Providers,click,,"admin.provider_service.providers.root.button"
-83.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
-84.Filter Plumber List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
-85.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
-86.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
-87.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
-88.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
-89.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
-90.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
-91.Click Submit, click, , "web.global.action.submit"
-92.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-93.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
-94.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
-95.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-96.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-97.Click Providers,click,,"admin.provider_service.products.menu_category_btn"
-98.Click Add New Category,click,,"admin.provider_service.category.add_new.btn"
-99.Enter Category Name, type,residentialPainter{randomAlpha}&gt;&gt; painterCategoryName, "admin.provider_service.category.name.input"
-100.Enter Category Name Tamil, type, குடியிருப்பு பெயிண்டர், "admin.provider_service.category.name_tamil.input"
-101.Enter Category Name Arabic, type, دهان سكني, "admin.provider_service.category.name_arabic.input"
-102.Enter Category Name Hindi, type, आवासीय पेंटर, "admin.provider_service.category.name_hindi.input"
-103.Open Category status Dropdown,click,,"admin.provider_service.category.status.dropdown"
-104.Select Activate,click,,"admin.provider_service.category.status.option_active"
-105.Upload Category Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.category.image.file"
-106.wait,2000,,
-107.Click Submit,click,,"web.global.action.submit"
-108.Filter Category Name,type,{painterCategoryName},"admin.provider_service.category.filter.input"
-109.Click Providers,click,,"admin.provider_service.providers.root.button"
-110.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
-111.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
-112.Scroll Grid, tab, 7, "admin.provider_service.providers.grid.name_filter"
-113.Click Package Icon,click,,"admin.provider_service.packages.icon"
-114.Click Add Package,click,,"admin.provider_service.packages.add_new.btn"
-115.Open Category Dropdown,click,,"admin.provider_service.packages.category.dropdown"
-116.Select Activate,click,,"admin.provider_service.packages.category.option_dynamic"
-117.Enter Package Name, type, package{randomAlpha}&gt;&gt; packageName, "admin.provider_service.packages.name.input"
-118.Enter Amount, type, 1000, "admin.provider_service.packages.amount.input"
-119.Open Max Book Quantity Dropdown,click,,"admin.provider_service.packages.max_book_qty.dropdown"
-120.Select 4,click,,"admin.provider_service.packages.max_book_qty.option_4"
-121.Open Status Dropdown,click,,"admin.provider_service.packages.status.dropdown"
-122.Select Activate,click,,"admin.provider_service.packages.status.option_activate"
-123.Enter Description, type, Premium residential painting package, "admin.provider_service.packages.description.textarea"
-124.Click Submit,click,,"web.global.action.submit"
-125.wait,1000,,
-126.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
-127.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-128.Click Delivery Services,click,,"admin.provider_service.menu_link"
-129.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
-130.Click Edit Icon ,click,,"admin.provider_service.services.edit.icon"
-131.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
-132.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
-133.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
-134.Scroll Grid, tab, 4, "admin.provider_service.services.name_hindi.input"
-135.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
-136.Select Deactivate,click,,"admin.provider_service.services.status.option_deactivate"
-137.Click Submit,click,,"web.global.action.submit"
-138.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
-139. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-140.Click badge,click,,"admin.provider_service.badge.icon"
-141.Click provider Services,click,,"admin.provider_service.menu_link"
-142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
-143.wait,1000,,</t>
-  </si>
-  <si>
-    <t>TC_CA_16_Panic_Call_Test</t>
-  </si>
-  <si>
-    <t>Verify the complete lifecycle of a panic call configuration—including creation with multilingual names (English, Tamil, Hindi), searching, updating its status to inactive, and successful deletion.</t>
-  </si>
-  <si>
-    <t>Panic Call Test</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
-2.Click Setting,click,,"admin.setting.sidebar.menu"
-3.Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
-4.Click Add panic call button,click,,"admin.setting.panic_call.add_btn"
-5.Enter name,type,police_{randomAlpha}&gt;&gt;policeName,"admin.setting.panic_call.name_input"
-6.Enter name in tamil,type,காவல்துறை,"admin.setting.panic_call.tamil_name_input"
-7.Enter name in hindi,type,पुलिस,"admin.setting.panic_call.hindi_name_input"
-8.Contact number,type,{randomPhone},"admin.setting.panic_call.contact_number"
-9.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
-10.Select Active status,click,,"admin.setting.panic_call.activate_status_dropdown"
-11.Submit button,click,,"web.global.action.submit"
-12.Search name,type,{policeName},"admin.setting.panic_call.search_name"
-13.Click Edit Button,click,,"admin.setting.panic_call.edit_btn"
-14.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
-15.Select Deactive status button,click,,"admin.setting.panic_call.deactivate_status_dropdown"
-16.Click Submit button,click,,"web.global.action.submit"
-17.Click Delete button,click,,"admin.setting.panic_call.delete_btn"
-18.Click Yes delete it button,click,,"admin.setting.panic_call.confirm_delete_btn"</t>
-  </si>
-  <si>
-    <t>SA_TS_17</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Customer Icon,click,,"admin.menu.customer_icon"
-3. Click Add Customers,click,,"admin.menu.add_customers"
-4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
-5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
-6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
-7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
-8.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
-9. Open Gender,click,,"admin.customer.dropdown_gender"
-10. Select Male,click,,"admin.customer.select_gender_male"
-11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
-12. Click Submit,click,,"web.global.action.submit"
-13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-14. Click Dashboard,click,,"web.global.menu.dashboard"
-15. Click Customer Icon,click,,"admin.menu.customer_icon"
-16. Click Verified Customers,click,,"admin.menu.verified_customers"
-17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-19. Scroll Grid,tab,7,"admin.customer.filter_name"
-20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
-21. Click Close,click,,"web.global.action.close"
-22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
-23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
-25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
-27. Click Submit,click,,"web.global.action.submit"
-28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
-31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
-33. Click Submit,click,,"web.global.action.submit"
-34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-35. Click dashboard Icon,click,,"web.global.menu.dashboard"
-36. Click Customer Icon,click,,"admin.menu.customer_icon"
-37. Click Verified Customers,click,,"admin.menu.verified_customers"
-38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-40. Scroll Grid,tab,7,"admin.customer.filter_name"
-41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
-42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-44. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
-47. Enter Points,type,30,"admin.customer.loyalty.input_points"
-48. Click Submit,click,,"web.global.action.submit"
-49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-52. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
-55. Enter Points,type,10,"admin.customer.loyalty.input_points"
-56. Click Submit,click,,"web.global.action.submit"
-57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-59. Click Customer Icon,click,,"admin.menu.customer_icon"
-60. Click Verified Customers,click,,"admin.menu.verified_customers"
-61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-63. Scroll Grid,tab,7,"admin.customer.filter_name"
-64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
-65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
-66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
-67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-68. Verify Added Successfully,verify,,"web.global.toast.info"
-69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-70. Click Customer Icon,click,,"admin.menu.customer_icon"
-71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
-72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-73. Scroll Grid,tab,10,"admin.customer.filter_name"
-74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
-75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
-76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
-77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-78. Click Customer Icon,click,,"admin.menu.customer_icon"
-79. Click Verified Customers,click,,"admin.menu.verified_customers"
-80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
-  </si>
-  <si>
-    <t>Dashboard Test</t>
-  </si>
-  <si>
-    <t>TC_CA_17_Dashboard_Test</t>
-  </si>
-  <si>
-    <t>1.Click Today Button,Click,,"web.global.dashboard.today_statistics"
-2.Click Search Button,Click,,"web.global.dashboard.search_btn"
-3.Wait For Today Statistics,wait,2000,
-4.Click Clear Button,click,,"web.global.dashboard.clear_btn"
-5.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-6.Click Search Button,Click,,"web.global.dashboard.search_btn"
-7.Wait For Yesterday Statistics,wait,2000,
-8.Click Clear Button,click,,"web.global.dashboard.clear_btn"
-9.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-10.Click Search Button,Click,,"web.global.dashboard.search_btn"
-11.Wait For This Week Statistics,wait,2000,
-12.Click Clear Button,click,,"web.global.dashboard.clear_btn"
-13.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-14.Click Search Button,Click,,"web.global.dashboard.search_btn"
-15.Wait For This Month Statistics,wait,2000,
-16.Click Clear Button,click,,"web.global.dashboard.clear_btn"
-17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-18.Click Search Button,Click,,"web.global.dashboard.search_btn"
-19.Wait For Last Month Statistics,wait,2000,
-20.Click Clear Button,click,,"web.global.dashboard.clear_btn"
-21.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-22.Click Search Button,Click,,"web.global.dashboard.search_btn"
-23.Wait For This Year Statistics,wait,2000,
-24.Click Clear Button,click,,"web.global.dashboard.clear_btn"
-25.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-26.Click Search Button,Click,,"web.global.dashboard.search_btn"
-27.Wait For Last Year Statistics,wait,2000,
-28.Click Clear Button,click,,"web.global.dashboard.clear_btn"</t>
-  </si>
-  <si>
-    <t>This test suite validates the dynamic filtering and search functionality of the global dashboard dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
-  </si>
-  <si>
-    <t>SA_TS_18</t>
-  </si>
-  <si>
-    <t>Tranport Service Statistic Test</t>
-  </si>
-  <si>
-    <t>TC_CA_18_Tranport_Service_Statistic_Test</t>
-  </si>
-  <si>
-    <t>This test suite validates the dynamic filtering and search functionality of the transport Serivice dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Transports Services Menu,click,, "admin.transport.menu.card"
-3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
-4.Click Home Icon ,click,, "admin.transport.home.icon"
-5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
-6.Click Search Button,Click,,"web.global.dashboard.search_btn"
-7.wait For Today Statistics,wait,2000,
-8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-9.Click Search Button,Click,,"web.global.dashboard.search_btn"
-10.wait For Yesterday Statistics,wait,2000,
-11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-12.Click Search Button,Click,,"web.global.dashboard.search_btn"
-13.wait For This Week Statistics,wait,2000,
-14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-15.Click Search Button,Click,,"web.global.dashboard.search_btn"
-16.wait For This Month Statistics,wait,2000,
-17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-18.Click Search Button,Click,,"web.global.dashboard.search_btn"
-19.wait For Last Month Statistics,wait,2000,
-20.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-21.Click Search Button,Click,,"web.global.dashboard.search_btn"
-22.wait For This Year Statistics,wait,2000,
-23.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-24.Click Search Button,Click,,"web.global.dashboard.search_btn"
-25.wait For Last Year Statistics,wait,2000,</t>
-  </si>
-  <si>
-    <t>SA_TS_19</t>
-  </si>
-  <si>
-    <t>This test suite validates the dynamic filtering and search functionality of the transport Serivice driver dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
-  </si>
-  <si>
-    <t>Tranport Driver Statistic Test</t>
-  </si>
-  <si>
-    <t>TC_CA_19_Tranport_Driver_Statistic_Test</t>
-  </si>
-  <si>
-    <t>SA_TS_20</t>
-  </si>
-  <si>
-    <t>Transport Service Ride Tests</t>
-  </si>
-  <si>
-    <t>TC_CA_20_Transport_Service_Ride_Test</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Transports Services Menu,click,, "admin.transport.menu.card"
-3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
-4.Click Drivers Icon,Click,,"admin.transport.driver.icon"
-5.Wait For Load,wait,2000,
-6.Click Today Button,Click,,"web.global.dashboard.today_statistics"
-7.Click Search Button,Click,,"web.global.dashboard.search_btn"
-8.wait For Today Statistics,wait,2000,
-9.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-10.Click Search Button,Click,,"web.global.dashboard.search_btn"
-11.wait For Yesterday Statistics,wait,2000,
-12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-13.Click Search Button,Click,,"web.global.dashboard.search_btn"
-14.wait For This Week Statistics,wait,2000,
-15.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-16.Click Search Button,Click,,"web.global.dashboard.search_btn"
-17.wait For This Month Statistics,wait,2000,
-18.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-19.Click Search Button,Click,,"web.global.dashboard.search_btn"
-20.wait For Last Month Statistics,wait,2000,
-21.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-22.Click Search Button,Click,,"web.global.dashboard.search_btn"
-23.wait For Last Year Statistics,wait,2000,
-24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-25.Click Search Button,Click,,"web.global.dashboard.search_btn"
-26.wait For This Year Statistics,wait,2000,
-27.Click Select Driver Dropdown,Click,,"admin.drivers.approved_driver.driver_dropdown"
-28.Enter Name In Drop Down,type,regression.approved_driver.name,"admin.drivers.approved_driver.driver_dropdown_searchbox"
-29.Click Driver Name,Click,,"admin.drivers.approved_driver.driver_dropdown_first"
-30.Click Vehicle Type Dropdown,Click,,"admin.drivers.approved_driver.vehicle_dropdown"
-31.Enter Vehicle Name,type,pink Auto,"admin.drivers.approved_driver.driver_dropdown_searchbox"
-32.Click Vehicle Name,click,,"admin.drivers.approved_driver.vehicle_dropdown_first"
-33.Click Service Dropdown,click,,"admin.drivers.approved_driver.service_dropdown"
-34.Select Service,type,Auto Ride,"admin.drivers.approved_driver.driver_dropdown_searchbox"
-35.Click Service Option,click,,"admin.drivers.approved_driver.service_dropdown_first"
-36.Click Search Button,Click,,"web.global.dashboard.search_btn"
-37.wait for Approved Driver Filtering,wait,3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Transports Services Menu,click,, "admin.transport.menu.card"
-3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
-4.Click Ride Button,click,,"admin.transport.rides.icon"
-5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
-6.Click Search Button,Click,,"admin.transport.search_btn"
-7.wait For Today Statistics,wait,2000,
-8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-9.Click Search Button,Click,,"admin.transport.search_btn"
-10.wait For Yesterday Statistics,wait,2000,
-11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-12.Click Search Button,Click,,"admin.transport.search_btn"
-13.wait For This Week Statistics,wait,2000,
-14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-15.Click Search Button,Click,,"admin.transport.search_btn"
-16.wait For This Month Statistics,wait,2000,
-17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-18.Click Search Button,Click,,"admin.transport.search_btn"
-19.wait For Last Month Statistics,wait,2000,
-20.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-21.Click Search Button,Click,,"admin.transport.search_btn"
-22.wait For Last Year Statistics,wait,2000,
-23.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-24.Click Search Button,Click,,"admin.transport.search_btn"
-25.wait For This Year Statistics,wait,2000,
-26.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
-27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
-28.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
-29.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
-30.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
-31.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
-32.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
-33.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
-34.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
-35.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-36.Enter Status Type In Drop Down,type,Completed Rides,"admin.transport.status_type_dropdown_searchbox"
-37.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-38.Click Search Button,click,,"admin.transport.search_btn"
-39.Click Status Filter Input,click,,"admin.transport.status_filter_input"
-40.Enter Status,type,complete,"admin.transport.status_filter_input"
-41.Click Chat Box,click,,"admin.transport.chat_box.icon"
-42.Wait For Chat,wait,2000,
-43.Close Chat,click,,"admin.transport.rides.messages_close.btn"
-44.Click Ride Detail Button,click,,"admin.transport.ride_details.icon" 
-45.Wait For Ride Detail,wait,2000
-46.Show Ride Details,click,,"admin.transport.ride_details.arrival_time_box"
-47.Wait For Ride Detail,wait,2000
-48.Click Back Button,click,,"admin.transport.ride_details.back_btn"
-49.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
-50.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
-51.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
-52.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
-53.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
-54.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
-55.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
-56.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
-57.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
-58.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-59.Enter Status Type In Drop Down,type,Incomplete Rides,"admin.transport.status_type_dropdown_searchbox"
-60.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-61.Click Search Button,click,,"admin.transport.search_btn"
-62.Wait For Incomplete Rides,wait,2000,
-63.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
-64.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-65.Enter Status Type In Drop Down,type,Cancelled Rides,"admin.transport.status_type_dropdown_searchbox"
-66.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-67.Click Search Button,click,,"admin.transport.search_btn"
-68.Wait For Cancelled Rides,wait,2000,
-69.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
-70.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-71.Enter Status Type In Drop Down,type,Scheduled Rides,"admin.transport.status_type_dropdown_searchbox"
-72.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-73.Click Search Button,click,,"admin.transport.search_btn"
-74.Wait For Scheduled Rides,wait,2000,
-75.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
-76.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-77.Enter Status Type In Drop Down,type,Pre-Acceptance Cancel Rides,"admin.transport.status_type_dropdown_searchbox"
-78.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-79.Click Search Button,click,,"admin.transport.search_btn"
-80.Wait For Pre-Acceptance Cancel Rides,wait,2000,
-</t>
-  </si>
-  <si>
-    <t>SA_TS_21</t>
-  </si>
-  <si>
-    <t>TC_CA_21_test_data_cleanup</t>
-  </si>
-  <si>
-    <t>This end-to-end regression test suite thoroughly validates the data filtering, search capabilities, and transaction monitoring matrices within the Transport Services administration panel. The test starts by targeting a specific vehicle class ("Auto Ride") and systematically loops through chronological milestone filters—ranging from Today to Last Year—to verify date-partitioned metrics rendering. It then transitions to a complex granular query verification phase by isolating discrete parameters across multiple dependent dropdown elements, including specific customer names, registered driver profiles, vehicle types ("Pink Auto"), and ride lifecycles (Completed, Incomplete, Cancelled, Scheduled, and Pre-Acceptance Cancel Rides). Additionally, the script tests contextual UI elements by verifying the operational initialization of intra-ride chat boxes and auditing specialized tracking panels, such as arrival time breakdowns and deep-dive ride detail metrics grids, ensuring robust data reporting with zero caching conflicts across state changes.</t>
+166.Edit Service Name,type,Bus Ride{randomAlpha}&gt;&gt;editedTransportName,"admin.transport.name.input"
+167.Edit Slug,type,bus ride123,"admin.transport.slug.input"
+168.Open status Dropdown,click,, "admin.transport.status.dropdown"
+169.Select Deactivate,click,, "admin.transport.status.deactivate_option"
+170.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
+171.Select {areaName},click,, "admin.transport.city.dynamic_option"
+172.Click  Submit,click,, "web.global.action.submit"
+173.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+174.wait,2000,,</t>
+  </si>
+  <si>
+    <t>1.Remove Test Area,sql delete,,"DELETE FROM we1.admin_area_list WHERE name = '{areaName}';"
+2.Remove Customer,sql delete,,"DELETE FROM we1.users WHERE first_name = '{customerName}';"
+3.Remove City Admin,sql delete,,"DELETE FROM we1.super_admin WHERE name = '{adminName}';"
+4.Remove Auto Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{autoName}';"
+5.Remove Auto Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{autoName}';"
+6.Remove Auto Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{autoCompanyName}';"
+7.Remove Bike Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{bikeName}';"
+8.Remove Bike Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{bikeName}';"
+9.Remove Bike Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{bikeCompanyName}';"
+10.Remove Taxi Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{taxiName}';"
+11.Remove Taxi Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{taxiName}';"
+12.Remove Taxi Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{taxiCompanyName}';"
+13.Remove Bus Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{busDriverName}';"
+14.Remove Bus Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{busDriverName}';"
+15.Remove Bus Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{busCompanyName}';"
+16.Remove Bus Driver Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{documentName}';"
+17.Remove Transport Service PromoCode,sql delete,,"DELETE FROM we1.promocode_details WHERE promo_code = '{promoCodeName}';"
+18.Remove Bus Vehicle Variation Volvo,sql delete,,"DELETE FROM we1.transport_vehicle_type WHERE name = '{busTypeName}';"
+19.Remove  Transport Ride,sql delete,,"DELETE FROM we1.service_category WHERE name = '{editedTransportName}';"
+20.Remove Kfc Private Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{kfcdriverName}';"
+21.Remove Kfc Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{kfcBikeCompanyName}';"
+22.Remove Kfc Product Details,sql delete,,"DELETE FROM we1.store_product_details WHERE name = '{kfcProductName}';"
+23.Remove Kfc Owner Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{storeOwner}';"
+24.Remove Kfc Owner From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{storeOwner}';"
+25.Remove Kfc Store Details,sql delete,,"DELETE FROM we1.store_details WHERE name = '{storeName}';"
+26.Remove Bilal Owner Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{hotelOwner}';"
+27.Remove Bilal Owner From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{hotelOwner}';"
+28.Remove Bilal Store Details,sql delete,,"DELETE FROM we1.store_details WHERE name = '{hotelName}';"
+29.Remove Amul Owner Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{milkStoreOwner}';"
+30.Remove Amul Owner From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{milkStoreOwner}';"
+31.Remove Amul Store Details,sql delete,,"DELETE FROM we1.store_details WHERE name = '{milkStore}';"
+32.Remove Curd Product Category,sql delete,,"DELETE FROM we1.store_product_category WHERE name = '{MilkCategoryName}';"
+33.Remove Delievery Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{deliveryDocumentName}';"
+34.Remove Delievery Service PromoCode,sql delete,,"DELETE FROM we1.promocode_details WHERE promo_code = '{deliveryPromoCodeName}';"
+35.Remove  Deleivrey Service,sql delete,,"DELETE FROM we1.service_category WHERE name = '{deliveryName}';"
+36.Remove Plumber Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{plumberName}';"
+37.Remove Plumber Provider Details,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{plumberName}';"
+38.Remove Painter Package,sql delete,,"DELETE FROM we1.other_service_provider_packages WHERE name = '{packageName}';"
+39.Remove Painter Sub Category,sql delete,,"DELETE FROM we1.other_service_sub_category WHERE name = '{painterCategoryName}';"
+40.Remove Provider Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{providerDocumentName}';"
+41.Remove Provider Service PromoCode,sql delete,,"DELETE FROM we1.promocode_details WHERE promo_code = '{providerPromoCodeName}';"
+42.Remove Painter Bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{painterName}';"
+43.Remove Painter From Providers,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{painterName}';"
+44.Remove Provider Service,sql delete,,"DELETE FROM we1.service_category WHERE name = '{serviceName}';"
+45.Remove Lorry Driver,sql delete,,"DELETE FROM we1.providers WHERE first_name = '{lorrydriverName}';"
+46.Remove Bus Driver bank Details,sql delete,,"DELETE FROM we1.provider_bank_details WHERE holder_name = '{lorrydriverName}';"
+47.Remove Lorry Vehicle Details,sql delete,,"DELETE FROM we1.transport_driver_details WHERE vehicle_company = '{lorrycompanyName}';"
+48.Remove Lorry Vehicle Variation tempo,sql delete,,"DELETE FROM we1.transport_vehicle_type WHERE name = '{lorryTypeName}';"
+49.Remove  Transport Ride,sql delete,,"DELETE FROM we1.service_category WHERE name = '{lorryTransportName}';"
+50.Remove Transport City Admin,sql delete,,"DELETE FROM we1.super_admin WHERE name = '{transAdminName}';"
+51.wait,2000,,</t>
+  </si>
+  <si>
+    <t>SA_RD_01</t>
+  </si>
+  <si>
+    <t>SA_RD_21
+SA_RD_22
+SA_RD_23
+SA_RD_24</t>
+  </si>
+  <si>
+    <t>SA_RD_56</t>
+  </si>
+  <si>
+    <t>SA_RD_64</t>
+  </si>
+  <si>
+    <t>SA_RD_26
+SA_RD_27
+SA_RD_28</t>
+  </si>
+  <si>
+    <t>SA_TS_09</t>
+  </si>
+  <si>
+    <t>TC_CA_09_Tranport_Service_Statistic_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_10_Tranport_Driver_Statistic_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_11_Transport_Service_Ride_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_12_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>TC_CA_13_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_14_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_15_add_store</t>
+  </si>
+  <si>
+    <t>TC_CA_16_store_oprerations</t>
+  </si>
+  <si>
+    <t>TC_CA_17_store_status_management</t>
+  </si>
+  <si>
+    <t>TC_CA_18_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_CA_19_add_provider</t>
+  </si>
+  <si>
+    <t>TC_CA_20_provider_service_full_lifecycle_test</t>
   </si>
 </sst>
 </file>
@@ -3995,22 +3992,22 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4029,6 +4026,438 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FEA58B-ACBB-4068-8C66-F4A14C3E8CAE}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04AC2C5-FB17-478C-B9F4-6CCC13A451B0}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55FCD48-3B50-4EDD-B265-9AB60F809D78}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4070,22 +4499,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4100,7 +4529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4142,22 +4571,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4172,7 +4601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4214,22 +4643,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4244,7 +4673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4279,468 +4708,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FEA58B-ACBB-4068-8C66-F4A14C3E8CAE}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4790,33 +4787,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
+      <c r="A2" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4835,7 +4832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04AC2C5-FB17-478C-B9F4-6CCC13A451B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4876,22 +4873,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>136</v>
+        <v>111</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4907,7 +4904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55FCD48-3B50-4EDD-B265-9AB60F809D78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4948,22 +4945,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5020,22 +5017,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5095,22 +5092,22 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5162,7 +5159,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5170,25 +5167,25 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5230,33 +5227,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
+      <c r="A2" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5305,33 +5302,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
+      <c r="A2" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5380,33 +5377,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>26</v>
+      <c r="A2" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5455,33 +5452,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
+      <c r="A2" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5539,22 +5536,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CD1B2E-433C-4905-B32A-49654B080792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478306CE-18DC-4A19-A861-631FCDFB7C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E09C16-5673-4917-BAF0-BB9DBF048673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187C733B-455F-4454-993D-10A1E6145C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -28,16 +28,21 @@
     <sheet name="TransportServiceAerialView" sheetId="54" r:id="rId13"/>
     <sheet name="TransportServiceEarningReports" sheetId="55" r:id="rId14"/>
     <sheet name="TransportProviderLists" sheetId="56" r:id="rId15"/>
-    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId16"/>
-    <sheet name="PanicCallTest" sheetId="49" r:id="rId17"/>
-    <sheet name="DashboardTest" sheetId="50" r:id="rId18"/>
-    <sheet name="AddStore" sheetId="40" r:id="rId19"/>
-    <sheet name="StoreOperations" sheetId="42" r:id="rId20"/>
-    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId21"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId22"/>
-    <sheet name="AddProvider" sheetId="45" r:id="rId23"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId24"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId25"/>
+    <sheet name="TransportServiceReview" sheetId="57" r:id="rId16"/>
+    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId17"/>
+    <sheet name="GeoFencingTest" sheetId="62" r:id="rId18"/>
+    <sheet name="PanicCallTest" sheetId="49" r:id="rId19"/>
+    <sheet name="DashboardTest" sheetId="50" r:id="rId20"/>
+    <sheet name="ReportIssueFaqs" sheetId="58" r:id="rId21"/>
+    <sheet name="CustomerReportIssues" sheetId="60" r:id="rId22"/>
+    <sheet name="DriverReportIssues" sheetId="61" r:id="rId23"/>
+    <sheet name="AddStore" sheetId="40" r:id="rId24"/>
+    <sheet name="StoreOperations" sheetId="42" r:id="rId25"/>
+    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId26"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId27"/>
+    <sheet name="AddProvider" sheetId="45" r:id="rId28"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId29"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId30"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -49,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="184">
   <si>
     <t>City Area</t>
   </si>
@@ -1528,354 +1533,6 @@
 118.Enter Loyalty points per default currency (for ex. $1 = 10 points), type, 5, "admin.transport.loyalty.ratio.input"
 119.Click Submit ,click,, "web.global.action.submit"
 120.Wait For Sucess, wait_until_visible, , "web.global.toast.info"</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click drivers menu,click,,"admin.drivers.menu.icon"
-3. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
-4. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
-5.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
-6.Select Auto Ride Option,click,,"admin.drivers.service_dropdown.auto_ride"
-7. Enter Driver Name,type,autodriver{randomAlpha} &gt;&gt; autoName,"admin.drivers.fullname.input"
-8. Enter Email,type,autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail,"admin.drivers.email.input"
-9.Enter Contact Number,type,{randomPhone}&gt;&gt;autoPhone,"admin.drivers.phone.input"
-10.Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
-11.Enter Whatspp Number,type,{autoPhone},"admin.drivers.whatsapp_phone.input"
-12.Upload Profile Image,uploadfile,"src/main/resources/test-data/autodriver.jpg","admin.drivers.profile_image.file"
-13.Select Source,click,,"admin.drivers.source_dropdown.select"
-14.Select Instagram,click,,"admin.drivers.instagram_option.span"
-15.Select Male Gender,click,,"admin.drivers.male_gender.div"
-16.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
-17.Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
-18. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
-19.Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
-20.Enter Model Name,type,petrol,"admin.drivers.modelname.input"
-21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/vehicle.jpg","admin.drivers.vehicle_image.file"
-22. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
-23. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
-24.Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
-25.Enter Account Holder Name,type,{autoName},"admin.drivers.accountholder.input"
-26. Enter Payment Email Address,type,{autoEmail},"admin.drivers.paymentemail.input"
-27. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
-28. Click Submit,click,,"web.global.action.submit"
-29. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
-30. Wait for Toast to hide,wait,1000,
-31.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-32.Click drivers menu,click,,"admin.drivers.menu.icon"
-33.Click Pending Documents,click,,"admin.drivers.pending_docs.link"
-34.Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
-35.Scroll Grid,tab,7,"admin.drivers.name_filter.input"
-36.Click Doc Icon,click,,"admin.drivers.docs.icon"
-37. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
-38.FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
-39.Add Driving License,click,,"admin.drivers.docs.edit_icon"
-40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg","admin.drivers.profile_image.file"
-41.Enter Expiry Date,type,12-12-2026,"admin.drivers.doc_expiry.input"
-42.Click Submit,click,,"web.global.action.submit"
-43.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-44.Click Approve Driver,click,,"admin.drivers.docs.approval"
-45.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-46.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-47.Click drivers menu,click,,"admin.drivers.menu.icon"
-48.Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
-49.Wait For Drivers List,wait_until_visible,,"admin.drivers.approved_page.header"
-50.Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
-51.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
-52.Click Doc Icon,click,,"admin.drivers.approved_docs.grid_icon"
-53.Click Eye Icon,click,,"admin.drivers.approved_docs.eye_icon"
-54.wait,1000,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click drivers menu,click,, "admin.drivers.menu.icon"
-3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
-4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
-5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
-6.Select Bike Ride Option,click,, "admin.drivers.service_dropdown.bike_ride"
-7. Enter Driver Name,type,bikedriver{randomAlpha} &gt;&gt; bikeName, "admin.drivers.fullname.input"
-8. Enter Email,type,bikedriver_{timestamp}@gmail.com&gt;&gt;bikeEmail, "admin.drivers.email.input"
-9.Enter Contact Number,type,{randomPhone}&gt;&gt;bikePhone, "admin.drivers.phone.input"
-10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
-11.Enter Whatspp Number,type,{bikePhone}, "admin.drivers.whatsapp_phone.input"
-12.Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg", "admin.drivers.profile_image.file"
-13.Select Source,click,, "admin.drivers.source_dropdown.select"
-14.Select Instagram,click,, "admin.drivers.instagram_option.span"
-15.Select Male Gender,click,, "admin.drivers.male_gender.div"
-16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
-17.Select  Bike Option,click,, "admin.drivers.vehicle_option.scooter"
-18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
-19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
-20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
-21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg", "admin.drivers.vehicle_image.file"
-22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
-23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
-24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
-25.Enter Account Holder Name,type,{bikeName}, "admin.drivers.accountholder.input"
-26. Enter Payment Email Address,type,{bikeEmail}, "admin.drivers.paymentemail.input"
-27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
-28. Click Submit,click,, "web.global.action.submit"
-29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
-30. Wait for Toast to hide,wait,1000,
-31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-32.Click drivers menu,click,, "admin.drivers.menu.icon"
-33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
-34.Filter by Name,type,{bikeName}, "admin.drivers.name_filter.input"
-35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
-36.Click Doc Icon,click,, "admin.drivers.docs.icon"
-37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
-38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
-39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
-40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
-41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
-42.Click Submit,click,, "web.global.action.submit"
-43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-44.Click Approve Driver,click,, "admin.drivers.docs.approval"
-45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-47.Click drivers menu,click,, "admin.drivers.menu.icon"
-48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
-49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
-50.Filter Approved Driver,type,{bikeName}, "admin.drivers.name_filter.input"
-51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
-52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
-53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
-54.wait,1000,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click drivers menu,click,, "admin.drivers.menu.icon"
-3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
-4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
-5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
-6.Select Taxi Ride Option,click,, "admin.drivers.service_dropdown.taxi_ride"
-7. Enter Driver Name,type,taxidriver{randomAlpha} &gt;&gt; taxiName, "admin.drivers.fullname.input"
-8. Enter Email,type,taxidriver_{timestamp}@gmail.com&gt;&gt;taxiEmail, "admin.drivers.email.input"
-9.Enter Contact Number,type,{randomPhone}&gt;&gt;taxiPhone, "admin.drivers.phone.input"
-10.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
-11.Enter Whatspp Number,type,{taxiPhone}, "admin.drivers.whatsapp_phone.input"
-12.Upload Profile Image,uploadfile,"src/main/resources/test-data/taxidriver.jpg", "admin.drivers.profile_image.file"
-13.Select Source,click,, "admin.drivers.source_dropdown.select"
-14.Select Instagram,click,, "admin.drivers.instagram_option.span"
-15.Select Male Gender,click,, "admin.drivers.male_gender.div"
-16.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
-17.Select  Suv Option,click,, "admin.drivers.vehicle_option.suv"
-18. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
-19.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
-20.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
-21.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/taxi.jpg", "admin.drivers.vehicle_image.file"
-22. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
-23. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
-24.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
-25.Enter Account Holder Name,type,{taxiName}, "admin.drivers.accountholder.input"
-26. Enter Payment Email Address,type,{taxiEmail}, "admin.drivers.paymentemail.input"
-27. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
-28. Click Submit,click,, "web.global.action.submit"
-29. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
-30. Wait for Toast to hide,wait,1000,
-31.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-32.Click drivers menu,click,, "admin.drivers.menu.icon"
-33.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
-34.Filter by Name,type,{taxiName}, "admin.drivers.name_filter.input"
-35.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
-36.Click Doc Icon,click,, "admin.drivers.docs.icon"
-37. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
-38.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
-39.Add Driving License,click,, "admin.drivers.docs.edit_icon"
-40.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
-41.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
-42.Click Submit,click,, "web.global.action.submit"
-43.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-44.Click Approve Driver,click,, "admin.drivers.docs.approval"
-45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
-46.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-47.Click drivers menu,click,, "admin.drivers.menu.icon"
-48.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
-49.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
-50.Filter Approved Driver,type,{taxiName}, "admin.drivers.name_filter.input"
-51.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
-52.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
-53.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
-54.wait,1000,</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Transports Services Menu,click,,"admin.transport.menu.card"
-3. Wait For Transport Services,wait_until_visible,,"admin.transport.page.header"
-4. Click Add Category,click,,"admin.transport.add_category.btn"
-5. Enter Service Name,type,lorryRide{randomAlpha}&gt;&gt;lorryTransportName,"admin.transport.name.input"
-6. Enter Service Name Arabic,type,رحلة بالحافلة,"admin.transport.name_ar.input"
-7. Enter Slug,type,{lorryTransportName},"admin.transport.slug.input"
-8. Upload Transport Service Image,uploadfile,"src/main/resources/test-data/lorry.png","admin.transport.image.file"
-9. wait,2000,,
-10. Open status Dropdown,click,,"admin.transport.status.dropdown"
-11. Select Activate,click,,"admin.transport.status.activate_option"
-12. Open Select City Dropdown,click,,"admin.transport.city.dropdown"
-13. Select {areaName},click,,"admin.transport.city.dynamic_option"
-14. Click Submit,click,,"web.global.action.submit"
-15. Sucess,wait_until_visible,,"web.global.toast.info"
-16. wait,2000,,
-17. Click Dashboard Home Icon,click,,"web.global.menu.dashboard"
-18. Click Transports Services Menu,click,,"admin.transport.menu.card"
-19. Filter Services List,type,{lorryTransportName},"admin.transport.grid.name_filter"
-20. Click Home Icon,click,,"admin.transport.home.icon"
-21. Click Settings,click,,"admin.transport.menu.settings"
-22. Click Vehicle Type,click,,"admin.transport.settings.vehicle_type"
-23. Click Add Vehicle Type,click,,"admin.transport.vehicle.add_type.btn"
-24. Enter Vehicle Type Name,type,tempo{randomAlpha}&gt;&gt;lorryTypeName,"admin.transport.vehicle.name.input"
-25. Enter Base Fare,type,150,"admin.transport.vehicle.base_fare.input"
-26. Enter Base Fare Max Kilometer,type,10,"admin.transport.vehicle.base_km.input"
-27. Open Extra Distance Fare Dropdown,click,,"admin.transport.vehicle.extra_fare_type.dropdown"
-28. Select Amount,click,,"admin.transport.status.amount_option"
-29. Enter Extra Distance Fare,type,10,"admin.transport.vehicle.extra_fare.input"
-30. Enter Free Waiting Time,type,10,"admin.transport.vehicle.waiting_free.input"
-31. Open Waiting Charge Dropdown,click,,"admin.transport.vehicle.waiting_type.dropdown"
-32. Select Amount,click,,"admin.transport.status.amount_option"
-33. Enter Waiting Rate,type,10,"admin.transport.vehicle.waiting_rate.input"
-34. Enter Included Trip Waiting,type,10,"admin.transport.vehicle.trip_waiting_free.input"
-35. Open Trip Waiting Charge Dropdown,click,,"admin.transport.vehicle.trip_waiting_type.dropdown"
-36. Select Amount,click,,"admin.transport.status.amount_option"
-37. Enter Trip Waiting Rate,type,50,"admin.transport.vehicle.trip_waiting_rate.input"
-38. Enter Free Pickup Distance,type,5,"admin.transport.vehicle.pickup_free.input"
-39. Open Pickup Charge Dropdown,click,,"admin.transport.vehicle.pickup_type.dropdown"
-40. Select Amount,click,,"admin.transport.status.amount_option"
-41. Enter Pickup Fee,type,50,"admin.transport.vehicle.pickup_fee.input"
-42. Open Customer Fee Dropdown,click,,"admin.transport.vehicle.customer_type.dropdown"
-43. Select Amount,click,,"admin.transport.status.amount_option"
-44. Enter Customer Fee,type,50,"admin.transport.vehicle.customer_fee.input"
-45. Open Customer GST Dropdown,click,,"admin.transport.vehicle.customer_gst_type.dropdown"
-46. Select Amount,click,,"admin.transport.status.amount_option"
-47. Enter GST amount,type,50,"admin.transport.vehicle.customer_gst.input"
-48. Open Driver Fee Dropdown,click,,"admin.transport.vehicle.driver_type.dropdown"
-49. Select Amount,click,,"admin.transport.status.amount_option"
-50. Enter Driver Fee,type,50,"admin.transport.vehicle.driver_fee.input"
-51. Open Driver GST Dropdown,click,,"admin.transport.vehicle.driver_gst_type.dropdown"
-52. Select Amount,click,,"admin.transport.status.amount_option"
-53. Enter Driver Gst,type,50,"admin.transport.vehicle.driver_gst.input"
-54. Open Status Dropdown,click,,"admin.transport.vehicle.status.dropdown"
-55. Select Active,click,,"admin.transport.status.active_option"
-56. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/tempo.jpg","admin.transport.vehicle.image.file"
-57. Enter Notifiacation,type,50,"admin.transport.vehicle.notify_km.input"
-58. Enter Driver Request ETA,type,50,"admin.transport.vehicle.eta_limit.input"
-59. Enter Driver Request KM,type,50,"admin.transport.vehicle.km_limit.input"
-60. Open Night Charge Timing Status Dropdown,click,,"admin.transport.night.status.dropdown"
-61. Select Active,click,,"admin.transport.status.active_option"
-62. Click Surcharge Time Checkbox,click,,"admin.transport.night.everyday.checkbox"
-63. Enter From Time,type,100000AM,"admin.transport.night.from_time.input"
-64. Enter To Time,type,220000PM,"admin.transport.night.to_time.input"
-65. Open Dropdown,click,,"admin.transport.night.type.dropdown"
-66. Select Amount,click,,"admin.transport.status.amount_option"
-67. Enter Price,type,50,"admin.transport.night.price.input"
-68. Click Submit,click,,"web.global.action.submit"
-69. Wait Until Sucess,wait_until_visible,,"web.global.toast.info"
-70. Click Setting menu,click,,"web.global.menu.settings"
-71. Click City admin menu,click,,"admin.menu.city_admin"
-72. Verify City Admin List,verify,,"admin.city_admin.list_heading"
-73. Click Add City Admin button,click,,"admin.city_admin.btn_add"
-74. Verify City Admin heading,verify,,"admin.city_admin.add_heading"
-75. Select Name field,click,,"admin.city_admin.input_name"
-76. Enter Admin Name,type,newAdmin{randomAlpha} &gt;&gt; transAdminName,"admin.city_admin.input_name"
-77. Select Email field,click,,"admin.city_admin.input_email"
-78. Enter Email,type,transAdmin_{timestamp}@gmail.com &gt;&gt; transAdminEmail,"admin.city_admin.input_email"
-79. select the password field,click,,"admin.city_admin.input_password"
-80. Enter the Password,type,password{timestamp}&gt;&gt; transAdminPassword,"admin.city_admin.input_password"
-81. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
-82. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
-83. Click on the Bike Ride checkbox,click,,"admin.city_admin.chk_transport_bike_ride"
-84. Click on the Taxi Ride checkbox,click,,"admin.city_admin.chk_transport_taxi_ride"
-85. Click on the Auto Ride checkbox,click,,"admin.city_admin.chk_transport_auto_ride"
-86. Click on the dynamic service checkbox,click,,"admin.transport.dropdown.dynamic_lorry_service"
-87. Click on the Add Driver checkbox,click,,"admin.city_admin.chk_driver_add"
-88. Click on the Approved Drivers checkbox,click,,"admin.city_admin.chk_driver_approved"
-89. Click on the Un-Approved Drivers checkbox,click,,"admin.city_admin.chk_driver_unapproved"
-90. Click on the Blocked Drivers checkbox,click,,"admin.city_admin.chk_driver_blocked"
-91. Click on the Reject Drivers checkbox,click,,"admin.city_admin.chk_driver_rejected"
-92. Click on the Deleted Drivers checkbox,click,,"admin.city_admin.chk_driver_deleted"
-93. Click on the Driver Pending Documents checkbox,click,,"admin.city_admin.chk_driver_pending_docs"
-94. Click on the Driver Expired Documents checkbox,click,,"admin.city_admin.chk_driver_expired_docs"
-95. Click Submit,click,,"web.global.login.submit_btn"
-96. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-97. Filter admin name,type,{transAdminName},"admin.city_admin.input_name_filter"
-98. Click Logout Icon,click,,"web.global.action.logout_link"
-99. Click Confirm Logout,click,,"web.global.action.logout_confirm"
-100. Wait For Login Page,wait_until_visible,,"web.global.login.email"
-101. Enter Email,type,{transAdminEmail},"web.global.login.email"
-102. Enter Password,type,{transAdminPassword},"web.global.login.password"
-103. Click Login,click,,"web.global.login.submit_btn"
-104. Wait For Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"
-105. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-106. Click drivers menu,click,,"admin.drivers.menu.icon"
-107. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
-108. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
-109. Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
-110. Select Lorry Ride Option,click,,"admin.transport.dropdown.dynamic_lorry_transport_service"
-111. Enter Driver Name,type,lorrydriver{randomAlpha} &gt;&gt; lorrydriverName,"admin.drivers.fullname.input"
-112. Enter Email,type,lorrydriver_{timestamp}@gmail.com&gt;&gt;lorrydriverEmail,"admin.drivers.email.input"
-113. Enter Contact Number,type,{randomPhone}&gt;&gt;lorryPhone,"admin.drivers.phone.input"
-114. Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
-115. Enter Whatspp Number,type,{lorryPhone},"admin.drivers.whatsapp_phone.input"
-116. Upload Profile Image,uploadfile,"src/main/resources/test-data/lorrydriver.jpg","admin.drivers.profile_image.file"
-117. Select Source,click,,"admin.drivers.source_dropdown.select"
-118. Select Instagram,click,,"admin.drivers.instagram_option.span"
-119. Select Male Gender,click,,"admin.drivers.male_gender.div"
-120. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
-121. Select Lorry Option,click,,"admin.transport.dropdown.dynamic_vehicle_lorry_type"
-122. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
-123. Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
-124. Enter Model Name,type,petrol,"admin.drivers.modelname.input"
-125. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/lorry.png","admin.drivers.vehicle_image.file"
-126. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
-127. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
-128. Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
-129. Enter Account Holder Name,type,{lorrydriverName},"admin.drivers.accountholder.input"
-130. Enter Payment Email Address,type,{lorrydriverEmail},"admin.drivers.paymentemail.input"
-131. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
-132. Click Submit,click,,"web.global.action.submit"
-133. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
-134. wait,5000,,
-135. Click sidebar,click,,"web.global.action.sidebar_toggle"
-136. wait,2000,,
-137. Check Transport Menu exists,element_present,,"admin.transport.menu.card"
-138. wait,2000,,
-139. Check Deleivery Service exists,element_absent,,"admin.city_admin.chk_web_delivery"
-140. wait,2000,,
-141. Check Provider Service exists,element_absent,,"admin.city_admin.chk_provider_list"
-142. wait,2000,,
-143. Check Add Driver exists,element_present,,"admin.drivers.add_menu.link"
-144. wait,2000,,
-145. Check Approved Driver exists,element_present,,"admin.drivers.approved_docs.link"
-146. wait,2000,,
-147. Check Un-Approved Drivers exists,element_present,,"admin.drivers.unapproved_docs.link"
-148. wait,2000,,
-149. Check Blocked Driver exists,element_present,,"admin.drivers.blocked_docs.link"
-150. wait,2000,,
-151. Check Reject Driver exists,element_present,,"admin.drivers.reject_docs.link"
-152. wait,2000,,
-153. Check Deleted Driver exists,element_present,,"admin.drivers.deleted_docs.link"
-154. wait,2000,,
-155. Check pending Documents exists,element_present,,"admin.drivers.driver_pending_docs.link"
-156. wait,2000,,
-157. Check Driver Expired Documents exists,element_present,,"admin.drivers.driver_expired_docs.link"
-158. wait,2000,,
-159. Click Logout Icon,click,,"web.global.action.sidebar_logout_btn"
-160. Click Confirm Logout,click,,"web.global.action.logout_confirm"
-161. Wait For Login Page,wait_until_visible,,"web.global.login.email"
-162. Enter Email,type,super_admin@gmail.com,"web.global.login.email"
-163. Enter Password,type,R1mep@321,"web.global.login.password"
-164. Click Login,click,,"web.global.login.submit_btn"
-165. Wait For Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"
-166. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-167. Click Transports Services Menu,click,,"admin.transport.menu.card"
-168. Wait For Transport Services,wait_until_visible,,"admin.transport.page.header"
-169. Filter Services List,type,{lorryTransportName},"admin.transport.grid.name_filter"
-170. Click Edit Icon,click,,"admin.transport.docs.edit_icon"
-171. wait,2000,,
-172. Scroll Grid,tab,5,"admin.transport.name.input"
-173. wait,2000,,
-174. Open status Dropdown,click,,"admin.transport.status.dropdown"
-175. Select Deactivate,click,,"admin.transport.status.deactivate_option"
-176. Click Submit,click,,"web.global.action.submit"
-177. Wait For Sucess,wait_until_visible,,"web.global.toast.info"
-178. wait,2000,,</t>
   </si>
   <si>
     <t>Deleted Test Steps</t>
@@ -2200,85 +1857,6 @@
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
 5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
 6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Add Store,click,,"admin.store.submenu.add_store"
-8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
-9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
-10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
-11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
-12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
-13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
-14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
-15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
-16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
-17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
-18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
-19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
-20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
-21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
-22. Select Active,click,,"admin.store.current_status.option_active"
-23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
-24. wait,3000,,
-25. Confirm Store Address,press_enter,,"admin.store.location.input"
-26. wait,3000,,
-27. Select First Option,arrow_down,,"admin.store.location.input"
-28. Confirm Option,press_enter,,"admin.store.location.input"
-29. wait,2000,,
-30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
-31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
-32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
-33. Select Amount,click,,"admin.store.offer_type.option_amount"
-34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
-35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
-36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
-37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
-38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
-39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
-40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
-41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
-42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
-43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
-44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
-45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
-46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
-47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
-48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
-49. Submit Add Store,click,,"web.global.action.submit"
-50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-51. Click Stores,click,,"admin.store.menu.toggle_btn"
-52. Select Store List,click,,"admin.store.submenu.store_list"
-53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-55. Click Stores,click,,"admin.store.menu.toggle_btn"
-56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
-57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
-58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
-59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-61. Store Required Documents,verify,,"admin.store.documents_page.header"
-62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
-63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
-64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
-65. Click Submit,click,,"web.global.action.submit"
-66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
-68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-69. Click Back,click,,"admin.store.grid.back_btn"
-70. Click Stores,click,,"admin.store.menu.toggle_btn"
-71. Select Store List,click,,"admin.store.submenu.store_list"
-72. Verify Add Store,verify,,"admin.store.list_page.header"
-73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
-74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
-77. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
 7. Select Store List,click,,"admin.store.submenu.store_list"
 8. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
 9. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
@@ -2338,508 +1916,6 @@
 63. Filter Driver List,type,{kfcdriverName},"admin.drivers.name_filter.input"
 64. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
 65. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Delivery Services,click,,"admin.deliveryservice.menu"
-3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
-4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
-5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
-6. Click Stores,click,,"admin.store.menu.toggle_btn"
-7. Select Add Store,click,,"admin.store.submenu.add_store"
-8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
-9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
-10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
-11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
-12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
-13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
-14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
-15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
-16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
-17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
-18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
-19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
-20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
-21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
-22. Select Active,click,,"admin.store.current_status.option_active"
-23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
-24. wait,3000,,
-25. Confirm Store Address,press_enter,,"admin.store.location.input"
-26. wait,3000,,
-27. Select First Option,arrow_down,,"admin.store.location.input"
-28. Confirm Option,press_enter,,"admin.store.location.input"
-29. wait,2000,,
-30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
-31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
-32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
-33. Select Amount,click,,"admin.store.offer_type.option_amount"
-34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
-35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
-36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
-37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
-38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
-39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
-40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
-41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
-42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
-43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
-44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
-45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
-46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
-47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
-48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
-49. Submit Add Store,click,,"web.global.action.submit"
-50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
-51. Click Stores,click,,"admin.store.menu.toggle_btn"
-52. Select Store List,click,,"admin.store.submenu.store_list"
-53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-55. Click Stores,click,,"admin.store.menu.toggle_btn"
-56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
-57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
-58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
-59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
-61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
-62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
-63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
-64. Enter Expiry Date,type,2026-12-12,"admin.store.doc.expiry_input"
-65. Click Submit,click,,"web.global.action.submit"
-66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
-67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
-68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
-69. Click Back,click,,"admin.store.grid.back_btn"
-70. Click Stores,click,,"admin.store.menu.toggle_btn"
-71. Select Store List,click,,"admin.store.submenu.store_list"
-72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
-73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-75. Click Block Icon,click,,"admin.store.grid.block_icon"
-76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
-77. Click Stores,click,,"admin.store.menu.toggle_btn"
-78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
-79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
-82. Click Stores,click,,"admin.store.menu.toggle_btn"
-83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
-84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
-86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
-87. Click Stores,click,,"admin.store.menu.toggle_btn"
-88. Select Store List,click,,"admin.store.submenu.store_list"
-89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
-90. wait,3000,,
-91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
-92. Click Doc Icon,click,,"admin.store.grid.document_icon"
-93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
-94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
-96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-97. wait,1000,,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Delivery Services, click, , "admin.deliveryservice.menu"
-3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
-4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
-5.Enter Category Name, type, milk Delivery{randomAlpha} &gt;&gt; deliveryName, "admin.deliveryservice.category_name.input"
-6.Enter Slug, type, Milk Delivery, "admin.deliveryservice.slug.input"
-7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "admin.deliveryservice.image.file"
-8.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
-9.Select Activate, click, , "admin.deliveryservice.status.option_activate"
-10.Open Category Flow Dropdown, click, , "admin.deliveryservice.flow.dropdown"
-11.Select default flow(food-delivery), click, , "admin.deliveryservice.flow.option_food_delivery"
-12.Enter Delivery Name Tamil, type, பால்காரர், "admin.deliveryservice.lang_tamil.input"
-13.Enter Delivery Name Arabic, type, لبّان, "admin.deliveryservice.lang_arabic.input"
-14.Enter Delivery Name Hindi, type, दूधवाला, "admin.deliveryservice.lang_hindi.input"
-15.Click Submit, click, , "web.global.action.submit"
-16.Verify Success, verify, , "web.global.toast.info"
-17.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-18.Click Home Icon, click, , "admin.deliveryservice.home.icon"
-19.Click Settings, click, , "admin.deliveryservice.settings.menu"
-20.Click Requirement Document, click, , "admin.deliveryservice.required_docs"
-21.Click Add Document, click, , "admin.deliveryservice.docs.add_btn"
-22.Enter Name, type, document{randomAlpha} &gt;&gt; deliveryDocumentName, "admin.deliveryservice.docs.name_input"
-23.Open status Dropdown, click, , "admin.deliveryservice.docs.status_dropdown"
-24.Select Active, click, , "admin.deliveryservice.docs.status_option_active"
-25.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
-26.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
-27.Click Mandatory Document, click, , "admin.deliveryservice.docs.mandatory_checkbox"
-28.Click Require Proof Number, click, , "admin.deliveryservice.docs.proof_number_checkbox"
-29.Enter Display Order, type, 10, "admin.deliveryservice.docs.display_order_input"
-30.Click Submit, click, , "web.global.action.submit"
-31.Verify Success, verify, , "web.global.toast.info"
-32.Filter Document List, type, {deliveryDocumentName}, "admin.deliveryservice.docs.grid.filter_input"
-33.wait, 2000, , ""
-34.Click Settings, click, , "admin.deliveryservice.settings.menu"
-35.Click Service Settings, click, , "admin.deliveryservice.submenu.service_settings"
-36.Enter Driver Search Radius, type, 50, "admin.deliveryservice.config.search_radius_input"
-37.Open Tax Type Dropdown, click, , "admin.deliveryservice.config.tax_type_dropdown"
-38.Select Amount, click, , "admin.deliveryservice.config.tax_type_option_amount"
-39.Enter Tax, type, 20, "admin.deliveryservice.config.tax_input"
-40.Open Platform Fee Type Dropdown, click, , "admin.deliveryservice.config.fee_type_dropdown"
-41.Select Amount, click, , "admin.deliveryservice.config.fee_type_option_amount"
-42.Enter Platform Fee, type, 20, "admin.deliveryservice.config.platform_fee_input"
-43.Enter Cancel Charge (in %):, type, 20, "admin.deliveryservice.config.cancel_charge_input"
-44.Enter Driver Accept Timeout (in Second):, type, 20, "admin.deliveryservice.config.driver_timeout_input"
-45.Click Submit, click, , "web.global.action.submit"
-46.Verify Success, verify, , "web.global.toast.info"
-47.Click Stores, click, , "admin.store.menu.toggle_btn"
-48.Select Add Store, click, , "admin.store.submenu.add_store"
-49.Verify Add Store, verify, , "admin.store.add_page.header"
-50.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "admin.store.name.input"
-51.Open Delivery Radius Dropdown, click, , "admin.store.radius.dropdown"
-52.Select Twenty Five Kilometer, click, , "admin.store.radius.option_25km"
-53.Open Estimated Delivery Time, click, , "admin.store.eta.dropdown"
-54.Select Thirty Minute, click, , "admin.store.eta.option_30min"
-55.Enter Order Minimum Amount, type, 300, "admin.store.min_amount.input"
-56.Enter Packaging Charges, type, 50, "admin.store.packaging_charge.input"
-57.Enter Short Description, type, amul taste of india, "admin.store.description.input"
-58.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "admin.store.banner.file"
-59.Open Driver Notification, click, , "admin.store.driver_notification.dropdown"
-60.Select Both Driver, click, , "admin.store.driver_notification.option_both"
-61.Click Checkbox Allow For Pickup, click, , "admin.store.allow_pickup.checkbox"
-62.Open Current Status Dropdown, click, , "admin.store.current_status.dropdown"
-63.Select Active, click, , "admin.store.current_status.option_active"
-64.Enter Store Address, type, Amul chennai, "admin.store.location.input"
-65.wait, 3000, , ""
-66.Confirm Store Address, press_enter, , "admin.store.location.input"
-67.wait, 3000, , ""
-68.Select First Option, arrow_down, , "admin.store.location.input"
-69.Confirm Option, press_enter, , "admin.store.location.input"
-70.wait, 2000, , ""
-71.Click Storewise Commission Checkbox, click, , "admin.store.commission.checkbox"
-72.Enter Store Commission, type, 25, "admin.store.commission_rate.input"
-73.Open Driver Notification, click, , "admin.store.offer_type.dropdown"
-74.Select Amount, click, , "admin.store.offer_type.option_amount"
-75.Enter Offer Amount, type, 50, "admin.store.offer_amount.input"
-76.Enter Offer Min Amount, type, 500, "admin.store.offer_min_amount.input"
-77.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "admin.store.contact_name.input"
-78.Enter Email, type, amul_{timestamp}@gmail.com &gt;&gt; storeEmail, "admin.store.email.input"
-79.Enter Contact Number, type, {randomPhone}, "admin.store.phone.input"
-80.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "admin.store.profile.file"
-81.Enter Bank Name, type, federal, "admin.store.bank.name_input"
-82.Enter Bank Location, type, chennai, "admin.store.bank.location_input"
-83.Enter Account Number, type, 123456789012, "admin.store.bank.account_input"
-84.Enter Account Holder Name, type, {milkStoreOwner}, "admin.store.bank.holder_input"
-85.Enter Payment Email Address, type, {storeEmail}, "admin.store.bank.payment_email"
-86.Enter BIC Code, type, 1234, "admin.store.bank.bic_input"
-87.Click Store Timing Checkbox, click, , "admin.store.timing.everyday_checkbox"
-88.Enter From Time, type, 100000AM, "admin.store.timing.from_input"
-89.Enter To Time, type, 100000PM, "admin.store.timing.to_input"
-90.Submit Add Store, click, , "web.global.action.submit"
-91.Verify Success Message, verify, , "web.global.toast.info"
-92.Click Stores, click, , "admin.store.menu.toggle_btn"
-93.Select Store List, click, , "admin.store.submenu.store_list"
-94.Verify Add Store, verify, , "admin.store.list_page.header"
-95.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-96.Click Stores, click, , "admin.store.menu.toggle_btn"
-97.Select Pending Documents Stores List, click, , "admin.store.submenu.pending_docs"
-98.Verify Add Store, verify, , "admin.store.pending_page.header"
-99.Filter Pending Document Store List, type, {milkStore}, "admin.store.grid.name_filter"
-100.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
-101.Click Doc Icon, click, , "admin.store.grid.doc_icon"
-102.Store Required Documents, verify, , "admin.store.documents_page.header"
-103.Add Address Proof, click, , "admin.store.grid.edit_doc_icon"
-104.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.store.doc.file_input"
-105.Enter Expiry Date, type, 2026-12-12, "admin.store.doc.expiry_input"
-106.Click Submit, click, , "web.global.action.submit"
-107.Verify Updated Successfully, verify, , "web.global.toast.updated"
-108.Click Approve Store, click, , "admin.store.grid.approve_doc_icon"
-109.Verify Updated Successfully, verify, , "web.global.toast.updated"
-110.Click Back, click, , "admin.store.grid.back_btn"
-111.Click Stores, click, , "admin.store.menu.toggle_btn"
-112.Select Store List, click, , "admin.store.submenu.store_list"
-113.Verify Add Store, verify, , "admin.store.list_page.header"
-114.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-115.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
-116.Click Doc Icon, click, , "admin.store.grid.doc_icon"
-117.wait for back button,wait,3000,
-118.Click Back, click, , "admin.store.grid.back_btn"
-119.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
-120.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
-121.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
-122.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
-123.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
-124.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
-125.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
-126.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
-127.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
-128.wait, 2000, , ""
-129.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
-130.Click Submit, click, , "web.global.action.submit"
-131.Verify Success Message, verify, , "web.global.toast.info"
-132.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
-133.Click Stores, click, , "admin.store.menu.toggle_btn"
-134.Select Store List, click, , "admin.store.submenu.store_list"
-135.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
-136.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
-137.Click Product Icon, click, , "admin.store.products.grid_icon"
-138.Click Add Products, click, , "admin.store.products.add_btn"
-139.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
-140.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
-141.wait, 1000, ,""
-142.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-143.Click Delivery Services, click, , "admin.deliveryservice.menu"
-144.Verify Delivery Services, verify, , "admin.deliveryservice.header"
-145.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-146.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
-147.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
-148.wait, 1000, , ""
-149.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
-150.Click Submit, click, , "web.global.action.submit"
-151.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
-152.wait, 1000, ,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Delivery Services,click,,"admin.provider_service.menu_link"
-3.Verify Delivery Services,verify,,"admin.provider_service.on_demand_header"
-4.Filter service List,type,Plumbers,"admin.provider_service.services.filter.input"
-5.Click Home Icon Plumbers,click,,"admin.provider_service.services.home.icon_by_row_plumbers"
-6.Verify Plumbers Summary,verify,,"admin.provider_service.services.plumbers_summary.header"
-7.Click Providers,click,,"admin.provider_service.providers.root.button"
-8.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
-9.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
-10.Enter Provider Full Name, type, Plumber{randomAlpha}&gt;&gt; plumberName, "admin.provider_service.provider_form.fullname.input"
-11.Upload Plumber Image, uploadfile, "src/main/resources/test-data/plumber.jpg", "admin.provider_service.provider_form.avatar.file"
-12.Enter Email, type, Plumber_{timestamp}@gmail.com&gt;&gt;plumberEmail, "admin.provider_service.provider_form.email.input"
-13.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
-14.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
-15.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
-16.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
-17.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
-18.Enter Provider Address, type, plumber chennai, "admin.provider_service.provider_form.address.input"
-19.wait,1000,,
-20.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
-21.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
-22.wait,1000,,
-23.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
-24.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
-25.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
-26.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
-27.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
-28.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
-29.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
-30.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
-31.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
-32.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
-33.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
-34.Enter Account Holder Name, type, {plumberName}, "admin.provider_service.provider_form.account_holder.input"
-35.Enter Payment Email Address, type, {plumberEmail}, "admin.provider_service.provider_form.payment_email.input"
-36.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
-37.Click Save, click, , "web.global.login.submit_btn"
-38.Verify Sucess, verify, , "web.global.toast.info"
-39.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-40.Click Providers,click,,"admin.provider_service.providers.root.button"
-41.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
-42.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-43.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
-44.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
-45.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
-46.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
-47.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
-48.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
-49.Click Submit, click, , "web.global.action.submit"
-50.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-51.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
-52.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
-53.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-54.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-55.Click Providers,click,,"admin.provider_service.providers.root.button"
-56.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
-57.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
-58.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-59.Click Doc Icon,click,,"admin.provider_service.providers.grid.document.icon"
-60.Click Eye Icon,click,,"admin.provider_service.providers.grid.view_eye.icon"
-61.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-62.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
-63.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-64.Scroll Grid, tab, 11, "admin.provider_service.providers.grid.name_filter"
-65.Click Wallet Icon,click,,"admin.provider_service.providers.grid.wallet.icon"
-66.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
-67.Enter Wallet Amount, type, 1000, "admin.provider_service.wallet.amount.input"
-68.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
-69.Select Add Money,click, , "admin.provider_service.wallet.options.add_money"
-70.Click Submit, click, , "web.global.action.submit"
-71.Verify Saved Succesfully, verify, , "web.global.toast.success"
-72.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
-73.Enter Wallet Amount, type, 200, "admin.provider_service.wallet.amount.input"
-74.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
-75.Select Deduct Money,click, , "admin.provider_service.wallet.options.deduct_money"
-76.Click Submit, click, , "web.global.action.submit"
-77.Verify Saved Succesfully, verify, , "web.global.toast.success"
-78.Click Back, click, , "admin.provider_service.global.action.back_normal_btn"
-79.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-80.Click Doc Icon,click, , "admin.provider_service.providers.grid.document.icon"
-81.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
-82.Click Reject Document,click, , "admin.provider_service.provider_docs.reject.icon"
-83.Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
-84.Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
-85..Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
-86.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-87.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-88.Scroll Grid, tab, 13, "admin.provider_service.providers.grid.name_filter"
-89.Click Block Provider,click, , "admin.provider_service.providers.grid.block.icon"
-90.Click Block Yes,click, , "web.global.dialog.btn_confirm_yes"
-91.Blocking Reason,type,customer complaints,"web.global.dialog.textarea_reason"
-92.Click block Yes,click, , "web.global.dialog.btn_confirm_yes"
-93.Click Providers,click, , "admin.provider_service.providers.root.button"
-94.Select Blocked Providers,click, , "admin.provider_service.providers.blocked_list.menu"
-95.Verify Blocked Provider,verify, , "admin.provider_service.providers.grid.blocked_plumbers.header"
-96.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-97.Scroll Grid, tab, 12, "admin.provider_service.providers.grid.name_filter"
-98.Click Unblock Provider,click, , "admin.provider_service.providers.grid.unblock.icon"
-99.Click Providers,click, , "admin.provider_service.providers.root.button"
-100.Select Provider List,click, , "admin.provider_service.providers.provider_list.menu"
-101.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
-102.wait,1000,,</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Provider Services,click,,"admin.provider_service.menu_link"
-3.Verify Provider Services,verify,,"admin.provider_service.on_demand_header"
-4.Click Add New Services,click,,"admin.provider_service.services.add_new.btn"
-5.Enter Service Name, type, Painter{randomAlpha}&gt;&gt; serviceName, "admin.provider_service.services.name.input"
-6.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
-7.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
-8.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
-9.Enter Slug, type, painter, "admin.provider_service.services.slug.input"
-10.Upload Service Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.services.image.file"
-11.wait,2000,,
-12.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
-13.Select Activate,click,,"admin.provider_service.services.status.option_activate"
-14.Open Select City Dropdown,click,,"admin.provider_service.services.city.dropdown"
-15.Select {areaName},click,,"admin.provider_service.services.city.option_dynamic"
-16.Click Submit,click,,"web.global.action.submit"
-17.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
-18.Click Home Icon ,click,,"admin.provider_service.services.home.icon"
-19.Click Settings ,click,,"admin.provider_service.settings.menu.button"
-20.Click Requirment Document ,click,,"admin.provider_service.settings.req_document.tab"
-21.Click Add Document ,click,,"admin.provider_service.req_docs.add.btn"
-22.Enter Name, type, documet{randomAlpha}&gt;&gt; providerDocumentName, "admin.provider_service.req_docs.name.input"
-23.Open status Dropdown,click,,"admin.provider_service.req_docs.status.dropdown"
-24.Select Active,click,,"admin.provider_service.req_docs.status.option_active"
-25.Click Document Expiry ,click,,"admin.provider_service.req_docs.expiry_toggle"
-26.Click Mandatory Document ,click,,"admin.provider_service.req_docs.mandatory_toggle"
-27.Click Submit ,click,,"web.global.action.submit"
-28.Verify Sucess, verify, , "web.global.toast.info"
-29.Filter Document List,type,{providerDocumentName},"admin.provider_service.req_docs.filter.input"
-30.Click Settings ,click,,"admin.provider_service.settings.menu.button"
-31.Click Promocode ,click,,"admin.provider_service.settings.promocode.tab"
-32.Click Add Promo Code ,click,,"admin.provider_service.promocode.add.btn"
-33.Open User List Dropdown,click,,"admin.provider_service.promocode.user_list.dropdown"
-34.Select User,click,,"admin.provider_service.promocode.user_list.option_dynamic"
-35.Click Code Name Box,click,,"admin.provider_service.promocode.code_name.box"
-36.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; providerPromoCodeName, "admin.provider_service.promocode.code_name.box"
-37.Open Discout Type Dropdown,click,,"admin.provider_service.promocode.discount_type.dropdown"
-38.Select Discout Type,click,,"admin.provider_service.promocode.discount_type.option_amount"
-39.Enter Expiry Date,type,12122026,"admin.provider_service.promocode.expiry_date.input"
-40.Enter Discount Amount, type, 100, "admin.provider_service.promocode.discount_amount.input"
-41.Enter Minimum Order Amount, type, 1000, "admin.provider_service.promocode.min_order_amount.input"
-42.Enter Maximum Discount Amount, type, 100, "admin.provider_service.promocode.max_discount.input"
-43.Enter Coupon Limit, type, 5,"admin.provider_service.promocode.coupon_limit.input"
-44.Enter Usage Limit for One User, type, 2,"admin.provider_service.promocode.usage_limit_per_user.input"
-45.Enter Promo Code Description, type, Promo Dode For Gold Member,"admin.provider_service.promocode.description.textarea"
-46.Click Submit ,click,,"web.global.action.submit"
-47.Verify Sucess, verify, , "web.global.toast.info"
-48.Filter PromoCode List,type,{providerPromoCodeName},"admin.provider_service.promocode.filter.input"
-49.Click Providers,click,,"admin.provider_service.providers.root.button"
-50.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
-51.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
-52.Enter Provider Full Name, type, Painter{randomAlpha}&gt;&gt; painterName, "admin.provider_service.provider_form.fullname.input"
-53.Upload Painter Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.provider_form.avatar.file"
-54.Enter Email, type, Painter_{timestamp}@gmail.com&gt;&gt;painterEmail, "admin.provider_service.provider_form.email.input"
-55.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
-56.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
-57.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
-58.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
-59.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
-60.Enter Provider Address, type, painter chennai, "admin.provider_service.provider_form.address.input"
-61.wait,1000,,
-62.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
-63.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
-64.wait,1000,,
-65.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
-66.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
-67.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
-68.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
-69.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
-70.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
-71.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
-72.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
-73.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
-74.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
-75.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
-76.Enter Accont Holder Name, type, {painterName}, "admin.provider_service.provider_form.account_holder.input"
-77.Enter Payment Email Address, type, {painterEmail}, "admin.provider_service.provider_form.payment_email.input"
-78.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
-79.Click Save, click, , "web.global.login.submit_btn"
-80.Verify Sucess, verify, , "web.global.toast.info"
-81.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
-82.Click Providers,click,,"admin.provider_service.providers.root.button"
-83.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
-84.Filter Plumber List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
-85.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
-86.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
-87.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
-88.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
-89.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
-90.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
-91.Click Submit, click, , "web.global.action.submit"
-92.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-93.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
-94.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
-95.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-96.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
-97.Click Providers,click,,"admin.provider_service.products.menu_category_btn"
-98.Click Add New Category,click,,"admin.provider_service.category.add_new.btn"
-99.Enter Category Name, type,residentialPainter{randomAlpha}&gt;&gt; painterCategoryName, "admin.provider_service.category.name.input"
-100.Enter Category Name Tamil, type, குடியிருப்பு பெயிண்டர், "admin.provider_service.category.name_tamil.input"
-101.Enter Category Name Arabic, type, دهان سكني, "admin.provider_service.category.name_arabic.input"
-102.Enter Category Name Hindi, type, आवासीय पेंटर, "admin.provider_service.category.name_hindi.input"
-103.Open Category status Dropdown,click,,"admin.provider_service.category.status.dropdown"
-104.Select Activate,click,,"admin.provider_service.category.status.option_active"
-105.Upload Category Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.category.image.file"
-106.wait,2000,,
-107.Click Submit,click,,"web.global.action.submit"
-108.Filter Category Name,type,{painterCategoryName},"admin.provider_service.category.filter.input"
-109.Click Providers,click,,"admin.provider_service.providers.root.button"
-110.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
-111.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
-112.Scroll Grid, tab, 7, "admin.provider_service.providers.grid.name_filter"
-113.Click Package Icon,click,,"admin.provider_service.packages.icon"
-114.Click Add Package,click,,"admin.provider_service.packages.add_new.btn"
-115.Open Category Dropdown,click,,"admin.provider_service.packages.category.dropdown"
-116.Select Activate,click,,"admin.provider_service.packages.category.option_dynamic"
-117.Enter Package Name, type, package{randomAlpha}&gt;&gt; packageName, "admin.provider_service.packages.name.input"
-118.Enter Amount, type, 1000, "admin.provider_service.packages.amount.input"
-119.Open Max Book Quantity Dropdown,click,,"admin.provider_service.packages.max_book_qty.dropdown"
-120.Select 4,click,,"admin.provider_service.packages.max_book_qty.option_4"
-121.Open Status Dropdown,click,,"admin.provider_service.packages.status.dropdown"
-122.Select Activate,click,,"admin.provider_service.packages.status.option_activate"
-123.Enter Description, type, Premium residential painting package, "admin.provider_service.packages.description.textarea"
-124.Click Submit,click,,"web.global.action.submit"
-125.wait,1000,,
-126.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
-127.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-128.Click Delivery Services,click,,"admin.provider_service.menu_link"
-129.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
-130.Click Edit Icon ,click,,"admin.provider_service.services.edit.icon"
-131.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
-132.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
-133.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
-134.Scroll Grid, tab, 4, "admin.provider_service.services.name_hindi.input"
-135.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
-136.Select Deactivate,click,,"admin.provider_service.services.status.option_deactivate"
-137.Click Submit,click,,"web.global.action.submit"
-138.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
-139. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-140.Click badge,click,,"admin.provider_service.badge.icon"
-141.Click provider Services,click,,"admin.provider_service.menu_link"
-142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
-143.wait,1000,,</t>
   </si>
   <si>
     <t>Verify the complete lifecycle of a panic call configuration—including creation with multilingual names (English, Tamil, Hindi), searching, updating its status to inactive, and successful deletion.</t>
@@ -3078,89 +2154,6 @@
 35.Click Service Option,click,,"admin.drivers.approved_driver.service_dropdown_first"
 36.Click Search Button,Click,,"web.global.dashboard.search_btn"
 37.wait for Approved Driver Filtering,wait,3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Transports Services Menu,click,, "admin.transport.menu.card"
-3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
-4.Click Ride Button,click,,"admin.transport.rides.icon"
-5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
-6.Click Search Button,Click,,"admin.transport.search_btn"
-7.wait For Today Statistics,wait,2000,
-8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-9.Click Search Button,Click,,"admin.transport.search_btn"
-10.wait For Yesterday Statistics,wait,2000,
-11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-12.Click Search Button,Click,,"admin.transport.search_btn"
-13.wait For This Week Statistics,wait,2000,
-14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-15.Click Search Button,Click,,"admin.transport.search_btn"
-16.wait For This Month Statistics,wait,2000,
-17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-18.Click Search Button,Click,,"admin.transport.search_btn"
-19.wait For Last Month Statistics,wait,2000,
-20.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-21.Click Search Button,Click,,"admin.transport.search_btn"
-22.wait For Last Year Statistics,wait,2000,
-23.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-24.Click Search Button,Click,,"admin.transport.search_btn"
-25.wait For This Year Statistics,wait,2000,
-26.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
-27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
-28.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
-29.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
-30.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
-31.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
-32.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
-33.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
-34.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
-35.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-36.Enter Status Type In Drop Down,type,Completed Rides,"admin.transport.status_type_dropdown_searchbox"
-37.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-38.Click Search Button,click,,"admin.transport.search_btn"
-39.Click Status Filter Input,click,,"admin.transport.status_filter_input"
-40.Enter Status,type,complete,"admin.transport.status_filter_input"
-41.Click Chat Box,click,,"admin.transport.chat_box.icon"
-42.Wait For Chat,wait,2000,
-43.Close Chat,click,,"admin.transport.rides.messages_close.btn"
-44.Click Ride Detail Button,click,,"admin.transport.ride_details.icon" 
-45.Wait For Ride Detail,wait,2000
-46.Show Ride Details,click,,"admin.transport.ride_details.arrival_time_box"
-47.Wait For Ride Detail,wait,2000
-48.Click Back Button,click,,"admin.transport.ride_details.back_btn"
-49.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
-50.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
-51.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
-52.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
-53.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
-54.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
-55.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
-56.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
-57.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
-58.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-59.Enter Status Type In Drop Down,type,Incomplete Rides,"admin.transport.status_type_dropdown_searchbox"
-60.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-61.Click Search Button,click,,"admin.transport.search_btn"
-62.Wait For Incomplete Rides,wait,2000,
-63.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
-64.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-65.Enter Status Type In Drop Down,type,Cancelled Rides,"admin.transport.status_type_dropdown_searchbox"
-66.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-67.Click Search Button,click,,"admin.transport.search_btn"
-68.Wait For Cancelled Rides,wait,2000,
-69.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
-70.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-71.Enter Status Type In Drop Down,type,Scheduled Rides,"admin.transport.status_type_dropdown_searchbox"
-72.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-73.Click Search Button,click,,"admin.transport.search_btn"
-74.Wait For Scheduled Rides,wait,2000,
-75.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
-76.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
-77.Enter Status Type In Drop Down,type,Pre-Acceptance Cancel Rides,"admin.transport.status_type_dropdown_searchbox"
-78.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
-79.Click Search Button,click,,"admin.transport.search_btn"
-80.Wait For Pre-Acceptance Cancel Rides,wait,2000,
-</t>
   </si>
   <si>
     <t>SA_TS_21</t>
@@ -3293,182 +2286,6 @@
 122.wait,3000,,</t>
   </si>
   <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Transports Services Menu,click,, "admin.transport.menu.card"
-3.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
-4.Click  Add Category,click,, "admin.transport.add_category.btn"
-5.Enter Service Name, type, Bus Ride{randomAlpha}&gt;&gt;transportName, "admin.transport.name.input"
-6.Enter Service Name Arabic, type, رحلة بالحافلة, "admin.transport.name_ar.input"
-7.Enter Slug, type, Bus Ride, "admin.transport.slug.input"
-8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/bus.jpg", "admin.transport.image.file"
-9.wait,2000,,
-10.Open status Dropdown,click,, "admin.transport.status.dropdown"
-11.Select Activate,click,, "admin.transport.status.activate_option"
-12.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
-13.Select {areaName},click,, "admin.transport.city.dynamic_option"
-14.Click  Submit,click,, "web.global.action.submit"
-15.Wait Till Sucess, wait_until_visible, , "web.global.toast.info"
-16.wait,2000,,
-17.Click  back,click,, "admin.transport.back.btn"
-18. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-19.Click Transports Services Menu,click,, "admin.transport.menu.card"
-20.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
-21.Click Home Icon ,click,, "admin.transport.home.icon"
-22.Click Settings ,click,, "admin.transport.menu.settings"
-23.Click Vehicle Type,click,, "admin.transport.settings.vehicle_type"
-24.Click Add Vehicle Type,click,, "admin.transport.vehicle.add_type.btn"
-25.Enter Vehicle Type Name, type, volvo{randomAlpha}&gt;&gt;busTypeName, "admin.transport.vehicle.name.input"
-26.Enter Base Fare, type, 150, "admin.transport.vehicle.base_fare.input"
-27.Enter Base Fare Max Kilometer, type, 10, "admin.transport.vehicle.base_km.input"
-28.Open Extra Distance Fare Dropdown,click,, "admin.transport.vehicle.extra_fare_type.dropdown"
-29.Select Amount,click,, "admin.transport.status.amount_option"
-30.Enter Extra Distance Fare , type, 10, "admin.transport.vehicle.extra_fare.input"
-31.Enter Free Waiting Time , type, 10, "admin.transport.vehicle.waiting_free.input"
-32.Open Waiting Charge Dropdown,click,, "admin.transport.vehicle.waiting_type.dropdown"
-33.Select Amount,click,, "admin.transport.status.amount_option"
-34.Enter Waiting Rate , type, 10, "admin.transport.vehicle.waiting_rate.input"
-35.Enter Included Trip Waiting , type, 10, "admin.transport.vehicle.trip_waiting_free.input"
-36.Open Trip Waiting Charge Dropdown,click,, "admin.transport.vehicle.trip_waiting_type.dropdown"
-37.Select Amount,click,, "admin.transport.status.amount_option"
-38.Enter Trip Waiting Rate , type,50, "admin.transport.vehicle.trip_waiting_rate.input"
-39.Enter Free Pickup Distance , type,5, "admin.transport.vehicle.pickup_free.input"
-40.Open Pickup Charge Dropdown,click,, "admin.transport.vehicle.pickup_type.dropdown"
-41.Select Amount,click,, "admin.transport.status.amount_option"
-42.Enter Pickup Fee, type,50, "admin.transport.vehicle.pickup_fee.input"
-43.Open Customer Fee  Dropdown,click,, "admin.transport.vehicle.customer_type.dropdown"
-44.Select Amount,click,, "admin.transport.status.amount_option"
-45.Enter Customer Fee, type,50, "admin.transport.vehicle.customer_fee.input"
-46.Open Customer GST  Dropdown,click,, "admin.transport.vehicle.customer_gst_type.dropdown"
-47.Select Amount,click,, "admin.transport.status.amount_option"
-48.Enter  GST amount, type,50, "admin.transport.vehicle.customer_gst.input"
-49.Open Driver Fee  Dropdown,click,, "admin.transport.vehicle.driver_type.dropdown"
-50.Select Amount,click,, "admin.transport.status.amount_option"
-51.Enter  Driver Fee, type,50, "admin.transport.vehicle.driver_fee.input"
-52.Open Driver GST  Dropdown,click,, "admin.transport.vehicle.driver_gst_type.dropdown"
-53.Select Amount,click,, "admin.transport.status.amount_option"
-54.Enter Driver Gst,type,50, "admin.transport.vehicle.driver_gst.input"
-55.Open Status Dropdown,click,, "admin.transport.vehicle.status.dropdown"
-56.Select Active,click,, "admin.transport.status.active_option"
-57.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/volvo.jpg", "admin.transport.vehicle.image.file"
-58.Enter Notifiacation,type,50, "admin.transport.vehicle.notify_km.input"
-59.Enter Driver Request ETA,type,50, "admin.transport.vehicle.eta_limit.input"
-60.Enter Driver Request KM,type,50, "admin.transport.vehicle.km_limit.input"
-61.Open Night Charge Timing Status Dropdown,click,, "admin.transport.night.status.dropdown"
-62.Select Active,click,, "admin.transport.status.active_option"
-63.Click Surcharge Time Checkbox, click, , "admin.transport.night.everyday.checkbox"
-64.Enter From Time, type, 100000AM, "admin.transport.night.from_time.input"
-65.Enter To Time, type, 220000PM, "admin.transport.night.to_time.input"
-66.Open  Dropdown,click,, "admin.transport.night.type.dropdown"
-67.Select Amount,click,, "admin.transport.status.amount_option"
-68.Enter  Price, type,50, "admin.transport.night.price.input"
-69.Click  Submit,click,, "web.global.action.submit"
-70.Wait For Sucess,wait_until_visible, , "web.global.toast.info"
-71.Click Settings ,click,, "admin.transport.menu.settings"
-72.Click Promocode,click,, "admin.transport.promo.menu_item"
-73.Click Add Promo Code ,click,, "admin.transport.promo.add.btn"
-74.Open User List Dropdown,click,, "admin.transport.promo.user_list.dropdown"
-75.Select User,click,, "admin.transport.promo.user_option"
-76.Click Code Name Box,click,, "admin.transport.promo.codename.input"
-77.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; promoCodeName, "admin.transport.promo.codename.input"
-78.Open Discout Type Dropdown,click,, "admin.transport.promo.discount_type.dropdown"
-79.Select Discout Type,click,, "admin.transport.promo.discount_type.amount_option"
-80.Enter Expiry Date,type,12122026, "admin.transport.promo.expiry.input"
-81.Enter Discount Amount, type, 100, "admin.transport.promo.amount.input"
-82.Enter Minimum Order Amount, type, 1000, "admin.transport.promo.min_order.input"
-83.Enter Maximum Discount Amount, type, 100, "admin.transport.promo.max_discount.input"
-84.Enter Coupon Limit, type, 5, "admin.transport.promo.coupon_limit.input"
-85.Enter Usage Limit for One User, type, 2, "admin.transport.promo.user_limit.input"
-86.Enter Promo Code Description, type, Promo Dode For Gold Member, "admin.transport.promo.desc.textarea"
-87.Click Submit ,click,, "web.global.action.submit"
-88.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-89.wait,2000,,
-90.Click Settings ,click,, "admin.transport.menu.settings"
-91.Click Service Settings ,click,, "admin.transport.rules.menu_item"
-92.Enter Driver Accept Timeout, type, 60, "admin.transport.rules.timeout.input"
-93.Enter Driver Serach Radius, type, 50, "admin.transport.rules.radius.input"
-94.Click Submit ,click,, "web.global.action.submit"
-95.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-96.wait,1000,,
-97.Click Settings ,click,, "admin.transport.menu.settings"
-98.Click Requirment Document ,click,, "admin.transport.docs.menu_item"
-99.Click Add Document ,click,, "admin.transport.docs.add.btn"
-100.Enter Name, type, documet{randomAlpha}&gt;&gt; documentName, "admin.transport.docs.name.input"
-101.Open status Dropdown,click,, "admin.transport.docs.status.dropdown"
-102.Select Active,click,, "admin.transport.status.active_option"
-103.Click Document Expiry ,click,, "admin.transport.docs.expiry.checkbox"
-104.Click Mandatory Document ,click,, "admin.transport.docs.mandatory.checkbox"
-105.Click  Require Proof Number,click,, "admin.transport.docs.proof_no.checkbox"
-106.Enter Display Order, type, 10, "admin.transport.docs.order.input"
-107.Click Submit ,click,, "web.global.action.submit"
-108.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-109.Filter Document List,type,{documentName}, "admin.transport.docs.grid.name_filter"
-110.wait,1000,,
-111. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-112.Click drivers menu,click,, "admin.drivers.menu.icon"
-113.Click Add Driver menu,click,, "admin.drivers.add_menu.link"
-114.Wait For Add Driver, wait_until_visible,, "admin.drivers.add_page.header"
-115.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
-116.Select Bus Ride Option,click,, "admin.transport.dropdown.dynamic_service"
-117.Enter Driver Name, type, busdriver_{timestamp} &gt;&gt; busDriverName, "admin.drivers.fullname.input"
-118.Enter Email, type, busdriver_{timestamp}@gmail.com&gt;&gt;busEmail, "admin.drivers.email.input"
-119.Enter Contact Number, type, {randomPhone}&gt;&gt;busPhone, "admin.drivers.phone.input"
-120.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
-121.Enter Whatspp Number,type,{busPhone}, "admin.drivers.whatsapp_phone.input"
-122.Upload Profile Image, uploadfile, "src/main/resources/test-data/busdriver.jpg", "admin.drivers.profile_image.file"
-123.Select Source,click,, "admin.drivers.source_dropdown.select"
-124.Select Instagram,click,, "admin.drivers.instagram_option.span"
-125.Select Male Gender, click, , "admin.drivers.male_gender.div"
-126.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
-127.Select  volvo Option,click,, "admin.transport.dropdown.dynamic_vehicle"
-128.Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
-129.Enter Plate No, type, KL-01-AB-1634, "admin.drivers.plateno.input"
-130. Enter Model Name, type, deisel, "admin.drivers.modelname.input"
-131.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/busvolvo.jpeg", "admin.drivers.vehicle_image.file"
-132.Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
-133.Enter Bank Location, type, Chennai, "admin.drivers.banklocation.input"
-134.Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
-135.Enter Account Holder Name, type, {busDriverName}, "admin.drivers.accountholder.input"
-136.Enter Payment Email Address, type, {busEmail}, "admin.drivers.paymentemail.input"
-137.Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
-138.Click Submit, click, , "web.global.action.submit"
-139.Wait For Driver Added,wait_until_visible, , "web.global.toast.success"
-140.Wait for Toast to hide, wait, 1000,
-141. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-142.Click drivers menu,click,, "admin.drivers.menu.icon"
-143.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
-144.Filter by Name,type,{busDriverName}, "admin.drivers.name_filter.input"
-145.Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
-146.Click Doc Icon,click,, "admin.drivers.docs.icon"
-147.Driver Required Documents,verify,, "admin.drivers.required_docs.header"
-148.FilterDocumet List,type,{documentName}, "admin.drivers.docs_filter.input"
-149.Add Driving License,click,, "admin.drivers.docs.edit_icon"
-150.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
-151.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
-152.Click Submit, click, , "web.global.action.submit"
-153.Wait For Updated Succesfully, wait_until_visible, , "web.global.toast.updated"
-154.Click Approve Driver,click,, "admin.drivers.docs.approval"
-155.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-156. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-157.Click drivers menu,click,, "admin.drivers.menu.icon"
-158.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
-159.Wait For Approved Drivers List, wait_until_visible,, "admin.drivers.approved_page.header"
-160.Filter Approved Driver,type,{busDriverName}, "admin.drivers.name_filter.input"
-161.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-162.Click Transports Services Menu,click,, "admin.transport.menu.card"
-163.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
-164.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
-165.Click Edit Icon ,click,, "admin.drivers.docs.edit_icon"
-166.Edit Service Name,type,Bus Ride{randomAlpha}&gt;&gt;editedTransportName,"admin.transport.name.input"
-167.Edit Slug,type,bus ride123,"admin.transport.slug.input"
-168.Open status Dropdown,click,, "admin.transport.status.dropdown"
-169.Select Deactivate,click,, "admin.transport.status.deactivate_option"
-170.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
-171.Select {areaName},click,, "admin.transport.city.dynamic_option"
-172.Click  Submit,click,, "web.global.action.submit"
-173.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-174.wait,2000,,</t>
-  </si>
-  <si>
     <t>1.Remove Test Area,sql delete,,"DELETE FROM we1.admin_area_list WHERE name = '{areaName}';"
 2.Remove Customer,sql delete,,"DELETE FROM we1.users WHERE first_name = '{customerName}';"
 3.Remove City Admin,sql delete,,"DELETE FROM we1.super_admin WHERE name = '{adminName}';"
@@ -3835,37 +2652,7 @@
     <t>TC_CA_14_Transport_Provider_List_Test</t>
   </si>
   <si>
-    <t>TC_CA_15_subscription_plan_test</t>
-  </si>
-  <si>
-    <t>TC_CA_16_Panic_Call_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_17_Dashboard_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_18_add_store</t>
-  </si>
-  <si>
-    <t>TC_CA_19_store_oprerations</t>
-  </si>
-  <si>
-    <t>TC_CA_20_store_status_management</t>
-  </si>
-  <si>
-    <t>TC_CA_21_delivery_service_complete_test</t>
-  </si>
-  <si>
-    <t>TC_CA_22_add_provider</t>
-  </si>
-  <si>
-    <t>TC_CA_23_provider_service_full_lifecycle_test</t>
-  </si>
-  <si>
     <t>SA_TS_24</t>
-  </si>
-  <si>
-    <t>TC_CA_24_test_data_cleanup</t>
   </si>
   <si>
     <t>This end-to-end regression test suite thoroughly validates the data segmentation, grid pagination, and report generation matrices within the Transport Providers List administrative module. The script begins by executing a complete chronological analytics loop across time boundaries—including Today, Yesterday, This Week, This Month, Last Month, and This Year—to confirm the accuracy of date-partitioned metrics rendering. It then transitions to structural grid filtering by systematically isolating discrete vehicle classes—specifically Taxi Ride, Bike Ride, and Auto Ride profiles—and verifying layout updates post-clearance. Finally, the test exercises grid controls by navigating structural data pagination anchors (Next, Previous, Last, and First pages) and executes a comprehensive verification of the reporting subsystem by triggering automated file extractions for both PDF and Excel formats, ensuring stable export channels with zero cross-query caching conflicts.</t>
@@ -3915,6 +2702,1520 @@
 42.Wait For Pdf Download,wait,5000,
 43.Click Excel Button,click,,"admin.provider.transport_provider_list.excel_download_btn"
 44.Wait For Excel Download,wait,2000,</t>
+  </si>
+  <si>
+    <t>SA_TS_25</t>
+  </si>
+  <si>
+    <t>Transport Service Review Tests</t>
+  </si>
+  <si>
+    <t>TC_CA_15_Transport_Service_Review_Test</t>
+  </si>
+  <si>
+    <t>14.Click Select Cutomer,click,,"//span[@aria-label='Select a customer']"
+15.Enter Name,type,Mohamed Yasir,"//input[@role='searchbox']"
+16.Click The Customer Name,click,,"//span[@class='ng-star-inserted']"
+17.Click Select Driver,click,,"//span[@aria-label='Select a Driver']"
+18.Enter The Driver Name,type,klo,"//input[@role='searchbox']"
+20.Click The Driver Name,click,,"//li[@id='Select Driver _0']"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Transport Service,Click,,"admin.transport.menu.card"
+3.Enter Services,type,Auto Ride,"admin.transport.grid.name_filter"
+4.Click Home Icon,Click,,"admin.transport.home.icon"
+5.Click Review Button,click,,"admin.transport.reviews.top_menu_btn"
+6.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+7.Wait For Today Statistics,wait,2000,
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Wait For Yesterday Statistics,wait,2000,
+10.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+11.Wait For This Week Statistics,wait,2000,
+12.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+13.Wait For This Month Statistics,wait,2000,
+14.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+15.Wait For Last Month Statistics,wait,2000,
+16.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+17.Wait For This Year Statistics,wait,2000,
+18.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+19.Wait For Last Year Statistics,wait,2000,
+20.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+21.Wait For This Year Statistics,wait,2000,
+22.Click Clear Button,click,,"admin.transport.reviews.clear_btn"
+23.Wait For Clear,wait,2000
+24.Filter Customer Name List,type,regression.customer.name,"admin.transport.reviews.customer_filter_name"
+25.Wait For Loading,wait,1000,
+26.Filter Driver Name List,type,regression.approved_driver.name,"admin.transport.reviews.driver_filter_name"
+27.Wait For Loading,wait,1000,
+28.Click Disapprove ratings,click,,"admin.transport.reviews.dis_approve_btn"
+29.Wait For Disapproval,wait,1000,
+30.Click Approve ratings,click,,"admin.transport.reviews.approve_btn"
+31.Wait For Approval,wait,1000,
+32.Click Delete ratings,click,,"admin.transport.reviews.delete_btn"
+33.Click Cancel Delete,click,,"admin.transport.reviews.cancel_delete_btn"
+34.Wait For Cancel Delete,wait,1000,
+</t>
+  </si>
+  <si>
+    <t>This targeted regression test suite validates the moderation workflows, feedback grids, and status update mechanisms within the Transport Services Reviews control panel. The test targets a specific logistical segment ("Auto Ride") and systematically loops through chronological time boundaries—including Today, Yesterday, This Week, This Month, Last Month, and This Year—to verify the accuracy of date-partitioned customer feedback metrics. It then transitions to granular record auditing by filtering the data grid against specific, parameterized customer names and approved driver profiles. Crucially, the script exercises administrator moderation privileges by triggering state-change operations on user ratings, specifically testing the sequential execution of Disapprove, Approve, and Delete actions, alongside confirming the stability of safety safeguards like the Cancel Delete command to guarantee data persistence rules operate with zero caching conflicts.</t>
+  </si>
+  <si>
+    <t>SA_TS_26</t>
+  </si>
+  <si>
+    <t>TC_CA_16_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>Report Issue FAQ Tests</t>
+  </si>
+  <si>
+    <t>This targeted regression test suite validates the complete administrative content lifecycle, state transitions, and search indexing within the Report Issue FAQs configuration panel. The script executes a strict CRUD (Create, Read, Update, Delete) verification loop, beginning with the dynamic creation of a user help document by mapping a structured title and description query. It then performs search indexing lookups before testing core operational visibility toggles via sequential Deactivate and Activate action triggers to verify live UI rendering states. Finally, the test exercises backend modification paths by updating the entry with new troubleshooting instructions, re-filtering the system data grid to find the revised asset, and executing an authenticated Confirm Delete command to guarantee clean data purging from the support matrix with zero lingering records.</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard,click,,"web.global.menu.dashboard"
+2.Click Report Issue,click,,"admin.report_issue.side_bar.menu"
+3.Click FAQs,click,,"admin.report_issue.side_bar_sub_menu.faqs"
+4.Click Add FAQs,click,,"admin.report_issue.faqs.add_faq_btn"
+5.Enter FAQ Title Name,type,How do I permanently delete my account?,"admin.report_issue.faqs.add_faq_input_title"
+6.Enter FAQ Description,type,You can request account deletion from the mobile app manage accounts section,"admin.report_issue.faqs.add_faq_input_description"
+7.Click Submit Button,click,,"admin.report_issue.faqs.add_faq_submit_button"
+8.Wait For Faq Upload,wait,3000,
+9.Search Faq,type,How do I permanently delete my account?,"admin.report_issue.faqs.search_faq_filter_input"
+10.Wait For Load,wait,1000,
+11.Click Deactive Button,click,,"admin.report_issue.faqs.faq_deactivate_btn"
+12.Wait For Deactivate,wait,2000,
+13..Click Active Button,click,,"admin.report_issue.faqs.faq_activate_btn"
+14.Wait For Activate,wait,2000,
+15.Click Edit Button,click,,"admin.report_issue.faqs.faq_edit_btn"
+16. Change The Faq Title Name,type,how to report issue that you faced?,"admin.report_issue.faqs.add_faq_input_title"
+17.Enter Description,type,contact the helpline number 101,"admin.report_issue.faqs.add_faq_input_description"
+18.Click Submit Button,click,,"admin.report_issue.faqs.add_faq_submit_button"
+19.Wait For Faq Update,wait,3000,
+20..Search Faq,type,how to report issue that you faced?,"admin.report_issue.faqs.search_faq_filter_input"
+21.Wait For Load,wait,1000,
+22.Click Delete Button,click,,"admin.report_issue.faqs.faq_delete_btn"
+23.wait for popup,wait,1000,
+24.Click Yes Delete It Button,click,,"admin.report_issue.faqs.faq_confirm_delete_btn"
+25.Wait For Delete,wait,3000,</t>
+  </si>
+  <si>
+    <t>SA_TS_27</t>
+  </si>
+  <si>
+    <t>Customer Report Issues</t>
+  </si>
+  <si>
+    <t>This end-to-end regression test suite thoroughly validates the submission tracking, helpdesk analytics, and ticket lifecycle workflows within the Customer Report Issues administrative module. The test sequence begins by executing a complete chronological data audit across multiple time-partition boundaries—including Today, Yesterday, This Week, This Month, Last Month, and This Year—ensuring the grid accurate renders date-segmented support queries. It then transitions to granular lookup verifications by filtering the issue records against specialized dropdown metrics, specifically isolating specific reporter names ("Created By") and ticket states. Crucially, the script audits active communication channels and entry logging by scrolling through the primary data grid, launching detail modals via the tracking eye icon, and validating intra-ticket support chat box instances. Finally, the suite tests helpdesk remediation paths by isolating pending entries, triggering a modal Confirm Resolve action sequence to alter ticket properties on the fly, and performing grid clearances to guarantee seamless system state updates with zero stale cross-query caching issues.</t>
+  </si>
+  <si>
+    <t>Driver Report Issues</t>
+  </si>
+  <si>
+    <t>This end-to-end regression test suite thoroughly validates the submission tracking, helpdesk analytics, and ticket lifecycle workflows within the Driver Report Issues administrative module. The test sequence begins by executing a complete chronological data audit across multiple time-partition boundaries—including Today, Yesterday, This Week, This Month, Last Month, and This Year—ensuring the grid accurate renders date-segmented support queries. It then transitions to granular lookup verifications by filtering the issue records against specialized dropdown metrics, specifically isolating specific reporter names ("Created By") and ticket states. Crucially, the script audits active communication channels and entry logging by scrolling through the primary data grid, launching detail modals via the tracking eye icon, and validating intra-ticket support chat box instances. Finally, the suite tests helpdesk remediation paths by isolating pending entries, triggering a modal Confirm Resolve action sequence to alter ticket properties on the fly, and performing grid clearances to guarantee seamless system state updates with zero stale cross-query caching issues.</t>
+  </si>
+  <si>
+    <t>SA_TS_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard,click,,"web.global.menu.dashboard"
+2.Click Report Issue,click,,"admin.report_issue.side_bar.menu"
+3.Click Customer Report Issue,click,,"admin.report_issue.side_bar_sub_menu.customer_report_issues"
+4.Click Today Button,click,,"web.global.dashboard.today_statistics"
+5.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+6.Wait For Today Statistics,wait,2000,
+7.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+10.Wait For Yesterday Statistics,wait,2000,
+11.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+13.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+14.Wait For This Week Statistics,wait,2000,
+15.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+16.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+17.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+18.Wait For This Month Statistics,wait,2000,
+19.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+20.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+21.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+22.Wait For Last Month Statistics,wait,2000,
+23.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+25.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+26.Wait For This Year Statistics,wait,2000,
+27.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+28.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+29.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+30.Wait For Last Year Statistics,wait,2000,
+31.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+32.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+33.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+34.Wait For This Year Statistics,wait,2000,
+35.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+37.Click Created By Dropdown,click,,"admin.report_issue.customer_report_issues.created_by_dropdown"
+38.Click Search Box ,click,,"admin.report_issue.customer_report_issues.created_by_dropdown_search_box"
+39.Click The First Name,click,,"admin.report_issue.customer_report_issues.created_by_dropdown_first_name"
+40.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+41.Wait For Name Load,wait,2000
+42.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+43.Click Status Dropdown,click,,"admin.report_issue.customer_report_issues.status_dropdown"
+43.Click Unresolved Option,click,,"admin.report_issue.customer_report_issues.status_dropdown_unresolved_option"
+44.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+45.Wait For Unresolved Load,wait,2000
+46.Scroll Grid,tab,8,"admin.report_issue.customer_report_issues.ticket_id_filter_input"
+47.Click Eye Icon,click,,"admin.report_issue.customer_report_issues.eye_icon"
+48.Click Close Eye View,click,,"admin.report_issue.customer_report_issues.close_eye_icon"
+49.Click Chat Button,click,,"admin.report_issue.customer_report_issues.chat_icon"
+50.Wait For Chat load,wait,2000
+51.Click Chat close,click_if_present,,"admin.report_issue.customer_report_issues.close_chat_icon"
+52.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+53.Wait For Clear,wait,1000,
+54.Click Status Dropdown,click,,"admin.report_issue.customer_report_issues.status_dropdown"
+55.Click resolved Option,click,,"admin.report_issue.customer_report_issues.status_dropdown_resolved_option"
+56.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+57.Wait For Resolved Load,wait,2000
+58.Click Resolve Button,click,,"admin.report_issue.customer_report_issues.resolve_thumbs_icon"
+59.Click Confirm Resolve,click,,"admin.report_issue.customer_report_issues.resolve_confirm_yes"
+60.Wait For Resolve,wait,1000,
+61.Click Clear Button,click,,"admin.report_issue.customer_report_issues.clear_btn"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard,click,,"web.global.menu.dashboard"
+2.Click Report Issue,click,,"admin.report_issue.side_bar.menu"
+3.Click Customer Report Issue,click,,"admin.report_issue.side_bar_sub_menu.driver_report_issues"
+4.Click Today Button,click,,"web.global.dashboard.today_statistics"
+5.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+6.Wait For Today Statistics,wait,2000,
+7.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+10.Wait For Yesterday Statistics,wait,2000,
+11.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+13.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+14.Wait For This Week Statistics,wait,2000,
+15.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+16.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+17.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+18.Wait For This Month Statistics,wait,2000,
+19.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+20.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+21.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+22.Wait For Last Month Statistics,wait,2000,
+23.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+25.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+26.Wait For This Year Statistics,wait,2000,
+27.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+28.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+29.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+30.Wait For Last Year Statistics,wait,2000,
+31.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+32.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+33.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+34.Wait For This Year Statistics,wait,2000,
+35.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+37.Click Created By Dropdown,click,,"admin.report_issue.driver_report_issues.created_by_dropdown"
+38.Click Search Box ,click,,"admin.report_issue.driver_report_issues.created_by_dropdown_search_box"
+39.Click The First Name,click,,"admin.report_issue.driver_report_issues.created_by_dropdown_first_name"
+40.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+41.Wait For Name Load,wait,2000
+42.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+43.Click Status Dropdown,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown"
+43.Click Unresolved Option,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown_unresolved_option"
+44.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+45.Wait For Unresolved Load,wait,2000
+46.Scroll Grid,tab,8,"admin.report_issue.driver_report_issues.ticket_id_filter_input"
+47.Click Eye Icon,click,,"admin.report_issue.driver_report_issues.eye_icon"
+48.Click Close Eye View,click,,"admin.report_issue.driver_report_issues.close_eye_icon"
+49.Click Chat Button,click,,"admin.report_issue.driver_report_issues.chat_icon"
+50.Wait For Chat load,wait,2000
+51.Click Chat close,click_if_present,,"admin.report_issue.driver_report_issues.close_chat_icon"
+52.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+53.Wait For Clear,wait,1000,
+54.Click Status Dropdown,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown"
+55.Click resolved Option,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown_resolved_option"
+56.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+57.Wait For Resolved Load,wait,2000
+58.Click Resolve Button,click,,"admin.report_issue.driver_report_issues.resolve_thumbs_icon"
+59.Click Confirm Resolve,click,,"admin.report_issue.driver_report_issues.resolve_confirm_yes"
+60.Wait For Resolve,wait,1000,
+61.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+</t>
+  </si>
+  <si>
+    <t>Geo Fencing Test</t>
+  </si>
+  <si>
+    <t>TC_CA_17_Geo_Fencing_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_18_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_19_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_20_Report_Issue_Faq_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_21_Customer_Report_Issues</t>
+  </si>
+  <si>
+    <t>TC_CA_22_Driver_Report_Issues</t>
+  </si>
+  <si>
+    <t>TC_CA_23_add_store</t>
+  </si>
+  <si>
+    <t>TC_CA_24_store_oprerations</t>
+  </si>
+  <si>
+    <t>TC_CA_25_store_status_management</t>
+  </si>
+  <si>
+    <t>TC_CA_26_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_CA_27_add_provider</t>
+  </si>
+  <si>
+    <t>TC_CA_28_provider_service_full_lifecycle_test</t>
+  </si>
+  <si>
+    <t>SA_TS_29</t>
+  </si>
+  <si>
+    <t>TC_CA_29_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
+2.Click Setting Button,click,,"admin.setting.sidebar.menu"
+3.Click Geo Fencing,click,,"admin.setting.geo_fencing.sidebar_menu"
+4.Add Restrict Area,click,,"admin.setting.geo_fencing.add_restricted_area_btn"
+5.Enter Restricted Area Name,type,officers training academy chennai,"admin.setting.geo_fencing.area_name_input_field"
+6.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
+7.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+8.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
+9.Wait For Submit,wait,2000,
+10.Enter Search Area,type,officers training academy chennai,"admin.setting.geo_fencing.area_search_filter"
+11.Wait For Load,wait,2000
+12.Click Edit Button,click,,"admin.setting.geo_fencing.edit_button"
+13.Enter Restricted Area Name,type,Airport Chennai,"admin.setting.geo_fencing.area_name_input_field"
+14.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
+15.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+16.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
+17.Wait For Submit,wait,2000,
+18.Enter Search Area,type,Airport Chennai,"admin.setting.geo_fencing.area_search_filter"
+19.Wait For Load,wait,2000,
+20.Click Delete Button,click,,"admin.setting.geo_fencing.delete_button"
+21.Click Yes Delete It Button,click,,"admin.setting.geo_fencing.confirm_delete_button"
+22.Wait For Delete,wait,2000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click drivers menu,click,,"admin.drivers.menu.icon"
+3. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+6.Select Auto Ride Option,click,,"admin.drivers.service_dropdown.auto_ride"
+7.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+8.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+9. Enter Driver Name,type,autodriver{randomAlpha} &gt;&gt; autoName,"admin.drivers.fullname.input"
+10. Enter Email,type,autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail,"admin.drivers.email.input"
+11.Enter Contact Number,type,{randomPhone}&gt;&gt;autoPhone,"admin.drivers.phone.input"
+12.Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
+13.Enter Whatspp Number,type,{autoPhone},"admin.drivers.whatsapp_phone.input"
+14.Upload Profile Image,uploadfile,"src/main/resources/test-data/autodriver.jpg","admin.drivers.profile_image.file"
+15.Select Source,click,,"admin.drivers.source_dropdown.select"
+16.Select Instagram,click,,"admin.drivers.instagram_option.span"
+17.Select Male Gender,click,,"admin.drivers.male_gender.div"
+18.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+19.Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
+20. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+21.Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
+22.Enter Model Name,type,petrol,"admin.drivers.modelname.input"
+23.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/vehicle.jpg","admin.drivers.vehicle_image.file"
+24. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
+25. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
+26.Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
+27.Enter Account Holder Name,type,{autoName},"admin.drivers.accountholder.input"
+28. Enter Payment Email Address,type,{autoEmail},"admin.drivers.paymentemail.input"
+29. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
+30. Click Submit,click,,"web.global.action.submit"
+31. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+32. Wait for Toast to hide,wait,1000,
+33.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+34.Click drivers menu,click,,"admin.drivers.menu.icon"
+35.Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+36.Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
+37.Scroll Grid,tab,7,"admin.drivers.name_filter.input"
+38.Click Doc Icon,click,,"admin.drivers.docs.icon"
+39. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
+40.FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+41.Add Drivi ng License,click,,"admin.drivers.docs.edit_icon"
+42.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg","admin.drivers.profile_image.file"
+43.Enter Expiry Date,set_date,2026-12-12,"admin.drivers.doc_expiry.input"
+44.Click Submit,click,,"web.global.action.submit"
+45.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+46.Click Approve Driver,click,,"admin.drivers.docs.approval"
+47.Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+48.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+49.Click drivers menu,click,,"admin.drivers.menu.icon"
+50.Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+51.Wait For Drivers List,wait_until_visible,,"admin.drivers.approved_page.header"
+52.Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
+53.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+54.Click Doc Icon,click,,"admin.drivers.approved_docs.grid_icon"
+55.Click Eye Icon,click,,"admin.drivers.approved_docs.eye_icon"
+56.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click drivers menu,click,, "admin.drivers.menu.icon"
+3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+6.Select Bike Ride Option,click,, "admin.drivers.service_dropdown.bike_ride"
+7.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+8.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+9. Enter Driver Name,type,bikedriver{randomAlpha} &gt;&gt; bikeName, "admin.drivers.fullname.input"
+10. Enter Email,type,bikedriver_{timestamp}@gmail.com&gt;&gt;bikeEmail, "admin.drivers.email.input"
+11.Enter Contact Number,type,{randomPhone}&gt;&gt;bikePhone, "admin.drivers.phone.input"
+12.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+13.Enter Whatspp Number,type,{bikePhone}, "admin.drivers.whatsapp_phone.input"
+14.Upload Profile Image,uploadfile,"src/main/resources/test-data/bikedriver.jpg", "admin.drivers.profile_image.file"
+15.Select Source,click,, "admin.drivers.source_dropdown.select"
+16.Select Instagram,click,, "admin.drivers.instagram_option.span"
+17.Select Male Gender,click,, "admin.drivers.male_gender.div"
+18.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+19.Select  Bike Option,click,, "admin.drivers.vehicle_option.scooter"
+20. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
+21.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
+22.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
+23.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/bike.jpg", "admin.drivers.vehicle_image.file"
+24. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
+25. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
+26.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
+27.Enter Account Holder Name,type,{bikeName}, "admin.drivers.accountholder.input"
+28. Enter Payment Email Address,type,{bikeEmail}, "admin.drivers.paymentemail.input"
+29. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
+30. Click Submit,click,, "web.global.action.submit"
+31. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
+32. Wait for Toast to hide,wait,1000,
+33.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+34.Click drivers menu,click,, "admin.drivers.menu.icon"
+35.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+36.Filter by Name,type,{bikeName}, "admin.drivers.name_filter.input"
+37.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
+38.Click Doc Icon,click,, "admin.drivers.docs.icon"
+39. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+40.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
+41.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+42.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+43.Enter Expiry Date,set_date,2026-12-12, "admin.drivers.doc_expiry.input"
+44.Click Submit,click,, "web.global.action.submit"
+45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+46.Click Approve Driver,click,, "admin.drivers.docs.approval"
+47.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+48.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+49.Click drivers menu,click,, "admin.drivers.menu.icon"
+50.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+51.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
+52.Filter Approved Driver,type,{bikeName}, "admin.drivers.name_filter.input"
+53.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
+54.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
+55.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
+56.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click drivers menu,click,, "admin.drivers.menu.icon"
+3. Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+4. Wait For Add Driver,wait_until_visible,, "admin.drivers.add_page.header"
+5.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+6.Select Taxi Ride Option,click,, "admin.drivers.service_dropdown.taxi_ride"
+7.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+8.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+9. Enter Driver Name,type,taxidriver{randomAlpha} &gt;&gt; taxiName, "admin.drivers.fullname.input"
+10. Enter Email,type,taxidriver_{timestamp}@gmail.com&gt;&gt;taxiEmail, "admin.drivers.email.input"
+11.Enter Contact Number,type,{randomPhone}&gt;&gt;taxiPhone, "admin.drivers.phone.input"
+12.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+13.Enter Whatspp Number,type,{taxiPhone}, "admin.drivers.whatsapp_phone.input"
+14.Upload Profile Image,uploadfile,"src/main/resources/test-data/taxidriver.jpg", "admin.drivers.profile_image.file"
+15.Select Source,click,, "admin.drivers.source_dropdown.select"
+16.Select Instagram,click,, "admin.drivers.instagram_option.span"
+17.Select Male Gender,click,, "admin.drivers.male_gender.div"
+18.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+19.Select  Suv Option,click,, "admin.drivers.vehicle_option.suv"
+20. Enter Model Year,type,2014, "admin.drivers.modelyear.input"
+21.Enter Plate No,type,KL-01-AB-1234, "admin.drivers.plateno.input"
+22.Enter Model Name,type,petrol, "admin.drivers.modelname.input"
+23.Upload Vehicle Image,uploadfile,"src/main/resources/test-data/taxi.jpg", "admin.drivers.vehicle_image.file"
+24. Enter Bank Name,type,HDFC Bank, "admin.drivers.bankname.input"
+25. Enter Bank Location,type,Chennai, "admin.drivers.banklocation.input"
+26.Enter Account Number,type,50100123456789, "admin.drivers.accountno.input"
+27.Enter Account Holder Name,type,{taxiName}, "admin.drivers.accountholder.input"
+28. Enter Payment Email Address,type,{taxiEmail}, "admin.drivers.paymentemail.input"
+29. Enter IFSC Code,type,HDFC0001234, "admin.drivers.ifsc.input"
+30. Click Submit,click,, "web.global.action.submit"
+31. Wait For Driver Added,wait_until_visible,, "web.global.toast.success"
+32. Wait for Toast to hide,wait,1000,
+33.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+34.Click drivers menu,click,, "admin.drivers.menu.icon"
+35.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+36.Filter by Name,type,{taxiName}, "admin.drivers.name_filter.input"
+37.Scroll Grid,tab,7, "admin.drivers.name_filter.input"
+38.Click Doc Icon,click,, "admin.drivers.docs.icon"
+39. Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+40.FilterDocumet List,type,Driving Licence, "admin.drivers.docs_filter.input"
+41.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+42.Upload Driving Iicense,uploadfile,"src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+43.Enter Expiry Date,set_date,2026-12-12, "admin.drivers.doc_expiry.input"
+44.Click Submit,click,, "web.global.action.submit"
+45.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+46.Click Approve Driver,click,, "admin.drivers.docs.approval"
+47.Wait For Updated Succesfully,wait_until_visible,, "web.global.toast.updated"
+48.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+49.Click drivers menu,click,, "admin.drivers.menu.icon"
+50.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+51.Wait For Drivers List,wait_until_visible,, "admin.drivers.approved_page.header"
+52.Filter Approved Driver,type,{taxiName}, "admin.drivers.name_filter.input"
+53.Scroll Grid,tab,10, "admin.drivers.name_filter.input"
+54.Click Doc Icon,click,, "admin.drivers.approved_docs.grid_icon"
+55.Click Eye Icon,click,, "admin.drivers.approved_docs.eye_icon"
+56.wait,1000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
+4.Click  Add Category,click,, "admin.transport.add_category.btn"
+5.Enter Service Name, type, Bus Ride{randomAlpha}&gt;&gt;transportName, "admin.transport.name.input"
+6.Enter Service Name Arabic, type, رحلة بالحافلة, "admin.transport.name_ar.input"
+7.Enter Slug, type, Bus Ride, "admin.transport.slug.input"
+8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/bus.jpg", "admin.transport.image.file"
+9.wait,2000,,
+10.Open status Dropdown,click,, "admin.transport.status.dropdown"
+11.Select Activate,click,, "admin.transport.status.activate_option"
+12.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
+13.Select {areaName},click,, "admin.transport.city.dynamic_option"
+14.Click  Submit,click,, "web.global.action.submit"
+15.Wait Till Sucess, wait_until_visible, , "web.global.toast.info"
+16.wait,2000,,
+17.Click  back,click,, "admin.transport.back.btn"
+18. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+19.Click Transports Services Menu,click,, "admin.transport.menu.card"
+20.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
+21.Click Home Icon ,click,, "admin.transport.home.icon"
+22.Click Settings ,click,, "admin.transport.menu.settings"
+23.Click Vehicle Type,click,, "admin.transport.settings.vehicle_type"
+24.Click Add Vehicle Type,click,, "admin.transport.vehicle.add_type.btn"
+25.Enter Vehicle Type Name, type, volvo{randomAlpha}&gt;&gt;busTypeName, "admin.transport.vehicle.name.input"
+26.Enter Base Fare, type, 150, "admin.transport.vehicle.base_fare.input"
+27.Enter Base Fare Max Kilometer, type, 10, "admin.transport.vehicle.base_km.input"
+28.Open Extra Distance Fare Dropdown,click,, "admin.transport.vehicle.extra_fare_type.dropdown"
+29.Select Amount,click,, "admin.transport.status.amount_option"
+30.Enter Extra Distance Fare , type, 10, "admin.transport.vehicle.extra_fare.input"
+31.Enter Free Waiting Time , type, 10, "admin.transport.vehicle.waiting_free.input"
+32.Open Waiting Charge Dropdown,click,, "admin.transport.vehicle.waiting_type.dropdown"
+33.Select Amount,click,, "admin.transport.status.amount_option"
+34.Enter Waiting Rate , type, 10, "admin.transport.vehicle.waiting_rate.input"
+35.Enter Included Trip Waiting , type, 10, "admin.transport.vehicle.trip_waiting_free.input"
+36.Open Trip Waiting Charge Dropdown,click,, "admin.transport.vehicle.trip_waiting_type.dropdown"
+37.Select Amount,click,, "admin.transport.status.amount_option"
+38.Enter Trip Waiting Rate , type,50, "admin.transport.vehicle.trip_waiting_rate.input"
+39.Enter Free Pickup Distance , type,5, "admin.transport.vehicle.pickup_free.input"
+40.Open Pickup Charge Dropdown,click,, "admin.transport.vehicle.pickup_type.dropdown"
+41.Select Amount,click,, "admin.transport.status.amount_option"
+42.Enter Pickup Fee, type,50, "admin.transport.vehicle.pickup_fee.input"
+43.Open Customer Fee  Dropdown,click,, "admin.transport.vehicle.customer_type.dropdown"
+44.Select Amount,click,, "admin.transport.status.amount_option"
+45.Enter Customer Fee, type,50, "admin.transport.vehicle.customer_fee.input"
+46.Open Customer GST  Dropdown,click,, "admin.transport.vehicle.customer_gst_type.dropdown"
+47.Select Amount,click,, "admin.transport.status.amount_option"
+48.Enter  GST amount, type,50, "admin.transport.vehicle.customer_gst.input"
+49.Open Driver Fee  Dropdown,click,, "admin.transport.vehicle.driver_type.dropdown"
+50.Select Amount,click,, "admin.transport.status.amount_option"
+51.Enter  Driver Fee, type,50, "admin.transport.vehicle.driver_fee.input"
+52.Open Driver GST  Dropdown,click,, "admin.transport.vehicle.driver_gst_type.dropdown"
+53.Select Amount,click,, "admin.transport.status.amount_option"
+54.Enter Driver Gst,type,50, "admin.transport.vehicle.driver_gst.input"
+55.Open Status Dropdown,click,, "admin.transport.vehicle.status.dropdown"
+56.Select Active,click,, "admin.transport.status.active_option"
+57.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/volvo.jpg", "admin.transport.vehicle.image.file"
+58.Enter Notifiacation,type,50, "admin.transport.vehicle.notify_km.input"
+59.Enter Driver Request ETA,type,50, "admin.transport.vehicle.eta_limit.input"
+60.Enter Driver Request KM,type,50, "admin.transport.vehicle.km_limit.input"
+61.Enter Package Idle Free Time,type,30,"admin.transport.vehicle.package_idle_free_time"
+62.Enter Package Idle Time Fee,type,50,"admin.transport.vehicle.package_idle_time_fee"
+63.Open Night Charge Timing Status Dropdown,click,, "admin.transport.night.status.dropdown"
+64.Select Active,click,, "admin.transport.status.active_option"
+65.Click Surcharge Time Checkbox, click, , "admin.transport.night.everyday.checkbox"
+66.Enter From Time, type, 100000AM, "admin.transport.night.from_time.input"
+67.Enter To Time, type, 220000PM, "admin.transport.night.to_time.input"
+68.Open  Dropdown,click,, "admin.transport.night.type.dropdown"
+69.Select Amount,click,, "admin.transport.status.amount_option"
+70.Enter  Price, type,50, "admin.transport.night.price.input"
+71.Click  Submit,click,, "web.global.action.submit"
+72.Wait For Sucess,wait_until_visible, , "web.global.toast.info"
+73.Click Settings ,click,, "admin.transport.menu.settings"
+74.Click Promocode,click,, "admin.transport.promo.menu_item"
+75.Click Add Promo Code ,click,, "admin.transport.promo.add.btn"
+76.Open User List Dropdown,click,, "admin.transport.promo.user_list.dropdown"
+77.Select User,click,, "admin.transport.promo.user_option"
+78.Click Code Name Box,click,, "admin.transport.promo.codename.input"
+79.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; promoCodeName, "admin.transport.promo.codename.input"
+80.Open Discout Type Dropdown,click,, "admin.transport.promo.discount_type.dropdown"
+81.Select Discout Type,click,, "admin.transport.promo.discount_type.amount_option"
+82.Enter Expiry Date,set_date,2026-12-12, "admin.transport.promo.expiry.input"
+83.Enter Discount Amount, type, 100, "admin.transport.promo.amount.input"
+84.Enter Minimum Order Amount, type, 1000, "admin.transport.promo.min_order.input"
+85.Enter Maximum Discount Amount, type, 100, "admin.transport.promo.max_discount.input"
+86.Enter Coupon Limit, type, 5, "admin.transport.promo.coupon_limit.input"
+87.Enter Usage Limit for One User, type, 2, "admin.transport.promo.user_limit.input"
+88.Enter Promo Code Description, type, Promo Dode For Gold Member, "admin.transport.promo.desc.textarea"
+89.Click Submit ,click,, "web.global.action.submit"
+90.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+91.wait,2000,,
+92.Click Settings ,click,, "admin.transport.menu.settings"
+93.Click Service Settings ,click,, "admin.transport.rules.menu_item"
+94.Enter Driver Accept Timeout, type, 60, "admin.transport.rules.timeout.input"
+95.Enter Driver Serach Radius, type, 50, "admin.transport.rules.radius.input"
+96.Click Submit ,click,, "web.global.action.submit"
+97.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+98.wait,1000,,
+99.Click Settings ,click,, "admin.transport.menu.settings"
+100.Click Requirment Document ,click,, "admin.transport.docs.menu_item"
+101.Click Add Document ,click,, "admin.transport.docs.add.btn"
+102.Enter Name, type, documet{randomAlpha}&gt;&gt; documentName, "admin.transport.docs.name.input"
+103.Open status Dropdown,click,, "admin.transport.docs.status.dropdown"
+104.Select Active,click,, "admin.transport.status.active_option"
+105.Click Document Expiry ,click,, "admin.transport.docs.expiry.checkbox"
+106.Click Mandatory Document ,click,, "admin.transport.docs.mandatory.checkbox"
+107.Click  Require Proof Number,click,, "admin.transport.docs.proof_no.checkbox"
+108.Enter Display Order, type, 10, "admin.transport.docs.order.input"
+109.Click Submit ,click,, "web.global.action.submit"
+110.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+111.Filter Document List,type,{documentName}, "admin.transport.docs.grid.name_filter"
+112.wait,1000,,
+113. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+114.Click drivers menu,click,, "admin.drivers.menu.icon"
+115.Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+116.Wait For Add Driver, wait_until_visible,, "admin.drivers.add_page.header"
+117.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+118.Select Bus Ride Option,click,, "admin.transport.dropdown.dynamic_service"
+119.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+120.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+121.Enter Driver Name, type, busdriver_{timestamp} &gt;&gt; busDriverName, "admin.drivers.fullname.input"
+122.Enter Email, type, busdriver_{timestamp}@gmail.com&gt;&gt;busEmail, "admin.drivers.email.input"
+123.Enter Contact Number, type, {randomPhone}&gt;&gt;busPhone, "admin.drivers.phone.input"
+124.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+125.Enter Whatspp Number,type,{busPhone}, "admin.drivers.whatsapp_phone.input"
+126.Upload Profile Image, uploadfile, "src/main/resources/test-data/busdriver.jpg", "admin.drivers.profile_image.file"
+127.Select Source,click,, "admin.drivers.source_dropdown.select"
+128.Select Instagram,click,, "admin.drivers.instagram_option.span"
+129.Select Male Gender, click, , "admin.drivers.male_gender.div"
+130.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+131.Select  volvo Option,click,, "admin.transport.dropdown.dynamic_vehicle"
+132.Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
+133.Enter Plate No, type, KL-01-AB-1634, "admin.drivers.plateno.input"
+134. Enter Model Name, type, deisel, "admin.drivers.modelname.input"
+135.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/busvolvo.jpeg", "admin.drivers.vehicle_image.file"
+136.Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
+137.Enter Bank Location, type, Chennai, "admin.drivers.banklocation.input"
+138.Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
+139.Enter Account Holder Name, type, {busDriverName}, "admin.drivers.accountholder.input"
+140.Enter Payment Email Address, type, {busEmail}, "admin.drivers.paymentemail.input"
+141.Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
+142.Click Submit, click, , "web.global.action.submit"
+143.Wait For Driver Added,wait_until_visible, , "web.global.toast.success"
+144.Wait for Toast to hide, wait, 1000,
+145. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+146.Click drivers menu,click,, "admin.drivers.menu.icon"
+147.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+148.Filter by Name,type,{busDriverName}, "admin.drivers.name_filter.input"
+149.Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
+150.Click Doc Icon,click,, "admin.drivers.docs.icon"
+151.Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+152.FilterDocumet List,type,{documentName}, "admin.drivers.docs_filter.input"
+153.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+154.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+155.Enter Expiry Date,set_date,2026-12-12, "admin.drivers.doc_expiry.input"
+156.Click Submit, click, , "web.global.action.submit"
+157.Wait For Updated Succesfully, wait_until_visible, , "web.global.toast.updated"
+158.Click Approve Driver,click,, "admin.drivers.docs.approval"
+159.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+160. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+161.Click drivers menu,click,, "admin.drivers.menu.icon"
+162.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+163.Wait For Approved Drivers List, wait_until_visible,, "admin.drivers.approved_page.header"
+164.Filter Approved Driver,type,{busDriverName}, "admin.drivers.name_filter.input"
+165.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+166.Click Transports Services Menu,click,, "admin.transport.menu.card"
+167.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
+168.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
+169.Click Edit Icon ,click,, "admin.drivers.docs.edit_icon"
+170.Edit Service Name,type,Bus Ride{randomAlpha}&gt;&gt;editedTransportName,"admin.transport.name.input"
+171.Edit Slug,type,bus ride123,"admin.transport.slug.input"
+172.Open status Dropdown,click,, "admin.transport.status.dropdown"
+173.Select Deactivate,click,, "admin.transport.status.deactivate_option"
+174.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
+175.Select {areaName},click,, "admin.transport.city.dynamic_option"
+176.Click  Submit,click,, "web.global.action.submit"
+177.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+178.wait,2000,,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Transports Services Menu,click,,"admin.transport.menu.card"
+3. Wait For Transport Services,wait_until_visible,,"admin.transport.page.header"
+4. Click Add Category,click,,"admin.transport.add_category.btn"
+5. Enter Service Name,type,lorryRide{randomAlpha}&gt;&gt;lorryTransportName,"admin.transport.name.input"
+6. Enter Service Name Arabic,type,رحلة بالحافلة,"admin.transport.name_ar.input"
+7. Enter Slug,type,{lorryTransportName},"admin.transport.slug.input"
+8. Upload Transport Service Image,uploadfile,"src/main/resources/test-data/lorry.png","admin.transport.image.file"
+9. wait,2000,,
+10. Open status Dropdown,click,,"admin.transport.status.dropdown"
+11. Select Activate,click,,"admin.transport.status.activate_option"
+12. Open Select City Dropdown,click,,"admin.transport.city.dropdown"
+13. Select {areaName},click,,"admin.transport.city.dynamic_option"
+14. Click Submit,click,,"web.global.action.submit"
+15. Sucess,wait_until_visible,,"web.global.toast.info"
+16. wait,2000,,
+17. Click Dashboard Home Icon,click,,"web.global.menu.dashboard"
+18. Click Transports Services Menu,click,,"admin.transport.menu.card"
+19. Filter Services List,type,{lorryTransportName},"admin.transport.grid.name_filter"
+20. Click Home Icon,click,,"admin.transport.home.icon"
+21. Click Settings,click,,"admin.transport.menu.settings"
+22. Click Vehicle Type,click,,"admin.transport.settings.vehicle_type"
+23. Click Add Vehicle Type,click,,"admin.transport.vehicle.add_type.btn"
+24. Enter Vehicle Type Name,type,tempo{randomAlpha}&gt;&gt;lorryTypeName,"admin.transport.vehicle.name.input"
+25. Enter Base Fare,type,150,"admin.transport.vehicle.base_fare.input"
+26. Enter Base Fare Max Kilometer,type,10,"admin.transport.vehicle.base_km.input"
+27. Open Extra Distance Fare Dropdown,click,,"admin.transport.vehicle.extra_fare_type.dropdown"
+28. Select Amount,click,,"admin.transport.status.amount_option"
+29. Enter Extra Distance Fare,type,10,"admin.transport.vehicle.extra_fare.input"
+30. Enter Free Waiting Time,type,10,"admin.transport.vehicle.waiting_free.input"
+31. Open Waiting Charge Dropdown,click,,"admin.transport.vehicle.waiting_type.dropdown"
+32. Select Amount,click,,"admin.transport.status.amount_option"
+33. Enter Waiting Rate,type,10,"admin.transport.vehicle.waiting_rate.input"
+34. Enter Included Trip Waiting,type,10,"admin.transport.vehicle.trip_waiting_free.input"
+35. Open Trip Waiting Charge Dropdown,click,,"admin.transport.vehicle.trip_waiting_type.dropdown"
+36. Select Amount,click,,"admin.transport.status.amount_option"
+37. Enter Trip Waiting Rate,type,50,"admin.transport.vehicle.trip_waiting_rate.input"
+38. Enter Free Pickup Distance,type,5,"admin.transport.vehicle.pickup_free.input"
+39. Open Pickup Charge Dropdown,click,,"admin.transport.vehicle.pickup_type.dropdown"
+40. Select Amount,click,,"admin.transport.status.amount_option"
+41. Enter Pickup Fee,type,50,"admin.transport.vehicle.pickup_fee.input"
+42. Open Customer Fee Dropdown,click,,"admin.transport.vehicle.customer_type.dropdown"
+43. Select Amount,click,,"admin.transport.status.amount_option"
+44. Enter Customer Fee,type,50,"admin.transport.vehicle.customer_fee.input"
+45. Open Customer GST Dropdown,click,,"admin.transport.vehicle.customer_gst_type.dropdown"
+46. Select Amount,click,,"admin.transport.status.amount_option"
+47. Enter GST amount,type,50,"admin.transport.vehicle.customer_gst.input"
+48. Open Driver Fee Dropdown,click,,"admin.transport.vehicle.driver_type.dropdown"
+49. Select Amount,click,,"admin.transport.status.amount_option"
+50. Enter Driver Fee,type,50,"admin.transport.vehicle.driver_fee.input"
+51. Open Driver GST Dropdown,click,,"admin.transport.vehicle.driver_gst_type.dropdown"
+52. Select Amount,click,,"admin.transport.status.amount_option"
+53. Enter Driver Gst,type,50,"admin.transport.vehicle.driver_gst.input"
+54. Open Status Dropdown,click,,"admin.transport.vehicle.status.dropdown"
+55. Select Active,click,,"admin.transport.status.active_option"
+56. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/tempo.jpg","admin.transport.vehicle.image.file"
+57. Enter Notifiacation,type,50,"admin.transport.vehicle.notify_km.input"
+58. Enter Driver Request ETA,type,50,"admin.transport.vehicle.eta_limit.input"
+59. Enter Driver Request KM,type,50,"admin.transport.vehicle.km_limit.input"
+60.Enter Package Idle Free Time,type,30,"admin.transport.vehicle.package_idle_free_time"
+61.Enter Package Idle Time Fee,type,50,"admin.transport.vehicle.package_idle_time_fee"
+62. Open Night Charge Timing Status Dropdown,click,,"admin.transport.night.status.dropdown"
+63. Select Active,click,,"admin.transport.status.active_option"
+64. Click Surcharge Time Checkbox,click,,"admin.transport.night.everyday.checkbox"
+65. Enter From Time,type,100000AM,"admin.transport.night.from_time.input"
+66. Enter To Time,type,220000PM,"admin.transport.night.to_time.input"
+67. Open Dropdown,click,,"admin.transport.night.type.dropdown"
+68. Select Amount,click,,"admin.transport.status.amount_option"
+69. Enter Price,type,50,"admin.transport.night.price.input"
+70. Click Submit,click,,"web.global.action.submit"
+71. Wait Until Sucess,wait_until_visible,,"web.global.toast.info"
+72. Click Setting menu,click,,"web.global.menu.settings"
+73. Click City admin menu,click,,"admin.menu.city_admin"
+74. Verify City Admin List,verify,,"admin.city_admin.list_heading"
+75. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+76. Verify City Admin heading,verify,,"admin.city_admin.add_heading"
+77. Select Name field,click,,"admin.city_admin.input_name"
+78. Enter Admin Name,type,newAdmin{randomAlpha} &gt;&gt; transAdminName,"admin.city_admin.input_name"
+79. Select Email field,click,,"admin.city_admin.input_email"
+80. Enter Email,type,transAdmin_{timestamp}@gmail.com &gt;&gt; transAdminEmail,"admin.city_admin.input_email"
+81. select the password field,click,,"admin.city_admin.input_password"
+82. Enter the Password,type,password{timestamp}&gt;&gt; transAdminPassword,"admin.city_admin.input_password"
+83. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+84. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+85. Click on the Bike Ride checkbox,click,,"admin.city_admin.chk_transport_bike_ride"
+86. Click on the Taxi Ride checkbox,click,,"admin.city_admin.chk_transport_taxi_ride"
+87. Click on the Auto Ride checkbox,click,,"admin.city_admin.chk_transport_auto_ride"
+88. Click on the dynamic service checkbox,click,,"admin.transport.dropdown.dynamic_lorry_service"
+89. Click on the Add Driver checkbox,click,,"admin.city_admin.chk_driver_add"
+90. Click on the Approved Drivers checkbox,click,,"admin.city_admin.chk_driver_approved"
+91. Click on the Un-Approved Drivers checkbox,click,,"admin.city_admin.chk_driver_unapproved"
+92. Click on the Blocked Drivers checkbox,click,,"admin.city_admin.chk_driver_blocked"
+93. Click on the Reject Drivers checkbox,click,,"admin.city_admin.chk_driver_rejected"
+94. Click on the Deleted Drivers checkbox,click,,"admin.city_admin.chk_driver_deleted"
+95. Click on the Driver Pending Documents checkbox,click,,"admin.city_admin.chk_driver_pending_docs"
+96. Click on the Driver Expired Documents checkbox,click,,"admin.city_admin.chk_driver_expired_docs"
+97. Click Submit,click,,"web.global.login.submit_btn"
+98. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+99. Filter admin name,type,{transAdminName},"admin.city_admin.input_name_filter"
+100. Click Logout Icon,click,,"web.global.action.logout_link"
+101. Click Confirm Logout,click,,"web.global.action.logout_confirm"
+102. Wait For Login Page,wait_until_visible,,"web.global.login.email"
+103. Enter Email,type,{transAdminEmail},"web.global.login.email"
+104. Enter Password,type,{transAdminPassword},"web.global.login.password"
+105. Click Login,click,,"web.global.login.submit_btn"
+106. Wait For Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"
+107. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+108. Click drivers menu,click,,"admin.drivers.menu.icon"
+109. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+110. Wait For Add Driver,wait_until_visible,,"admin.drivers.add_page.header"
+111. Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+112. Select Lorry Ride Option,click,,"admin.transport.dropdown.dynamic_lorry_transport_service"
+113.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+114.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+115. Enter Driver Name,type,lorrydriver{randomAlpha} &gt;&gt; lorrydriverName,"admin.drivers.fullname.input"
+116. Enter Email,type,lorrydriver_{timestamp}@gmail.com&gt;&gt;lorrydriverEmail,"admin.drivers.email.input"
+117. Enter Contact Number,type,{randomPhone}&gt;&gt;lorryPhone,"admin.drivers.phone.input"
+118. Click Whatspp,click,,"admin.drivers.whatsapp.checkbox"
+119. Enter Whatspp Number,type,{lorryPhone},"admin.drivers.whatsapp_phone.input"
+120. Upload Profile Image,uploadfile,"src/main/resources/test-data/lorrydriver.jpg","admin.drivers.profile_image.file"
+121. Select Source,click,,"admin.drivers.source_dropdown.select"
+122. Select Instagram,click,,"admin.drivers.instagram_option.span"
+123. Select Male Gender,click,,"admin.drivers.male_gender.div"
+124. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+125. Select Lorry Option,click,,"admin.transport.dropdown.dynamic_vehicle_lorry_type"
+126. Enter Model Year,type,2013,"admin.drivers.modelyear.input"
+127. Enter Plate No,type,KL-01-AB-1234,"admin.drivers.plateno.input"
+128. Enter Model Name,type,petrol,"admin.drivers.modelname.input"
+129. Upload Vehicle Image,uploadfile,"src/main/resources/test-data/lorry.png","admin.drivers.vehicle_image.file"
+130. Enter Bank Name,type,HDFC Bank,"admin.drivers.bankname.input"
+131. Enter Bank Location,type,Chennai,"admin.drivers.banklocation.input"
+132. Enter Account Number,type,50100123456789,"admin.drivers.accountno.input"
+133. Enter Account Holder Name,type,{lorrydriverName},"admin.drivers.accountholder.input"
+134. Enter Payment Email Address,type,{lorrydriverEmail},"admin.drivers.paymentemail.input"
+135. Enter IFSC Code,type,HDFC0001234,"admin.drivers.ifsc.input"
+136. Click Submit,click,,"web.global.action.submit"
+137. Wait For Driver Added,wait_until_visible,,"web.global.toast.success"
+138. wait,5000,,
+139. Click sidebar,click,,"web.global.action.sidebar_toggle"
+140. wait,2000,,
+141. Check Transport Menu exists,element_present,,"admin.transport.menu.card"
+142. wait,2000,,
+143. Check Deleivery Service exists,element_absent,,"admin.city_admin.chk_web_delivery"
+144. wait,2000,,
+145. Check Provider Service exists,element_absent,,"admin.city_admin.chk_provider_list"
+146. wait,2000,,
+147. Check Add Driver exists,element_present,,"admin.drivers.add_menu.link"
+148. wait,2000,,
+149. Check Approved Driver exists,element_present,,"admin.drivers.approved_docs.link"
+150. wait,2000,,
+151. Check Un-Approved Drivers exists,element_present,,"admin.drivers.unapproved_docs.link"
+152. wait,2000,,
+153. Check Blocked Driver exists,element_present,,"admin.drivers.blocked_docs.link"
+154. wait,2000,,
+155. Check Reject Driver exists,element_present,,"admin.drivers.reject_docs.link"
+156. wait,2000,,
+157. Check Deleted Driver exists,element_present,,"admin.drivers.deleted_docs.link"
+158. wait,2000,,
+159. Check pending Documents exists,element_present,,"admin.drivers.driver_pending_docs.link"
+160. wait,2000,,
+161. Check Driver Expired Documents exists,element_present,,"admin.drivers.driver_expired_docs.link"
+162. wait,2000,,
+163. Click Logout Icon,click,,"web.global.action.sidebar_logout_btn"
+164. Click Confirm Logout,click,,"web.global.action.logout_confirm"
+165. Wait For Login Page,wait_until_visible,,"web.global.login.email"
+166. Enter Email,type,super_admin@gmail.com,"web.global.login.email"
+167. Enter Password,type,R1mep@321,"web.global.login.password"
+168. Click Login,click,,"web.global.login.submit_btn"
+169. Wait For Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"
+170. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+171. Click Transports Services Menu,click,,"admin.transport.menu.card"
+172. Wait For Transport Services,wait_until_visible,,"admin.transport.page.header"
+173. Filter Services List,type,{lorryTransportName},"admin.transport.grid.name_filter"
+174. Click Edit Icon,click,,"admin.transport.docs.edit_icon"
+175. wait,2000,,
+176. Scroll Grid,tab,5,"admin.transport.name.input"
+177. wait,2000,,
+178. Open status Dropdown,click,,"admin.transport.status.dropdown"
+179. Select Deactivate,click,,"admin.transport.status.deactivate_option"
+180. Click Submit,click,,"web.global.action.submit"
+181. Wait For Sucess,wait_until_visible,,"web.global.toast.info"
+182. wait,2000,,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Ride Button,click,,"admin.transport.rides.icon"
+5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+6.Click Search Button,Click,,"admin.transport.search_btn"
+7.wait For Today Statistics,wait,2000,
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,Click,,"admin.transport.search_btn"
+10.wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Click Search Button,Click,,"admin.transport.search_btn"
+13.wait For This Week Statistics,wait,2000,
+14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+15.Click Search Button,Click,,"admin.transport.search_btn"
+16.wait For This Month Statistics,wait,2000,
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"admin.transport.search_btn"
+19.wait For Last Month Statistics,wait,2000,
+20.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+21.Click Search Button,Click,,"admin.transport.search_btn"
+22.wait For Last Year Statistics,wait,2000,
+23.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+24.Click Search Button,Click,,"admin.transport.search_btn"
+25.wait For This Year Statistics,wait,2000,
+26.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
+27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+28.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
+29.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
+30.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+31.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
+32.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
+33.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
+34.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
+35.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+36.Enter Status Type In Drop Down,type,Completed Rides,"admin.transport.status_type_dropdown_searchbox"
+37.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+38.Click Search Button,click,,"admin.transport.search_btn"
+39.Click Status Filter Input,click,,"admin.transport.status_filter_input"
+40.Enter Status,type,complete,"admin.transport.status_filter_input"
+41.Click Chat Box,click,,"admin.transport.chat_box.icon"
+42.Wait For Chat,wait,2000,
+43.Close Chat,click,,"admin.transport.rides.messages_close.btn"
+44.Click Ride Detail Button,click,,"admin.transport.ride_details.icon" 
+45.Wait For Ride Detail,wait,2000
+46.Show Ride Details,click,,"admin.transport.ride_details.arrival_time_box"
+47.Wait For Ride Detail,wait,2000
+48.Click Back Button,click,,"admin.transport.ride_details.back_btn"
+49.Click rides Button,click,,"admin.transport.ride_details.ride_top_menu_btn"
+50.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
+51.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+52.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
+53.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
+54.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+55.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
+56.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
+57.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
+58.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
+59.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+60.Enter Status Type In Drop Down,type,Incomplete Rides,"admin.transport.status_type_dropdown_searchbox"
+61.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+62.Click Search Button,click,,"admin.transport.search_btn"
+63.Wait For Incomplete Rides,wait,2000,
+64.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+65.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+66.Enter Status Type In Drop Down,type,Cancelled Rides,"admin.transport.status_type_dropdown_searchbox"
+67.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+68.Click Search Button,click,,"admin.transport.search_btn"
+69.Wait For Cancelled Rides,wait,2000,
+70.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+71.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+72.Enter Status Type In Drop Down,type,Scheduled Rides,"admin.transport.status_type_dropdown_searchbox"
+73.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+74.Click Search Button,click,,"admin.transport.search_btn"
+75.Wait For Scheduled Rides,wait,2000,
+76.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+77.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+78.Enter Status Type In Drop Down,type,Pre-Acceptance Cancel Rides,"admin.transport.status_type_dropdown_searchbox"
+79.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+80.Click Search Button,click,,"admin.transport.search_btn"
+81.Wait For Pre-Acceptance Cancel Rides,wait,2000,
+</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,KFC_{timestamp} &gt;&gt; storeName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,storeowner_{timestamp} &gt;&gt; storeOwner,"admin.store.contact_name.input"
+37. Enter Email,type,kfc_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{storeOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{storeName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Store Required Documents,verify,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,set_date,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Verify Add Store,verify,,"admin.store.list_page.header"
+73. Filter Store List,type,{storeName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+76. Click Eye Icon,click,,"admin.store.grid.eye_view_icon"
+77. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Delivery Services,click,,"admin.deliveryservice.menu"
+3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
+4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
+5. Wait For Food Delivery Summary,wait_until_visible,,"admin.store.food_delivery.summary_header"
+6. Click Stores,click,,"admin.store.menu.toggle_btn"
+7. Select Add Store,click,,"admin.store.submenu.add_store"
+8. Wait For Add Store,wait_until_visible,,"admin.store.add_page.header"
+9. Enter Store Name,type,bilal_{timestamp} &gt;&gt; hotelName,"admin.store.name.input"
+10. Open Delivery Radius Dropdown,click,,"admin.store.radius.dropdown"
+11. Select Twenty Five Kilometer,click,,"admin.store.radius.option_25km"
+12. Open Estimated Delivery Time,click,,"admin.store.eta.dropdown"
+13. Select Thirty Minute,click,,"admin.store.eta.option_30min"
+14. Enter Order Minimum Amount,type,300,"admin.store.min_amount.input"
+15. Enter Packaging Charges,type,50,"admin.store.packaging_charge.input"
+16. Enter Short Description,type,KFC is a global fast-food giant famous for its Original Recipe fried chicken,"admin.store.description.input"
+17. Upload Banner Image,uploadfile,"src/main/resources/test-data/kfcbanner.jpg","admin.store.banner.file"
+18. Open Driver Notification,click,,"admin.store.driver_notification.dropdown"
+19. Select Both Driver,click,,"admin.store.driver_notification.option_both"
+20. Click Checkbox Allow For Pickup,click,,"admin.store.allow_pickup.checkbox"
+21. Open Current Status Dropdown,click,,"admin.store.current_status.dropdown"
+22. Select Active,click,,"admin.store.current_status.option_active"
+23. Enter Store Address,type,KFC chennai,"admin.store.location.input"
+24. wait,3000,,
+25. Confirm Store Address,press_enter,,"admin.store.location.input"
+26. wait,3000,,
+27. Select First Option,arrow_down,,"admin.store.location.input"
+28. Confirm Option,press_enter,,"admin.store.location.input"
+29. wait,2000,,
+30. Click Storewise Comission Checkbox,click,,"admin.store.commission.checkbox"
+31. Enter Store Commision,type,25,"admin.store.commission_rate.input"
+32. Open Driver Notification,click,,"admin.store.offer_type.dropdown"
+33. Select Amount,click,,"admin.store.offer_type.option_amount"
+34. Enter Offer Amount,type,50,"admin.store.offer_amount.input"
+35. Enter Offer Min Amount,type,500,"admin.store.offer_min_amount.input"
+36. Enter Contact Person Full Name,type,bilalowner_{timestamp} &gt;&gt; hotelOwner,"admin.store.contact_name.input"
+37. Enter Email,type,bilal_{timestamp}@gmail.com&gt;&gt;storeEmail,"admin.store.email.input"
+38. Enter Contact Number,type,{randomPhone},"admin.store.phone.input"
+39. Upload Store Image,uploadfile,"src/main/resources/test-data/kfcstore.jpg","admin.store.profile.file"
+40. Enter Bank Name,type,federal,"admin.store.bank.name_input"
+41. Enter Bank Location,type,chennai,"admin.store.bank.location_input"
+42. Enter Account Number,type,123456789012,"admin.store.bank.account_input"
+43. Enter Accont Holder Name,type,{hotelOwner},"admin.store.bank.holder_input"
+44. Enter Payment Email Address,type,{storeEmail},"admin.store.bank.payment_email"
+45. Enter BIC Code,type,1234,"admin.store.bank.bic_input"
+46. Click Store Timing Checkbox,click,,"admin.store.timing.everyday_checkbox"
+47. Enter From Time,type,100000AM,"admin.store.timing.from_input"
+48. Enter To Time,type,100000PM,"admin.store.timing.to_input"
+49. Submit Add Store,click,,"web.global.action.submit"
+50. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+51. Click Stores,click,,"admin.store.menu.toggle_btn"
+52. Select Store List,click,,"admin.store.submenu.store_list"
+53. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+54. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+55. Click Stores,click,,"admin.store.menu.toggle_btn"
+56. Select Pending Documents Stores List,click,,"admin.store.submenu.pending_docs"
+57. Wait For Add Store,wait_until_visible,,"admin.store.pending_page.header"
+58. Filter Pending Document Store List,type,{hotelName},"admin.store.grid.name_filter"
+59. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+60. Click Doc Icon,click,,"admin.store.grid.doc_icon"
+61. Wait For Store Required Documents,wait_until_visible,,"admin.store.documents_page.header"
+62. Add Address Proof,click,,"admin.store.grid.edit_doc_icon"
+63. Upload Address Proof,uploadfile,"src/main/resources/test-data/addressproof.png","admin.store.doc.file_input"
+64. Enter Expiry Date,set_date,2026-12-12,"admin.store.doc.expiry_input"
+65. Click Submit,click,,"web.global.action.submit"
+66. Wait For Updated Succesfully,wait_until_visible,,"web.global.toast.updated"
+67. Click Approve Store,click,,"admin.store.grid.approve_doc_icon"
+68. Verify Updated Succesfully,verify,,"web.global.toast.updated"
+69. Click Back,click,,"admin.store.grid.back_btn"
+70. Click Stores,click,,"admin.store.menu.toggle_btn"
+71. Select Store List,click,,"admin.store.submenu.store_list"
+72. Wait For Add Store,wait_until_visible,,"admin.store.list_page.header"
+73. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+74. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+75. Click Block Icon,click,,"admin.store.grid.block_icon"
+76. Click Block Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Stores,click,,"admin.store.menu.toggle_btn"
+78. Select Blocked Store,click,,"admin.store.submenu.blocked_stores"
+79. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+80. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+81. Click unBlock Icon,click,,"admin.store.grid.unblock_icon"
+82. Click Stores,click,,"admin.store.menu.toggle_btn"
+83. Select Rejected Store,click,,"admin.store.submenu.rejected_stores"
+84. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+85. Scroll Grid,tab,7,"admin.store.grid.name_filter"
+86. Click Approve Icon,click,,"admin.store.grid.approve_icon"
+87. Click Stores,click,,"admin.store.menu.toggle_btn"
+88. Select Store List,click,,"admin.store.submenu.store_list"
+89. Filter Store List,type,{hotelName},"admin.store.grid.name_filter"
+90. wait,3000,,
+91. Scroll Grid,tab,8,"admin.store.grid.name_filter"
+92. Click Doc Icon,click,,"admin.store.grid.document_icon"
+93. Click UnApprove Icon,click,,"admin.store.grid.unapprove_icon"
+94. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+95. Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+96. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+97. wait,1000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Delivery Services, click, , "admin.deliveryservice.menu"
+3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
+5.Enter Category Name, type, milk Delivery{randomAlpha} &gt;&gt; deliveryName, "admin.deliveryservice.category_name.input"
+6.Enter Slug, type, Milk Delivery, "admin.deliveryservice.slug.input"
+7.Upload Category Image, uploadfile, "src/main/resources/test-data/milkman.jpg", "admin.deliveryservice.image.file"
+8.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+9.Select Activate, click, , "admin.deliveryservice.status.option_activate"
+10.Open Category Flow Dropdown, click, , "admin.deliveryservice.flow.dropdown"
+11.Select default flow(food-delivery), click, , "admin.deliveryservice.flow.option_food_delivery"
+12.Enter Delivery Name Tamil, type, பால்காரர், "admin.deliveryservice.lang_tamil.input"
+13.Enter Delivery Name Arabic, type, لبّان, "admin.deliveryservice.lang_arabic.input"
+14.Enter Delivery Name Hindi, type, दूधवाला, "admin.deliveryservice.lang_hindi.input"
+15.Click Submit, click, , "web.global.action.submit"
+16.Verify Success, verify, , "web.global.toast.info"
+17.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+18.Click Home Icon, click, , "admin.deliveryservice.home.icon"
+19.Click Settings, click, , "admin.deliveryservice.settings.menu"
+20.Click Requirement Document, click, , "admin.deliveryservice.required_docs"
+21.Click Add Document, click, , "admin.deliveryservice.docs.add_btn"
+22.Enter Name, type, document{randomAlpha} &gt;&gt; deliveryDocumentName, "admin.deliveryservice.docs.name_input"
+23.Open status Dropdown, click, , "admin.deliveryservice.docs.status_dropdown"
+24.Select Active, click, , "admin.deliveryservice.docs.status_option_active"
+25.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+26.Click Document Expiry, click, , "admin.deliveryservice.docs.expiry_checkbox"
+27.Click Mandatory Document, click, , "admin.deliveryservice.docs.mandatory_checkbox"
+28.Click Require Proof Number, click, , "admin.deliveryservice.docs.proof_number_checkbox"
+29.Enter Display Order, type, 10, "admin.deliveryservice.docs.display_order_input"
+30.Click Submit, click, , "web.global.action.submit"
+31.Verify Success, verify, , "web.global.toast.info"
+32.Filter Document List, type, {deliveryDocumentName}, "admin.deliveryservice.docs.grid.filter_input"
+33.wait, 2000, , ""
+34.Click Settings, click, , "admin.deliveryservice.settings.menu"
+35.Click Service Settings, click, , "admin.deliveryservice.submenu.service_settings"
+36.Enter Driver Search Radius, type, 50, "admin.deliveryservice.config.search_radius_input"
+37.Open Tax Type Dropdown, click, , "admin.deliveryservice.config.tax_type_dropdown"
+38.Select Amount, click, , "admin.deliveryservice.config.tax_type_option_amount"
+39.Enter Tax, type, 20, "admin.deliveryservice.config.tax_input"
+40.Open Platform Fee Type Dropdown, click, , "admin.deliveryservice.config.fee_type_dropdown"
+41.Select Amount, click, , "admin.deliveryservice.config.fee_type_option_amount"
+42.Enter Platform Fee, type, 20, "admin.deliveryservice.config.platform_fee_input"
+43.Enter Cancel Charge (in %):, type, 20, "admin.deliveryservice.config.cancel_charge_input"
+44.Enter Driver Accept Timeout (in Second):, type, 20, "admin.deliveryservice.config.driver_timeout_input"
+45.Click Submit, click, , "web.global.action.submit"
+46.Verify Success, verify, , "web.global.toast.info"
+47.Click Stores, click, , "admin.store.menu.toggle_btn"
+48.Select Add Store, click, , "admin.store.submenu.add_store"
+49.Verify Add Store, verify, , "admin.store.add_page.header"
+50.Enter Store Name, type, amul_{timestamp} &gt;&gt; milkStore, "admin.store.name.input"
+51.Open Delivery Radius Dropdown, click, , "admin.store.radius.dropdown"
+52.Select Twenty Five Kilometer, click, , "admin.store.radius.option_25km"
+53.Open Estimated Delivery Time, click, , "admin.store.eta.dropdown"
+54.Select Thirty Minute, click, , "admin.store.eta.option_30min"
+55.Enter Order Minimum Amount, type, 300, "admin.store.min_amount.input"
+56.Enter Packaging Charges, type, 50, "admin.store.packaging_charge.input"
+57.Enter Short Description, type, amul taste of india, "admin.store.description.input"
+58.Upload Banner Image, uploadfile, "src/main/resources/test-data/amulbanner.jpg", "admin.store.banner.file"
+59.Open Driver Notification, click, , "admin.store.driver_notification.dropdown"
+60.Select Both Driver, click, , "admin.store.driver_notification.option_both"
+61.Click Checkbox Allow For Pickup, click, , "admin.store.allow_pickup.checkbox"
+62.Open Current Status Dropdown, click, , "admin.store.current_status.dropdown"
+63.Select Active, click, , "admin.store.current_status.option_active"
+64.Enter Store Address, type, Amul chennai, "admin.store.location.input"
+65.wait, 3000, , ""
+66.Confirm Store Address, press_enter, , "admin.store.location.input"
+67.wait, 3000, , ""
+68.Select First Option, arrow_down, , "admin.store.location.input"
+69.Confirm Option, press_enter, , "admin.store.location.input"
+70.wait, 2000, , ""
+71.Click Storewise Commission Checkbox, click, , "admin.store.commission.checkbox"
+72.Enter Store Commission, type, 25, "admin.store.commission_rate.input"
+73.Open Driver Notification, click, , "admin.store.offer_type.dropdown"
+74.Select Amount, click, , "admin.store.offer_type.option_amount"
+75.Enter Offer Amount, type, 50, "admin.store.offer_amount.input"
+76.Enter Offer Min Amount, type, 500, "admin.store.offer_min_amount.input"
+77.Enter Contact Person Full Name, type, amulStoreowner_{timestamp} &gt;&gt; milkStoreOwner, "admin.store.contact_name.input"
+78.Enter Email, type, amul_{timestamp}@gmail.com &gt;&gt; storeEmail, "admin.store.email.input"
+79.Enter Contact Number, type, {randomPhone}, "admin.store.phone.input"
+80.Upload Store Image, uploadfile, "src/main/resources/test-data/milkbooth.jpeg", "admin.store.profile.file"
+81.Enter Bank Name, type, federal, "admin.store.bank.name_input"
+82.Enter Bank Location, type, chennai, "admin.store.bank.location_input"
+83.Enter Account Number, type, 123456789012, "admin.store.bank.account_input"
+84.Enter Account Holder Name, type, {milkStoreOwner}, "admin.store.bank.holder_input"
+85.Enter Payment Email Address, type, {storeEmail}, "admin.store.bank.payment_email"
+86.Enter BIC Code, type, 1234, "admin.store.bank.bic_input"
+87.Click Store Timing Checkbox, click, , "admin.store.timing.everyday_checkbox"
+88.Enter From Time, type, 100000AM, "admin.store.timing.from_input"
+89.Enter To Time, type, 100000PM, "admin.store.timing.to_input"
+90.Submit Add Store, click, , "web.global.action.submit"
+91.Verify Success Message, verify, , "web.global.toast.info"
+92.Click Stores, click, , "admin.store.menu.toggle_btn"
+93.Select Store List, click, , "admin.store.submenu.store_list"
+94.Verify Add Store, verify, , "admin.store.list_page.header"
+95.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+96.Click Stores, click, , "admin.store.menu.toggle_btn"
+97.Select Pending Documents Stores List, click, , "admin.store.submenu.pending_docs"
+98.Verify Add Store, verify, , "admin.store.pending_page.header"
+99.Filter Pending Document Store List, type, {milkStore}, "admin.store.grid.name_filter"
+100.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+101.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+102.Store Required Documents, verify, , "admin.store.documents_page.header"
+103.Add Address Proof, click, , "admin.store.grid.edit_doc_icon"
+104.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.store.doc.file_input"
+105.Enter Expiry Date,set_date,2026-12-12, "admin.store.doc.expiry_input"
+106.Click Submit, click, , "web.global.action.submit"
+107.Verify Updated Successfully, verify, , "web.global.toast.updated"
+108.Click Approve Store, click, , "admin.store.grid.approve_doc_icon"
+109.Verify Updated Successfully, verify, , "web.global.toast.updated"
+110.Click Back, click, , "admin.store.grid.back_btn"
+111.Click Stores, click, , "admin.store.menu.toggle_btn"
+112.Select Store List, click, , "admin.store.submenu.store_list"
+113.Verify Add Store, verify, , "admin.store.list_page.header"
+114.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+115.Scroll Grid, tab, 8, "admin.store.grid.name_filter"
+116.Click Doc Icon, click, , "admin.store.grid.doc_icon"
+117.wait for back button,wait,3000,
+118.Click Back, click, , "admin.store.grid.back_btn"
+119.Click Category, click, , "admin.deliveryservice.products.menu_category_btn"
+120.Click Add New Category, click, , "admin.deliveryservice.products.category.add_btn"
+121.Enter Category Name, type, curd{randomAlpha} &gt;&gt; MilkCategoryName, "admin.deliveryservice.products.category.name_input"
+122.Enter Category Name Arabic, type, رائب, "admin.deliveryservice.products.category.lang_arabic"
+123.Enter Category Name Tamil, type, தயிர், "admin.deliveryservice.products.category.lang_tamil"
+124.Enter Category Name Hindi, type, दही, "admin.deliveryservice.products.category.lang_hindi"
+125.Open Category status Dropdown, click, , "admin.deliveryservice.products.category.status_dropdown"
+126.Select Active, click, , "admin.deliveryservice.products.category.status_option_active"
+127.Upload Category Image, uploadfile, "src/main/resources/test-data/curd.jpeg", "admin.deliveryservice.image.file"
+128.wait, 2000, , ""
+129.Enter Slug Name, type, curd, "admin.deliveryservice.products.category.slug_input"
+130.Click Submit, click, , "web.global.action.submit"
+131.Verify Success Message, verify, , "web.global.toast.info"
+132.Filter Category Name, type, {MilkCategoryName}, "admin.deliveryservice.products.category.grid.filter_input"
+133.Click Stores, click, , "admin.store.menu.toggle_btn"
+134.Select Store List, click, , "admin.store.submenu.store_list"
+135.Filter Store List, type, {milkStore}, "admin.store.grid.name_filter"
+136.Scroll Grid, tab, 9, "admin.store.grid.name_filter"
+137.Click Product Icon, click, , "admin.store.products.grid_icon"
+138.Click Add Products, click, , "admin.store.products.add_btn"
+139.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
+140.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
+141.wait, 1000, ,""
+142.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+143.Click Delivery Services, click, , "admin.deliveryservice.menu"
+144.Verify Delivery Services, verify, , "admin.deliveryservice.header"
+145.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+146.Click Edit Icon, click, , "admin.deliveryservice.grid.edit_icon"
+147.Open status Dropdown, click, , "admin.deliveryservice.status.dropdown"
+148.wait, 1000, , ""
+149.Select Deactivate, click, , "admin.deliveryservice.status.option_deactivate"
+150.Click Submit, click, , "web.global.action.submit"
+151.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
+152.wait, 1000, ,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Delivery Services,click,,"admin.provider_service.menu_link"
+3.Verify Delivery Services,verify,,"admin.provider_service.on_demand_header"
+4.Filter service List,type,Plumbers,"admin.provider_service.services.filter.input"
+5.Click Home Icon Plumbers,click,,"admin.provider_service.services.home.icon_by_row_plumbers"
+6.Verify Plumbers Summary,verify,,"admin.provider_service.services.plumbers_summary.header"
+7.Click Providers,click,,"admin.provider_service.providers.root.button"
+8.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
+9.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
+10.Enter Provider Full Name, type, Plumber{randomAlpha}&gt;&gt; plumberName, "admin.provider_service.provider_form.fullname.input"
+11.Upload Plumber Image, uploadfile, "src/main/resources/test-data/plumber.jpg", "admin.provider_service.provider_form.avatar.file"
+12.Enter Email, type, Plumber_{timestamp}@gmail.com&gt;&gt;plumberEmail, "admin.provider_service.provider_form.email.input"
+13.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
+14.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
+15.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
+16.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
+17.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
+18.Enter Provider Address, type, plumber chennai, "admin.provider_service.provider_form.address.input"
+19.wait,1000,,
+20.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
+21.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
+22.wait,1000,,
+23.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
+24.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
+25.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
+26.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
+27.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
+28.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
+29.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
+30.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
+31.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
+32.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
+33.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
+34.Enter Account Holder Name, type, {plumberName}, "admin.provider_service.provider_form.account_holder.input"
+35.Enter Payment Email Address, type, {plumberEmail}, "admin.provider_service.provider_form.payment_email.input"
+36.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
+37.Click Save, click, , "web.global.login.submit_btn"
+38.Verify Sucess, verify, , "web.global.toast.info"
+39.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+40.Click Providers,click,,"admin.provider_service.providers.root.button"
+41.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
+42.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+43.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
+44.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
+45.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+46.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
+47.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
+48.Enter Expiry Date,set_date,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
+49.Click Submit, click, , "web.global.action.submit"
+50.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+51.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+52.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
+53.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+54.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+55.Click Providers,click,,"admin.provider_service.providers.root.button"
+56.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
+57.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
+58.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+59.Click Doc Icon,click,,"admin.provider_service.providers.grid.document.icon"
+60.Click Eye Icon,click,,"admin.provider_service.providers.grid.view_eye.icon"
+61.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+62.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
+63.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+64.Scroll Grid, tab, 11, "admin.provider_service.providers.grid.name_filter"
+65.Click Wallet Icon,click,,"admin.provider_service.providers.grid.wallet.icon"
+66.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
+67.Enter Wallet Amount, type, 1000, "admin.provider_service.wallet.amount.input"
+68.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
+69.Select Add Money,click, , "admin.provider_service.wallet.options.add_money"
+70.Click Submit, click, , "web.global.action.submit"
+71.Verify Saved Succesfully, verify, , "web.global.toast.success"
+72.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
+73.Enter Wallet Amount, type, 200, "admin.provider_service.wallet.amount.input"
+74.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
+75.Select Deduct Money,click, , "admin.provider_service.wallet.options.deduct_money"
+76.Click Submit, click, , "web.global.action.submit"
+77.Verify Saved Succesfully, verify, , "web.global.toast.success"
+78.Click Back, click, , "admin.provider_service.global.action.back_normal_btn"
+79.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+80.Click Doc Icon,click, , "admin.provider_service.providers.grid.document.icon"
+81.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+82.Click Reject Document,click, , "admin.provider_service.provider_docs.reject.icon"
+83.Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
+84.Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+85..Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
+86.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+87.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+88.Scroll Grid, tab, 13, "admin.provider_service.providers.grid.name_filter"
+89.Click Block Provider,click, , "admin.provider_service.providers.grid.block.icon"
+90.Click Block Yes,click, , "web.global.dialog.btn_confirm_yes"
+91.Blocking Reason,type,customer complaints,"web.global.dialog.textarea_reason"
+92.Click block Yes,click, , "web.global.dialog.btn_confirm_yes"
+93.Click Providers,click, , "admin.provider_service.providers.root.button"
+94.Select Blocked Providers,click, , "admin.provider_service.providers.blocked_list.menu"
+95.Verify Blocked Provider,verify, , "admin.provider_service.providers.grid.blocked_plumbers.header"
+96.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+97.Scroll Grid, tab, 12, "admin.provider_service.providers.grid.name_filter"
+98.Click Unblock Provider,click, , "admin.provider_service.providers.grid.unblock.icon"
+99.Click Providers,click, , "admin.provider_service.providers.root.button"
+100.Select Provider List,click, , "admin.provider_service.providers.provider_list.menu"
+101.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+102.wait,1000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Provider Services,click,,"admin.provider_service.menu_link"
+3.Verify Provider Services,verify,,"admin.provider_service.on_demand_header"
+4.Click Add New Services,click,,"admin.provider_service.services.add_new.btn"
+5.Enter Service Name, type, Painter{randomAlpha}&gt;&gt; serviceName, "admin.provider_service.services.name.input"
+6.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
+7.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
+8.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
+9.Enter Slug, type, painter, "admin.provider_service.services.slug.input"
+10.Upload Service Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.services.image.file"
+11.wait,2000,,
+12.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
+13.Select Activate,click,,"admin.provider_service.services.status.option_activate"
+14.Open Select City Dropdown,click,,"admin.provider_service.services.city.dropdown"
+15.Select {areaName},click,,"admin.provider_service.services.city.option_dynamic"
+16.Click Submit,click,,"web.global.action.submit"
+17.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+18.Click Home Icon ,click,,"admin.provider_service.services.home.icon"
+19.Click Settings ,click,,"admin.provider_service.settings.menu.button"
+20.Click Requirment Document ,click,,"admin.provider_service.settings.req_document.tab"
+21.Click Add Document ,click,,"admin.provider_service.req_docs.add.btn"
+22.Enter Name, type, documet{randomAlpha}&gt;&gt; providerDocumentName, "admin.provider_service.req_docs.name.input"
+23.Open status Dropdown,click,,"admin.provider_service.req_docs.status.dropdown"
+24.Select Active,click,,"admin.provider_service.req_docs.status.option_active"
+25.Click Document Expiry ,click,,"admin.provider_service.req_docs.expiry_toggle"
+26.Click Mandatory Document ,click,,"admin.provider_service.req_docs.mandatory_toggle"
+27.Click Submit ,click,,"web.global.action.submit"
+28.Verify Sucess, verify, , "web.global.toast.info"
+29.Filter Document List,type,{providerDocumentName},"admin.provider_service.req_docs.filter.input"
+30.Click Settings ,click,,"admin.provider_service.settings.menu.button"
+31.Click Promocode ,click,,"admin.provider_service.settings.promocode.tab"
+32.Click Add Promo Code ,click,,"admin.provider_service.promocode.add.btn"
+33.Open User List Dropdown,click,,"admin.provider_service.promocode.user_list.dropdown"
+34.Select User,click,,"admin.provider_service.promocode.user_list.option_dynamic"
+35.Click Code Name Box,click,,"admin.provider_service.promocode.code_name.box"
+36.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; providerPromoCodeName, "admin.provider_service.promocode.code_name.box"
+37.Open Discout Type Dropdown,click,,"admin.provider_service.promocode.discount_type.dropdown"
+38.Select Discout Type,click,,"admin.provider_service.promocode.discount_type.option_amount"
+39.Enter Expiry Date,set_date,2026-12-12,"admin.provider_service.promocode.expiry_date.input"
+40.Enter Discount Amount, type, 100, "admin.provider_service.promocode.discount_amount.input"
+41.Enter Minimum Order Amount, type, 1000, "admin.provider_service.promocode.min_order_amount.input"
+42.Enter Maximum Discount Amount, type, 100, "admin.provider_service.promocode.max_discount.input"
+43.Enter Coupon Limit, type, 5,"admin.provider_service.promocode.coupon_limit.input"
+44.Enter Usage Limit for One User, type, 2,"admin.provider_service.promocode.usage_limit_per_user.input"
+45.Enter Promo Code Description, type, Promo Dode For Gold Member,"admin.provider_service.promocode.description.textarea"
+46.Click Submit ,click,,"web.global.action.submit"
+47.Verify Sucess, verify, , "web.global.toast.info"
+48.Filter PromoCode List,type,{providerPromoCodeName},"admin.provider_service.promocode.filter.input"
+49.Click Providers,click,,"admin.provider_service.providers.root.button"
+50.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
+51.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
+52.Enter Provider Full Name, type, Painter{randomAlpha}&gt;&gt; painterName, "admin.provider_service.provider_form.fullname.input"
+53.Upload Painter Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.provider_form.avatar.file"
+54.Enter Email, type, Painter_{timestamp}@gmail.com&gt;&gt;painterEmail, "admin.provider_service.provider_form.email.input"
+55.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
+56.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
+57.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
+58.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
+59.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
+60.Enter Provider Address, type, painter chennai, "admin.provider_service.provider_form.address.input"
+61.wait,1000,,
+62.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
+63.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
+64.wait,1000,,
+65.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
+66.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
+67.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
+68.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
+69.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
+70.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
+71.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
+72.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
+73.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
+74.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
+75.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
+76.Enter Accont Holder Name, type, {painterName}, "admin.provider_service.provider_form.account_holder.input"
+77.Enter Payment Email Address, type, {painterEmail}, "admin.provider_service.provider_form.payment_email.input"
+78.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
+79.Click Save, click, , "web.global.login.submit_btn"
+80.Verify Sucess, verify, , "web.global.toast.info"
+81.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+82.Click Providers,click,,"admin.provider_service.providers.root.button"
+83.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
+84.Filter Plumber List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+85.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
+86.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
+87.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
+88.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
+89.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
+90.Enter Expiry Date,set_date,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
+91.Click Submit, click, , "web.global.action.submit"
+92.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+93.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
+94.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
+95.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+96.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+97.Click Providers,click,,"admin.provider_service.products.menu_category_btn"
+98.Click Add New Category,click,,"admin.provider_service.category.add_new.btn"
+99.Enter Category Name, type,residentialPainter{randomAlpha}&gt;&gt; painterCategoryName, "admin.provider_service.category.name.input"
+100.Enter Category Name Tamil, type, குடியிருப்பு பெயிண்டர், "admin.provider_service.category.name_tamil.input"
+101.Enter Category Name Arabic, type, دهان سكني, "admin.provider_service.category.name_arabic.input"
+102.Enter Category Name Hindi, type, आवासीय पेंटर, "admin.provider_service.category.name_hindi.input"
+103.Open Category status Dropdown,click,,"admin.provider_service.category.status.dropdown"
+104.Select Activate,click,,"admin.provider_service.category.status.option_active"
+105.Upload Category Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.category.image.file"
+106.wait,2000,,
+107.Click Submit,click,,"web.global.action.submit"
+108.Filter Category Name,type,{painterCategoryName},"admin.provider_service.category.filter.input"
+109.Click Providers,click,,"admin.provider_service.providers.root.button"
+110.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
+111.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+112.Scroll Grid, tab, 7, "admin.provider_service.providers.grid.name_filter"
+113.Click Package Icon,click,,"admin.provider_service.packages.icon"
+114.Click Add Package,click,,"admin.provider_service.packages.add_new.btn"
+115.Open Category Dropdown,click,,"admin.provider_service.packages.category.dropdown"
+116.Select Activate,click,,"admin.provider_service.packages.category.option_dynamic"
+117.Enter Package Name, type, package{randomAlpha}&gt;&gt; packageName, "admin.provider_service.packages.name.input"
+118.Enter Amount, type, 1000, "admin.provider_service.packages.amount.input"
+119.Open Max Book Quantity Dropdown,click,,"admin.provider_service.packages.max_book_qty.dropdown"
+120.Select 4,click,,"admin.provider_service.packages.max_book_qty.option_4"
+121.Open Status Dropdown,click,,"admin.provider_service.packages.status.dropdown"
+122.Select Activate,click,,"admin.provider_service.packages.status.option_activate"
+123.Enter Description, type, Premium residential painting package, "admin.provider_service.packages.description.textarea"
+124.Click Submit,click,,"web.global.action.submit"
+125.wait,1000,,
+126.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
+127.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+128.Click Delivery Services,click,,"admin.provider_service.menu_link"
+129.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+130.Click Edit Icon ,click,,"admin.provider_service.services.edit.icon"
+131.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
+132.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
+133.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
+134.Scroll Grid, tab, 4, "admin.provider_service.services.name_hindi.input"
+135.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
+136.Select Deactivate,click,,"admin.provider_service.services.status.option_deactivate"
+137.Click Submit,click,,"web.global.action.submit"
+138.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
+139. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+140.Click badge,click,,"admin.provider_service.badge.icon"
+141.Click provider Services,click,,"admin.provider_service.menu_link"
+142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+143.wait,1000,,</t>
   </si>
 </sst>
 </file>
@@ -4328,7 +4629,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
@@ -4403,19 +4704,19 @@
     </row>
     <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4478,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4550,16 +4851,16 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4622,19 +4923,19 @@
         <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4694,19 +4995,19 @@
         <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4766,19 +5067,19 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4794,6 +5095,81 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4E6D23-5EFE-4C84-AF6B-0AD768B8F6CC}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4835,19 +5211,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4865,7 +5241,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB72DFB-F4E3-4531-A41F-FCF21B5BBF59}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4907,166 +5355,22 @@
     </row>
     <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5116,7 +5420,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5124,7 +5428,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
@@ -5136,13 +5440,13 @@
         <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5161,6 +5465,369 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F1688F-2A0A-4B72-B3D2-D238F1ED2ADC}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F16F73-60F9-4B7A-AD34-4E583B7CB7A7}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065D1DC2-3D69-4BD0-B526-3FD12D803726}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5202,22 +5869,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5232,7 +5899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5274,19 +5941,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
@@ -5304,7 +5971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5339,36 +6006,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5383,7 +6050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5425,19 +6092,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -5455,7 +6122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5497,19 +6164,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>49</v>
@@ -5524,80 +6191,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5644,7 +6237,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -5674,6 +6267,80 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5719,7 +6386,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -5731,7 +6398,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>29</v>
@@ -5787,7 +6454,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -5799,7 +6466,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>33</v>
@@ -5862,7 +6529,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -5874,7 +6541,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>34</v>
@@ -5937,7 +6604,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -5949,7 +6616,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>35</v>
@@ -6012,7 +6679,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
@@ -6024,7 +6691,7 @@
         <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>52</v>
@@ -6100,7 +6767,7 @@
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FAD1B5-8A6A-4744-B3C4-77AA53A1DBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC472F1-866B-4609-A023-418DE2A35072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA42DD-6314-4ABC-850C-0AA7A6F7CB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512B79EF-7F04-4A2C-A84C-EFB163308031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
